--- a/data/blumen_data.xlsx
+++ b/data/blumen_data.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4798"/>
+  <dimension ref="A1:AD4898"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -55993,6 +55993,14 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
+      <c r="D4682" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4682" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="4683">
       <c r="A4683" t="inlineStr">
@@ -56101,6 +56109,14 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
+      <c r="D4691" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4691" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="4692">
       <c r="A4692" t="inlineStr">
@@ -56125,6 +56141,14 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
+      <c r="D4693" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4693" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="4694">
       <c r="A4694" t="inlineStr">
@@ -56171,6 +56195,14 @@
       <c r="B4697" t="inlineStr">
         <is>
           <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="D4697" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4697" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -56873,6 +56905,14 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
+      <c r="D4759" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4759" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="4760">
       <c r="A4760" t="inlineStr">
@@ -56885,6 +56925,14 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
+      <c r="D4760" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4760" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="4761">
       <c r="A4761" t="inlineStr">
@@ -56897,6 +56945,14 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
+      <c r="D4761" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4761" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="4762">
       <c r="A4762" t="inlineStr">
@@ -56945,6 +57001,14 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
+      <c r="D4765" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4765" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="4766">
       <c r="A4766" t="inlineStr">
@@ -57005,6 +57069,14 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
+      <c r="D4770" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4770" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="4771">
       <c r="A4771" t="inlineStr">
@@ -57075,6 +57147,14 @@
       <c r="B4776" t="inlineStr">
         <is>
           <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="D4776" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4776" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -57320,6 +57400,1151 @@
       </c>
     </row>
     <row r="4798"/>
+    <row r="4799">
+      <c r="A4799" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4799" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4800">
+      <c r="A4800" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4800" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="4801">
+      <c r="A4801" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4801" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="4802">
+      <c r="A4802" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4802" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="4803">
+      <c r="A4803" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4803" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4804">
+      <c r="A4804" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4804" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4805">
+      <c r="A4805" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4805" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="4806">
+      <c r="A4806" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4806" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="4807">
+      <c r="A4807" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4807" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4808">
+      <c r="A4808" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4808" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4809">
+      <c r="A4809" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4809" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4810">
+      <c r="A4810" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4810" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4811">
+      <c r="A4811" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4811" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4812">
+      <c r="A4812" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4812" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="4813">
+      <c r="A4813" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4813" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="4814">
+      <c r="A4814" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4814" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="4815">
+      <c r="A4815" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4815" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4816">
+      <c r="A4816" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4816" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="4817">
+      <c r="A4817" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B4817" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="4818"/>
+    <row r="4819">
+      <c r="A4819" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4819" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4820">
+      <c r="A4820" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4820" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="4821">
+      <c r="A4821" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4821" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="4822">
+      <c r="A4822" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4822" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="4823">
+      <c r="A4823" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4823" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4824">
+      <c r="A4824" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4824" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4825">
+      <c r="A4825" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4825" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="4826">
+      <c r="A4826" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4826" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="4827">
+      <c r="A4827" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4827" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4828">
+      <c r="A4828" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4828" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4829">
+      <c r="A4829" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4829" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4830">
+      <c r="A4830" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4830" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4831">
+      <c r="A4831" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4831" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4832">
+      <c r="A4832" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4832" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="4833">
+      <c r="A4833" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4833" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="4834">
+      <c r="A4834" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4834" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="4835">
+      <c r="A4835" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4835" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4836">
+      <c r="A4836" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4836" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="4837">
+      <c r="A4837" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="B4837" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="4838"/>
+    <row r="4839">
+      <c r="A4839" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4839" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4840">
+      <c r="A4840" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4840" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="4841">
+      <c r="A4841" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4841" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="4842">
+      <c r="A4842" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4842" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="4843">
+      <c r="A4843" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4843" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4844">
+      <c r="A4844" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4844" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4845">
+      <c r="A4845" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4845" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="4846">
+      <c r="A4846" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4846" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="4847">
+      <c r="A4847" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4847" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4848">
+      <c r="A4848" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4848" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4849">
+      <c r="A4849" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4849" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4850">
+      <c r="A4850" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4850" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4851">
+      <c r="A4851" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4851" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4852">
+      <c r="A4852" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4852" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="4853">
+      <c r="A4853" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4853" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="4854">
+      <c r="A4854" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4854" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="4855">
+      <c r="A4855" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4855" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4856">
+      <c r="A4856" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4856" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="4857">
+      <c r="A4857" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="B4857" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="4858"/>
+    <row r="4859">
+      <c r="A4859" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4859" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4860">
+      <c r="A4860" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4860" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="4861">
+      <c r="A4861" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4861" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="4862">
+      <c r="A4862" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4862" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="4863">
+      <c r="A4863" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4863" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4864">
+      <c r="A4864" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4864" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4865">
+      <c r="A4865" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4865" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="4866">
+      <c r="A4866" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4866" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="4867">
+      <c r="A4867" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4867" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4868">
+      <c r="A4868" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4868" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4869">
+      <c r="A4869" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4869" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4870">
+      <c r="A4870" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4870" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4871">
+      <c r="A4871" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4871" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4872">
+      <c r="A4872" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4872" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="4873">
+      <c r="A4873" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4873" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="4874">
+      <c r="A4874" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4874" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="4875">
+      <c r="A4875" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4875" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4876">
+      <c r="A4876" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4876" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="4877">
+      <c r="A4877" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="B4877" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="4878"/>
+    <row r="4879">
+      <c r="A4879" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4879" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4880">
+      <c r="A4880" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4880" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="4881">
+      <c r="A4881" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4881" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="4882">
+      <c r="A4882" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4882" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="4883">
+      <c r="A4883" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4883" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4884">
+      <c r="A4884" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4884" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4885">
+      <c r="A4885" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4885" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="4886">
+      <c r="A4886" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4886" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="4887">
+      <c r="A4887" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4887" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4888">
+      <c r="A4888" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4888" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4889">
+      <c r="A4889" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4889" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4890">
+      <c r="A4890" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4890" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4891">
+      <c r="A4891" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4891" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4892">
+      <c r="A4892" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4892" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="4893">
+      <c r="A4893" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4893" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="4894">
+      <c r="A4894" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4894" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="4895">
+      <c r="A4895" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4895" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4896">
+      <c r="A4896" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4896" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="4897">
+      <c r="A4897" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="B4897" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="4898"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/data/blumen_data.xlsx
+++ b/data/blumen_data.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5418"/>
+  <dimension ref="A1:AD5518"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -63868,27 +63868,43 @@
       </c>
     </row>
     <row r="5358"/>
-    <row r="5359">
-      <c r="A5359" t="inlineStr">
+    <row r="5359" customFormat="1" s="7">
+      <c r="A5359" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5359" t="inlineStr">
+      <c r="B5359" s="7" t="inlineStr">
         <is>
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-    </row>
-    <row r="5360">
-      <c r="A5360" t="inlineStr">
+      <c r="D5359" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5359" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5360" customFormat="1" s="7">
+      <c r="A5360" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5360" t="inlineStr">
+      <c r="B5360" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="D5360" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5360" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -63904,27 +63920,43 @@
         </is>
       </c>
     </row>
-    <row r="5362">
-      <c r="A5362" t="inlineStr">
+    <row r="5362" customFormat="1" s="7">
+      <c r="A5362" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5362" t="inlineStr">
+      <c r="B5362" s="7" t="inlineStr">
         <is>
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-    </row>
-    <row r="5363">
-      <c r="A5363" t="inlineStr">
+      <c r="D5362" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5362" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5363" customFormat="1" s="7">
+      <c r="A5363" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5363" t="inlineStr">
+      <c r="B5363" s="7" t="inlineStr">
         <is>
           <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="D5363" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5363" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -63952,27 +63984,43 @@
         </is>
       </c>
     </row>
-    <row r="5366">
-      <c r="A5366" t="inlineStr">
+    <row r="5366" customFormat="1" s="7">
+      <c r="A5366" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5366" t="inlineStr">
+      <c r="B5366" s="7" t="inlineStr">
         <is>
           <t>Hoya Mathilde</t>
         </is>
       </c>
-    </row>
-    <row r="5367">
-      <c r="A5367" t="inlineStr">
+      <c r="D5366" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5366" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5367" customFormat="1" s="7">
+      <c r="A5367" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5367" t="inlineStr">
+      <c r="B5367" s="7" t="inlineStr">
         <is>
           <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="D5367" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5367" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -63988,15 +64036,23 @@
         </is>
       </c>
     </row>
-    <row r="5369">
-      <c r="A5369" t="inlineStr">
+    <row r="5369" customFormat="1" s="7">
+      <c r="A5369" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5369" t="inlineStr">
+      <c r="B5369" s="7" t="inlineStr">
         <is>
           <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="D5369" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5369" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -64012,15 +64068,23 @@
         </is>
       </c>
     </row>
-    <row r="5371">
-      <c r="A5371" t="inlineStr">
+    <row r="5371" customFormat="1" s="7">
+      <c r="A5371" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5371" t="inlineStr">
+      <c r="B5371" s="7" t="inlineStr">
         <is>
           <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="D5371" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5371" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -64036,63 +64100,103 @@
         </is>
       </c>
     </row>
-    <row r="5373">
-      <c r="A5373" t="inlineStr">
+    <row r="5373" customFormat="1" s="7">
+      <c r="A5373" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5373" t="inlineStr">
+      <c r="B5373" s="7" t="inlineStr">
         <is>
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-    </row>
-    <row r="5374">
-      <c r="A5374" t="inlineStr">
+      <c r="D5373" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5373" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5374" customFormat="1" s="7">
+      <c r="A5374" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5374" t="inlineStr">
+      <c r="B5374" s="7" t="inlineStr">
         <is>
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-    </row>
-    <row r="5375">
-      <c r="A5375" t="inlineStr">
+      <c r="D5374" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5374" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5375" customFormat="1" s="7">
+      <c r="A5375" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5375" t="inlineStr">
+      <c r="B5375" s="7" t="inlineStr">
         <is>
           <t>Philodendron Birkin</t>
         </is>
       </c>
-    </row>
-    <row r="5376">
-      <c r="A5376" t="inlineStr">
+      <c r="D5375" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5375" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5376" customFormat="1" s="7">
+      <c r="A5376" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5376" t="inlineStr">
+      <c r="B5376" s="7" t="inlineStr">
         <is>
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-    </row>
-    <row r="5377">
-      <c r="A5377" t="inlineStr">
+      <c r="D5376" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5376" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5377" customFormat="1" s="7">
+      <c r="A5377" s="7" t="inlineStr">
         <is>
           <t>24.03.2026</t>
         </is>
       </c>
-      <c r="B5377" t="inlineStr">
+      <c r="B5377" s="7" t="inlineStr">
         <is>
           <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="D5377" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5377" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -64555,6 +64659,1816 @@
       </c>
     </row>
     <row r="5418"/>
+    <row r="5419">
+      <c r="A5419" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5419" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5419" t="inlineStr"/>
+      <c r="D5419" t="inlineStr"/>
+      <c r="E5419" t="inlineStr"/>
+      <c r="F5419" t="inlineStr"/>
+      <c r="G5419" t="inlineStr"/>
+      <c r="H5419" t="inlineStr"/>
+      <c r="I5419" t="inlineStr"/>
+    </row>
+    <row r="5420">
+      <c r="A5420" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5420" t="inlineStr"/>
+      <c r="D5420" t="inlineStr"/>
+      <c r="E5420" t="inlineStr"/>
+      <c r="F5420" t="inlineStr"/>
+      <c r="G5420" t="inlineStr"/>
+      <c r="H5420" t="inlineStr"/>
+      <c r="I5420" t="inlineStr"/>
+    </row>
+    <row r="5421">
+      <c r="A5421" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5421" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5421" t="inlineStr"/>
+      <c r="D5421" t="inlineStr"/>
+      <c r="E5421" t="inlineStr"/>
+      <c r="F5421" t="inlineStr"/>
+      <c r="G5421" t="inlineStr"/>
+      <c r="H5421" t="inlineStr"/>
+      <c r="I5421" t="inlineStr"/>
+    </row>
+    <row r="5422">
+      <c r="A5422" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5422" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5422" t="inlineStr"/>
+      <c r="D5422" t="inlineStr"/>
+      <c r="E5422" t="inlineStr"/>
+      <c r="F5422" t="inlineStr"/>
+      <c r="G5422" t="inlineStr"/>
+      <c r="H5422" t="inlineStr"/>
+      <c r="I5422" t="inlineStr"/>
+    </row>
+    <row r="5423">
+      <c r="A5423" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5423" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5423" t="inlineStr"/>
+      <c r="D5423" t="inlineStr"/>
+      <c r="E5423" t="inlineStr"/>
+      <c r="F5423" t="inlineStr"/>
+      <c r="G5423" t="inlineStr"/>
+      <c r="H5423" t="inlineStr"/>
+      <c r="I5423" t="inlineStr"/>
+    </row>
+    <row r="5424">
+      <c r="A5424" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5424" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5424" t="inlineStr"/>
+      <c r="D5424" t="inlineStr"/>
+      <c r="E5424" t="inlineStr"/>
+      <c r="F5424" t="inlineStr"/>
+      <c r="G5424" t="inlineStr"/>
+      <c r="H5424" t="inlineStr"/>
+      <c r="I5424" t="inlineStr"/>
+    </row>
+    <row r="5425">
+      <c r="A5425" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5425" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5425" t="inlineStr"/>
+      <c r="D5425" t="inlineStr"/>
+      <c r="E5425" t="inlineStr"/>
+      <c r="F5425" t="inlineStr"/>
+      <c r="G5425" t="inlineStr"/>
+      <c r="H5425" t="inlineStr"/>
+      <c r="I5425" t="inlineStr"/>
+    </row>
+    <row r="5426">
+      <c r="A5426" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5426" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5426" t="inlineStr"/>
+      <c r="D5426" t="inlineStr"/>
+      <c r="E5426" t="inlineStr"/>
+      <c r="F5426" t="inlineStr"/>
+      <c r="G5426" t="inlineStr"/>
+      <c r="H5426" t="inlineStr"/>
+      <c r="I5426" t="inlineStr"/>
+    </row>
+    <row r="5427">
+      <c r="A5427" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5427" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5427" t="inlineStr"/>
+      <c r="D5427" t="inlineStr"/>
+      <c r="E5427" t="inlineStr"/>
+      <c r="F5427" t="inlineStr"/>
+      <c r="G5427" t="inlineStr"/>
+      <c r="H5427" t="inlineStr"/>
+      <c r="I5427" t="inlineStr"/>
+    </row>
+    <row r="5428">
+      <c r="A5428" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5428" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5428" t="inlineStr"/>
+      <c r="D5428" t="inlineStr"/>
+      <c r="E5428" t="inlineStr"/>
+      <c r="F5428" t="inlineStr"/>
+      <c r="G5428" t="inlineStr"/>
+      <c r="H5428" t="inlineStr"/>
+      <c r="I5428" t="inlineStr"/>
+    </row>
+    <row r="5429">
+      <c r="A5429" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5429" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5429" t="inlineStr"/>
+      <c r="D5429" t="inlineStr"/>
+      <c r="E5429" t="inlineStr"/>
+      <c r="F5429" t="inlineStr"/>
+      <c r="G5429" t="inlineStr"/>
+      <c r="H5429" t="inlineStr"/>
+      <c r="I5429" t="inlineStr"/>
+    </row>
+    <row r="5430">
+      <c r="A5430" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5430" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5430" t="inlineStr"/>
+      <c r="D5430" t="inlineStr"/>
+      <c r="E5430" t="inlineStr"/>
+      <c r="F5430" t="inlineStr"/>
+      <c r="G5430" t="inlineStr"/>
+      <c r="H5430" t="inlineStr"/>
+      <c r="I5430" t="inlineStr"/>
+    </row>
+    <row r="5431">
+      <c r="A5431" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5431" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5431" t="inlineStr"/>
+      <c r="D5431" t="inlineStr"/>
+      <c r="E5431" t="inlineStr"/>
+      <c r="F5431" t="inlineStr"/>
+      <c r="G5431" t="inlineStr"/>
+      <c r="H5431" t="inlineStr"/>
+      <c r="I5431" t="inlineStr"/>
+    </row>
+    <row r="5432">
+      <c r="A5432" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5432" t="inlineStr"/>
+      <c r="D5432" t="inlineStr"/>
+      <c r="E5432" t="inlineStr"/>
+      <c r="F5432" t="inlineStr"/>
+      <c r="G5432" t="inlineStr"/>
+      <c r="H5432" t="inlineStr"/>
+      <c r="I5432" t="inlineStr"/>
+    </row>
+    <row r="5433">
+      <c r="A5433" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5433" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5433" t="inlineStr"/>
+      <c r="D5433" t="inlineStr"/>
+      <c r="E5433" t="inlineStr"/>
+      <c r="F5433" t="inlineStr"/>
+      <c r="G5433" t="inlineStr"/>
+      <c r="H5433" t="inlineStr"/>
+      <c r="I5433" t="inlineStr"/>
+    </row>
+    <row r="5434">
+      <c r="A5434" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5434" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5434" t="inlineStr"/>
+      <c r="D5434" t="inlineStr"/>
+      <c r="E5434" t="inlineStr"/>
+      <c r="F5434" t="inlineStr"/>
+      <c r="G5434" t="inlineStr"/>
+      <c r="H5434" t="inlineStr"/>
+      <c r="I5434" t="inlineStr"/>
+    </row>
+    <row r="5435">
+      <c r="A5435" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5435" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5435" t="inlineStr"/>
+      <c r="D5435" t="inlineStr"/>
+      <c r="E5435" t="inlineStr"/>
+      <c r="F5435" t="inlineStr"/>
+      <c r="G5435" t="inlineStr"/>
+      <c r="H5435" t="inlineStr"/>
+      <c r="I5435" t="inlineStr"/>
+    </row>
+    <row r="5436">
+      <c r="A5436" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5436" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5436" t="inlineStr"/>
+      <c r="D5436" t="inlineStr"/>
+      <c r="E5436" t="inlineStr"/>
+      <c r="F5436" t="inlineStr"/>
+      <c r="G5436" t="inlineStr"/>
+      <c r="H5436" t="inlineStr"/>
+      <c r="I5436" t="inlineStr"/>
+    </row>
+    <row r="5437">
+      <c r="A5437" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B5437" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5437" t="inlineStr"/>
+      <c r="D5437" t="inlineStr"/>
+      <c r="E5437" t="inlineStr"/>
+      <c r="F5437" t="inlineStr"/>
+      <c r="G5437" t="inlineStr"/>
+      <c r="H5437" t="inlineStr"/>
+      <c r="I5437" t="inlineStr"/>
+    </row>
+    <row r="5438"/>
+    <row r="5439">
+      <c r="A5439" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5439" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5439" t="inlineStr"/>
+      <c r="D5439" t="inlineStr"/>
+      <c r="E5439" t="inlineStr"/>
+      <c r="F5439" t="inlineStr"/>
+      <c r="G5439" t="inlineStr"/>
+      <c r="H5439" t="inlineStr"/>
+      <c r="I5439" t="inlineStr"/>
+    </row>
+    <row r="5440">
+      <c r="A5440" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5440" t="inlineStr"/>
+      <c r="D5440" t="inlineStr"/>
+      <c r="E5440" t="inlineStr"/>
+      <c r="F5440" t="inlineStr"/>
+      <c r="G5440" t="inlineStr"/>
+      <c r="H5440" t="inlineStr"/>
+      <c r="I5440" t="inlineStr"/>
+    </row>
+    <row r="5441">
+      <c r="A5441" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5441" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5441" t="inlineStr"/>
+      <c r="D5441" t="inlineStr"/>
+      <c r="E5441" t="inlineStr"/>
+      <c r="F5441" t="inlineStr"/>
+      <c r="G5441" t="inlineStr"/>
+      <c r="H5441" t="inlineStr"/>
+      <c r="I5441" t="inlineStr"/>
+    </row>
+    <row r="5442">
+      <c r="A5442" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5442" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5442" t="inlineStr"/>
+      <c r="D5442" t="inlineStr"/>
+      <c r="E5442" t="inlineStr"/>
+      <c r="F5442" t="inlineStr"/>
+      <c r="G5442" t="inlineStr"/>
+      <c r="H5442" t="inlineStr"/>
+      <c r="I5442" t="inlineStr"/>
+    </row>
+    <row r="5443">
+      <c r="A5443" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5443" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5443" t="inlineStr"/>
+      <c r="D5443" t="inlineStr"/>
+      <c r="E5443" t="inlineStr"/>
+      <c r="F5443" t="inlineStr"/>
+      <c r="G5443" t="inlineStr"/>
+      <c r="H5443" t="inlineStr"/>
+      <c r="I5443" t="inlineStr"/>
+    </row>
+    <row r="5444">
+      <c r="A5444" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5444" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5444" t="inlineStr"/>
+      <c r="D5444" t="inlineStr"/>
+      <c r="E5444" t="inlineStr"/>
+      <c r="F5444" t="inlineStr"/>
+      <c r="G5444" t="inlineStr"/>
+      <c r="H5444" t="inlineStr"/>
+      <c r="I5444" t="inlineStr"/>
+    </row>
+    <row r="5445">
+      <c r="A5445" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5445" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5445" t="inlineStr"/>
+      <c r="D5445" t="inlineStr"/>
+      <c r="E5445" t="inlineStr"/>
+      <c r="F5445" t="inlineStr"/>
+      <c r="G5445" t="inlineStr"/>
+      <c r="H5445" t="inlineStr"/>
+      <c r="I5445" t="inlineStr"/>
+    </row>
+    <row r="5446">
+      <c r="A5446" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5446" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5446" t="inlineStr"/>
+      <c r="D5446" t="inlineStr"/>
+      <c r="E5446" t="inlineStr"/>
+      <c r="F5446" t="inlineStr"/>
+      <c r="G5446" t="inlineStr"/>
+      <c r="H5446" t="inlineStr"/>
+      <c r="I5446" t="inlineStr"/>
+    </row>
+    <row r="5447">
+      <c r="A5447" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5447" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5447" t="inlineStr"/>
+      <c r="D5447" t="inlineStr"/>
+      <c r="E5447" t="inlineStr"/>
+      <c r="F5447" t="inlineStr"/>
+      <c r="G5447" t="inlineStr"/>
+      <c r="H5447" t="inlineStr"/>
+      <c r="I5447" t="inlineStr"/>
+    </row>
+    <row r="5448">
+      <c r="A5448" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5448" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5448" t="inlineStr"/>
+      <c r="D5448" t="inlineStr"/>
+      <c r="E5448" t="inlineStr"/>
+      <c r="F5448" t="inlineStr"/>
+      <c r="G5448" t="inlineStr"/>
+      <c r="H5448" t="inlineStr"/>
+      <c r="I5448" t="inlineStr"/>
+    </row>
+    <row r="5449">
+      <c r="A5449" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5449" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5449" t="inlineStr"/>
+      <c r="D5449" t="inlineStr"/>
+      <c r="E5449" t="inlineStr"/>
+      <c r="F5449" t="inlineStr"/>
+      <c r="G5449" t="inlineStr"/>
+      <c r="H5449" t="inlineStr"/>
+      <c r="I5449" t="inlineStr"/>
+    </row>
+    <row r="5450">
+      <c r="A5450" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5450" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5450" t="inlineStr"/>
+      <c r="D5450" t="inlineStr"/>
+      <c r="E5450" t="inlineStr"/>
+      <c r="F5450" t="inlineStr"/>
+      <c r="G5450" t="inlineStr"/>
+      <c r="H5450" t="inlineStr"/>
+      <c r="I5450" t="inlineStr"/>
+    </row>
+    <row r="5451">
+      <c r="A5451" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5451" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5451" t="inlineStr"/>
+      <c r="D5451" t="inlineStr"/>
+      <c r="E5451" t="inlineStr"/>
+      <c r="F5451" t="inlineStr"/>
+      <c r="G5451" t="inlineStr"/>
+      <c r="H5451" t="inlineStr"/>
+      <c r="I5451" t="inlineStr"/>
+    </row>
+    <row r="5452">
+      <c r="A5452" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5452" t="inlineStr"/>
+      <c r="D5452" t="inlineStr"/>
+      <c r="E5452" t="inlineStr"/>
+      <c r="F5452" t="inlineStr"/>
+      <c r="G5452" t="inlineStr"/>
+      <c r="H5452" t="inlineStr"/>
+      <c r="I5452" t="inlineStr"/>
+    </row>
+    <row r="5453">
+      <c r="A5453" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5453" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5453" t="inlineStr"/>
+      <c r="D5453" t="inlineStr"/>
+      <c r="E5453" t="inlineStr"/>
+      <c r="F5453" t="inlineStr"/>
+      <c r="G5453" t="inlineStr"/>
+      <c r="H5453" t="inlineStr"/>
+      <c r="I5453" t="inlineStr"/>
+    </row>
+    <row r="5454">
+      <c r="A5454" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5454" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5454" t="inlineStr"/>
+      <c r="D5454" t="inlineStr"/>
+      <c r="E5454" t="inlineStr"/>
+      <c r="F5454" t="inlineStr"/>
+      <c r="G5454" t="inlineStr"/>
+      <c r="H5454" t="inlineStr"/>
+      <c r="I5454" t="inlineStr"/>
+    </row>
+    <row r="5455">
+      <c r="A5455" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5455" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5455" t="inlineStr"/>
+      <c r="D5455" t="inlineStr"/>
+      <c r="E5455" t="inlineStr"/>
+      <c r="F5455" t="inlineStr"/>
+      <c r="G5455" t="inlineStr"/>
+      <c r="H5455" t="inlineStr"/>
+      <c r="I5455" t="inlineStr"/>
+    </row>
+    <row r="5456">
+      <c r="A5456" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5456" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5456" t="inlineStr"/>
+      <c r="D5456" t="inlineStr"/>
+      <c r="E5456" t="inlineStr"/>
+      <c r="F5456" t="inlineStr"/>
+      <c r="G5456" t="inlineStr"/>
+      <c r="H5456" t="inlineStr"/>
+      <c r="I5456" t="inlineStr"/>
+    </row>
+    <row r="5457">
+      <c r="A5457" t="inlineStr">
+        <is>
+          <t>28.03.2026</t>
+        </is>
+      </c>
+      <c r="B5457" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5457" t="inlineStr"/>
+      <c r="D5457" t="inlineStr"/>
+      <c r="E5457" t="inlineStr"/>
+      <c r="F5457" t="inlineStr"/>
+      <c r="G5457" t="inlineStr"/>
+      <c r="H5457" t="inlineStr"/>
+      <c r="I5457" t="inlineStr"/>
+    </row>
+    <row r="5458"/>
+    <row r="5459">
+      <c r="A5459" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5459" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5459" t="inlineStr"/>
+      <c r="D5459" t="inlineStr"/>
+      <c r="E5459" t="inlineStr"/>
+      <c r="F5459" t="inlineStr"/>
+      <c r="G5459" t="inlineStr"/>
+      <c r="H5459" t="inlineStr"/>
+      <c r="I5459" t="inlineStr"/>
+    </row>
+    <row r="5460">
+      <c r="A5460" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5460" t="inlineStr"/>
+      <c r="D5460" t="inlineStr"/>
+      <c r="E5460" t="inlineStr"/>
+      <c r="F5460" t="inlineStr"/>
+      <c r="G5460" t="inlineStr"/>
+      <c r="H5460" t="inlineStr"/>
+      <c r="I5460" t="inlineStr"/>
+    </row>
+    <row r="5461">
+      <c r="A5461" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5461" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5461" t="inlineStr"/>
+      <c r="D5461" t="inlineStr"/>
+      <c r="E5461" t="inlineStr"/>
+      <c r="F5461" t="inlineStr"/>
+      <c r="G5461" t="inlineStr"/>
+      <c r="H5461" t="inlineStr"/>
+      <c r="I5461" t="inlineStr"/>
+    </row>
+    <row r="5462">
+      <c r="A5462" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5462" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5462" t="inlineStr"/>
+      <c r="D5462" t="inlineStr"/>
+      <c r="E5462" t="inlineStr"/>
+      <c r="F5462" t="inlineStr"/>
+      <c r="G5462" t="inlineStr"/>
+      <c r="H5462" t="inlineStr"/>
+      <c r="I5462" t="inlineStr"/>
+    </row>
+    <row r="5463">
+      <c r="A5463" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5463" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5463" t="inlineStr"/>
+      <c r="D5463" t="inlineStr"/>
+      <c r="E5463" t="inlineStr"/>
+      <c r="F5463" t="inlineStr"/>
+      <c r="G5463" t="inlineStr"/>
+      <c r="H5463" t="inlineStr"/>
+      <c r="I5463" t="inlineStr"/>
+    </row>
+    <row r="5464">
+      <c r="A5464" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5464" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5464" t="inlineStr"/>
+      <c r="D5464" t="inlineStr"/>
+      <c r="E5464" t="inlineStr"/>
+      <c r="F5464" t="inlineStr"/>
+      <c r="G5464" t="inlineStr"/>
+      <c r="H5464" t="inlineStr"/>
+      <c r="I5464" t="inlineStr"/>
+    </row>
+    <row r="5465">
+      <c r="A5465" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5465" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5465" t="inlineStr"/>
+      <c r="D5465" t="inlineStr"/>
+      <c r="E5465" t="inlineStr"/>
+      <c r="F5465" t="inlineStr"/>
+      <c r="G5465" t="inlineStr"/>
+      <c r="H5465" t="inlineStr"/>
+      <c r="I5465" t="inlineStr"/>
+    </row>
+    <row r="5466">
+      <c r="A5466" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5466" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5466" t="inlineStr"/>
+      <c r="D5466" t="inlineStr"/>
+      <c r="E5466" t="inlineStr"/>
+      <c r="F5466" t="inlineStr"/>
+      <c r="G5466" t="inlineStr"/>
+      <c r="H5466" t="inlineStr"/>
+      <c r="I5466" t="inlineStr"/>
+    </row>
+    <row r="5467">
+      <c r="A5467" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5467" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5467" t="inlineStr"/>
+      <c r="D5467" t="inlineStr"/>
+      <c r="E5467" t="inlineStr"/>
+      <c r="F5467" t="inlineStr"/>
+      <c r="G5467" t="inlineStr"/>
+      <c r="H5467" t="inlineStr"/>
+      <c r="I5467" t="inlineStr"/>
+    </row>
+    <row r="5468">
+      <c r="A5468" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5468" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5468" t="inlineStr"/>
+      <c r="D5468" t="inlineStr"/>
+      <c r="E5468" t="inlineStr"/>
+      <c r="F5468" t="inlineStr"/>
+      <c r="G5468" t="inlineStr"/>
+      <c r="H5468" t="inlineStr"/>
+      <c r="I5468" t="inlineStr"/>
+    </row>
+    <row r="5469">
+      <c r="A5469" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5469" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5469" t="inlineStr"/>
+      <c r="D5469" t="inlineStr"/>
+      <c r="E5469" t="inlineStr"/>
+      <c r="F5469" t="inlineStr"/>
+      <c r="G5469" t="inlineStr"/>
+      <c r="H5469" t="inlineStr"/>
+      <c r="I5469" t="inlineStr"/>
+    </row>
+    <row r="5470">
+      <c r="A5470" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5470" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5470" t="inlineStr"/>
+      <c r="D5470" t="inlineStr"/>
+      <c r="E5470" t="inlineStr"/>
+      <c r="F5470" t="inlineStr"/>
+      <c r="G5470" t="inlineStr"/>
+      <c r="H5470" t="inlineStr"/>
+      <c r="I5470" t="inlineStr"/>
+    </row>
+    <row r="5471">
+      <c r="A5471" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5471" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5471" t="inlineStr"/>
+      <c r="D5471" t="inlineStr"/>
+      <c r="E5471" t="inlineStr"/>
+      <c r="F5471" t="inlineStr"/>
+      <c r="G5471" t="inlineStr"/>
+      <c r="H5471" t="inlineStr"/>
+      <c r="I5471" t="inlineStr"/>
+    </row>
+    <row r="5472">
+      <c r="A5472" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5472" t="inlineStr"/>
+      <c r="D5472" t="inlineStr"/>
+      <c r="E5472" t="inlineStr"/>
+      <c r="F5472" t="inlineStr"/>
+      <c r="G5472" t="inlineStr"/>
+      <c r="H5472" t="inlineStr"/>
+      <c r="I5472" t="inlineStr"/>
+    </row>
+    <row r="5473">
+      <c r="A5473" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5473" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5473" t="inlineStr"/>
+      <c r="D5473" t="inlineStr"/>
+      <c r="E5473" t="inlineStr"/>
+      <c r="F5473" t="inlineStr"/>
+      <c r="G5473" t="inlineStr"/>
+      <c r="H5473" t="inlineStr"/>
+      <c r="I5473" t="inlineStr"/>
+    </row>
+    <row r="5474">
+      <c r="A5474" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5474" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5474" t="inlineStr"/>
+      <c r="D5474" t="inlineStr"/>
+      <c r="E5474" t="inlineStr"/>
+      <c r="F5474" t="inlineStr"/>
+      <c r="G5474" t="inlineStr"/>
+      <c r="H5474" t="inlineStr"/>
+      <c r="I5474" t="inlineStr"/>
+    </row>
+    <row r="5475">
+      <c r="A5475" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5475" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5475" t="inlineStr"/>
+      <c r="D5475" t="inlineStr"/>
+      <c r="E5475" t="inlineStr"/>
+      <c r="F5475" t="inlineStr"/>
+      <c r="G5475" t="inlineStr"/>
+      <c r="H5475" t="inlineStr"/>
+      <c r="I5475" t="inlineStr"/>
+    </row>
+    <row r="5476">
+      <c r="A5476" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5476" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5476" t="inlineStr"/>
+      <c r="D5476" t="inlineStr"/>
+      <c r="E5476" t="inlineStr"/>
+      <c r="F5476" t="inlineStr"/>
+      <c r="G5476" t="inlineStr"/>
+      <c r="H5476" t="inlineStr"/>
+      <c r="I5476" t="inlineStr"/>
+    </row>
+    <row r="5477">
+      <c r="A5477" t="inlineStr">
+        <is>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="B5477" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5477" t="inlineStr"/>
+      <c r="D5477" t="inlineStr"/>
+      <c r="E5477" t="inlineStr"/>
+      <c r="F5477" t="inlineStr"/>
+      <c r="G5477" t="inlineStr"/>
+      <c r="H5477" t="inlineStr"/>
+      <c r="I5477" t="inlineStr"/>
+    </row>
+    <row r="5478"/>
+    <row r="5479">
+      <c r="A5479" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5479" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5479" t="inlineStr"/>
+      <c r="D5479" t="inlineStr"/>
+      <c r="E5479" t="inlineStr"/>
+      <c r="F5479" t="inlineStr"/>
+      <c r="G5479" t="inlineStr"/>
+      <c r="H5479" t="inlineStr"/>
+      <c r="I5479" t="inlineStr"/>
+    </row>
+    <row r="5480">
+      <c r="A5480" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5480" t="inlineStr"/>
+      <c r="D5480" t="inlineStr"/>
+      <c r="E5480" t="inlineStr"/>
+      <c r="F5480" t="inlineStr"/>
+      <c r="G5480" t="inlineStr"/>
+      <c r="H5480" t="inlineStr"/>
+      <c r="I5480" t="inlineStr"/>
+    </row>
+    <row r="5481">
+      <c r="A5481" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5481" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5481" t="inlineStr"/>
+      <c r="D5481" t="inlineStr"/>
+      <c r="E5481" t="inlineStr"/>
+      <c r="F5481" t="inlineStr"/>
+      <c r="G5481" t="inlineStr"/>
+      <c r="H5481" t="inlineStr"/>
+      <c r="I5481" t="inlineStr"/>
+    </row>
+    <row r="5482">
+      <c r="A5482" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5482" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5482" t="inlineStr"/>
+      <c r="D5482" t="inlineStr"/>
+      <c r="E5482" t="inlineStr"/>
+      <c r="F5482" t="inlineStr"/>
+      <c r="G5482" t="inlineStr"/>
+      <c r="H5482" t="inlineStr"/>
+      <c r="I5482" t="inlineStr"/>
+    </row>
+    <row r="5483">
+      <c r="A5483" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5483" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5483" t="inlineStr"/>
+      <c r="D5483" t="inlineStr"/>
+      <c r="E5483" t="inlineStr"/>
+      <c r="F5483" t="inlineStr"/>
+      <c r="G5483" t="inlineStr"/>
+      <c r="H5483" t="inlineStr"/>
+      <c r="I5483" t="inlineStr"/>
+    </row>
+    <row r="5484">
+      <c r="A5484" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5484" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5484" t="inlineStr"/>
+      <c r="D5484" t="inlineStr"/>
+      <c r="E5484" t="inlineStr"/>
+      <c r="F5484" t="inlineStr"/>
+      <c r="G5484" t="inlineStr"/>
+      <c r="H5484" t="inlineStr"/>
+      <c r="I5484" t="inlineStr"/>
+    </row>
+    <row r="5485">
+      <c r="A5485" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5485" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5485" t="inlineStr"/>
+      <c r="D5485" t="inlineStr"/>
+      <c r="E5485" t="inlineStr"/>
+      <c r="F5485" t="inlineStr"/>
+      <c r="G5485" t="inlineStr"/>
+      <c r="H5485" t="inlineStr"/>
+      <c r="I5485" t="inlineStr"/>
+    </row>
+    <row r="5486">
+      <c r="A5486" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5486" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5486" t="inlineStr"/>
+      <c r="D5486" t="inlineStr"/>
+      <c r="E5486" t="inlineStr"/>
+      <c r="F5486" t="inlineStr"/>
+      <c r="G5486" t="inlineStr"/>
+      <c r="H5486" t="inlineStr"/>
+      <c r="I5486" t="inlineStr"/>
+    </row>
+    <row r="5487">
+      <c r="A5487" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5487" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5487" t="inlineStr"/>
+      <c r="D5487" t="inlineStr"/>
+      <c r="E5487" t="inlineStr"/>
+      <c r="F5487" t="inlineStr"/>
+      <c r="G5487" t="inlineStr"/>
+      <c r="H5487" t="inlineStr"/>
+      <c r="I5487" t="inlineStr"/>
+    </row>
+    <row r="5488">
+      <c r="A5488" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5488" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5488" t="inlineStr"/>
+      <c r="D5488" t="inlineStr"/>
+      <c r="E5488" t="inlineStr"/>
+      <c r="F5488" t="inlineStr"/>
+      <c r="G5488" t="inlineStr"/>
+      <c r="H5488" t="inlineStr"/>
+      <c r="I5488" t="inlineStr"/>
+    </row>
+    <row r="5489">
+      <c r="A5489" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5489" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5489" t="inlineStr"/>
+      <c r="D5489" t="inlineStr"/>
+      <c r="E5489" t="inlineStr"/>
+      <c r="F5489" t="inlineStr"/>
+      <c r="G5489" t="inlineStr"/>
+      <c r="H5489" t="inlineStr"/>
+      <c r="I5489" t="inlineStr"/>
+    </row>
+    <row r="5490">
+      <c r="A5490" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5490" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5490" t="inlineStr"/>
+      <c r="D5490" t="inlineStr"/>
+      <c r="E5490" t="inlineStr"/>
+      <c r="F5490" t="inlineStr"/>
+      <c r="G5490" t="inlineStr"/>
+      <c r="H5490" t="inlineStr"/>
+      <c r="I5490" t="inlineStr"/>
+    </row>
+    <row r="5491">
+      <c r="A5491" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5491" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5491" t="inlineStr"/>
+      <c r="D5491" t="inlineStr"/>
+      <c r="E5491" t="inlineStr"/>
+      <c r="F5491" t="inlineStr"/>
+      <c r="G5491" t="inlineStr"/>
+      <c r="H5491" t="inlineStr"/>
+      <c r="I5491" t="inlineStr"/>
+    </row>
+    <row r="5492">
+      <c r="A5492" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5492" t="inlineStr"/>
+      <c r="D5492" t="inlineStr"/>
+      <c r="E5492" t="inlineStr"/>
+      <c r="F5492" t="inlineStr"/>
+      <c r="G5492" t="inlineStr"/>
+      <c r="H5492" t="inlineStr"/>
+      <c r="I5492" t="inlineStr"/>
+    </row>
+    <row r="5493">
+      <c r="A5493" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5493" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5493" t="inlineStr"/>
+      <c r="D5493" t="inlineStr"/>
+      <c r="E5493" t="inlineStr"/>
+      <c r="F5493" t="inlineStr"/>
+      <c r="G5493" t="inlineStr"/>
+      <c r="H5493" t="inlineStr"/>
+      <c r="I5493" t="inlineStr"/>
+    </row>
+    <row r="5494">
+      <c r="A5494" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5494" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5494" t="inlineStr"/>
+      <c r="D5494" t="inlineStr"/>
+      <c r="E5494" t="inlineStr"/>
+      <c r="F5494" t="inlineStr"/>
+      <c r="G5494" t="inlineStr"/>
+      <c r="H5494" t="inlineStr"/>
+      <c r="I5494" t="inlineStr"/>
+    </row>
+    <row r="5495">
+      <c r="A5495" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5495" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5495" t="inlineStr"/>
+      <c r="D5495" t="inlineStr"/>
+      <c r="E5495" t="inlineStr"/>
+      <c r="F5495" t="inlineStr"/>
+      <c r="G5495" t="inlineStr"/>
+      <c r="H5495" t="inlineStr"/>
+      <c r="I5495" t="inlineStr"/>
+    </row>
+    <row r="5496">
+      <c r="A5496" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5496" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5496" t="inlineStr"/>
+      <c r="D5496" t="inlineStr"/>
+      <c r="E5496" t="inlineStr"/>
+      <c r="F5496" t="inlineStr"/>
+      <c r="G5496" t="inlineStr"/>
+      <c r="H5496" t="inlineStr"/>
+      <c r="I5496" t="inlineStr"/>
+    </row>
+    <row r="5497">
+      <c r="A5497" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B5497" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5497" t="inlineStr"/>
+      <c r="D5497" t="inlineStr"/>
+      <c r="E5497" t="inlineStr"/>
+      <c r="F5497" t="inlineStr"/>
+      <c r="G5497" t="inlineStr"/>
+      <c r="H5497" t="inlineStr"/>
+      <c r="I5497" t="inlineStr"/>
+    </row>
+    <row r="5498"/>
+    <row r="5499">
+      <c r="A5499" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5499" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5499" t="inlineStr"/>
+      <c r="D5499" t="inlineStr"/>
+      <c r="E5499" t="inlineStr"/>
+      <c r="F5499" t="inlineStr"/>
+      <c r="G5499" t="inlineStr"/>
+      <c r="H5499" t="inlineStr"/>
+      <c r="I5499" t="inlineStr"/>
+    </row>
+    <row r="5500">
+      <c r="A5500" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5500" t="inlineStr"/>
+      <c r="D5500" t="inlineStr"/>
+      <c r="E5500" t="inlineStr"/>
+      <c r="F5500" t="inlineStr"/>
+      <c r="G5500" t="inlineStr"/>
+      <c r="H5500" t="inlineStr"/>
+      <c r="I5500" t="inlineStr"/>
+    </row>
+    <row r="5501">
+      <c r="A5501" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5501" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5501" t="inlineStr"/>
+      <c r="D5501" t="inlineStr"/>
+      <c r="E5501" t="inlineStr"/>
+      <c r="F5501" t="inlineStr"/>
+      <c r="G5501" t="inlineStr"/>
+      <c r="H5501" t="inlineStr"/>
+      <c r="I5501" t="inlineStr"/>
+    </row>
+    <row r="5502">
+      <c r="A5502" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5502" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5502" t="inlineStr"/>
+      <c r="D5502" t="inlineStr"/>
+      <c r="E5502" t="inlineStr"/>
+      <c r="F5502" t="inlineStr"/>
+      <c r="G5502" t="inlineStr"/>
+      <c r="H5502" t="inlineStr"/>
+      <c r="I5502" t="inlineStr"/>
+    </row>
+    <row r="5503">
+      <c r="A5503" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5503" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5503" t="inlineStr"/>
+      <c r="D5503" t="inlineStr"/>
+      <c r="E5503" t="inlineStr"/>
+      <c r="F5503" t="inlineStr"/>
+      <c r="G5503" t="inlineStr"/>
+      <c r="H5503" t="inlineStr"/>
+      <c r="I5503" t="inlineStr"/>
+    </row>
+    <row r="5504">
+      <c r="A5504" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5504" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5504" t="inlineStr"/>
+      <c r="D5504" t="inlineStr"/>
+      <c r="E5504" t="inlineStr"/>
+      <c r="F5504" t="inlineStr"/>
+      <c r="G5504" t="inlineStr"/>
+      <c r="H5504" t="inlineStr"/>
+      <c r="I5504" t="inlineStr"/>
+    </row>
+    <row r="5505">
+      <c r="A5505" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5505" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5505" t="inlineStr"/>
+      <c r="D5505" t="inlineStr"/>
+      <c r="E5505" t="inlineStr"/>
+      <c r="F5505" t="inlineStr"/>
+      <c r="G5505" t="inlineStr"/>
+      <c r="H5505" t="inlineStr"/>
+      <c r="I5505" t="inlineStr"/>
+    </row>
+    <row r="5506">
+      <c r="A5506" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5506" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5506" t="inlineStr"/>
+      <c r="D5506" t="inlineStr"/>
+      <c r="E5506" t="inlineStr"/>
+      <c r="F5506" t="inlineStr"/>
+      <c r="G5506" t="inlineStr"/>
+      <c r="H5506" t="inlineStr"/>
+      <c r="I5506" t="inlineStr"/>
+    </row>
+    <row r="5507">
+      <c r="A5507" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5507" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5507" t="inlineStr"/>
+      <c r="D5507" t="inlineStr"/>
+      <c r="E5507" t="inlineStr"/>
+      <c r="F5507" t="inlineStr"/>
+      <c r="G5507" t="inlineStr"/>
+      <c r="H5507" t="inlineStr"/>
+      <c r="I5507" t="inlineStr"/>
+    </row>
+    <row r="5508">
+      <c r="A5508" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5508" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5508" t="inlineStr"/>
+      <c r="D5508" t="inlineStr"/>
+      <c r="E5508" t="inlineStr"/>
+      <c r="F5508" t="inlineStr"/>
+      <c r="G5508" t="inlineStr"/>
+      <c r="H5508" t="inlineStr"/>
+      <c r="I5508" t="inlineStr"/>
+    </row>
+    <row r="5509">
+      <c r="A5509" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5509" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5509" t="inlineStr"/>
+      <c r="D5509" t="inlineStr"/>
+      <c r="E5509" t="inlineStr"/>
+      <c r="F5509" t="inlineStr"/>
+      <c r="G5509" t="inlineStr"/>
+      <c r="H5509" t="inlineStr"/>
+      <c r="I5509" t="inlineStr"/>
+    </row>
+    <row r="5510">
+      <c r="A5510" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5510" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5510" t="inlineStr"/>
+      <c r="D5510" t="inlineStr"/>
+      <c r="E5510" t="inlineStr"/>
+      <c r="F5510" t="inlineStr"/>
+      <c r="G5510" t="inlineStr"/>
+      <c r="H5510" t="inlineStr"/>
+      <c r="I5510" t="inlineStr"/>
+    </row>
+    <row r="5511">
+      <c r="A5511" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5511" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5511" t="inlineStr"/>
+      <c r="D5511" t="inlineStr"/>
+      <c r="E5511" t="inlineStr"/>
+      <c r="F5511" t="inlineStr"/>
+      <c r="G5511" t="inlineStr"/>
+      <c r="H5511" t="inlineStr"/>
+      <c r="I5511" t="inlineStr"/>
+    </row>
+    <row r="5512">
+      <c r="A5512" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5512" t="inlineStr"/>
+      <c r="D5512" t="inlineStr"/>
+      <c r="E5512" t="inlineStr"/>
+      <c r="F5512" t="inlineStr"/>
+      <c r="G5512" t="inlineStr"/>
+      <c r="H5512" t="inlineStr"/>
+      <c r="I5512" t="inlineStr"/>
+    </row>
+    <row r="5513">
+      <c r="A5513" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5513" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5513" t="inlineStr"/>
+      <c r="D5513" t="inlineStr"/>
+      <c r="E5513" t="inlineStr"/>
+      <c r="F5513" t="inlineStr"/>
+      <c r="G5513" t="inlineStr"/>
+      <c r="H5513" t="inlineStr"/>
+      <c r="I5513" t="inlineStr"/>
+    </row>
+    <row r="5514">
+      <c r="A5514" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5514" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5514" t="inlineStr"/>
+      <c r="D5514" t="inlineStr"/>
+      <c r="E5514" t="inlineStr"/>
+      <c r="F5514" t="inlineStr"/>
+      <c r="G5514" t="inlineStr"/>
+      <c r="H5514" t="inlineStr"/>
+      <c r="I5514" t="inlineStr"/>
+    </row>
+    <row r="5515">
+      <c r="A5515" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5515" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5515" t="inlineStr"/>
+      <c r="D5515" t="inlineStr"/>
+      <c r="E5515" t="inlineStr"/>
+      <c r="F5515" t="inlineStr"/>
+      <c r="G5515" t="inlineStr"/>
+      <c r="H5515" t="inlineStr"/>
+      <c r="I5515" t="inlineStr"/>
+    </row>
+    <row r="5516">
+      <c r="A5516" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5516" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5516" t="inlineStr"/>
+      <c r="D5516" t="inlineStr"/>
+      <c r="E5516" t="inlineStr"/>
+      <c r="F5516" t="inlineStr"/>
+      <c r="G5516" t="inlineStr"/>
+      <c r="H5516" t="inlineStr"/>
+      <c r="I5516" t="inlineStr"/>
+    </row>
+    <row r="5517">
+      <c r="A5517" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B5517" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5517" t="inlineStr"/>
+      <c r="D5517" t="inlineStr"/>
+      <c r="E5517" t="inlineStr"/>
+      <c r="F5517" t="inlineStr"/>
+      <c r="G5517" t="inlineStr"/>
+      <c r="H5517" t="inlineStr"/>
+      <c r="I5517" t="inlineStr"/>
+    </row>
+    <row r="5518"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/data/blumen_data.xlsx
+++ b/data/blumen_data.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5518"/>
+  <dimension ref="A1:AD5918"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -64670,13 +64670,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5419" t="inlineStr"/>
-      <c r="D5419" t="inlineStr"/>
-      <c r="E5419" t="inlineStr"/>
-      <c r="F5419" t="inlineStr"/>
-      <c r="G5419" t="inlineStr"/>
-      <c r="H5419" t="inlineStr"/>
-      <c r="I5419" t="inlineStr"/>
     </row>
     <row r="5420">
       <c r="A5420" t="inlineStr">
@@ -64689,32 +64682,26 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5420" t="inlineStr"/>
-      <c r="D5420" t="inlineStr"/>
-      <c r="E5420" t="inlineStr"/>
-      <c r="F5420" t="inlineStr"/>
-      <c r="G5420" t="inlineStr"/>
-      <c r="H5420" t="inlineStr"/>
-      <c r="I5420" t="inlineStr"/>
-    </row>
-    <row r="5421">
-      <c r="A5421" t="inlineStr">
+    </row>
+    <row r="5421" customFormat="1" s="7">
+      <c r="A5421" s="7" t="inlineStr">
         <is>
           <t>27.03.2026</t>
         </is>
       </c>
-      <c r="B5421" t="inlineStr">
+      <c r="B5421" s="7" t="inlineStr">
         <is>
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5421" t="inlineStr"/>
-      <c r="D5421" t="inlineStr"/>
-      <c r="E5421" t="inlineStr"/>
-      <c r="F5421" t="inlineStr"/>
-      <c r="G5421" t="inlineStr"/>
-      <c r="H5421" t="inlineStr"/>
-      <c r="I5421" t="inlineStr"/>
+      <c r="D5421" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5421" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5422">
       <c r="A5422" t="inlineStr">
@@ -64727,13 +64714,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5422" t="inlineStr"/>
-      <c r="D5422" t="inlineStr"/>
-      <c r="E5422" t="inlineStr"/>
-      <c r="F5422" t="inlineStr"/>
-      <c r="G5422" t="inlineStr"/>
-      <c r="H5422" t="inlineStr"/>
-      <c r="I5422" t="inlineStr"/>
     </row>
     <row r="5423">
       <c r="A5423" t="inlineStr">
@@ -64746,13 +64726,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5423" t="inlineStr"/>
-      <c r="D5423" t="inlineStr"/>
-      <c r="E5423" t="inlineStr"/>
-      <c r="F5423" t="inlineStr"/>
-      <c r="G5423" t="inlineStr"/>
-      <c r="H5423" t="inlineStr"/>
-      <c r="I5423" t="inlineStr"/>
     </row>
     <row r="5424">
       <c r="A5424" t="inlineStr">
@@ -64765,32 +64738,26 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5424" t="inlineStr"/>
-      <c r="D5424" t="inlineStr"/>
-      <c r="E5424" t="inlineStr"/>
-      <c r="F5424" t="inlineStr"/>
-      <c r="G5424" t="inlineStr"/>
-      <c r="H5424" t="inlineStr"/>
-      <c r="I5424" t="inlineStr"/>
-    </row>
-    <row r="5425">
-      <c r="A5425" t="inlineStr">
+    </row>
+    <row r="5425" customFormat="1" s="7">
+      <c r="A5425" s="7" t="inlineStr">
         <is>
           <t>27.03.2026</t>
         </is>
       </c>
-      <c r="B5425" t="inlineStr">
+      <c r="B5425" s="7" t="inlineStr">
         <is>
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5425" t="inlineStr"/>
-      <c r="D5425" t="inlineStr"/>
-      <c r="E5425" t="inlineStr"/>
-      <c r="F5425" t="inlineStr"/>
-      <c r="G5425" t="inlineStr"/>
-      <c r="H5425" t="inlineStr"/>
-      <c r="I5425" t="inlineStr"/>
+      <c r="D5425" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5425" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5426">
       <c r="A5426" t="inlineStr">
@@ -64803,13 +64770,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5426" t="inlineStr"/>
-      <c r="D5426" t="inlineStr"/>
-      <c r="E5426" t="inlineStr"/>
-      <c r="F5426" t="inlineStr"/>
-      <c r="G5426" t="inlineStr"/>
-      <c r="H5426" t="inlineStr"/>
-      <c r="I5426" t="inlineStr"/>
     </row>
     <row r="5427">
       <c r="A5427" t="inlineStr">
@@ -64822,13 +64782,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5427" t="inlineStr"/>
-      <c r="D5427" t="inlineStr"/>
-      <c r="E5427" t="inlineStr"/>
-      <c r="F5427" t="inlineStr"/>
-      <c r="G5427" t="inlineStr"/>
-      <c r="H5427" t="inlineStr"/>
-      <c r="I5427" t="inlineStr"/>
     </row>
     <row r="5428">
       <c r="A5428" t="inlineStr">
@@ -64841,13 +64794,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5428" t="inlineStr"/>
-      <c r="D5428" t="inlineStr"/>
-      <c r="E5428" t="inlineStr"/>
-      <c r="F5428" t="inlineStr"/>
-      <c r="G5428" t="inlineStr"/>
-      <c r="H5428" t="inlineStr"/>
-      <c r="I5428" t="inlineStr"/>
     </row>
     <row r="5429">
       <c r="A5429" t="inlineStr">
@@ -64860,32 +64806,26 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5429" t="inlineStr"/>
-      <c r="D5429" t="inlineStr"/>
-      <c r="E5429" t="inlineStr"/>
-      <c r="F5429" t="inlineStr"/>
-      <c r="G5429" t="inlineStr"/>
-      <c r="H5429" t="inlineStr"/>
-      <c r="I5429" t="inlineStr"/>
-    </row>
-    <row r="5430">
-      <c r="A5430" t="inlineStr">
+    </row>
+    <row r="5430" customFormat="1" s="7">
+      <c r="A5430" s="7" t="inlineStr">
         <is>
           <t>27.03.2026</t>
         </is>
       </c>
-      <c r="B5430" t="inlineStr">
+      <c r="B5430" s="7" t="inlineStr">
         <is>
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5430" t="inlineStr"/>
-      <c r="D5430" t="inlineStr"/>
-      <c r="E5430" t="inlineStr"/>
-      <c r="F5430" t="inlineStr"/>
-      <c r="G5430" t="inlineStr"/>
-      <c r="H5430" t="inlineStr"/>
-      <c r="I5430" t="inlineStr"/>
+      <c r="D5430" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5430" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5431">
       <c r="A5431" t="inlineStr">
@@ -64898,32 +64838,26 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5431" t="inlineStr"/>
-      <c r="D5431" t="inlineStr"/>
-      <c r="E5431" t="inlineStr"/>
-      <c r="F5431" t="inlineStr"/>
-      <c r="G5431" t="inlineStr"/>
-      <c r="H5431" t="inlineStr"/>
-      <c r="I5431" t="inlineStr"/>
-    </row>
-    <row r="5432">
-      <c r="A5432" t="inlineStr">
+    </row>
+    <row r="5432" customFormat="1" s="7">
+      <c r="A5432" s="7" t="inlineStr">
         <is>
           <t>27.03.2026</t>
         </is>
       </c>
-      <c r="B5432" t="inlineStr">
+      <c r="B5432" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5432" t="inlineStr"/>
-      <c r="D5432" t="inlineStr"/>
-      <c r="E5432" t="inlineStr"/>
-      <c r="F5432" t="inlineStr"/>
-      <c r="G5432" t="inlineStr"/>
-      <c r="H5432" t="inlineStr"/>
-      <c r="I5432" t="inlineStr"/>
+      <c r="D5432" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5432" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5433">
       <c r="A5433" t="inlineStr">
@@ -64936,13 +64870,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5433" t="inlineStr"/>
-      <c r="D5433" t="inlineStr"/>
-      <c r="E5433" t="inlineStr"/>
-      <c r="F5433" t="inlineStr"/>
-      <c r="G5433" t="inlineStr"/>
-      <c r="H5433" t="inlineStr"/>
-      <c r="I5433" t="inlineStr"/>
     </row>
     <row r="5434">
       <c r="A5434" t="inlineStr">
@@ -64955,51 +64882,46 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5434" t="inlineStr"/>
-      <c r="D5434" t="inlineStr"/>
-      <c r="E5434" t="inlineStr"/>
-      <c r="F5434" t="inlineStr"/>
-      <c r="G5434" t="inlineStr"/>
-      <c r="H5434" t="inlineStr"/>
-      <c r="I5434" t="inlineStr"/>
-    </row>
-    <row r="5435">
-      <c r="A5435" t="inlineStr">
+    </row>
+    <row r="5435" customFormat="1" s="7">
+      <c r="A5435" s="7" t="inlineStr">
         <is>
           <t>27.03.2026</t>
         </is>
       </c>
-      <c r="B5435" t="inlineStr">
+      <c r="B5435" s="7" t="inlineStr">
         <is>
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5435" t="inlineStr"/>
-      <c r="D5435" t="inlineStr"/>
-      <c r="E5435" t="inlineStr"/>
-      <c r="F5435" t="inlineStr"/>
-      <c r="G5435" t="inlineStr"/>
-      <c r="H5435" t="inlineStr"/>
-      <c r="I5435" t="inlineStr"/>
-    </row>
-    <row r="5436">
-      <c r="A5436" t="inlineStr">
+      <c r="D5435" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5435" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5436" customFormat="1" s="7">
+      <c r="A5436" s="7" t="inlineStr">
         <is>
           <t>27.03.2026</t>
         </is>
       </c>
-      <c r="B5436" t="inlineStr">
+      <c r="B5436" s="7" t="inlineStr">
         <is>
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5436" t="inlineStr"/>
-      <c r="D5436" t="inlineStr"/>
-      <c r="E5436" t="inlineStr"/>
-      <c r="F5436" t="inlineStr"/>
-      <c r="G5436" t="inlineStr"/>
-      <c r="H5436" t="inlineStr"/>
-      <c r="I5436" t="inlineStr"/>
+      <c r="D5436" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5436" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5437">
       <c r="A5437" t="inlineStr">
@@ -65012,71 +64934,63 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5437" t="inlineStr"/>
-      <c r="D5437" t="inlineStr"/>
-      <c r="E5437" t="inlineStr"/>
-      <c r="F5437" t="inlineStr"/>
-      <c r="G5437" t="inlineStr"/>
-      <c r="H5437" t="inlineStr"/>
-      <c r="I5437" t="inlineStr"/>
     </row>
     <row r="5438"/>
-    <row r="5439">
-      <c r="A5439" t="inlineStr">
+    <row r="5439" customFormat="1" s="7">
+      <c r="A5439" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5439" t="inlineStr">
+      <c r="B5439" s="7" t="inlineStr">
         <is>
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5439" t="inlineStr"/>
-      <c r="D5439" t="inlineStr"/>
-      <c r="E5439" t="inlineStr"/>
-      <c r="F5439" t="inlineStr"/>
-      <c r="G5439" t="inlineStr"/>
-      <c r="H5439" t="inlineStr"/>
-      <c r="I5439" t="inlineStr"/>
-    </row>
-    <row r="5440">
-      <c r="A5440" t="inlineStr">
+      <c r="I5439" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5440" customFormat="1" s="7">
+      <c r="A5440" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5440" t="inlineStr">
+      <c r="B5440" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5440" t="inlineStr"/>
-      <c r="D5440" t="inlineStr"/>
-      <c r="E5440" t="inlineStr"/>
-      <c r="F5440" t="inlineStr"/>
-      <c r="G5440" t="inlineStr"/>
-      <c r="H5440" t="inlineStr"/>
-      <c r="I5440" t="inlineStr"/>
-    </row>
-    <row r="5441">
-      <c r="A5441" t="inlineStr">
+      <c r="I5440" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K5440" s="7" t="inlineStr">
+        <is>
+          <t>bad, some pest bugs with black little shits</t>
+        </is>
+      </c>
+    </row>
+    <row r="5441" customFormat="1" s="7">
+      <c r="A5441" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5441" t="inlineStr">
+      <c r="B5441" s="7" t="inlineStr">
         <is>
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5441" t="inlineStr"/>
-      <c r="D5441" t="inlineStr"/>
-      <c r="E5441" t="inlineStr"/>
-      <c r="F5441" t="inlineStr"/>
-      <c r="G5441" t="inlineStr"/>
-      <c r="H5441" t="inlineStr"/>
-      <c r="I5441" t="inlineStr"/>
+      <c r="I5441" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="5442">
       <c r="A5442" t="inlineStr">
@@ -65089,13 +65003,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5442" t="inlineStr"/>
-      <c r="D5442" t="inlineStr"/>
-      <c r="E5442" t="inlineStr"/>
-      <c r="F5442" t="inlineStr"/>
-      <c r="G5442" t="inlineStr"/>
-      <c r="H5442" t="inlineStr"/>
-      <c r="I5442" t="inlineStr"/>
     </row>
     <row r="5443">
       <c r="A5443" t="inlineStr">
@@ -65108,13 +65015,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5443" t="inlineStr"/>
-      <c r="D5443" t="inlineStr"/>
-      <c r="E5443" t="inlineStr"/>
-      <c r="F5443" t="inlineStr"/>
-      <c r="G5443" t="inlineStr"/>
-      <c r="H5443" t="inlineStr"/>
-      <c r="I5443" t="inlineStr"/>
     </row>
     <row r="5444">
       <c r="A5444" t="inlineStr">
@@ -65127,13 +65027,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5444" t="inlineStr"/>
-      <c r="D5444" t="inlineStr"/>
-      <c r="E5444" t="inlineStr"/>
-      <c r="F5444" t="inlineStr"/>
-      <c r="G5444" t="inlineStr"/>
-      <c r="H5444" t="inlineStr"/>
-      <c r="I5444" t="inlineStr"/>
     </row>
     <row r="5445">
       <c r="A5445" t="inlineStr">
@@ -65146,32 +65039,23 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5445" t="inlineStr"/>
-      <c r="D5445" t="inlineStr"/>
-      <c r="E5445" t="inlineStr"/>
-      <c r="F5445" t="inlineStr"/>
-      <c r="G5445" t="inlineStr"/>
-      <c r="H5445" t="inlineStr"/>
-      <c r="I5445" t="inlineStr"/>
-    </row>
-    <row r="5446">
-      <c r="A5446" t="inlineStr">
+    </row>
+    <row r="5446" customFormat="1" s="7">
+      <c r="A5446" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5446" t="inlineStr">
+      <c r="B5446" s="7" t="inlineStr">
         <is>
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5446" t="inlineStr"/>
-      <c r="D5446" t="inlineStr"/>
-      <c r="E5446" t="inlineStr"/>
-      <c r="F5446" t="inlineStr"/>
-      <c r="G5446" t="inlineStr"/>
-      <c r="H5446" t="inlineStr"/>
-      <c r="I5446" t="inlineStr"/>
+      <c r="I5446" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="5447">
       <c r="A5447" t="inlineStr">
@@ -65184,13 +65068,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5447" t="inlineStr"/>
-      <c r="D5447" t="inlineStr"/>
-      <c r="E5447" t="inlineStr"/>
-      <c r="F5447" t="inlineStr"/>
-      <c r="G5447" t="inlineStr"/>
-      <c r="H5447" t="inlineStr"/>
-      <c r="I5447" t="inlineStr"/>
     </row>
     <row r="5448">
       <c r="A5448" t="inlineStr">
@@ -65203,13 +65080,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5448" t="inlineStr"/>
-      <c r="D5448" t="inlineStr"/>
-      <c r="E5448" t="inlineStr"/>
-      <c r="F5448" t="inlineStr"/>
-      <c r="G5448" t="inlineStr"/>
-      <c r="H5448" t="inlineStr"/>
-      <c r="I5448" t="inlineStr"/>
     </row>
     <row r="5449">
       <c r="A5449" t="inlineStr">
@@ -65222,13 +65092,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5449" t="inlineStr"/>
-      <c r="D5449" t="inlineStr"/>
-      <c r="E5449" t="inlineStr"/>
-      <c r="F5449" t="inlineStr"/>
-      <c r="G5449" t="inlineStr"/>
-      <c r="H5449" t="inlineStr"/>
-      <c r="I5449" t="inlineStr"/>
     </row>
     <row r="5450">
       <c r="A5450" t="inlineStr">
@@ -65241,13 +65104,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5450" t="inlineStr"/>
-      <c r="D5450" t="inlineStr"/>
-      <c r="E5450" t="inlineStr"/>
-      <c r="F5450" t="inlineStr"/>
-      <c r="G5450" t="inlineStr"/>
-      <c r="H5450" t="inlineStr"/>
-      <c r="I5450" t="inlineStr"/>
     </row>
     <row r="5451">
       <c r="A5451" t="inlineStr">
@@ -65260,70 +65116,57 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5451" t="inlineStr"/>
-      <c r="D5451" t="inlineStr"/>
-      <c r="E5451" t="inlineStr"/>
-      <c r="F5451" t="inlineStr"/>
-      <c r="G5451" t="inlineStr"/>
-      <c r="H5451" t="inlineStr"/>
-      <c r="I5451" t="inlineStr"/>
-    </row>
-    <row r="5452">
-      <c r="A5452" t="inlineStr">
+    </row>
+    <row r="5452" customFormat="1" s="7">
+      <c r="A5452" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5452" t="inlineStr">
+      <c r="B5452" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5452" t="inlineStr"/>
-      <c r="D5452" t="inlineStr"/>
-      <c r="E5452" t="inlineStr"/>
-      <c r="F5452" t="inlineStr"/>
-      <c r="G5452" t="inlineStr"/>
-      <c r="H5452" t="inlineStr"/>
-      <c r="I5452" t="inlineStr"/>
-    </row>
-    <row r="5453">
-      <c r="A5453" t="inlineStr">
+      <c r="I5452" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5453" customFormat="1" s="7">
+      <c r="A5453" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5453" t="inlineStr">
+      <c r="B5453" s="7" t="inlineStr">
         <is>
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5453" t="inlineStr"/>
-      <c r="D5453" t="inlineStr"/>
-      <c r="E5453" t="inlineStr"/>
-      <c r="F5453" t="inlineStr"/>
-      <c r="G5453" t="inlineStr"/>
-      <c r="H5453" t="inlineStr"/>
-      <c r="I5453" t="inlineStr"/>
-    </row>
-    <row r="5454">
-      <c r="A5454" t="inlineStr">
+      <c r="I5453" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5454" customFormat="1" s="7">
+      <c r="A5454" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5454" t="inlineStr">
+      <c r="B5454" s="7" t="inlineStr">
         <is>
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5454" t="inlineStr"/>
-      <c r="D5454" t="inlineStr"/>
-      <c r="E5454" t="inlineStr"/>
-      <c r="F5454" t="inlineStr"/>
-      <c r="G5454" t="inlineStr"/>
-      <c r="H5454" t="inlineStr"/>
-      <c r="I5454" t="inlineStr"/>
+      <c r="I5454" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="5455">
       <c r="A5455" t="inlineStr">
@@ -65336,51 +65179,45 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5455" t="inlineStr"/>
-      <c r="D5455" t="inlineStr"/>
-      <c r="E5455" t="inlineStr"/>
-      <c r="F5455" t="inlineStr"/>
-      <c r="G5455" t="inlineStr"/>
-      <c r="H5455" t="inlineStr"/>
-      <c r="I5455" t="inlineStr"/>
-    </row>
-    <row r="5456">
-      <c r="A5456" t="inlineStr">
+    </row>
+    <row r="5456" customFormat="1" s="7">
+      <c r="A5456" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5456" t="inlineStr">
+      <c r="B5456" s="7" t="inlineStr">
         <is>
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5456" t="inlineStr"/>
-      <c r="D5456" t="inlineStr"/>
-      <c r="E5456" t="inlineStr"/>
-      <c r="F5456" t="inlineStr"/>
-      <c r="G5456" t="inlineStr"/>
-      <c r="H5456" t="inlineStr"/>
-      <c r="I5456" t="inlineStr"/>
-    </row>
-    <row r="5457">
-      <c r="A5457" t="inlineStr">
+      <c r="I5456" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K5456" s="7" t="inlineStr">
+        <is>
+          <t>very bad, some pest bugs with black little shits</t>
+        </is>
+      </c>
+    </row>
+    <row r="5457" customFormat="1" s="7">
+      <c r="A5457" s="7" t="inlineStr">
         <is>
           <t>28.03.2026</t>
         </is>
       </c>
-      <c r="B5457" t="inlineStr">
+      <c r="B5457" s="7" t="inlineStr">
         <is>
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5457" t="inlineStr"/>
-      <c r="D5457" t="inlineStr"/>
-      <c r="E5457" t="inlineStr"/>
-      <c r="F5457" t="inlineStr"/>
-      <c r="G5457" t="inlineStr"/>
-      <c r="H5457" t="inlineStr"/>
-      <c r="I5457" t="inlineStr"/>
+      <c r="I5457" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="5458"/>
     <row r="5459">
@@ -65394,13 +65231,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5459" t="inlineStr"/>
-      <c r="D5459" t="inlineStr"/>
-      <c r="E5459" t="inlineStr"/>
-      <c r="F5459" t="inlineStr"/>
-      <c r="G5459" t="inlineStr"/>
-      <c r="H5459" t="inlineStr"/>
-      <c r="I5459" t="inlineStr"/>
     </row>
     <row r="5460">
       <c r="A5460" t="inlineStr">
@@ -65413,13 +65243,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5460" t="inlineStr"/>
-      <c r="D5460" t="inlineStr"/>
-      <c r="E5460" t="inlineStr"/>
-      <c r="F5460" t="inlineStr"/>
-      <c r="G5460" t="inlineStr"/>
-      <c r="H5460" t="inlineStr"/>
-      <c r="I5460" t="inlineStr"/>
     </row>
     <row r="5461">
       <c r="A5461" t="inlineStr">
@@ -65432,13 +65255,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5461" t="inlineStr"/>
-      <c r="D5461" t="inlineStr"/>
-      <c r="E5461" t="inlineStr"/>
-      <c r="F5461" t="inlineStr"/>
-      <c r="G5461" t="inlineStr"/>
-      <c r="H5461" t="inlineStr"/>
-      <c r="I5461" t="inlineStr"/>
     </row>
     <row r="5462">
       <c r="A5462" t="inlineStr">
@@ -65451,13 +65267,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5462" t="inlineStr"/>
-      <c r="D5462" t="inlineStr"/>
-      <c r="E5462" t="inlineStr"/>
-      <c r="F5462" t="inlineStr"/>
-      <c r="G5462" t="inlineStr"/>
-      <c r="H5462" t="inlineStr"/>
-      <c r="I5462" t="inlineStr"/>
     </row>
     <row r="5463">
       <c r="A5463" t="inlineStr">
@@ -65470,13 +65279,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5463" t="inlineStr"/>
-      <c r="D5463" t="inlineStr"/>
-      <c r="E5463" t="inlineStr"/>
-      <c r="F5463" t="inlineStr"/>
-      <c r="G5463" t="inlineStr"/>
-      <c r="H5463" t="inlineStr"/>
-      <c r="I5463" t="inlineStr"/>
     </row>
     <row r="5464">
       <c r="A5464" t="inlineStr">
@@ -65489,13 +65291,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5464" t="inlineStr"/>
-      <c r="D5464" t="inlineStr"/>
-      <c r="E5464" t="inlineStr"/>
-      <c r="F5464" t="inlineStr"/>
-      <c r="G5464" t="inlineStr"/>
-      <c r="H5464" t="inlineStr"/>
-      <c r="I5464" t="inlineStr"/>
     </row>
     <row r="5465">
       <c r="A5465" t="inlineStr">
@@ -65508,13 +65303,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5465" t="inlineStr"/>
-      <c r="D5465" t="inlineStr"/>
-      <c r="E5465" t="inlineStr"/>
-      <c r="F5465" t="inlineStr"/>
-      <c r="G5465" t="inlineStr"/>
-      <c r="H5465" t="inlineStr"/>
-      <c r="I5465" t="inlineStr"/>
     </row>
     <row r="5466">
       <c r="A5466" t="inlineStr">
@@ -65527,13 +65315,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5466" t="inlineStr"/>
-      <c r="D5466" t="inlineStr"/>
-      <c r="E5466" t="inlineStr"/>
-      <c r="F5466" t="inlineStr"/>
-      <c r="G5466" t="inlineStr"/>
-      <c r="H5466" t="inlineStr"/>
-      <c r="I5466" t="inlineStr"/>
     </row>
     <row r="5467">
       <c r="A5467" t="inlineStr">
@@ -65546,13 +65327,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5467" t="inlineStr"/>
-      <c r="D5467" t="inlineStr"/>
-      <c r="E5467" t="inlineStr"/>
-      <c r="F5467" t="inlineStr"/>
-      <c r="G5467" t="inlineStr"/>
-      <c r="H5467" t="inlineStr"/>
-      <c r="I5467" t="inlineStr"/>
     </row>
     <row r="5468">
       <c r="A5468" t="inlineStr">
@@ -65565,13 +65339,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5468" t="inlineStr"/>
-      <c r="D5468" t="inlineStr"/>
-      <c r="E5468" t="inlineStr"/>
-      <c r="F5468" t="inlineStr"/>
-      <c r="G5468" t="inlineStr"/>
-      <c r="H5468" t="inlineStr"/>
-      <c r="I5468" t="inlineStr"/>
     </row>
     <row r="5469">
       <c r="A5469" t="inlineStr">
@@ -65584,13 +65351,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5469" t="inlineStr"/>
-      <c r="D5469" t="inlineStr"/>
-      <c r="E5469" t="inlineStr"/>
-      <c r="F5469" t="inlineStr"/>
-      <c r="G5469" t="inlineStr"/>
-      <c r="H5469" t="inlineStr"/>
-      <c r="I5469" t="inlineStr"/>
     </row>
     <row r="5470">
       <c r="A5470" t="inlineStr">
@@ -65603,13 +65363,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5470" t="inlineStr"/>
-      <c r="D5470" t="inlineStr"/>
-      <c r="E5470" t="inlineStr"/>
-      <c r="F5470" t="inlineStr"/>
-      <c r="G5470" t="inlineStr"/>
-      <c r="H5470" t="inlineStr"/>
-      <c r="I5470" t="inlineStr"/>
     </row>
     <row r="5471">
       <c r="A5471" t="inlineStr">
@@ -65622,13 +65375,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5471" t="inlineStr"/>
-      <c r="D5471" t="inlineStr"/>
-      <c r="E5471" t="inlineStr"/>
-      <c r="F5471" t="inlineStr"/>
-      <c r="G5471" t="inlineStr"/>
-      <c r="H5471" t="inlineStr"/>
-      <c r="I5471" t="inlineStr"/>
     </row>
     <row r="5472">
       <c r="A5472" t="inlineStr">
@@ -65641,13 +65387,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5472" t="inlineStr"/>
-      <c r="D5472" t="inlineStr"/>
-      <c r="E5472" t="inlineStr"/>
-      <c r="F5472" t="inlineStr"/>
-      <c r="G5472" t="inlineStr"/>
-      <c r="H5472" t="inlineStr"/>
-      <c r="I5472" t="inlineStr"/>
     </row>
     <row r="5473">
       <c r="A5473" t="inlineStr">
@@ -65660,13 +65399,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5473" t="inlineStr"/>
-      <c r="D5473" t="inlineStr"/>
-      <c r="E5473" t="inlineStr"/>
-      <c r="F5473" t="inlineStr"/>
-      <c r="G5473" t="inlineStr"/>
-      <c r="H5473" t="inlineStr"/>
-      <c r="I5473" t="inlineStr"/>
     </row>
     <row r="5474">
       <c r="A5474" t="inlineStr">
@@ -65679,13 +65411,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5474" t="inlineStr"/>
-      <c r="D5474" t="inlineStr"/>
-      <c r="E5474" t="inlineStr"/>
-      <c r="F5474" t="inlineStr"/>
-      <c r="G5474" t="inlineStr"/>
-      <c r="H5474" t="inlineStr"/>
-      <c r="I5474" t="inlineStr"/>
     </row>
     <row r="5475">
       <c r="A5475" t="inlineStr">
@@ -65698,13 +65423,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5475" t="inlineStr"/>
-      <c r="D5475" t="inlineStr"/>
-      <c r="E5475" t="inlineStr"/>
-      <c r="F5475" t="inlineStr"/>
-      <c r="G5475" t="inlineStr"/>
-      <c r="H5475" t="inlineStr"/>
-      <c r="I5475" t="inlineStr"/>
     </row>
     <row r="5476">
       <c r="A5476" t="inlineStr">
@@ -65717,13 +65435,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5476" t="inlineStr"/>
-      <c r="D5476" t="inlineStr"/>
-      <c r="E5476" t="inlineStr"/>
-      <c r="F5476" t="inlineStr"/>
-      <c r="G5476" t="inlineStr"/>
-      <c r="H5476" t="inlineStr"/>
-      <c r="I5476" t="inlineStr"/>
     </row>
     <row r="5477">
       <c r="A5477" t="inlineStr">
@@ -65736,13 +65447,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5477" t="inlineStr"/>
-      <c r="D5477" t="inlineStr"/>
-      <c r="E5477" t="inlineStr"/>
-      <c r="F5477" t="inlineStr"/>
-      <c r="G5477" t="inlineStr"/>
-      <c r="H5477" t="inlineStr"/>
-      <c r="I5477" t="inlineStr"/>
     </row>
     <row r="5478"/>
     <row r="5479">
@@ -65756,13 +65460,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5479" t="inlineStr"/>
-      <c r="D5479" t="inlineStr"/>
-      <c r="E5479" t="inlineStr"/>
-      <c r="F5479" t="inlineStr"/>
-      <c r="G5479" t="inlineStr"/>
-      <c r="H5479" t="inlineStr"/>
-      <c r="I5479" t="inlineStr"/>
     </row>
     <row r="5480">
       <c r="A5480" t="inlineStr">
@@ -65775,13 +65472,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5480" t="inlineStr"/>
-      <c r="D5480" t="inlineStr"/>
-      <c r="E5480" t="inlineStr"/>
-      <c r="F5480" t="inlineStr"/>
-      <c r="G5480" t="inlineStr"/>
-      <c r="H5480" t="inlineStr"/>
-      <c r="I5480" t="inlineStr"/>
     </row>
     <row r="5481">
       <c r="A5481" t="inlineStr">
@@ -65794,13 +65484,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5481" t="inlineStr"/>
-      <c r="D5481" t="inlineStr"/>
-      <c r="E5481" t="inlineStr"/>
-      <c r="F5481" t="inlineStr"/>
-      <c r="G5481" t="inlineStr"/>
-      <c r="H5481" t="inlineStr"/>
-      <c r="I5481" t="inlineStr"/>
     </row>
     <row r="5482">
       <c r="A5482" t="inlineStr">
@@ -65813,13 +65496,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5482" t="inlineStr"/>
-      <c r="D5482" t="inlineStr"/>
-      <c r="E5482" t="inlineStr"/>
-      <c r="F5482" t="inlineStr"/>
-      <c r="G5482" t="inlineStr"/>
-      <c r="H5482" t="inlineStr"/>
-      <c r="I5482" t="inlineStr"/>
     </row>
     <row r="5483">
       <c r="A5483" t="inlineStr">
@@ -65832,13 +65508,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5483" t="inlineStr"/>
-      <c r="D5483" t="inlineStr"/>
-      <c r="E5483" t="inlineStr"/>
-      <c r="F5483" t="inlineStr"/>
-      <c r="G5483" t="inlineStr"/>
-      <c r="H5483" t="inlineStr"/>
-      <c r="I5483" t="inlineStr"/>
     </row>
     <row r="5484">
       <c r="A5484" t="inlineStr">
@@ -65851,13 +65520,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5484" t="inlineStr"/>
-      <c r="D5484" t="inlineStr"/>
-      <c r="E5484" t="inlineStr"/>
-      <c r="F5484" t="inlineStr"/>
-      <c r="G5484" t="inlineStr"/>
-      <c r="H5484" t="inlineStr"/>
-      <c r="I5484" t="inlineStr"/>
     </row>
     <row r="5485">
       <c r="A5485" t="inlineStr">
@@ -65870,13 +65532,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5485" t="inlineStr"/>
-      <c r="D5485" t="inlineStr"/>
-      <c r="E5485" t="inlineStr"/>
-      <c r="F5485" t="inlineStr"/>
-      <c r="G5485" t="inlineStr"/>
-      <c r="H5485" t="inlineStr"/>
-      <c r="I5485" t="inlineStr"/>
     </row>
     <row r="5486">
       <c r="A5486" t="inlineStr">
@@ -65889,13 +65544,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5486" t="inlineStr"/>
-      <c r="D5486" t="inlineStr"/>
-      <c r="E5486" t="inlineStr"/>
-      <c r="F5486" t="inlineStr"/>
-      <c r="G5486" t="inlineStr"/>
-      <c r="H5486" t="inlineStr"/>
-      <c r="I5486" t="inlineStr"/>
     </row>
     <row r="5487">
       <c r="A5487" t="inlineStr">
@@ -65908,13 +65556,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5487" t="inlineStr"/>
-      <c r="D5487" t="inlineStr"/>
-      <c r="E5487" t="inlineStr"/>
-      <c r="F5487" t="inlineStr"/>
-      <c r="G5487" t="inlineStr"/>
-      <c r="H5487" t="inlineStr"/>
-      <c r="I5487" t="inlineStr"/>
     </row>
     <row r="5488">
       <c r="A5488" t="inlineStr">
@@ -65927,13 +65568,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5488" t="inlineStr"/>
-      <c r="D5488" t="inlineStr"/>
-      <c r="E5488" t="inlineStr"/>
-      <c r="F5488" t="inlineStr"/>
-      <c r="G5488" t="inlineStr"/>
-      <c r="H5488" t="inlineStr"/>
-      <c r="I5488" t="inlineStr"/>
     </row>
     <row r="5489">
       <c r="A5489" t="inlineStr">
@@ -65946,13 +65580,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5489" t="inlineStr"/>
-      <c r="D5489" t="inlineStr"/>
-      <c r="E5489" t="inlineStr"/>
-      <c r="F5489" t="inlineStr"/>
-      <c r="G5489" t="inlineStr"/>
-      <c r="H5489" t="inlineStr"/>
-      <c r="I5489" t="inlineStr"/>
     </row>
     <row r="5490">
       <c r="A5490" t="inlineStr">
@@ -65965,13 +65592,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5490" t="inlineStr"/>
-      <c r="D5490" t="inlineStr"/>
-      <c r="E5490" t="inlineStr"/>
-      <c r="F5490" t="inlineStr"/>
-      <c r="G5490" t="inlineStr"/>
-      <c r="H5490" t="inlineStr"/>
-      <c r="I5490" t="inlineStr"/>
     </row>
     <row r="5491">
       <c r="A5491" t="inlineStr">
@@ -65984,13 +65604,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5491" t="inlineStr"/>
-      <c r="D5491" t="inlineStr"/>
-      <c r="E5491" t="inlineStr"/>
-      <c r="F5491" t="inlineStr"/>
-      <c r="G5491" t="inlineStr"/>
-      <c r="H5491" t="inlineStr"/>
-      <c r="I5491" t="inlineStr"/>
     </row>
     <row r="5492">
       <c r="A5492" t="inlineStr">
@@ -66003,13 +65616,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5492" t="inlineStr"/>
-      <c r="D5492" t="inlineStr"/>
-      <c r="E5492" t="inlineStr"/>
-      <c r="F5492" t="inlineStr"/>
-      <c r="G5492" t="inlineStr"/>
-      <c r="H5492" t="inlineStr"/>
-      <c r="I5492" t="inlineStr"/>
     </row>
     <row r="5493">
       <c r="A5493" t="inlineStr">
@@ -66022,13 +65628,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5493" t="inlineStr"/>
-      <c r="D5493" t="inlineStr"/>
-      <c r="E5493" t="inlineStr"/>
-      <c r="F5493" t="inlineStr"/>
-      <c r="G5493" t="inlineStr"/>
-      <c r="H5493" t="inlineStr"/>
-      <c r="I5493" t="inlineStr"/>
     </row>
     <row r="5494">
       <c r="A5494" t="inlineStr">
@@ -66041,13 +65640,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5494" t="inlineStr"/>
-      <c r="D5494" t="inlineStr"/>
-      <c r="E5494" t="inlineStr"/>
-      <c r="F5494" t="inlineStr"/>
-      <c r="G5494" t="inlineStr"/>
-      <c r="H5494" t="inlineStr"/>
-      <c r="I5494" t="inlineStr"/>
     </row>
     <row r="5495">
       <c r="A5495" t="inlineStr">
@@ -66060,13 +65652,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5495" t="inlineStr"/>
-      <c r="D5495" t="inlineStr"/>
-      <c r="E5495" t="inlineStr"/>
-      <c r="F5495" t="inlineStr"/>
-      <c r="G5495" t="inlineStr"/>
-      <c r="H5495" t="inlineStr"/>
-      <c r="I5495" t="inlineStr"/>
     </row>
     <row r="5496">
       <c r="A5496" t="inlineStr">
@@ -66079,13 +65664,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5496" t="inlineStr"/>
-      <c r="D5496" t="inlineStr"/>
-      <c r="E5496" t="inlineStr"/>
-      <c r="F5496" t="inlineStr"/>
-      <c r="G5496" t="inlineStr"/>
-      <c r="H5496" t="inlineStr"/>
-      <c r="I5496" t="inlineStr"/>
     </row>
     <row r="5497">
       <c r="A5497" t="inlineStr">
@@ -66098,13 +65676,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5497" t="inlineStr"/>
-      <c r="D5497" t="inlineStr"/>
-      <c r="E5497" t="inlineStr"/>
-      <c r="F5497" t="inlineStr"/>
-      <c r="G5497" t="inlineStr"/>
-      <c r="H5497" t="inlineStr"/>
-      <c r="I5497" t="inlineStr"/>
     </row>
     <row r="5498"/>
     <row r="5499">
@@ -66118,32 +65689,26 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5499" t="inlineStr"/>
-      <c r="D5499" t="inlineStr"/>
-      <c r="E5499" t="inlineStr"/>
-      <c r="F5499" t="inlineStr"/>
-      <c r="G5499" t="inlineStr"/>
-      <c r="H5499" t="inlineStr"/>
-      <c r="I5499" t="inlineStr"/>
-    </row>
-    <row r="5500">
-      <c r="A5500" t="inlineStr">
+    </row>
+    <row r="5500" customFormat="1" s="7">
+      <c r="A5500" s="7" t="inlineStr">
         <is>
           <t>31.03.2026</t>
         </is>
       </c>
-      <c r="B5500" t="inlineStr">
+      <c r="B5500" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5500" t="inlineStr"/>
-      <c r="D5500" t="inlineStr"/>
-      <c r="E5500" t="inlineStr"/>
-      <c r="F5500" t="inlineStr"/>
-      <c r="G5500" t="inlineStr"/>
-      <c r="H5500" t="inlineStr"/>
-      <c r="I5500" t="inlineStr"/>
+      <c r="D5500" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5500" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5501">
       <c r="A5501" t="inlineStr">
@@ -66156,51 +65721,46 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5501" t="inlineStr"/>
-      <c r="D5501" t="inlineStr"/>
-      <c r="E5501" t="inlineStr"/>
-      <c r="F5501" t="inlineStr"/>
-      <c r="G5501" t="inlineStr"/>
-      <c r="H5501" t="inlineStr"/>
-      <c r="I5501" t="inlineStr"/>
-    </row>
-    <row r="5502">
-      <c r="A5502" t="inlineStr">
+    </row>
+    <row r="5502" customFormat="1" s="7">
+      <c r="A5502" s="7" t="inlineStr">
         <is>
           <t>31.03.2026</t>
         </is>
       </c>
-      <c r="B5502" t="inlineStr">
+      <c r="B5502" s="7" t="inlineStr">
         <is>
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5502" t="inlineStr"/>
-      <c r="D5502" t="inlineStr"/>
-      <c r="E5502" t="inlineStr"/>
-      <c r="F5502" t="inlineStr"/>
-      <c r="G5502" t="inlineStr"/>
-      <c r="H5502" t="inlineStr"/>
-      <c r="I5502" t="inlineStr"/>
-    </row>
-    <row r="5503">
-      <c r="A5503" t="inlineStr">
+      <c r="D5502" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5502" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5503" customFormat="1" s="7">
+      <c r="A5503" s="7" t="inlineStr">
         <is>
           <t>31.03.2026</t>
         </is>
       </c>
-      <c r="B5503" t="inlineStr">
+      <c r="B5503" s="7" t="inlineStr">
         <is>
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5503" t="inlineStr"/>
-      <c r="D5503" t="inlineStr"/>
-      <c r="E5503" t="inlineStr"/>
-      <c r="F5503" t="inlineStr"/>
-      <c r="G5503" t="inlineStr"/>
-      <c r="H5503" t="inlineStr"/>
-      <c r="I5503" t="inlineStr"/>
+      <c r="D5503" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5503" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5504">
       <c r="A5504" t="inlineStr">
@@ -66213,13 +65773,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5504" t="inlineStr"/>
-      <c r="D5504" t="inlineStr"/>
-      <c r="E5504" t="inlineStr"/>
-      <c r="F5504" t="inlineStr"/>
-      <c r="G5504" t="inlineStr"/>
-      <c r="H5504" t="inlineStr"/>
-      <c r="I5504" t="inlineStr"/>
     </row>
     <row r="5505">
       <c r="A5505" t="inlineStr">
@@ -66232,13 +65785,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5505" t="inlineStr"/>
-      <c r="D5505" t="inlineStr"/>
-      <c r="E5505" t="inlineStr"/>
-      <c r="F5505" t="inlineStr"/>
-      <c r="G5505" t="inlineStr"/>
-      <c r="H5505" t="inlineStr"/>
-      <c r="I5505" t="inlineStr"/>
     </row>
     <row r="5506">
       <c r="A5506" t="inlineStr">
@@ -66251,13 +65797,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5506" t="inlineStr"/>
-      <c r="D5506" t="inlineStr"/>
-      <c r="E5506" t="inlineStr"/>
-      <c r="F5506" t="inlineStr"/>
-      <c r="G5506" t="inlineStr"/>
-      <c r="H5506" t="inlineStr"/>
-      <c r="I5506" t="inlineStr"/>
     </row>
     <row r="5507">
       <c r="A5507" t="inlineStr">
@@ -66270,13 +65809,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5507" t="inlineStr"/>
-      <c r="D5507" t="inlineStr"/>
-      <c r="E5507" t="inlineStr"/>
-      <c r="F5507" t="inlineStr"/>
-      <c r="G5507" t="inlineStr"/>
-      <c r="H5507" t="inlineStr"/>
-      <c r="I5507" t="inlineStr"/>
     </row>
     <row r="5508">
       <c r="A5508" t="inlineStr">
@@ -66289,13 +65821,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5508" t="inlineStr"/>
-      <c r="D5508" t="inlineStr"/>
-      <c r="E5508" t="inlineStr"/>
-      <c r="F5508" t="inlineStr"/>
-      <c r="G5508" t="inlineStr"/>
-      <c r="H5508" t="inlineStr"/>
-      <c r="I5508" t="inlineStr"/>
     </row>
     <row r="5509">
       <c r="A5509" t="inlineStr">
@@ -66308,13 +65833,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5509" t="inlineStr"/>
-      <c r="D5509" t="inlineStr"/>
-      <c r="E5509" t="inlineStr"/>
-      <c r="F5509" t="inlineStr"/>
-      <c r="G5509" t="inlineStr"/>
-      <c r="H5509" t="inlineStr"/>
-      <c r="I5509" t="inlineStr"/>
     </row>
     <row r="5510">
       <c r="A5510" t="inlineStr">
@@ -66327,51 +65845,46 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5510" t="inlineStr"/>
-      <c r="D5510" t="inlineStr"/>
-      <c r="E5510" t="inlineStr"/>
-      <c r="F5510" t="inlineStr"/>
-      <c r="G5510" t="inlineStr"/>
-      <c r="H5510" t="inlineStr"/>
-      <c r="I5510" t="inlineStr"/>
-    </row>
-    <row r="5511">
-      <c r="A5511" t="inlineStr">
+    </row>
+    <row r="5511" customFormat="1" s="7">
+      <c r="A5511" s="7" t="inlineStr">
         <is>
           <t>31.03.2026</t>
         </is>
       </c>
-      <c r="B5511" t="inlineStr">
+      <c r="B5511" s="7" t="inlineStr">
         <is>
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5511" t="inlineStr"/>
-      <c r="D5511" t="inlineStr"/>
-      <c r="E5511" t="inlineStr"/>
-      <c r="F5511" t="inlineStr"/>
-      <c r="G5511" t="inlineStr"/>
-      <c r="H5511" t="inlineStr"/>
-      <c r="I5511" t="inlineStr"/>
-    </row>
-    <row r="5512">
-      <c r="A5512" t="inlineStr">
+      <c r="D5511" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5511" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5512" customFormat="1" s="7">
+      <c r="A5512" s="7" t="inlineStr">
         <is>
           <t>31.03.2026</t>
         </is>
       </c>
-      <c r="B5512" t="inlineStr">
+      <c r="B5512" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5512" t="inlineStr"/>
-      <c r="D5512" t="inlineStr"/>
-      <c r="E5512" t="inlineStr"/>
-      <c r="F5512" t="inlineStr"/>
-      <c r="G5512" t="inlineStr"/>
-      <c r="H5512" t="inlineStr"/>
-      <c r="I5512" t="inlineStr"/>
+      <c r="D5512" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5512" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5513">
       <c r="A5513" t="inlineStr">
@@ -66384,13 +65897,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5513" t="inlineStr"/>
-      <c r="D5513" t="inlineStr"/>
-      <c r="E5513" t="inlineStr"/>
-      <c r="F5513" t="inlineStr"/>
-      <c r="G5513" t="inlineStr"/>
-      <c r="H5513" t="inlineStr"/>
-      <c r="I5513" t="inlineStr"/>
     </row>
     <row r="5514">
       <c r="A5514" t="inlineStr">
@@ -66403,13 +65909,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5514" t="inlineStr"/>
-      <c r="D5514" t="inlineStr"/>
-      <c r="E5514" t="inlineStr"/>
-      <c r="F5514" t="inlineStr"/>
-      <c r="G5514" t="inlineStr"/>
-      <c r="H5514" t="inlineStr"/>
-      <c r="I5514" t="inlineStr"/>
     </row>
     <row r="5515">
       <c r="A5515" t="inlineStr">
@@ -66422,53 +65921,5618 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5515" t="inlineStr"/>
-      <c r="D5515" t="inlineStr"/>
-      <c r="E5515" t="inlineStr"/>
-      <c r="F5515" t="inlineStr"/>
-      <c r="G5515" t="inlineStr"/>
-      <c r="H5515" t="inlineStr"/>
-      <c r="I5515" t="inlineStr"/>
-    </row>
-    <row r="5516">
-      <c r="A5516" t="inlineStr">
+    </row>
+    <row r="5516" customFormat="1" s="7">
+      <c r="A5516" s="7" t="inlineStr">
         <is>
           <t>31.03.2026</t>
         </is>
       </c>
-      <c r="B5516" t="inlineStr">
+      <c r="B5516" s="7" t="inlineStr">
         <is>
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5516" t="inlineStr"/>
-      <c r="D5516" t="inlineStr"/>
-      <c r="E5516" t="inlineStr"/>
-      <c r="F5516" t="inlineStr"/>
-      <c r="G5516" t="inlineStr"/>
-      <c r="H5516" t="inlineStr"/>
-      <c r="I5516" t="inlineStr"/>
-    </row>
-    <row r="5517">
-      <c r="A5517" t="inlineStr">
+      <c r="D5516" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5516" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5517" customFormat="1" s="7">
+      <c r="A5517" s="7" t="inlineStr">
         <is>
           <t>31.03.2026</t>
         </is>
       </c>
-      <c r="B5517" t="inlineStr">
+      <c r="B5517" s="7" t="inlineStr">
         <is>
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5517" t="inlineStr"/>
-      <c r="D5517" t="inlineStr"/>
-      <c r="E5517" t="inlineStr"/>
-      <c r="F5517" t="inlineStr"/>
-      <c r="G5517" t="inlineStr"/>
-      <c r="H5517" t="inlineStr"/>
-      <c r="I5517" t="inlineStr"/>
+      <c r="D5517" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5517" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5518"/>
+    <row r="5519">
+      <c r="A5519" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5519" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5520">
+      <c r="A5520" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5520" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5521">
+      <c r="A5521" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5521" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5522">
+      <c r="A5522" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5522" s="7" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5523">
+      <c r="A5523" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5523" s="7" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5524">
+      <c r="A5524" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5524" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5525">
+      <c r="A5525" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5525" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5526">
+      <c r="A5526" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5526" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5527">
+      <c r="A5527" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5527" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5528">
+      <c r="A5528" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5528" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5529">
+      <c r="A5529" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5529" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5530">
+      <c r="A5530" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5530" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5531">
+      <c r="A5531" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5531" s="7" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5532">
+      <c r="A5532" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5532" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5533">
+      <c r="A5533" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5533" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5534">
+      <c r="A5534" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5534" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5535">
+      <c r="A5535" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5535" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5536">
+      <c r="A5536" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5536" s="7" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5537">
+      <c r="A5537" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B5537" s="7" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5538"/>
+    <row r="5539">
+      <c r="A5539" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5539" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5540">
+      <c r="A5540" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5540" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5541">
+      <c r="A5541" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5541" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5542">
+      <c r="A5542" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5542" s="7" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5543">
+      <c r="A5543" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5543" s="7" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5544">
+      <c r="A5544" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5544" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5545">
+      <c r="A5545" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5545" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5546">
+      <c r="A5546" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5546" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5547">
+      <c r="A5547" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5547" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5548">
+      <c r="A5548" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5548" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5549">
+      <c r="A5549" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5549" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5550">
+      <c r="A5550" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5550" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5551">
+      <c r="A5551" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5551" s="7" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5552">
+      <c r="A5552" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5552" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5553">
+      <c r="A5553" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5553" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5554">
+      <c r="A5554" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5554" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5555">
+      <c r="A5555" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5555" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5556">
+      <c r="A5556" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5556" s="7" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5557">
+      <c r="A5557" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B5557" s="7" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5558">
+      <c r="A5558" s="2" t="n"/>
+    </row>
+    <row r="5559">
+      <c r="A5559" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5559" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5560">
+      <c r="A5560" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5560" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5561">
+      <c r="A5561" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5561" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5562">
+      <c r="A5562" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5562" s="7" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5563">
+      <c r="A5563" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5563" s="7" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5564">
+      <c r="A5564" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5564" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5565">
+      <c r="A5565" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5565" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5566">
+      <c r="A5566" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5566" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5567">
+      <c r="A5567" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5567" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="D5567" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5568">
+      <c r="A5568" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5568" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5569">
+      <c r="A5569" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5569" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5570">
+      <c r="A5570" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5570" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5571">
+      <c r="A5571" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5571" s="7" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5572">
+      <c r="A5572" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5572" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5573">
+      <c r="A5573" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5573" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5574">
+      <c r="A5574" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5574" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5575">
+      <c r="A5575" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5575" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5576">
+      <c r="A5576" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5576" s="7" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="D5576" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5577">
+      <c r="A5577" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B5577" s="7" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5578"/>
+    <row r="5579">
+      <c r="A5579" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5579" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5580">
+      <c r="A5580" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5580" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5581">
+      <c r="A5581" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5581" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5582">
+      <c r="A5582" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5582" s="7" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5583">
+      <c r="A5583" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5583" s="7" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5584">
+      <c r="A5584" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5584" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5585">
+      <c r="A5585" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5585" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5586">
+      <c r="A5586" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5586" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5587">
+      <c r="A5587" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5587" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5588">
+      <c r="A5588" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5588" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5589">
+      <c r="A5589" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5589" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5590">
+      <c r="A5590" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5590" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5591">
+      <c r="A5591" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5591" s="7" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5592">
+      <c r="A5592" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5592" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5593">
+      <c r="A5593" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5593" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5594">
+      <c r="A5594" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5594" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5595">
+      <c r="A5595" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5595" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5596">
+      <c r="A5596" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5596" s="7" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5597">
+      <c r="A5597" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B5597" s="7" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5598"/>
+    <row r="5599">
+      <c r="A5599" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5599" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5600">
+      <c r="A5600" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5601">
+      <c r="A5601" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5601" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5602">
+      <c r="A5602" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5602" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5603">
+      <c r="A5603" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5603" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5604">
+      <c r="A5604" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5604" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5605">
+      <c r="A5605" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5605" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5606">
+      <c r="A5606" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5606" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5607">
+      <c r="A5607" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5607" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5608">
+      <c r="A5608" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5608" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5609">
+      <c r="A5609" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5609" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5610">
+      <c r="A5610" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5610" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5611">
+      <c r="A5611" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5611" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5612">
+      <c r="A5612" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5613">
+      <c r="A5613" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5613" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5614">
+      <c r="A5614" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5614" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5615">
+      <c r="A5615" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5615" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5616">
+      <c r="A5616" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5616" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5617">
+      <c r="A5617" t="inlineStr">
+        <is>
+          <t>05.04.2026</t>
+        </is>
+      </c>
+      <c r="B5617" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5618"/>
+    <row r="5619">
+      <c r="A5619" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5619" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="D5619" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5619" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5620">
+      <c r="A5620" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="D5620" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5620" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5621">
+      <c r="A5621" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5621" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5622">
+      <c r="A5622" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5622" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="D5622" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5622" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5623">
+      <c r="A5623" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5623" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="D5623" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5623" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5624">
+      <c r="A5624" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5624" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="D5624" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5624" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5625">
+      <c r="A5625" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5625" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="D5625" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5625" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5626">
+      <c r="A5626" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5626" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5627">
+      <c r="A5627" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5627" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5628">
+      <c r="A5628" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5628" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5629">
+      <c r="A5629" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5629" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="D5629" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5629" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5630">
+      <c r="A5630" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5630" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5631">
+      <c r="A5631" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5631" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="D5631" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5631" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5632">
+      <c r="A5632" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5632" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="D5632" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5632" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5633">
+      <c r="A5633" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5633" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5634">
+      <c r="A5634" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5634" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5635">
+      <c r="A5635" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5635" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="D5635" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5635" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5636">
+      <c r="A5636" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5636" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="D5636" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5636" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5637">
+      <c r="A5637" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="B5637" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5638"/>
+    <row r="5639">
+      <c r="A5639" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5639" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5640">
+      <c r="A5640" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5641">
+      <c r="A5641" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5641" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5642">
+      <c r="A5642" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5642" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5643">
+      <c r="A5643" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5643" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5644">
+      <c r="A5644" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5644" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5645">
+      <c r="A5645" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5645" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5646">
+      <c r="A5646" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5646" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5647">
+      <c r="A5647" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5647" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5648">
+      <c r="A5648" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5648" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5649">
+      <c r="A5649" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5649" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5650">
+      <c r="A5650" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5650" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5651">
+      <c r="A5651" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5651" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5652">
+      <c r="A5652" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5652" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5653">
+      <c r="A5653" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5653" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5654">
+      <c r="A5654" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5654" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5655">
+      <c r="A5655" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5655" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5656">
+      <c r="A5656" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5656" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5657">
+      <c r="A5657" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B5657" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5658"/>
+    <row r="5659">
+      <c r="A5659" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5659" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5660">
+      <c r="A5660" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5660" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5661">
+      <c r="A5661" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5661" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5662">
+      <c r="A5662" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5662" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5663">
+      <c r="A5663" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5663" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5664">
+      <c r="A5664" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5664" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5665">
+      <c r="A5665" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5665" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5666">
+      <c r="A5666" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5666" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5667">
+      <c r="A5667" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5667" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5668">
+      <c r="A5668" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5668" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5669">
+      <c r="A5669" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5669" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5670">
+      <c r="A5670" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5670" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5671">
+      <c r="A5671" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5671" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5672">
+      <c r="A5672" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5672" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5673">
+      <c r="A5673" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5673" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5674">
+      <c r="A5674" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5674" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5675">
+      <c r="A5675" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5675" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5676">
+      <c r="A5676" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5676" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5677">
+      <c r="A5677" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="B5677" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5678"/>
+    <row r="5679">
+      <c r="A5679" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5679" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5680">
+      <c r="A5680" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5680" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5681">
+      <c r="A5681" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5681" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="D5681" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5681" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5682">
+      <c r="A5682" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5682" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5683">
+      <c r="A5683" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5683" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5684">
+      <c r="A5684" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5684" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5685">
+      <c r="A5685" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5685" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5686">
+      <c r="A5686" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5686" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5687">
+      <c r="A5687" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5687" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="D5687" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5687" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5688">
+      <c r="A5688" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5688" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="D5688" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5688" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5689">
+      <c r="A5689" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5689" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5690">
+      <c r="A5690" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5690" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="D5690" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5690" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5691">
+      <c r="A5691" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5691" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5692">
+      <c r="A5692" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5692" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5693">
+      <c r="A5693" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5693" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="D5693" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5693" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5694">
+      <c r="A5694" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5694" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="D5694" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5694" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5695">
+      <c r="A5695" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5695" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5696">
+      <c r="A5696" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5696" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5697">
+      <c r="A5697" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="B5697" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="D5697" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5697" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5698"/>
+    <row r="5699">
+      <c r="A5699" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5699" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5700">
+      <c r="A5700" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5700" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5701">
+      <c r="A5701" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5701" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5702">
+      <c r="A5702" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5702" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5703">
+      <c r="A5703" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5703" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5704">
+      <c r="A5704" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5704" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5705">
+      <c r="A5705" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5705" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5706">
+      <c r="A5706" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5706" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5707">
+      <c r="A5707" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5707" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5708">
+      <c r="A5708" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5708" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5709">
+      <c r="A5709" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5709" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5710">
+      <c r="A5710" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5710" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5711">
+      <c r="A5711" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5711" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5712">
+      <c r="A5712" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5712" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5713">
+      <c r="A5713" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5713" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5714">
+      <c r="A5714" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5714" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5715">
+      <c r="A5715" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5715" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5716">
+      <c r="A5716" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5716" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="D5716" s="24" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5717">
+      <c r="A5717" t="inlineStr">
+        <is>
+          <t>10.04.2026</t>
+        </is>
+      </c>
+      <c r="B5717" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5718"/>
+    <row r="5719">
+      <c r="A5719" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5719" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5720">
+      <c r="A5720" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5720" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5721">
+      <c r="A5721" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5721" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5722">
+      <c r="A5722" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5722" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5723">
+      <c r="A5723" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5723" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5724">
+      <c r="A5724" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5724" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5725">
+      <c r="A5725" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5725" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5726">
+      <c r="A5726" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5726" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5727">
+      <c r="A5727" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5727" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5728">
+      <c r="A5728" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5728" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5729">
+      <c r="A5729" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5729" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5730">
+      <c r="A5730" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5730" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5731">
+      <c r="A5731" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5731" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5732">
+      <c r="A5732" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5732" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5733">
+      <c r="A5733" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5733" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5734">
+      <c r="A5734" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5734" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5735">
+      <c r="A5735" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5735" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5736">
+      <c r="A5736" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5736" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5737">
+      <c r="A5737" t="inlineStr">
+        <is>
+          <t>11.04.2026</t>
+        </is>
+      </c>
+      <c r="B5737" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5738"/>
+    <row r="5739">
+      <c r="A5739" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5739" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5740">
+      <c r="A5740" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5740" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="5741">
+      <c r="A5741" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5741" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5742">
+      <c r="A5742" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5742" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5743">
+      <c r="A5743" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5743" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5744">
+      <c r="A5744" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5744" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5745">
+      <c r="A5745" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5745" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5746">
+      <c r="A5746" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5746" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5747">
+      <c r="A5747" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5747" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5748">
+      <c r="A5748" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5748" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5749">
+      <c r="A5749" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5749" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5750">
+      <c r="A5750" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5750" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5751">
+      <c r="A5751" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5751" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5752">
+      <c r="A5752" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5752" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="5753">
+      <c r="A5753" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5753" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5754">
+      <c r="A5754" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5754" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5755">
+      <c r="A5755" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5755" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5756">
+      <c r="A5756" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5756" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5757">
+      <c r="A5757" t="inlineStr">
+        <is>
+          <t>12.04.2026</t>
+        </is>
+      </c>
+      <c r="B5757" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5758"/>
+    <row r="5759">
+      <c r="A5759" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5759" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5760">
+      <c r="A5760" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5760" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="D5760" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5760" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5761">
+      <c r="A5761" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5761" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5762">
+      <c r="A5762" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5762" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="D5762" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5762" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5763">
+      <c r="A5763" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5763" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="D5763" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5763" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5764">
+      <c r="A5764" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5764" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5765">
+      <c r="A5765" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5765" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="D5765" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5765" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5766">
+      <c r="A5766" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5766" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5767">
+      <c r="A5767" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5767" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5768">
+      <c r="A5768" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5768" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5769">
+      <c r="A5769" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5769" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5770">
+      <c r="A5770" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5770" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5771">
+      <c r="A5771" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5771" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="D5771" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5771" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5772">
+      <c r="A5772" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5772" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="D5772" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5772" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5773">
+      <c r="A5773" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5773" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="5774">
+      <c r="A5774" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5774" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5775">
+      <c r="A5775" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5775" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="D5775" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5775" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5776">
+      <c r="A5776" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5776" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5777">
+      <c r="A5777" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B5777" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="5778"/>
+    <row r="5779">
+      <c r="A5779" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5779" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5779" t="inlineStr"/>
+      <c r="D5779" t="inlineStr"/>
+      <c r="E5779" t="inlineStr"/>
+      <c r="F5779" t="inlineStr"/>
+      <c r="G5779" t="inlineStr"/>
+      <c r="H5779" t="inlineStr"/>
+      <c r="I5779" t="inlineStr"/>
+    </row>
+    <row r="5780">
+      <c r="A5780" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5780" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5780" t="inlineStr"/>
+      <c r="D5780" t="inlineStr"/>
+      <c r="E5780" t="inlineStr"/>
+      <c r="F5780" t="inlineStr"/>
+      <c r="G5780" t="inlineStr"/>
+      <c r="H5780" t="inlineStr"/>
+      <c r="I5780" t="inlineStr"/>
+    </row>
+    <row r="5781">
+      <c r="A5781" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5781" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5781" t="inlineStr"/>
+      <c r="D5781" t="inlineStr"/>
+      <c r="E5781" t="inlineStr"/>
+      <c r="F5781" t="inlineStr"/>
+      <c r="G5781" t="inlineStr"/>
+      <c r="H5781" t="inlineStr"/>
+      <c r="I5781" t="inlineStr"/>
+    </row>
+    <row r="5782">
+      <c r="A5782" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5782" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5782" t="inlineStr"/>
+      <c r="D5782" t="inlineStr"/>
+      <c r="E5782" t="inlineStr"/>
+      <c r="F5782" t="inlineStr"/>
+      <c r="G5782" t="inlineStr"/>
+      <c r="H5782" t="inlineStr"/>
+      <c r="I5782" t="inlineStr"/>
+    </row>
+    <row r="5783">
+      <c r="A5783" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5783" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5783" t="inlineStr"/>
+      <c r="D5783" t="inlineStr"/>
+      <c r="E5783" t="inlineStr"/>
+      <c r="F5783" t="inlineStr"/>
+      <c r="G5783" t="inlineStr"/>
+      <c r="H5783" t="inlineStr"/>
+      <c r="I5783" t="inlineStr"/>
+    </row>
+    <row r="5784">
+      <c r="A5784" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5784" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5784" t="inlineStr"/>
+      <c r="D5784" t="inlineStr"/>
+      <c r="E5784" t="inlineStr"/>
+      <c r="F5784" t="inlineStr"/>
+      <c r="G5784" t="inlineStr"/>
+      <c r="H5784" t="inlineStr"/>
+      <c r="I5784" t="inlineStr"/>
+    </row>
+    <row r="5785">
+      <c r="A5785" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5785" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5785" t="inlineStr"/>
+      <c r="D5785" t="inlineStr"/>
+      <c r="E5785" t="inlineStr"/>
+      <c r="F5785" t="inlineStr"/>
+      <c r="G5785" t="inlineStr"/>
+      <c r="H5785" t="inlineStr"/>
+      <c r="I5785" t="inlineStr"/>
+    </row>
+    <row r="5786">
+      <c r="A5786" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5786" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5786" t="inlineStr"/>
+      <c r="D5786" t="inlineStr"/>
+      <c r="E5786" t="inlineStr"/>
+      <c r="F5786" t="inlineStr"/>
+      <c r="G5786" t="inlineStr"/>
+      <c r="H5786" t="inlineStr"/>
+      <c r="I5786" t="inlineStr"/>
+    </row>
+    <row r="5787">
+      <c r="A5787" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5787" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5787" t="inlineStr"/>
+      <c r="D5787" t="inlineStr"/>
+      <c r="E5787" t="inlineStr"/>
+      <c r="F5787" t="inlineStr"/>
+      <c r="G5787" t="inlineStr"/>
+      <c r="H5787" t="inlineStr"/>
+      <c r="I5787" t="inlineStr"/>
+    </row>
+    <row r="5788">
+      <c r="A5788" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5788" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5788" t="inlineStr"/>
+      <c r="D5788" t="inlineStr"/>
+      <c r="E5788" t="inlineStr"/>
+      <c r="F5788" t="inlineStr"/>
+      <c r="G5788" t="inlineStr"/>
+      <c r="H5788" t="inlineStr"/>
+      <c r="I5788" t="inlineStr"/>
+    </row>
+    <row r="5789">
+      <c r="A5789" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5789" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5789" t="inlineStr"/>
+      <c r="D5789" t="inlineStr"/>
+      <c r="E5789" t="inlineStr"/>
+      <c r="F5789" t="inlineStr"/>
+      <c r="G5789" t="inlineStr"/>
+      <c r="H5789" t="inlineStr"/>
+      <c r="I5789" t="inlineStr"/>
+    </row>
+    <row r="5790">
+      <c r="A5790" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5790" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5790" t="inlineStr"/>
+      <c r="D5790" t="inlineStr"/>
+      <c r="E5790" t="inlineStr"/>
+      <c r="F5790" t="inlineStr"/>
+      <c r="G5790" t="inlineStr"/>
+      <c r="H5790" t="inlineStr"/>
+      <c r="I5790" t="inlineStr"/>
+    </row>
+    <row r="5791">
+      <c r="A5791" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5791" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5791" t="inlineStr"/>
+      <c r="D5791" t="inlineStr"/>
+      <c r="E5791" t="inlineStr"/>
+      <c r="F5791" t="inlineStr"/>
+      <c r="G5791" t="inlineStr"/>
+      <c r="H5791" t="inlineStr"/>
+      <c r="I5791" t="inlineStr"/>
+    </row>
+    <row r="5792">
+      <c r="A5792" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5792" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5792" t="inlineStr"/>
+      <c r="D5792" t="inlineStr"/>
+      <c r="E5792" t="inlineStr"/>
+      <c r="F5792" t="inlineStr"/>
+      <c r="G5792" t="inlineStr"/>
+      <c r="H5792" t="inlineStr"/>
+      <c r="I5792" t="inlineStr"/>
+    </row>
+    <row r="5793">
+      <c r="A5793" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5793" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5793" t="inlineStr"/>
+      <c r="D5793" t="inlineStr"/>
+      <c r="E5793" t="inlineStr"/>
+      <c r="F5793" t="inlineStr"/>
+      <c r="G5793" t="inlineStr"/>
+      <c r="H5793" t="inlineStr"/>
+      <c r="I5793" t="inlineStr"/>
+    </row>
+    <row r="5794">
+      <c r="A5794" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5794" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5794" t="inlineStr"/>
+      <c r="D5794" t="inlineStr"/>
+      <c r="E5794" t="inlineStr"/>
+      <c r="F5794" t="inlineStr"/>
+      <c r="G5794" t="inlineStr"/>
+      <c r="H5794" t="inlineStr"/>
+      <c r="I5794" t="inlineStr"/>
+    </row>
+    <row r="5795">
+      <c r="A5795" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5795" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5795" t="inlineStr"/>
+      <c r="D5795" t="inlineStr"/>
+      <c r="E5795" t="inlineStr"/>
+      <c r="F5795" t="inlineStr"/>
+      <c r="G5795" t="inlineStr"/>
+      <c r="H5795" t="inlineStr"/>
+      <c r="I5795" t="inlineStr"/>
+    </row>
+    <row r="5796">
+      <c r="A5796" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5796" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5796" t="inlineStr"/>
+      <c r="D5796" t="inlineStr"/>
+      <c r="E5796" t="inlineStr"/>
+      <c r="F5796" t="inlineStr"/>
+      <c r="G5796" t="inlineStr"/>
+      <c r="H5796" t="inlineStr"/>
+      <c r="I5796" t="inlineStr"/>
+    </row>
+    <row r="5797">
+      <c r="A5797" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B5797" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5797" t="inlineStr"/>
+      <c r="D5797" t="inlineStr"/>
+      <c r="E5797" t="inlineStr"/>
+      <c r="F5797" t="inlineStr"/>
+      <c r="G5797" t="inlineStr"/>
+      <c r="H5797" t="inlineStr"/>
+      <c r="I5797" t="inlineStr"/>
+    </row>
+    <row r="5798"/>
+    <row r="5799">
+      <c r="A5799" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5799" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5799" t="inlineStr"/>
+      <c r="D5799" t="inlineStr"/>
+      <c r="E5799" t="inlineStr"/>
+      <c r="F5799" t="inlineStr"/>
+      <c r="G5799" t="inlineStr"/>
+      <c r="H5799" t="inlineStr"/>
+      <c r="I5799" t="inlineStr"/>
+    </row>
+    <row r="5800">
+      <c r="A5800" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5800" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5800" t="inlineStr"/>
+      <c r="D5800" t="inlineStr"/>
+      <c r="E5800" t="inlineStr"/>
+      <c r="F5800" t="inlineStr"/>
+      <c r="G5800" t="inlineStr"/>
+      <c r="H5800" t="inlineStr"/>
+      <c r="I5800" t="inlineStr"/>
+    </row>
+    <row r="5801">
+      <c r="A5801" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5801" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5801" t="inlineStr"/>
+      <c r="D5801" t="inlineStr"/>
+      <c r="E5801" t="inlineStr"/>
+      <c r="F5801" t="inlineStr"/>
+      <c r="G5801" t="inlineStr"/>
+      <c r="H5801" t="inlineStr"/>
+      <c r="I5801" t="inlineStr"/>
+    </row>
+    <row r="5802">
+      <c r="A5802" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5802" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5802" t="inlineStr"/>
+      <c r="D5802" t="inlineStr"/>
+      <c r="E5802" t="inlineStr"/>
+      <c r="F5802" t="inlineStr"/>
+      <c r="G5802" t="inlineStr"/>
+      <c r="H5802" t="inlineStr"/>
+      <c r="I5802" t="inlineStr"/>
+    </row>
+    <row r="5803">
+      <c r="A5803" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5803" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5803" t="inlineStr"/>
+      <c r="D5803" t="inlineStr"/>
+      <c r="E5803" t="inlineStr"/>
+      <c r="F5803" t="inlineStr"/>
+      <c r="G5803" t="inlineStr"/>
+      <c r="H5803" t="inlineStr"/>
+      <c r="I5803" t="inlineStr"/>
+    </row>
+    <row r="5804">
+      <c r="A5804" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5804" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5804" t="inlineStr"/>
+      <c r="D5804" t="inlineStr"/>
+      <c r="E5804" t="inlineStr"/>
+      <c r="F5804" t="inlineStr"/>
+      <c r="G5804" t="inlineStr"/>
+      <c r="H5804" t="inlineStr"/>
+      <c r="I5804" t="inlineStr"/>
+    </row>
+    <row r="5805">
+      <c r="A5805" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5805" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5805" t="inlineStr"/>
+      <c r="D5805" t="inlineStr"/>
+      <c r="E5805" t="inlineStr"/>
+      <c r="F5805" t="inlineStr"/>
+      <c r="G5805" t="inlineStr"/>
+      <c r="H5805" t="inlineStr"/>
+      <c r="I5805" t="inlineStr"/>
+    </row>
+    <row r="5806">
+      <c r="A5806" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5806" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5806" t="inlineStr"/>
+      <c r="D5806" t="inlineStr"/>
+      <c r="E5806" t="inlineStr"/>
+      <c r="F5806" t="inlineStr"/>
+      <c r="G5806" t="inlineStr"/>
+      <c r="H5806" t="inlineStr"/>
+      <c r="I5806" t="inlineStr"/>
+    </row>
+    <row r="5807">
+      <c r="A5807" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5807" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5807" t="inlineStr"/>
+      <c r="D5807" t="inlineStr"/>
+      <c r="E5807" t="inlineStr"/>
+      <c r="F5807" t="inlineStr"/>
+      <c r="G5807" t="inlineStr"/>
+      <c r="H5807" t="inlineStr"/>
+      <c r="I5807" t="inlineStr"/>
+    </row>
+    <row r="5808">
+      <c r="A5808" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5808" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5808" t="inlineStr"/>
+      <c r="D5808" t="inlineStr"/>
+      <c r="E5808" t="inlineStr"/>
+      <c r="F5808" t="inlineStr"/>
+      <c r="G5808" t="inlineStr"/>
+      <c r="H5808" t="inlineStr"/>
+      <c r="I5808" t="inlineStr"/>
+    </row>
+    <row r="5809">
+      <c r="A5809" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5809" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5809" t="inlineStr"/>
+      <c r="D5809" t="inlineStr"/>
+      <c r="E5809" t="inlineStr"/>
+      <c r="F5809" t="inlineStr"/>
+      <c r="G5809" t="inlineStr"/>
+      <c r="H5809" t="inlineStr"/>
+      <c r="I5809" t="inlineStr"/>
+    </row>
+    <row r="5810">
+      <c r="A5810" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5810" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5810" t="inlineStr"/>
+      <c r="D5810" t="inlineStr"/>
+      <c r="E5810" t="inlineStr"/>
+      <c r="F5810" t="inlineStr"/>
+      <c r="G5810" t="inlineStr"/>
+      <c r="H5810" t="inlineStr"/>
+      <c r="I5810" t="inlineStr"/>
+    </row>
+    <row r="5811">
+      <c r="A5811" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5811" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5811" t="inlineStr"/>
+      <c r="D5811" t="inlineStr"/>
+      <c r="E5811" t="inlineStr"/>
+      <c r="F5811" t="inlineStr"/>
+      <c r="G5811" t="inlineStr"/>
+      <c r="H5811" t="inlineStr"/>
+      <c r="I5811" t="inlineStr"/>
+    </row>
+    <row r="5812">
+      <c r="A5812" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5812" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5812" t="inlineStr"/>
+      <c r="D5812" t="inlineStr"/>
+      <c r="E5812" t="inlineStr"/>
+      <c r="F5812" t="inlineStr"/>
+      <c r="G5812" t="inlineStr"/>
+      <c r="H5812" t="inlineStr"/>
+      <c r="I5812" t="inlineStr"/>
+    </row>
+    <row r="5813">
+      <c r="A5813" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5813" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5813" t="inlineStr"/>
+      <c r="D5813" t="inlineStr"/>
+      <c r="E5813" t="inlineStr"/>
+      <c r="F5813" t="inlineStr"/>
+      <c r="G5813" t="inlineStr"/>
+      <c r="H5813" t="inlineStr"/>
+      <c r="I5813" t="inlineStr"/>
+    </row>
+    <row r="5814">
+      <c r="A5814" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5814" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5814" t="inlineStr"/>
+      <c r="D5814" t="inlineStr"/>
+      <c r="E5814" t="inlineStr"/>
+      <c r="F5814" t="inlineStr"/>
+      <c r="G5814" t="inlineStr"/>
+      <c r="H5814" t="inlineStr"/>
+      <c r="I5814" t="inlineStr"/>
+    </row>
+    <row r="5815">
+      <c r="A5815" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5815" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5815" t="inlineStr"/>
+      <c r="D5815" t="inlineStr"/>
+      <c r="E5815" t="inlineStr"/>
+      <c r="F5815" t="inlineStr"/>
+      <c r="G5815" t="inlineStr"/>
+      <c r="H5815" t="inlineStr"/>
+      <c r="I5815" t="inlineStr"/>
+    </row>
+    <row r="5816">
+      <c r="A5816" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5816" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5816" t="inlineStr"/>
+      <c r="D5816" t="inlineStr"/>
+      <c r="E5816" t="inlineStr"/>
+      <c r="F5816" t="inlineStr"/>
+      <c r="G5816" t="inlineStr"/>
+      <c r="H5816" t="inlineStr"/>
+      <c r="I5816" t="inlineStr"/>
+    </row>
+    <row r="5817">
+      <c r="A5817" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B5817" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5817" t="inlineStr"/>
+      <c r="D5817" t="inlineStr"/>
+      <c r="E5817" t="inlineStr"/>
+      <c r="F5817" t="inlineStr"/>
+      <c r="G5817" t="inlineStr"/>
+      <c r="H5817" t="inlineStr"/>
+      <c r="I5817" t="inlineStr"/>
+    </row>
+    <row r="5818"/>
+    <row r="5819">
+      <c r="A5819" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5819" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5819" t="inlineStr"/>
+      <c r="D5819" t="inlineStr"/>
+      <c r="E5819" t="inlineStr"/>
+      <c r="F5819" t="inlineStr"/>
+      <c r="G5819" t="inlineStr"/>
+      <c r="H5819" t="inlineStr"/>
+      <c r="I5819" t="inlineStr"/>
+    </row>
+    <row r="5820">
+      <c r="A5820" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5820" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5820" t="inlineStr"/>
+      <c r="D5820" t="inlineStr"/>
+      <c r="E5820" t="inlineStr"/>
+      <c r="F5820" t="inlineStr"/>
+      <c r="G5820" t="inlineStr"/>
+      <c r="H5820" t="inlineStr"/>
+      <c r="I5820" t="inlineStr"/>
+    </row>
+    <row r="5821">
+      <c r="A5821" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5821" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5821" t="inlineStr"/>
+      <c r="D5821" t="inlineStr"/>
+      <c r="E5821" t="inlineStr"/>
+      <c r="F5821" t="inlineStr"/>
+      <c r="G5821" t="inlineStr"/>
+      <c r="H5821" t="inlineStr"/>
+      <c r="I5821" t="inlineStr"/>
+    </row>
+    <row r="5822">
+      <c r="A5822" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5822" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5822" t="inlineStr"/>
+      <c r="D5822" t="inlineStr"/>
+      <c r="E5822" t="inlineStr"/>
+      <c r="F5822" t="inlineStr"/>
+      <c r="G5822" t="inlineStr"/>
+      <c r="H5822" t="inlineStr"/>
+      <c r="I5822" t="inlineStr"/>
+    </row>
+    <row r="5823">
+      <c r="A5823" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5823" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5823" t="inlineStr"/>
+      <c r="D5823" t="inlineStr"/>
+      <c r="E5823" t="inlineStr"/>
+      <c r="F5823" t="inlineStr"/>
+      <c r="G5823" t="inlineStr"/>
+      <c r="H5823" t="inlineStr"/>
+      <c r="I5823" t="inlineStr"/>
+    </row>
+    <row r="5824">
+      <c r="A5824" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5824" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5824" t="inlineStr"/>
+      <c r="D5824" t="inlineStr"/>
+      <c r="E5824" t="inlineStr"/>
+      <c r="F5824" t="inlineStr"/>
+      <c r="G5824" t="inlineStr"/>
+      <c r="H5824" t="inlineStr"/>
+      <c r="I5824" t="inlineStr"/>
+    </row>
+    <row r="5825">
+      <c r="A5825" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5825" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5825" t="inlineStr"/>
+      <c r="D5825" t="inlineStr"/>
+      <c r="E5825" t="inlineStr"/>
+      <c r="F5825" t="inlineStr"/>
+      <c r="G5825" t="inlineStr"/>
+      <c r="H5825" t="inlineStr"/>
+      <c r="I5825" t="inlineStr"/>
+    </row>
+    <row r="5826">
+      <c r="A5826" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5826" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5826" t="inlineStr"/>
+      <c r="D5826" t="inlineStr"/>
+      <c r="E5826" t="inlineStr"/>
+      <c r="F5826" t="inlineStr"/>
+      <c r="G5826" t="inlineStr"/>
+      <c r="H5826" t="inlineStr"/>
+      <c r="I5826" t="inlineStr"/>
+    </row>
+    <row r="5827">
+      <c r="A5827" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5827" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5827" t="inlineStr"/>
+      <c r="D5827" t="inlineStr"/>
+      <c r="E5827" t="inlineStr"/>
+      <c r="F5827" t="inlineStr"/>
+      <c r="G5827" t="inlineStr"/>
+      <c r="H5827" t="inlineStr"/>
+      <c r="I5827" t="inlineStr"/>
+    </row>
+    <row r="5828">
+      <c r="A5828" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5828" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5828" t="inlineStr"/>
+      <c r="D5828" t="inlineStr"/>
+      <c r="E5828" t="inlineStr"/>
+      <c r="F5828" t="inlineStr"/>
+      <c r="G5828" t="inlineStr"/>
+      <c r="H5828" t="inlineStr"/>
+      <c r="I5828" t="inlineStr"/>
+    </row>
+    <row r="5829">
+      <c r="A5829" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5829" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5829" t="inlineStr"/>
+      <c r="D5829" t="inlineStr"/>
+      <c r="E5829" t="inlineStr"/>
+      <c r="F5829" t="inlineStr"/>
+      <c r="G5829" t="inlineStr"/>
+      <c r="H5829" t="inlineStr"/>
+      <c r="I5829" t="inlineStr"/>
+    </row>
+    <row r="5830">
+      <c r="A5830" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5830" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5830" t="inlineStr"/>
+      <c r="D5830" t="inlineStr"/>
+      <c r="E5830" t="inlineStr"/>
+      <c r="F5830" t="inlineStr"/>
+      <c r="G5830" t="inlineStr"/>
+      <c r="H5830" t="inlineStr"/>
+      <c r="I5830" t="inlineStr"/>
+    </row>
+    <row r="5831">
+      <c r="A5831" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5831" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5831" t="inlineStr"/>
+      <c r="D5831" t="inlineStr"/>
+      <c r="E5831" t="inlineStr"/>
+      <c r="F5831" t="inlineStr"/>
+      <c r="G5831" t="inlineStr"/>
+      <c r="H5831" t="inlineStr"/>
+      <c r="I5831" t="inlineStr"/>
+    </row>
+    <row r="5832">
+      <c r="A5832" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5832" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5832" t="inlineStr"/>
+      <c r="D5832" t="inlineStr"/>
+      <c r="E5832" t="inlineStr"/>
+      <c r="F5832" t="inlineStr"/>
+      <c r="G5832" t="inlineStr"/>
+      <c r="H5832" t="inlineStr"/>
+      <c r="I5832" t="inlineStr"/>
+    </row>
+    <row r="5833">
+      <c r="A5833" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5833" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5833" t="inlineStr"/>
+      <c r="D5833" t="inlineStr"/>
+      <c r="E5833" t="inlineStr"/>
+      <c r="F5833" t="inlineStr"/>
+      <c r="G5833" t="inlineStr"/>
+      <c r="H5833" t="inlineStr"/>
+      <c r="I5833" t="inlineStr"/>
+    </row>
+    <row r="5834">
+      <c r="A5834" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5834" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5834" t="inlineStr"/>
+      <c r="D5834" t="inlineStr"/>
+      <c r="E5834" t="inlineStr"/>
+      <c r="F5834" t="inlineStr"/>
+      <c r="G5834" t="inlineStr"/>
+      <c r="H5834" t="inlineStr"/>
+      <c r="I5834" t="inlineStr"/>
+    </row>
+    <row r="5835">
+      <c r="A5835" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5835" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5835" t="inlineStr"/>
+      <c r="D5835" t="inlineStr"/>
+      <c r="E5835" t="inlineStr"/>
+      <c r="F5835" t="inlineStr"/>
+      <c r="G5835" t="inlineStr"/>
+      <c r="H5835" t="inlineStr"/>
+      <c r="I5835" t="inlineStr"/>
+    </row>
+    <row r="5836">
+      <c r="A5836" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5836" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5836" t="inlineStr"/>
+      <c r="D5836" t="inlineStr"/>
+      <c r="E5836" t="inlineStr"/>
+      <c r="F5836" t="inlineStr"/>
+      <c r="G5836" t="inlineStr"/>
+      <c r="H5836" t="inlineStr"/>
+      <c r="I5836" t="inlineStr"/>
+    </row>
+    <row r="5837">
+      <c r="A5837" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B5837" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5837" t="inlineStr"/>
+      <c r="D5837" t="inlineStr"/>
+      <c r="E5837" t="inlineStr"/>
+      <c r="F5837" t="inlineStr"/>
+      <c r="G5837" t="inlineStr"/>
+      <c r="H5837" t="inlineStr"/>
+      <c r="I5837" t="inlineStr"/>
+    </row>
+    <row r="5838"/>
+    <row r="5839">
+      <c r="A5839" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5839" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5839" t="inlineStr"/>
+      <c r="D5839" t="inlineStr"/>
+      <c r="E5839" t="inlineStr"/>
+      <c r="F5839" t="inlineStr"/>
+      <c r="G5839" t="inlineStr"/>
+      <c r="H5839" t="inlineStr"/>
+      <c r="I5839" t="inlineStr"/>
+    </row>
+    <row r="5840">
+      <c r="A5840" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5840" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5840" t="inlineStr"/>
+      <c r="D5840" t="inlineStr"/>
+      <c r="E5840" t="inlineStr"/>
+      <c r="F5840" t="inlineStr"/>
+      <c r="G5840" t="inlineStr"/>
+      <c r="H5840" t="inlineStr"/>
+      <c r="I5840" t="inlineStr"/>
+    </row>
+    <row r="5841">
+      <c r="A5841" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5841" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5841" t="inlineStr"/>
+      <c r="D5841" t="inlineStr"/>
+      <c r="E5841" t="inlineStr"/>
+      <c r="F5841" t="inlineStr"/>
+      <c r="G5841" t="inlineStr"/>
+      <c r="H5841" t="inlineStr"/>
+      <c r="I5841" t="inlineStr"/>
+    </row>
+    <row r="5842">
+      <c r="A5842" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5842" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5842" t="inlineStr"/>
+      <c r="D5842" t="inlineStr"/>
+      <c r="E5842" t="inlineStr"/>
+      <c r="F5842" t="inlineStr"/>
+      <c r="G5842" t="inlineStr"/>
+      <c r="H5842" t="inlineStr"/>
+      <c r="I5842" t="inlineStr"/>
+    </row>
+    <row r="5843">
+      <c r="A5843" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5843" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5843" t="inlineStr"/>
+      <c r="D5843" t="inlineStr"/>
+      <c r="E5843" t="inlineStr"/>
+      <c r="F5843" t="inlineStr"/>
+      <c r="G5843" t="inlineStr"/>
+      <c r="H5843" t="inlineStr"/>
+      <c r="I5843" t="inlineStr"/>
+    </row>
+    <row r="5844">
+      <c r="A5844" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5844" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5844" t="inlineStr"/>
+      <c r="D5844" t="inlineStr"/>
+      <c r="E5844" t="inlineStr"/>
+      <c r="F5844" t="inlineStr"/>
+      <c r="G5844" t="inlineStr"/>
+      <c r="H5844" t="inlineStr"/>
+      <c r="I5844" t="inlineStr"/>
+    </row>
+    <row r="5845">
+      <c r="A5845" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5845" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5845" t="inlineStr"/>
+      <c r="D5845" t="inlineStr"/>
+      <c r="E5845" t="inlineStr"/>
+      <c r="F5845" t="inlineStr"/>
+      <c r="G5845" t="inlineStr"/>
+      <c r="H5845" t="inlineStr"/>
+      <c r="I5845" t="inlineStr"/>
+    </row>
+    <row r="5846">
+      <c r="A5846" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5846" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5846" t="inlineStr"/>
+      <c r="D5846" t="inlineStr"/>
+      <c r="E5846" t="inlineStr"/>
+      <c r="F5846" t="inlineStr"/>
+      <c r="G5846" t="inlineStr"/>
+      <c r="H5846" t="inlineStr"/>
+      <c r="I5846" t="inlineStr"/>
+    </row>
+    <row r="5847">
+      <c r="A5847" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5847" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5847" t="inlineStr"/>
+      <c r="D5847" t="inlineStr"/>
+      <c r="E5847" t="inlineStr"/>
+      <c r="F5847" t="inlineStr"/>
+      <c r="G5847" t="inlineStr"/>
+      <c r="H5847" t="inlineStr"/>
+      <c r="I5847" t="inlineStr"/>
+    </row>
+    <row r="5848">
+      <c r="A5848" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5848" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5848" t="inlineStr"/>
+      <c r="D5848" t="inlineStr"/>
+      <c r="E5848" t="inlineStr"/>
+      <c r="F5848" t="inlineStr"/>
+      <c r="G5848" t="inlineStr"/>
+      <c r="H5848" t="inlineStr"/>
+      <c r="I5848" t="inlineStr"/>
+    </row>
+    <row r="5849">
+      <c r="A5849" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5849" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5849" t="inlineStr"/>
+      <c r="D5849" t="inlineStr"/>
+      <c r="E5849" t="inlineStr"/>
+      <c r="F5849" t="inlineStr"/>
+      <c r="G5849" t="inlineStr"/>
+      <c r="H5849" t="inlineStr"/>
+      <c r="I5849" t="inlineStr"/>
+    </row>
+    <row r="5850">
+      <c r="A5850" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5850" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5850" t="inlineStr"/>
+      <c r="D5850" t="inlineStr"/>
+      <c r="E5850" t="inlineStr"/>
+      <c r="F5850" t="inlineStr"/>
+      <c r="G5850" t="inlineStr"/>
+      <c r="H5850" t="inlineStr"/>
+      <c r="I5850" t="inlineStr"/>
+    </row>
+    <row r="5851">
+      <c r="A5851" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5851" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5851" t="inlineStr"/>
+      <c r="D5851" t="inlineStr"/>
+      <c r="E5851" t="inlineStr"/>
+      <c r="F5851" t="inlineStr"/>
+      <c r="G5851" t="inlineStr"/>
+      <c r="H5851" t="inlineStr"/>
+      <c r="I5851" t="inlineStr"/>
+    </row>
+    <row r="5852">
+      <c r="A5852" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5852" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5852" t="inlineStr"/>
+      <c r="D5852" t="inlineStr"/>
+      <c r="E5852" t="inlineStr"/>
+      <c r="F5852" t="inlineStr"/>
+      <c r="G5852" t="inlineStr"/>
+      <c r="H5852" t="inlineStr"/>
+      <c r="I5852" t="inlineStr"/>
+    </row>
+    <row r="5853">
+      <c r="A5853" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5853" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5853" t="inlineStr"/>
+      <c r="D5853" t="inlineStr"/>
+      <c r="E5853" t="inlineStr"/>
+      <c r="F5853" t="inlineStr"/>
+      <c r="G5853" t="inlineStr"/>
+      <c r="H5853" t="inlineStr"/>
+      <c r="I5853" t="inlineStr"/>
+    </row>
+    <row r="5854">
+      <c r="A5854" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5854" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5854" t="inlineStr"/>
+      <c r="D5854" t="inlineStr"/>
+      <c r="E5854" t="inlineStr"/>
+      <c r="F5854" t="inlineStr"/>
+      <c r="G5854" t="inlineStr"/>
+      <c r="H5854" t="inlineStr"/>
+      <c r="I5854" t="inlineStr"/>
+    </row>
+    <row r="5855">
+      <c r="A5855" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5855" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5855" t="inlineStr"/>
+      <c r="D5855" t="inlineStr"/>
+      <c r="E5855" t="inlineStr"/>
+      <c r="F5855" t="inlineStr"/>
+      <c r="G5855" t="inlineStr"/>
+      <c r="H5855" t="inlineStr"/>
+      <c r="I5855" t="inlineStr"/>
+    </row>
+    <row r="5856">
+      <c r="A5856" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5856" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5856" t="inlineStr"/>
+      <c r="D5856" t="inlineStr"/>
+      <c r="E5856" t="inlineStr"/>
+      <c r="F5856" t="inlineStr"/>
+      <c r="G5856" t="inlineStr"/>
+      <c r="H5856" t="inlineStr"/>
+      <c r="I5856" t="inlineStr"/>
+    </row>
+    <row r="5857">
+      <c r="A5857" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B5857" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5857" t="inlineStr"/>
+      <c r="D5857" t="inlineStr"/>
+      <c r="E5857" t="inlineStr"/>
+      <c r="F5857" t="inlineStr"/>
+      <c r="G5857" t="inlineStr"/>
+      <c r="H5857" t="inlineStr"/>
+      <c r="I5857" t="inlineStr"/>
+    </row>
+    <row r="5858"/>
+    <row r="5859">
+      <c r="A5859" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5859" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5859" t="inlineStr"/>
+      <c r="D5859" t="inlineStr"/>
+      <c r="E5859" t="inlineStr"/>
+      <c r="F5859" t="inlineStr"/>
+      <c r="G5859" t="inlineStr"/>
+      <c r="H5859" t="inlineStr"/>
+      <c r="I5859" t="inlineStr"/>
+    </row>
+    <row r="5860">
+      <c r="A5860" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5860" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5860" t="inlineStr"/>
+      <c r="D5860" t="inlineStr"/>
+      <c r="E5860" t="inlineStr"/>
+      <c r="F5860" t="inlineStr"/>
+      <c r="G5860" t="inlineStr"/>
+      <c r="H5860" t="inlineStr"/>
+      <c r="I5860" t="inlineStr"/>
+    </row>
+    <row r="5861">
+      <c r="A5861" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5861" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5861" t="inlineStr"/>
+      <c r="D5861" t="inlineStr"/>
+      <c r="E5861" t="inlineStr"/>
+      <c r="F5861" t="inlineStr"/>
+      <c r="G5861" t="inlineStr"/>
+      <c r="H5861" t="inlineStr"/>
+      <c r="I5861" t="inlineStr"/>
+    </row>
+    <row r="5862">
+      <c r="A5862" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5862" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5862" t="inlineStr"/>
+      <c r="D5862" t="inlineStr"/>
+      <c r="E5862" t="inlineStr"/>
+      <c r="F5862" t="inlineStr"/>
+      <c r="G5862" t="inlineStr"/>
+      <c r="H5862" t="inlineStr"/>
+      <c r="I5862" t="inlineStr"/>
+    </row>
+    <row r="5863">
+      <c r="A5863" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5863" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5863" t="inlineStr"/>
+      <c r="D5863" t="inlineStr"/>
+      <c r="E5863" t="inlineStr"/>
+      <c r="F5863" t="inlineStr"/>
+      <c r="G5863" t="inlineStr"/>
+      <c r="H5863" t="inlineStr"/>
+      <c r="I5863" t="inlineStr"/>
+    </row>
+    <row r="5864">
+      <c r="A5864" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5864" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5864" t="inlineStr"/>
+      <c r="D5864" t="inlineStr"/>
+      <c r="E5864" t="inlineStr"/>
+      <c r="F5864" t="inlineStr"/>
+      <c r="G5864" t="inlineStr"/>
+      <c r="H5864" t="inlineStr"/>
+      <c r="I5864" t="inlineStr"/>
+    </row>
+    <row r="5865">
+      <c r="A5865" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5865" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5865" t="inlineStr"/>
+      <c r="D5865" t="inlineStr"/>
+      <c r="E5865" t="inlineStr"/>
+      <c r="F5865" t="inlineStr"/>
+      <c r="G5865" t="inlineStr"/>
+      <c r="H5865" t="inlineStr"/>
+      <c r="I5865" t="inlineStr"/>
+    </row>
+    <row r="5866">
+      <c r="A5866" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5866" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5866" t="inlineStr"/>
+      <c r="D5866" t="inlineStr"/>
+      <c r="E5866" t="inlineStr"/>
+      <c r="F5866" t="inlineStr"/>
+      <c r="G5866" t="inlineStr"/>
+      <c r="H5866" t="inlineStr"/>
+      <c r="I5866" t="inlineStr"/>
+    </row>
+    <row r="5867">
+      <c r="A5867" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5867" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5867" t="inlineStr"/>
+      <c r="D5867" t="inlineStr"/>
+      <c r="E5867" t="inlineStr"/>
+      <c r="F5867" t="inlineStr"/>
+      <c r="G5867" t="inlineStr"/>
+      <c r="H5867" t="inlineStr"/>
+      <c r="I5867" t="inlineStr"/>
+    </row>
+    <row r="5868">
+      <c r="A5868" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5868" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5868" t="inlineStr"/>
+      <c r="D5868" t="inlineStr"/>
+      <c r="E5868" t="inlineStr"/>
+      <c r="F5868" t="inlineStr"/>
+      <c r="G5868" t="inlineStr"/>
+      <c r="H5868" t="inlineStr"/>
+      <c r="I5868" t="inlineStr"/>
+    </row>
+    <row r="5869">
+      <c r="A5869" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5869" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5869" t="inlineStr"/>
+      <c r="D5869" t="inlineStr"/>
+      <c r="E5869" t="inlineStr"/>
+      <c r="F5869" t="inlineStr"/>
+      <c r="G5869" t="inlineStr"/>
+      <c r="H5869" t="inlineStr"/>
+      <c r="I5869" t="inlineStr"/>
+    </row>
+    <row r="5870">
+      <c r="A5870" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5870" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5870" t="inlineStr"/>
+      <c r="D5870" t="inlineStr"/>
+      <c r="E5870" t="inlineStr"/>
+      <c r="F5870" t="inlineStr"/>
+      <c r="G5870" t="inlineStr"/>
+      <c r="H5870" t="inlineStr"/>
+      <c r="I5870" t="inlineStr"/>
+    </row>
+    <row r="5871">
+      <c r="A5871" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5871" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5871" t="inlineStr"/>
+      <c r="D5871" t="inlineStr"/>
+      <c r="E5871" t="inlineStr"/>
+      <c r="F5871" t="inlineStr"/>
+      <c r="G5871" t="inlineStr"/>
+      <c r="H5871" t="inlineStr"/>
+      <c r="I5871" t="inlineStr"/>
+    </row>
+    <row r="5872">
+      <c r="A5872" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5872" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5872" t="inlineStr"/>
+      <c r="D5872" t="inlineStr"/>
+      <c r="E5872" t="inlineStr"/>
+      <c r="F5872" t="inlineStr"/>
+      <c r="G5872" t="inlineStr"/>
+      <c r="H5872" t="inlineStr"/>
+      <c r="I5872" t="inlineStr"/>
+    </row>
+    <row r="5873">
+      <c r="A5873" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5873" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5873" t="inlineStr"/>
+      <c r="D5873" t="inlineStr"/>
+      <c r="E5873" t="inlineStr"/>
+      <c r="F5873" t="inlineStr"/>
+      <c r="G5873" t="inlineStr"/>
+      <c r="H5873" t="inlineStr"/>
+      <c r="I5873" t="inlineStr"/>
+    </row>
+    <row r="5874">
+      <c r="A5874" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5874" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5874" t="inlineStr"/>
+      <c r="D5874" t="inlineStr"/>
+      <c r="E5874" t="inlineStr"/>
+      <c r="F5874" t="inlineStr"/>
+      <c r="G5874" t="inlineStr"/>
+      <c r="H5874" t="inlineStr"/>
+      <c r="I5874" t="inlineStr"/>
+    </row>
+    <row r="5875">
+      <c r="A5875" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5875" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5875" t="inlineStr"/>
+      <c r="D5875" t="inlineStr"/>
+      <c r="E5875" t="inlineStr"/>
+      <c r="F5875" t="inlineStr"/>
+      <c r="G5875" t="inlineStr"/>
+      <c r="H5875" t="inlineStr"/>
+      <c r="I5875" t="inlineStr"/>
+    </row>
+    <row r="5876">
+      <c r="A5876" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5876" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5876" t="inlineStr"/>
+      <c r="D5876" t="inlineStr"/>
+      <c r="E5876" t="inlineStr"/>
+      <c r="F5876" t="inlineStr"/>
+      <c r="G5876" t="inlineStr"/>
+      <c r="H5876" t="inlineStr"/>
+      <c r="I5876" t="inlineStr"/>
+    </row>
+    <row r="5877">
+      <c r="A5877" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="B5877" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5877" t="inlineStr"/>
+      <c r="D5877" t="inlineStr"/>
+      <c r="E5877" t="inlineStr"/>
+      <c r="F5877" t="inlineStr"/>
+      <c r="G5877" t="inlineStr"/>
+      <c r="H5877" t="inlineStr"/>
+      <c r="I5877" t="inlineStr"/>
+    </row>
+    <row r="5878"/>
+    <row r="5879">
+      <c r="A5879" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5879" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5879" t="inlineStr"/>
+      <c r="D5879" t="inlineStr"/>
+      <c r="E5879" t="inlineStr"/>
+      <c r="F5879" t="inlineStr"/>
+      <c r="G5879" t="inlineStr"/>
+      <c r="H5879" t="inlineStr"/>
+      <c r="I5879" t="inlineStr"/>
+    </row>
+    <row r="5880">
+      <c r="A5880" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5880" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5880" t="inlineStr"/>
+      <c r="D5880" t="inlineStr"/>
+      <c r="E5880" t="inlineStr"/>
+      <c r="F5880" t="inlineStr"/>
+      <c r="G5880" t="inlineStr"/>
+      <c r="H5880" t="inlineStr"/>
+      <c r="I5880" t="inlineStr"/>
+    </row>
+    <row r="5881">
+      <c r="A5881" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5881" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5881" t="inlineStr"/>
+      <c r="D5881" t="inlineStr"/>
+      <c r="E5881" t="inlineStr"/>
+      <c r="F5881" t="inlineStr"/>
+      <c r="G5881" t="inlineStr"/>
+      <c r="H5881" t="inlineStr"/>
+      <c r="I5881" t="inlineStr"/>
+    </row>
+    <row r="5882">
+      <c r="A5882" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5882" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5882" t="inlineStr"/>
+      <c r="D5882" t="inlineStr"/>
+      <c r="E5882" t="inlineStr"/>
+      <c r="F5882" t="inlineStr"/>
+      <c r="G5882" t="inlineStr"/>
+      <c r="H5882" t="inlineStr"/>
+      <c r="I5882" t="inlineStr"/>
+    </row>
+    <row r="5883">
+      <c r="A5883" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5883" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5883" t="inlineStr"/>
+      <c r="D5883" t="inlineStr"/>
+      <c r="E5883" t="inlineStr"/>
+      <c r="F5883" t="inlineStr"/>
+      <c r="G5883" t="inlineStr"/>
+      <c r="H5883" t="inlineStr"/>
+      <c r="I5883" t="inlineStr"/>
+    </row>
+    <row r="5884">
+      <c r="A5884" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5884" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5884" t="inlineStr"/>
+      <c r="D5884" t="inlineStr"/>
+      <c r="E5884" t="inlineStr"/>
+      <c r="F5884" t="inlineStr"/>
+      <c r="G5884" t="inlineStr"/>
+      <c r="H5884" t="inlineStr"/>
+      <c r="I5884" t="inlineStr"/>
+    </row>
+    <row r="5885">
+      <c r="A5885" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5885" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5885" t="inlineStr"/>
+      <c r="D5885" t="inlineStr"/>
+      <c r="E5885" t="inlineStr"/>
+      <c r="F5885" t="inlineStr"/>
+      <c r="G5885" t="inlineStr"/>
+      <c r="H5885" t="inlineStr"/>
+      <c r="I5885" t="inlineStr"/>
+    </row>
+    <row r="5886">
+      <c r="A5886" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5886" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5886" t="inlineStr"/>
+      <c r="D5886" t="inlineStr"/>
+      <c r="E5886" t="inlineStr"/>
+      <c r="F5886" t="inlineStr"/>
+      <c r="G5886" t="inlineStr"/>
+      <c r="H5886" t="inlineStr"/>
+      <c r="I5886" t="inlineStr"/>
+    </row>
+    <row r="5887">
+      <c r="A5887" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5887" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5887" t="inlineStr"/>
+      <c r="D5887" t="inlineStr"/>
+      <c r="E5887" t="inlineStr"/>
+      <c r="F5887" t="inlineStr"/>
+      <c r="G5887" t="inlineStr"/>
+      <c r="H5887" t="inlineStr"/>
+      <c r="I5887" t="inlineStr"/>
+    </row>
+    <row r="5888">
+      <c r="A5888" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5888" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5888" t="inlineStr"/>
+      <c r="D5888" t="inlineStr"/>
+      <c r="E5888" t="inlineStr"/>
+      <c r="F5888" t="inlineStr"/>
+      <c r="G5888" t="inlineStr"/>
+      <c r="H5888" t="inlineStr"/>
+      <c r="I5888" t="inlineStr"/>
+    </row>
+    <row r="5889">
+      <c r="A5889" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5889" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5889" t="inlineStr"/>
+      <c r="D5889" t="inlineStr"/>
+      <c r="E5889" t="inlineStr"/>
+      <c r="F5889" t="inlineStr"/>
+      <c r="G5889" t="inlineStr"/>
+      <c r="H5889" t="inlineStr"/>
+      <c r="I5889" t="inlineStr"/>
+    </row>
+    <row r="5890">
+      <c r="A5890" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5890" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5890" t="inlineStr"/>
+      <c r="D5890" t="inlineStr"/>
+      <c r="E5890" t="inlineStr"/>
+      <c r="F5890" t="inlineStr"/>
+      <c r="G5890" t="inlineStr"/>
+      <c r="H5890" t="inlineStr"/>
+      <c r="I5890" t="inlineStr"/>
+    </row>
+    <row r="5891">
+      <c r="A5891" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5891" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5891" t="inlineStr"/>
+      <c r="D5891" t="inlineStr"/>
+      <c r="E5891" t="inlineStr"/>
+      <c r="F5891" t="inlineStr"/>
+      <c r="G5891" t="inlineStr"/>
+      <c r="H5891" t="inlineStr"/>
+      <c r="I5891" t="inlineStr"/>
+    </row>
+    <row r="5892">
+      <c r="A5892" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5892" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5892" t="inlineStr"/>
+      <c r="D5892" t="inlineStr"/>
+      <c r="E5892" t="inlineStr"/>
+      <c r="F5892" t="inlineStr"/>
+      <c r="G5892" t="inlineStr"/>
+      <c r="H5892" t="inlineStr"/>
+      <c r="I5892" t="inlineStr"/>
+    </row>
+    <row r="5893">
+      <c r="A5893" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5893" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5893" t="inlineStr"/>
+      <c r="D5893" t="inlineStr"/>
+      <c r="E5893" t="inlineStr"/>
+      <c r="F5893" t="inlineStr"/>
+      <c r="G5893" t="inlineStr"/>
+      <c r="H5893" t="inlineStr"/>
+      <c r="I5893" t="inlineStr"/>
+    </row>
+    <row r="5894">
+      <c r="A5894" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5894" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5894" t="inlineStr"/>
+      <c r="D5894" t="inlineStr"/>
+      <c r="E5894" t="inlineStr"/>
+      <c r="F5894" t="inlineStr"/>
+      <c r="G5894" t="inlineStr"/>
+      <c r="H5894" t="inlineStr"/>
+      <c r="I5894" t="inlineStr"/>
+    </row>
+    <row r="5895">
+      <c r="A5895" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5895" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5895" t="inlineStr"/>
+      <c r="D5895" t="inlineStr"/>
+      <c r="E5895" t="inlineStr"/>
+      <c r="F5895" t="inlineStr"/>
+      <c r="G5895" t="inlineStr"/>
+      <c r="H5895" t="inlineStr"/>
+      <c r="I5895" t="inlineStr"/>
+    </row>
+    <row r="5896">
+      <c r="A5896" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5896" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5896" t="inlineStr"/>
+      <c r="D5896" t="inlineStr"/>
+      <c r="E5896" t="inlineStr"/>
+      <c r="F5896" t="inlineStr"/>
+      <c r="G5896" t="inlineStr"/>
+      <c r="H5896" t="inlineStr"/>
+      <c r="I5896" t="inlineStr"/>
+    </row>
+    <row r="5897">
+      <c r="A5897" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+      <c r="B5897" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5897" t="inlineStr"/>
+      <c r="D5897" t="inlineStr"/>
+      <c r="E5897" t="inlineStr"/>
+      <c r="F5897" t="inlineStr"/>
+      <c r="G5897" t="inlineStr"/>
+      <c r="H5897" t="inlineStr"/>
+      <c r="I5897" t="inlineStr"/>
+    </row>
+    <row r="5898"/>
+    <row r="5899">
+      <c r="A5899" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5899" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5899" t="inlineStr"/>
+      <c r="D5899" t="inlineStr"/>
+      <c r="E5899" t="inlineStr"/>
+      <c r="F5899" t="inlineStr"/>
+      <c r="G5899" t="inlineStr"/>
+      <c r="H5899" t="inlineStr"/>
+      <c r="I5899" t="inlineStr"/>
+    </row>
+    <row r="5900">
+      <c r="A5900" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5900" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5900" t="inlineStr"/>
+      <c r="D5900" t="inlineStr"/>
+      <c r="E5900" t="inlineStr"/>
+      <c r="F5900" t="inlineStr"/>
+      <c r="G5900" t="inlineStr"/>
+      <c r="H5900" t="inlineStr"/>
+      <c r="I5900" t="inlineStr"/>
+    </row>
+    <row r="5901">
+      <c r="A5901" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5901" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5901" t="inlineStr"/>
+      <c r="D5901" t="inlineStr"/>
+      <c r="E5901" t="inlineStr"/>
+      <c r="F5901" t="inlineStr"/>
+      <c r="G5901" t="inlineStr"/>
+      <c r="H5901" t="inlineStr"/>
+      <c r="I5901" t="inlineStr"/>
+    </row>
+    <row r="5902">
+      <c r="A5902" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5902" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5902" t="inlineStr"/>
+      <c r="D5902" t="inlineStr"/>
+      <c r="E5902" t="inlineStr"/>
+      <c r="F5902" t="inlineStr"/>
+      <c r="G5902" t="inlineStr"/>
+      <c r="H5902" t="inlineStr"/>
+      <c r="I5902" t="inlineStr"/>
+    </row>
+    <row r="5903">
+      <c r="A5903" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5903" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5903" t="inlineStr"/>
+      <c r="D5903" t="inlineStr"/>
+      <c r="E5903" t="inlineStr"/>
+      <c r="F5903" t="inlineStr"/>
+      <c r="G5903" t="inlineStr"/>
+      <c r="H5903" t="inlineStr"/>
+      <c r="I5903" t="inlineStr"/>
+    </row>
+    <row r="5904">
+      <c r="A5904" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5904" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5904" t="inlineStr"/>
+      <c r="D5904" t="inlineStr"/>
+      <c r="E5904" t="inlineStr"/>
+      <c r="F5904" t="inlineStr"/>
+      <c r="G5904" t="inlineStr"/>
+      <c r="H5904" t="inlineStr"/>
+      <c r="I5904" t="inlineStr"/>
+    </row>
+    <row r="5905">
+      <c r="A5905" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5905" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5905" t="inlineStr"/>
+      <c r="D5905" t="inlineStr"/>
+      <c r="E5905" t="inlineStr"/>
+      <c r="F5905" t="inlineStr"/>
+      <c r="G5905" t="inlineStr"/>
+      <c r="H5905" t="inlineStr"/>
+      <c r="I5905" t="inlineStr"/>
+    </row>
+    <row r="5906">
+      <c r="A5906" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5906" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5906" t="inlineStr"/>
+      <c r="D5906" t="inlineStr"/>
+      <c r="E5906" t="inlineStr"/>
+      <c r="F5906" t="inlineStr"/>
+      <c r="G5906" t="inlineStr"/>
+      <c r="H5906" t="inlineStr"/>
+      <c r="I5906" t="inlineStr"/>
+    </row>
+    <row r="5907">
+      <c r="A5907" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5907" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5907" t="inlineStr"/>
+      <c r="D5907" t="inlineStr"/>
+      <c r="E5907" t="inlineStr"/>
+      <c r="F5907" t="inlineStr"/>
+      <c r="G5907" t="inlineStr"/>
+      <c r="H5907" t="inlineStr"/>
+      <c r="I5907" t="inlineStr"/>
+    </row>
+    <row r="5908">
+      <c r="A5908" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5908" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5908" t="inlineStr"/>
+      <c r="D5908" t="inlineStr"/>
+      <c r="E5908" t="inlineStr"/>
+      <c r="F5908" t="inlineStr"/>
+      <c r="G5908" t="inlineStr"/>
+      <c r="H5908" t="inlineStr"/>
+      <c r="I5908" t="inlineStr"/>
+    </row>
+    <row r="5909">
+      <c r="A5909" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5909" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5909" t="inlineStr"/>
+      <c r="D5909" t="inlineStr"/>
+      <c r="E5909" t="inlineStr"/>
+      <c r="F5909" t="inlineStr"/>
+      <c r="G5909" t="inlineStr"/>
+      <c r="H5909" t="inlineStr"/>
+      <c r="I5909" t="inlineStr"/>
+    </row>
+    <row r="5910">
+      <c r="A5910" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5910" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5910" t="inlineStr"/>
+      <c r="D5910" t="inlineStr"/>
+      <c r="E5910" t="inlineStr"/>
+      <c r="F5910" t="inlineStr"/>
+      <c r="G5910" t="inlineStr"/>
+      <c r="H5910" t="inlineStr"/>
+      <c r="I5910" t="inlineStr"/>
+    </row>
+    <row r="5911">
+      <c r="A5911" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5911" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5911" t="inlineStr"/>
+      <c r="D5911" t="inlineStr"/>
+      <c r="E5911" t="inlineStr"/>
+      <c r="F5911" t="inlineStr"/>
+      <c r="G5911" t="inlineStr"/>
+      <c r="H5911" t="inlineStr"/>
+      <c r="I5911" t="inlineStr"/>
+    </row>
+    <row r="5912">
+      <c r="A5912" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5912" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5912" t="inlineStr"/>
+      <c r="D5912" t="inlineStr"/>
+      <c r="E5912" t="inlineStr"/>
+      <c r="F5912" t="inlineStr"/>
+      <c r="G5912" t="inlineStr"/>
+      <c r="H5912" t="inlineStr"/>
+      <c r="I5912" t="inlineStr"/>
+    </row>
+    <row r="5913">
+      <c r="A5913" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5913" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5913" t="inlineStr"/>
+      <c r="D5913" t="inlineStr"/>
+      <c r="E5913" t="inlineStr"/>
+      <c r="F5913" t="inlineStr"/>
+      <c r="G5913" t="inlineStr"/>
+      <c r="H5913" t="inlineStr"/>
+      <c r="I5913" t="inlineStr"/>
+    </row>
+    <row r="5914">
+      <c r="A5914" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5914" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5914" t="inlineStr"/>
+      <c r="D5914" t="inlineStr"/>
+      <c r="E5914" t="inlineStr"/>
+      <c r="F5914" t="inlineStr"/>
+      <c r="G5914" t="inlineStr"/>
+      <c r="H5914" t="inlineStr"/>
+      <c r="I5914" t="inlineStr"/>
+    </row>
+    <row r="5915">
+      <c r="A5915" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5915" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5915" t="inlineStr"/>
+      <c r="D5915" t="inlineStr"/>
+      <c r="E5915" t="inlineStr"/>
+      <c r="F5915" t="inlineStr"/>
+      <c r="G5915" t="inlineStr"/>
+      <c r="H5915" t="inlineStr"/>
+      <c r="I5915" t="inlineStr"/>
+    </row>
+    <row r="5916">
+      <c r="A5916" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5916" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5916" t="inlineStr"/>
+      <c r="D5916" t="inlineStr"/>
+      <c r="E5916" t="inlineStr"/>
+      <c r="F5916" t="inlineStr"/>
+      <c r="G5916" t="inlineStr"/>
+      <c r="H5916" t="inlineStr"/>
+      <c r="I5916" t="inlineStr"/>
+    </row>
+    <row r="5917">
+      <c r="A5917" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5917" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5917" t="inlineStr"/>
+      <c r="D5917" t="inlineStr"/>
+      <c r="E5917" t="inlineStr"/>
+      <c r="F5917" t="inlineStr"/>
+      <c r="G5917" t="inlineStr"/>
+      <c r="H5917" t="inlineStr"/>
+      <c r="I5917" t="inlineStr"/>
+    </row>
+    <row r="5918"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/data/blumen_data.xlsx
+++ b/data/blumen_data.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5918"/>
+  <dimension ref="A1:AD5998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -69010,13 +69010,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5779" t="inlineStr"/>
-      <c r="D5779" t="inlineStr"/>
-      <c r="E5779" t="inlineStr"/>
-      <c r="F5779" t="inlineStr"/>
-      <c r="G5779" t="inlineStr"/>
-      <c r="H5779" t="inlineStr"/>
-      <c r="I5779" t="inlineStr"/>
     </row>
     <row r="5780">
       <c r="A5780" t="inlineStr">
@@ -69029,13 +69022,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5780" t="inlineStr"/>
-      <c r="D5780" t="inlineStr"/>
-      <c r="E5780" t="inlineStr"/>
-      <c r="F5780" t="inlineStr"/>
-      <c r="G5780" t="inlineStr"/>
-      <c r="H5780" t="inlineStr"/>
-      <c r="I5780" t="inlineStr"/>
     </row>
     <row r="5781">
       <c r="A5781" t="inlineStr">
@@ -69048,13 +69034,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5781" t="inlineStr"/>
-      <c r="D5781" t="inlineStr"/>
-      <c r="E5781" t="inlineStr"/>
-      <c r="F5781" t="inlineStr"/>
-      <c r="G5781" t="inlineStr"/>
-      <c r="H5781" t="inlineStr"/>
-      <c r="I5781" t="inlineStr"/>
     </row>
     <row r="5782">
       <c r="A5782" t="inlineStr">
@@ -69067,13 +69046,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5782" t="inlineStr"/>
-      <c r="D5782" t="inlineStr"/>
-      <c r="E5782" t="inlineStr"/>
-      <c r="F5782" t="inlineStr"/>
-      <c r="G5782" t="inlineStr"/>
-      <c r="H5782" t="inlineStr"/>
-      <c r="I5782" t="inlineStr"/>
     </row>
     <row r="5783">
       <c r="A5783" t="inlineStr">
@@ -69086,13 +69058,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5783" t="inlineStr"/>
-      <c r="D5783" t="inlineStr"/>
-      <c r="E5783" t="inlineStr"/>
-      <c r="F5783" t="inlineStr"/>
-      <c r="G5783" t="inlineStr"/>
-      <c r="H5783" t="inlineStr"/>
-      <c r="I5783" t="inlineStr"/>
     </row>
     <row r="5784">
       <c r="A5784" t="inlineStr">
@@ -69105,13 +69070,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5784" t="inlineStr"/>
-      <c r="D5784" t="inlineStr"/>
-      <c r="E5784" t="inlineStr"/>
-      <c r="F5784" t="inlineStr"/>
-      <c r="G5784" t="inlineStr"/>
-      <c r="H5784" t="inlineStr"/>
-      <c r="I5784" t="inlineStr"/>
     </row>
     <row r="5785">
       <c r="A5785" t="inlineStr">
@@ -69124,13 +69082,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5785" t="inlineStr"/>
-      <c r="D5785" t="inlineStr"/>
-      <c r="E5785" t="inlineStr"/>
-      <c r="F5785" t="inlineStr"/>
-      <c r="G5785" t="inlineStr"/>
-      <c r="H5785" t="inlineStr"/>
-      <c r="I5785" t="inlineStr"/>
     </row>
     <row r="5786">
       <c r="A5786" t="inlineStr">
@@ -69143,13 +69094,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5786" t="inlineStr"/>
-      <c r="D5786" t="inlineStr"/>
-      <c r="E5786" t="inlineStr"/>
-      <c r="F5786" t="inlineStr"/>
-      <c r="G5786" t="inlineStr"/>
-      <c r="H5786" t="inlineStr"/>
-      <c r="I5786" t="inlineStr"/>
     </row>
     <row r="5787">
       <c r="A5787" t="inlineStr">
@@ -69162,13 +69106,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5787" t="inlineStr"/>
-      <c r="D5787" t="inlineStr"/>
-      <c r="E5787" t="inlineStr"/>
-      <c r="F5787" t="inlineStr"/>
-      <c r="G5787" t="inlineStr"/>
-      <c r="H5787" t="inlineStr"/>
-      <c r="I5787" t="inlineStr"/>
     </row>
     <row r="5788">
       <c r="A5788" t="inlineStr">
@@ -69181,13 +69118,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5788" t="inlineStr"/>
-      <c r="D5788" t="inlineStr"/>
-      <c r="E5788" t="inlineStr"/>
-      <c r="F5788" t="inlineStr"/>
-      <c r="G5788" t="inlineStr"/>
-      <c r="H5788" t="inlineStr"/>
-      <c r="I5788" t="inlineStr"/>
     </row>
     <row r="5789">
       <c r="A5789" t="inlineStr">
@@ -69200,13 +69130,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5789" t="inlineStr"/>
-      <c r="D5789" t="inlineStr"/>
-      <c r="E5789" t="inlineStr"/>
-      <c r="F5789" t="inlineStr"/>
-      <c r="G5789" t="inlineStr"/>
-      <c r="H5789" t="inlineStr"/>
-      <c r="I5789" t="inlineStr"/>
     </row>
     <row r="5790">
       <c r="A5790" t="inlineStr">
@@ -69219,13 +69142,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5790" t="inlineStr"/>
-      <c r="D5790" t="inlineStr"/>
-      <c r="E5790" t="inlineStr"/>
-      <c r="F5790" t="inlineStr"/>
-      <c r="G5790" t="inlineStr"/>
-      <c r="H5790" t="inlineStr"/>
-      <c r="I5790" t="inlineStr"/>
     </row>
     <row r="5791">
       <c r="A5791" t="inlineStr">
@@ -69238,13 +69154,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5791" t="inlineStr"/>
-      <c r="D5791" t="inlineStr"/>
-      <c r="E5791" t="inlineStr"/>
-      <c r="F5791" t="inlineStr"/>
-      <c r="G5791" t="inlineStr"/>
-      <c r="H5791" t="inlineStr"/>
-      <c r="I5791" t="inlineStr"/>
     </row>
     <row r="5792">
       <c r="A5792" t="inlineStr">
@@ -69257,13 +69166,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5792" t="inlineStr"/>
-      <c r="D5792" t="inlineStr"/>
-      <c r="E5792" t="inlineStr"/>
-      <c r="F5792" t="inlineStr"/>
-      <c r="G5792" t="inlineStr"/>
-      <c r="H5792" t="inlineStr"/>
-      <c r="I5792" t="inlineStr"/>
     </row>
     <row r="5793">
       <c r="A5793" t="inlineStr">
@@ -69276,13 +69178,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5793" t="inlineStr"/>
-      <c r="D5793" t="inlineStr"/>
-      <c r="E5793" t="inlineStr"/>
-      <c r="F5793" t="inlineStr"/>
-      <c r="G5793" t="inlineStr"/>
-      <c r="H5793" t="inlineStr"/>
-      <c r="I5793" t="inlineStr"/>
     </row>
     <row r="5794">
       <c r="A5794" t="inlineStr">
@@ -69295,13 +69190,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5794" t="inlineStr"/>
-      <c r="D5794" t="inlineStr"/>
-      <c r="E5794" t="inlineStr"/>
-      <c r="F5794" t="inlineStr"/>
-      <c r="G5794" t="inlineStr"/>
-      <c r="H5794" t="inlineStr"/>
-      <c r="I5794" t="inlineStr"/>
     </row>
     <row r="5795">
       <c r="A5795" t="inlineStr">
@@ -69314,13 +69202,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5795" t="inlineStr"/>
-      <c r="D5795" t="inlineStr"/>
-      <c r="E5795" t="inlineStr"/>
-      <c r="F5795" t="inlineStr"/>
-      <c r="G5795" t="inlineStr"/>
-      <c r="H5795" t="inlineStr"/>
-      <c r="I5795" t="inlineStr"/>
     </row>
     <row r="5796">
       <c r="A5796" t="inlineStr">
@@ -69333,13 +69214,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5796" t="inlineStr"/>
-      <c r="D5796" t="inlineStr"/>
-      <c r="E5796" t="inlineStr"/>
-      <c r="F5796" t="inlineStr"/>
-      <c r="G5796" t="inlineStr"/>
-      <c r="H5796" t="inlineStr"/>
-      <c r="I5796" t="inlineStr"/>
     </row>
     <row r="5797">
       <c r="A5797" t="inlineStr">
@@ -69352,13 +69226,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5797" t="inlineStr"/>
-      <c r="D5797" t="inlineStr"/>
-      <c r="E5797" t="inlineStr"/>
-      <c r="F5797" t="inlineStr"/>
-      <c r="G5797" t="inlineStr"/>
-      <c r="H5797" t="inlineStr"/>
-      <c r="I5797" t="inlineStr"/>
     </row>
     <row r="5798"/>
     <row r="5799">
@@ -69372,13 +69239,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5799" t="inlineStr"/>
-      <c r="D5799" t="inlineStr"/>
-      <c r="E5799" t="inlineStr"/>
-      <c r="F5799" t="inlineStr"/>
-      <c r="G5799" t="inlineStr"/>
-      <c r="H5799" t="inlineStr"/>
-      <c r="I5799" t="inlineStr"/>
     </row>
     <row r="5800">
       <c r="A5800" t="inlineStr">
@@ -69391,13 +69251,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5800" t="inlineStr"/>
-      <c r="D5800" t="inlineStr"/>
-      <c r="E5800" t="inlineStr"/>
-      <c r="F5800" t="inlineStr"/>
-      <c r="G5800" t="inlineStr"/>
-      <c r="H5800" t="inlineStr"/>
-      <c r="I5800" t="inlineStr"/>
     </row>
     <row r="5801">
       <c r="A5801" t="inlineStr">
@@ -69410,13 +69263,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5801" t="inlineStr"/>
-      <c r="D5801" t="inlineStr"/>
-      <c r="E5801" t="inlineStr"/>
-      <c r="F5801" t="inlineStr"/>
-      <c r="G5801" t="inlineStr"/>
-      <c r="H5801" t="inlineStr"/>
-      <c r="I5801" t="inlineStr"/>
     </row>
     <row r="5802">
       <c r="A5802" t="inlineStr">
@@ -69429,13 +69275,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5802" t="inlineStr"/>
-      <c r="D5802" t="inlineStr"/>
-      <c r="E5802" t="inlineStr"/>
-      <c r="F5802" t="inlineStr"/>
-      <c r="G5802" t="inlineStr"/>
-      <c r="H5802" t="inlineStr"/>
-      <c r="I5802" t="inlineStr"/>
     </row>
     <row r="5803">
       <c r="A5803" t="inlineStr">
@@ -69448,13 +69287,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5803" t="inlineStr"/>
-      <c r="D5803" t="inlineStr"/>
-      <c r="E5803" t="inlineStr"/>
-      <c r="F5803" t="inlineStr"/>
-      <c r="G5803" t="inlineStr"/>
-      <c r="H5803" t="inlineStr"/>
-      <c r="I5803" t="inlineStr"/>
     </row>
     <row r="5804">
       <c r="A5804" t="inlineStr">
@@ -69467,13 +69299,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5804" t="inlineStr"/>
-      <c r="D5804" t="inlineStr"/>
-      <c r="E5804" t="inlineStr"/>
-      <c r="F5804" t="inlineStr"/>
-      <c r="G5804" t="inlineStr"/>
-      <c r="H5804" t="inlineStr"/>
-      <c r="I5804" t="inlineStr"/>
     </row>
     <row r="5805">
       <c r="A5805" t="inlineStr">
@@ -69486,13 +69311,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5805" t="inlineStr"/>
-      <c r="D5805" t="inlineStr"/>
-      <c r="E5805" t="inlineStr"/>
-      <c r="F5805" t="inlineStr"/>
-      <c r="G5805" t="inlineStr"/>
-      <c r="H5805" t="inlineStr"/>
-      <c r="I5805" t="inlineStr"/>
     </row>
     <row r="5806">
       <c r="A5806" t="inlineStr">
@@ -69505,13 +69323,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5806" t="inlineStr"/>
-      <c r="D5806" t="inlineStr"/>
-      <c r="E5806" t="inlineStr"/>
-      <c r="F5806" t="inlineStr"/>
-      <c r="G5806" t="inlineStr"/>
-      <c r="H5806" t="inlineStr"/>
-      <c r="I5806" t="inlineStr"/>
     </row>
     <row r="5807">
       <c r="A5807" t="inlineStr">
@@ -69524,13 +69335,14 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5807" t="inlineStr"/>
-      <c r="D5807" t="inlineStr"/>
-      <c r="E5807" t="inlineStr"/>
-      <c r="F5807" t="inlineStr"/>
-      <c r="G5807" t="inlineStr"/>
-      <c r="H5807" t="inlineStr"/>
-      <c r="I5807" t="inlineStr"/>
+      <c r="D5807" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5807" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5808">
       <c r="A5808" t="inlineStr">
@@ -69543,13 +69355,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5808" t="inlineStr"/>
-      <c r="D5808" t="inlineStr"/>
-      <c r="E5808" t="inlineStr"/>
-      <c r="F5808" t="inlineStr"/>
-      <c r="G5808" t="inlineStr"/>
-      <c r="H5808" t="inlineStr"/>
-      <c r="I5808" t="inlineStr"/>
     </row>
     <row r="5809">
       <c r="A5809" t="inlineStr">
@@ -69562,13 +69367,14 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5809" t="inlineStr"/>
-      <c r="D5809" t="inlineStr"/>
-      <c r="E5809" t="inlineStr"/>
-      <c r="F5809" t="inlineStr"/>
-      <c r="G5809" t="inlineStr"/>
-      <c r="H5809" t="inlineStr"/>
-      <c r="I5809" t="inlineStr"/>
+      <c r="D5809" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5809" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5810">
       <c r="A5810" t="inlineStr">
@@ -69581,13 +69387,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5810" t="inlineStr"/>
-      <c r="D5810" t="inlineStr"/>
-      <c r="E5810" t="inlineStr"/>
-      <c r="F5810" t="inlineStr"/>
-      <c r="G5810" t="inlineStr"/>
-      <c r="H5810" t="inlineStr"/>
-      <c r="I5810" t="inlineStr"/>
     </row>
     <row r="5811">
       <c r="A5811" t="inlineStr">
@@ -69600,13 +69399,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5811" t="inlineStr"/>
-      <c r="D5811" t="inlineStr"/>
-      <c r="E5811" t="inlineStr"/>
-      <c r="F5811" t="inlineStr"/>
-      <c r="G5811" t="inlineStr"/>
-      <c r="H5811" t="inlineStr"/>
-      <c r="I5811" t="inlineStr"/>
     </row>
     <row r="5812">
       <c r="A5812" t="inlineStr">
@@ -69619,13 +69411,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5812" t="inlineStr"/>
-      <c r="D5812" t="inlineStr"/>
-      <c r="E5812" t="inlineStr"/>
-      <c r="F5812" t="inlineStr"/>
-      <c r="G5812" t="inlineStr"/>
-      <c r="H5812" t="inlineStr"/>
-      <c r="I5812" t="inlineStr"/>
     </row>
     <row r="5813">
       <c r="A5813" t="inlineStr">
@@ -69638,13 +69423,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5813" t="inlineStr"/>
-      <c r="D5813" t="inlineStr"/>
-      <c r="E5813" t="inlineStr"/>
-      <c r="F5813" t="inlineStr"/>
-      <c r="G5813" t="inlineStr"/>
-      <c r="H5813" t="inlineStr"/>
-      <c r="I5813" t="inlineStr"/>
     </row>
     <row r="5814">
       <c r="A5814" t="inlineStr">
@@ -69657,13 +69435,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5814" t="inlineStr"/>
-      <c r="D5814" t="inlineStr"/>
-      <c r="E5814" t="inlineStr"/>
-      <c r="F5814" t="inlineStr"/>
-      <c r="G5814" t="inlineStr"/>
-      <c r="H5814" t="inlineStr"/>
-      <c r="I5814" t="inlineStr"/>
     </row>
     <row r="5815">
       <c r="A5815" t="inlineStr">
@@ -69676,13 +69447,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5815" t="inlineStr"/>
-      <c r="D5815" t="inlineStr"/>
-      <c r="E5815" t="inlineStr"/>
-      <c r="F5815" t="inlineStr"/>
-      <c r="G5815" t="inlineStr"/>
-      <c r="H5815" t="inlineStr"/>
-      <c r="I5815" t="inlineStr"/>
     </row>
     <row r="5816">
       <c r="A5816" t="inlineStr">
@@ -69695,13 +69459,14 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5816" t="inlineStr"/>
-      <c r="D5816" t="inlineStr"/>
-      <c r="E5816" t="inlineStr"/>
-      <c r="F5816" t="inlineStr"/>
-      <c r="G5816" t="inlineStr"/>
-      <c r="H5816" t="inlineStr"/>
-      <c r="I5816" t="inlineStr"/>
+      <c r="D5816" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5816" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5817">
       <c r="A5817" t="inlineStr">
@@ -69714,13 +69479,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5817" t="inlineStr"/>
-      <c r="D5817" t="inlineStr"/>
-      <c r="E5817" t="inlineStr"/>
-      <c r="F5817" t="inlineStr"/>
-      <c r="G5817" t="inlineStr"/>
-      <c r="H5817" t="inlineStr"/>
-      <c r="I5817" t="inlineStr"/>
     </row>
     <row r="5818"/>
     <row r="5819">
@@ -69734,13 +69492,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5819" t="inlineStr"/>
-      <c r="D5819" t="inlineStr"/>
-      <c r="E5819" t="inlineStr"/>
-      <c r="F5819" t="inlineStr"/>
-      <c r="G5819" t="inlineStr"/>
-      <c r="H5819" t="inlineStr"/>
-      <c r="I5819" t="inlineStr"/>
     </row>
     <row r="5820">
       <c r="A5820" t="inlineStr">
@@ -69753,13 +69504,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5820" t="inlineStr"/>
-      <c r="D5820" t="inlineStr"/>
-      <c r="E5820" t="inlineStr"/>
-      <c r="F5820" t="inlineStr"/>
-      <c r="G5820" t="inlineStr"/>
-      <c r="H5820" t="inlineStr"/>
-      <c r="I5820" t="inlineStr"/>
     </row>
     <row r="5821">
       <c r="A5821" t="inlineStr">
@@ -69772,13 +69516,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5821" t="inlineStr"/>
-      <c r="D5821" t="inlineStr"/>
-      <c r="E5821" t="inlineStr"/>
-      <c r="F5821" t="inlineStr"/>
-      <c r="G5821" t="inlineStr"/>
-      <c r="H5821" t="inlineStr"/>
-      <c r="I5821" t="inlineStr"/>
     </row>
     <row r="5822">
       <c r="A5822" t="inlineStr">
@@ -69791,13 +69528,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5822" t="inlineStr"/>
-      <c r="D5822" t="inlineStr"/>
-      <c r="E5822" t="inlineStr"/>
-      <c r="F5822" t="inlineStr"/>
-      <c r="G5822" t="inlineStr"/>
-      <c r="H5822" t="inlineStr"/>
-      <c r="I5822" t="inlineStr"/>
     </row>
     <row r="5823">
       <c r="A5823" t="inlineStr">
@@ -69810,13 +69540,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5823" t="inlineStr"/>
-      <c r="D5823" t="inlineStr"/>
-      <c r="E5823" t="inlineStr"/>
-      <c r="F5823" t="inlineStr"/>
-      <c r="G5823" t="inlineStr"/>
-      <c r="H5823" t="inlineStr"/>
-      <c r="I5823" t="inlineStr"/>
     </row>
     <row r="5824">
       <c r="A5824" t="inlineStr">
@@ -69829,13 +69552,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5824" t="inlineStr"/>
-      <c r="D5824" t="inlineStr"/>
-      <c r="E5824" t="inlineStr"/>
-      <c r="F5824" t="inlineStr"/>
-      <c r="G5824" t="inlineStr"/>
-      <c r="H5824" t="inlineStr"/>
-      <c r="I5824" t="inlineStr"/>
     </row>
     <row r="5825">
       <c r="A5825" t="inlineStr">
@@ -69848,13 +69564,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5825" t="inlineStr"/>
-      <c r="D5825" t="inlineStr"/>
-      <c r="E5825" t="inlineStr"/>
-      <c r="F5825" t="inlineStr"/>
-      <c r="G5825" t="inlineStr"/>
-      <c r="H5825" t="inlineStr"/>
-      <c r="I5825" t="inlineStr"/>
     </row>
     <row r="5826">
       <c r="A5826" t="inlineStr">
@@ -69867,13 +69576,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5826" t="inlineStr"/>
-      <c r="D5826" t="inlineStr"/>
-      <c r="E5826" t="inlineStr"/>
-      <c r="F5826" t="inlineStr"/>
-      <c r="G5826" t="inlineStr"/>
-      <c r="H5826" t="inlineStr"/>
-      <c r="I5826" t="inlineStr"/>
     </row>
     <row r="5827">
       <c r="A5827" t="inlineStr">
@@ -69886,13 +69588,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5827" t="inlineStr"/>
-      <c r="D5827" t="inlineStr"/>
-      <c r="E5827" t="inlineStr"/>
-      <c r="F5827" t="inlineStr"/>
-      <c r="G5827" t="inlineStr"/>
-      <c r="H5827" t="inlineStr"/>
-      <c r="I5827" t="inlineStr"/>
     </row>
     <row r="5828">
       <c r="A5828" t="inlineStr">
@@ -69905,13 +69600,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5828" t="inlineStr"/>
-      <c r="D5828" t="inlineStr"/>
-      <c r="E5828" t="inlineStr"/>
-      <c r="F5828" t="inlineStr"/>
-      <c r="G5828" t="inlineStr"/>
-      <c r="H5828" t="inlineStr"/>
-      <c r="I5828" t="inlineStr"/>
     </row>
     <row r="5829">
       <c r="A5829" t="inlineStr">
@@ -69924,13 +69612,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5829" t="inlineStr"/>
-      <c r="D5829" t="inlineStr"/>
-      <c r="E5829" t="inlineStr"/>
-      <c r="F5829" t="inlineStr"/>
-      <c r="G5829" t="inlineStr"/>
-      <c r="H5829" t="inlineStr"/>
-      <c r="I5829" t="inlineStr"/>
     </row>
     <row r="5830">
       <c r="A5830" t="inlineStr">
@@ -69943,13 +69624,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5830" t="inlineStr"/>
-      <c r="D5830" t="inlineStr"/>
-      <c r="E5830" t="inlineStr"/>
-      <c r="F5830" t="inlineStr"/>
-      <c r="G5830" t="inlineStr"/>
-      <c r="H5830" t="inlineStr"/>
-      <c r="I5830" t="inlineStr"/>
     </row>
     <row r="5831">
       <c r="A5831" t="inlineStr">
@@ -69962,13 +69636,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5831" t="inlineStr"/>
-      <c r="D5831" t="inlineStr"/>
-      <c r="E5831" t="inlineStr"/>
-      <c r="F5831" t="inlineStr"/>
-      <c r="G5831" t="inlineStr"/>
-      <c r="H5831" t="inlineStr"/>
-      <c r="I5831" t="inlineStr"/>
     </row>
     <row r="5832">
       <c r="A5832" t="inlineStr">
@@ -69981,13 +69648,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5832" t="inlineStr"/>
-      <c r="D5832" t="inlineStr"/>
-      <c r="E5832" t="inlineStr"/>
-      <c r="F5832" t="inlineStr"/>
-      <c r="G5832" t="inlineStr"/>
-      <c r="H5832" t="inlineStr"/>
-      <c r="I5832" t="inlineStr"/>
     </row>
     <row r="5833">
       <c r="A5833" t="inlineStr">
@@ -70000,13 +69660,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5833" t="inlineStr"/>
-      <c r="D5833" t="inlineStr"/>
-      <c r="E5833" t="inlineStr"/>
-      <c r="F5833" t="inlineStr"/>
-      <c r="G5833" t="inlineStr"/>
-      <c r="H5833" t="inlineStr"/>
-      <c r="I5833" t="inlineStr"/>
     </row>
     <row r="5834">
       <c r="A5834" t="inlineStr">
@@ -70019,13 +69672,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5834" t="inlineStr"/>
-      <c r="D5834" t="inlineStr"/>
-      <c r="E5834" t="inlineStr"/>
-      <c r="F5834" t="inlineStr"/>
-      <c r="G5834" t="inlineStr"/>
-      <c r="H5834" t="inlineStr"/>
-      <c r="I5834" t="inlineStr"/>
     </row>
     <row r="5835">
       <c r="A5835" t="inlineStr">
@@ -70038,13 +69684,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5835" t="inlineStr"/>
-      <c r="D5835" t="inlineStr"/>
-      <c r="E5835" t="inlineStr"/>
-      <c r="F5835" t="inlineStr"/>
-      <c r="G5835" t="inlineStr"/>
-      <c r="H5835" t="inlineStr"/>
-      <c r="I5835" t="inlineStr"/>
     </row>
     <row r="5836">
       <c r="A5836" t="inlineStr">
@@ -70057,13 +69696,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5836" t="inlineStr"/>
-      <c r="D5836" t="inlineStr"/>
-      <c r="E5836" t="inlineStr"/>
-      <c r="F5836" t="inlineStr"/>
-      <c r="G5836" t="inlineStr"/>
-      <c r="H5836" t="inlineStr"/>
-      <c r="I5836" t="inlineStr"/>
     </row>
     <row r="5837">
       <c r="A5837" t="inlineStr">
@@ -70076,13 +69708,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5837" t="inlineStr"/>
-      <c r="D5837" t="inlineStr"/>
-      <c r="E5837" t="inlineStr"/>
-      <c r="F5837" t="inlineStr"/>
-      <c r="G5837" t="inlineStr"/>
-      <c r="H5837" t="inlineStr"/>
-      <c r="I5837" t="inlineStr"/>
     </row>
     <row r="5838"/>
     <row r="5839">
@@ -70096,13 +69721,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5839" t="inlineStr"/>
-      <c r="D5839" t="inlineStr"/>
-      <c r="E5839" t="inlineStr"/>
-      <c r="F5839" t="inlineStr"/>
-      <c r="G5839" t="inlineStr"/>
-      <c r="H5839" t="inlineStr"/>
-      <c r="I5839" t="inlineStr"/>
     </row>
     <row r="5840">
       <c r="A5840" t="inlineStr">
@@ -70115,13 +69733,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5840" t="inlineStr"/>
-      <c r="D5840" t="inlineStr"/>
-      <c r="E5840" t="inlineStr"/>
-      <c r="F5840" t="inlineStr"/>
-      <c r="G5840" t="inlineStr"/>
-      <c r="H5840" t="inlineStr"/>
-      <c r="I5840" t="inlineStr"/>
     </row>
     <row r="5841">
       <c r="A5841" t="inlineStr">
@@ -70134,13 +69745,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5841" t="inlineStr"/>
-      <c r="D5841" t="inlineStr"/>
-      <c r="E5841" t="inlineStr"/>
-      <c r="F5841" t="inlineStr"/>
-      <c r="G5841" t="inlineStr"/>
-      <c r="H5841" t="inlineStr"/>
-      <c r="I5841" t="inlineStr"/>
     </row>
     <row r="5842">
       <c r="A5842" t="inlineStr">
@@ -70153,13 +69757,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5842" t="inlineStr"/>
-      <c r="D5842" t="inlineStr"/>
-      <c r="E5842" t="inlineStr"/>
-      <c r="F5842" t="inlineStr"/>
-      <c r="G5842" t="inlineStr"/>
-      <c r="H5842" t="inlineStr"/>
-      <c r="I5842" t="inlineStr"/>
     </row>
     <row r="5843">
       <c r="A5843" t="inlineStr">
@@ -70172,13 +69769,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5843" t="inlineStr"/>
-      <c r="D5843" t="inlineStr"/>
-      <c r="E5843" t="inlineStr"/>
-      <c r="F5843" t="inlineStr"/>
-      <c r="G5843" t="inlineStr"/>
-      <c r="H5843" t="inlineStr"/>
-      <c r="I5843" t="inlineStr"/>
     </row>
     <row r="5844">
       <c r="A5844" t="inlineStr">
@@ -70191,13 +69781,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5844" t="inlineStr"/>
-      <c r="D5844" t="inlineStr"/>
-      <c r="E5844" t="inlineStr"/>
-      <c r="F5844" t="inlineStr"/>
-      <c r="G5844" t="inlineStr"/>
-      <c r="H5844" t="inlineStr"/>
-      <c r="I5844" t="inlineStr"/>
     </row>
     <row r="5845">
       <c r="A5845" t="inlineStr">
@@ -70210,13 +69793,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5845" t="inlineStr"/>
-      <c r="D5845" t="inlineStr"/>
-      <c r="E5845" t="inlineStr"/>
-      <c r="F5845" t="inlineStr"/>
-      <c r="G5845" t="inlineStr"/>
-      <c r="H5845" t="inlineStr"/>
-      <c r="I5845" t="inlineStr"/>
     </row>
     <row r="5846">
       <c r="A5846" t="inlineStr">
@@ -70229,13 +69805,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5846" t="inlineStr"/>
-      <c r="D5846" t="inlineStr"/>
-      <c r="E5846" t="inlineStr"/>
-      <c r="F5846" t="inlineStr"/>
-      <c r="G5846" t="inlineStr"/>
-      <c r="H5846" t="inlineStr"/>
-      <c r="I5846" t="inlineStr"/>
     </row>
     <row r="5847">
       <c r="A5847" t="inlineStr">
@@ -70248,13 +69817,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5847" t="inlineStr"/>
-      <c r="D5847" t="inlineStr"/>
-      <c r="E5847" t="inlineStr"/>
-      <c r="F5847" t="inlineStr"/>
-      <c r="G5847" t="inlineStr"/>
-      <c r="H5847" t="inlineStr"/>
-      <c r="I5847" t="inlineStr"/>
     </row>
     <row r="5848">
       <c r="A5848" t="inlineStr">
@@ -70267,13 +69829,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5848" t="inlineStr"/>
-      <c r="D5848" t="inlineStr"/>
-      <c r="E5848" t="inlineStr"/>
-      <c r="F5848" t="inlineStr"/>
-      <c r="G5848" t="inlineStr"/>
-      <c r="H5848" t="inlineStr"/>
-      <c r="I5848" t="inlineStr"/>
     </row>
     <row r="5849">
       <c r="A5849" t="inlineStr">
@@ -70286,13 +69841,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5849" t="inlineStr"/>
-      <c r="D5849" t="inlineStr"/>
-      <c r="E5849" t="inlineStr"/>
-      <c r="F5849" t="inlineStr"/>
-      <c r="G5849" t="inlineStr"/>
-      <c r="H5849" t="inlineStr"/>
-      <c r="I5849" t="inlineStr"/>
     </row>
     <row r="5850">
       <c r="A5850" t="inlineStr">
@@ -70305,13 +69853,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5850" t="inlineStr"/>
-      <c r="D5850" t="inlineStr"/>
-      <c r="E5850" t="inlineStr"/>
-      <c r="F5850" t="inlineStr"/>
-      <c r="G5850" t="inlineStr"/>
-      <c r="H5850" t="inlineStr"/>
-      <c r="I5850" t="inlineStr"/>
     </row>
     <row r="5851">
       <c r="A5851" t="inlineStr">
@@ -70324,13 +69865,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5851" t="inlineStr"/>
-      <c r="D5851" t="inlineStr"/>
-      <c r="E5851" t="inlineStr"/>
-      <c r="F5851" t="inlineStr"/>
-      <c r="G5851" t="inlineStr"/>
-      <c r="H5851" t="inlineStr"/>
-      <c r="I5851" t="inlineStr"/>
     </row>
     <row r="5852">
       <c r="A5852" t="inlineStr">
@@ -70343,13 +69877,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5852" t="inlineStr"/>
-      <c r="D5852" t="inlineStr"/>
-      <c r="E5852" t="inlineStr"/>
-      <c r="F5852" t="inlineStr"/>
-      <c r="G5852" t="inlineStr"/>
-      <c r="H5852" t="inlineStr"/>
-      <c r="I5852" t="inlineStr"/>
     </row>
     <row r="5853">
       <c r="A5853" t="inlineStr">
@@ -70362,13 +69889,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5853" t="inlineStr"/>
-      <c r="D5853" t="inlineStr"/>
-      <c r="E5853" t="inlineStr"/>
-      <c r="F5853" t="inlineStr"/>
-      <c r="G5853" t="inlineStr"/>
-      <c r="H5853" t="inlineStr"/>
-      <c r="I5853" t="inlineStr"/>
     </row>
     <row r="5854">
       <c r="A5854" t="inlineStr">
@@ -70381,13 +69901,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5854" t="inlineStr"/>
-      <c r="D5854" t="inlineStr"/>
-      <c r="E5854" t="inlineStr"/>
-      <c r="F5854" t="inlineStr"/>
-      <c r="G5854" t="inlineStr"/>
-      <c r="H5854" t="inlineStr"/>
-      <c r="I5854" t="inlineStr"/>
     </row>
     <row r="5855">
       <c r="A5855" t="inlineStr">
@@ -70400,13 +69913,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5855" t="inlineStr"/>
-      <c r="D5855" t="inlineStr"/>
-      <c r="E5855" t="inlineStr"/>
-      <c r="F5855" t="inlineStr"/>
-      <c r="G5855" t="inlineStr"/>
-      <c r="H5855" t="inlineStr"/>
-      <c r="I5855" t="inlineStr"/>
     </row>
     <row r="5856">
       <c r="A5856" t="inlineStr">
@@ -70419,13 +69925,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5856" t="inlineStr"/>
-      <c r="D5856" t="inlineStr"/>
-      <c r="E5856" t="inlineStr"/>
-      <c r="F5856" t="inlineStr"/>
-      <c r="G5856" t="inlineStr"/>
-      <c r="H5856" t="inlineStr"/>
-      <c r="I5856" t="inlineStr"/>
     </row>
     <row r="5857">
       <c r="A5857" t="inlineStr">
@@ -70438,13 +69937,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5857" t="inlineStr"/>
-      <c r="D5857" t="inlineStr"/>
-      <c r="E5857" t="inlineStr"/>
-      <c r="F5857" t="inlineStr"/>
-      <c r="G5857" t="inlineStr"/>
-      <c r="H5857" t="inlineStr"/>
-      <c r="I5857" t="inlineStr"/>
     </row>
     <row r="5858"/>
     <row r="5859">
@@ -70458,13 +69950,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5859" t="inlineStr"/>
-      <c r="D5859" t="inlineStr"/>
-      <c r="E5859" t="inlineStr"/>
-      <c r="F5859" t="inlineStr"/>
-      <c r="G5859" t="inlineStr"/>
-      <c r="H5859" t="inlineStr"/>
-      <c r="I5859" t="inlineStr"/>
     </row>
     <row r="5860">
       <c r="A5860" t="inlineStr">
@@ -70477,13 +69962,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5860" t="inlineStr"/>
-      <c r="D5860" t="inlineStr"/>
-      <c r="E5860" t="inlineStr"/>
-      <c r="F5860" t="inlineStr"/>
-      <c r="G5860" t="inlineStr"/>
-      <c r="H5860" t="inlineStr"/>
-      <c r="I5860" t="inlineStr"/>
     </row>
     <row r="5861">
       <c r="A5861" t="inlineStr">
@@ -70496,13 +69974,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5861" t="inlineStr"/>
-      <c r="D5861" t="inlineStr"/>
-      <c r="E5861" t="inlineStr"/>
-      <c r="F5861" t="inlineStr"/>
-      <c r="G5861" t="inlineStr"/>
-      <c r="H5861" t="inlineStr"/>
-      <c r="I5861" t="inlineStr"/>
     </row>
     <row r="5862">
       <c r="A5862" t="inlineStr">
@@ -70515,13 +69986,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5862" t="inlineStr"/>
-      <c r="D5862" t="inlineStr"/>
-      <c r="E5862" t="inlineStr"/>
-      <c r="F5862" t="inlineStr"/>
-      <c r="G5862" t="inlineStr"/>
-      <c r="H5862" t="inlineStr"/>
-      <c r="I5862" t="inlineStr"/>
     </row>
     <row r="5863">
       <c r="A5863" t="inlineStr">
@@ -70534,13 +69998,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5863" t="inlineStr"/>
-      <c r="D5863" t="inlineStr"/>
-      <c r="E5863" t="inlineStr"/>
-      <c r="F5863" t="inlineStr"/>
-      <c r="G5863" t="inlineStr"/>
-      <c r="H5863" t="inlineStr"/>
-      <c r="I5863" t="inlineStr"/>
     </row>
     <row r="5864">
       <c r="A5864" t="inlineStr">
@@ -70553,13 +70010,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5864" t="inlineStr"/>
-      <c r="D5864" t="inlineStr"/>
-      <c r="E5864" t="inlineStr"/>
-      <c r="F5864" t="inlineStr"/>
-      <c r="G5864" t="inlineStr"/>
-      <c r="H5864" t="inlineStr"/>
-      <c r="I5864" t="inlineStr"/>
     </row>
     <row r="5865">
       <c r="A5865" t="inlineStr">
@@ -70572,13 +70022,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5865" t="inlineStr"/>
-      <c r="D5865" t="inlineStr"/>
-      <c r="E5865" t="inlineStr"/>
-      <c r="F5865" t="inlineStr"/>
-      <c r="G5865" t="inlineStr"/>
-      <c r="H5865" t="inlineStr"/>
-      <c r="I5865" t="inlineStr"/>
     </row>
     <row r="5866">
       <c r="A5866" t="inlineStr">
@@ -70591,13 +70034,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5866" t="inlineStr"/>
-      <c r="D5866" t="inlineStr"/>
-      <c r="E5866" t="inlineStr"/>
-      <c r="F5866" t="inlineStr"/>
-      <c r="G5866" t="inlineStr"/>
-      <c r="H5866" t="inlineStr"/>
-      <c r="I5866" t="inlineStr"/>
     </row>
     <row r="5867">
       <c r="A5867" t="inlineStr">
@@ -70610,13 +70046,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5867" t="inlineStr"/>
-      <c r="D5867" t="inlineStr"/>
-      <c r="E5867" t="inlineStr"/>
-      <c r="F5867" t="inlineStr"/>
-      <c r="G5867" t="inlineStr"/>
-      <c r="H5867" t="inlineStr"/>
-      <c r="I5867" t="inlineStr"/>
     </row>
     <row r="5868">
       <c r="A5868" t="inlineStr">
@@ -70629,13 +70058,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5868" t="inlineStr"/>
-      <c r="D5868" t="inlineStr"/>
-      <c r="E5868" t="inlineStr"/>
-      <c r="F5868" t="inlineStr"/>
-      <c r="G5868" t="inlineStr"/>
-      <c r="H5868" t="inlineStr"/>
-      <c r="I5868" t="inlineStr"/>
     </row>
     <row r="5869">
       <c r="A5869" t="inlineStr">
@@ -70648,13 +70070,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5869" t="inlineStr"/>
-      <c r="D5869" t="inlineStr"/>
-      <c r="E5869" t="inlineStr"/>
-      <c r="F5869" t="inlineStr"/>
-      <c r="G5869" t="inlineStr"/>
-      <c r="H5869" t="inlineStr"/>
-      <c r="I5869" t="inlineStr"/>
     </row>
     <row r="5870">
       <c r="A5870" t="inlineStr">
@@ -70667,13 +70082,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5870" t="inlineStr"/>
-      <c r="D5870" t="inlineStr"/>
-      <c r="E5870" t="inlineStr"/>
-      <c r="F5870" t="inlineStr"/>
-      <c r="G5870" t="inlineStr"/>
-      <c r="H5870" t="inlineStr"/>
-      <c r="I5870" t="inlineStr"/>
     </row>
     <row r="5871">
       <c r="A5871" t="inlineStr">
@@ -70686,13 +70094,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5871" t="inlineStr"/>
-      <c r="D5871" t="inlineStr"/>
-      <c r="E5871" t="inlineStr"/>
-      <c r="F5871" t="inlineStr"/>
-      <c r="G5871" t="inlineStr"/>
-      <c r="H5871" t="inlineStr"/>
-      <c r="I5871" t="inlineStr"/>
     </row>
     <row r="5872">
       <c r="A5872" t="inlineStr">
@@ -70705,13 +70106,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5872" t="inlineStr"/>
-      <c r="D5872" t="inlineStr"/>
-      <c r="E5872" t="inlineStr"/>
-      <c r="F5872" t="inlineStr"/>
-      <c r="G5872" t="inlineStr"/>
-      <c r="H5872" t="inlineStr"/>
-      <c r="I5872" t="inlineStr"/>
     </row>
     <row r="5873">
       <c r="A5873" t="inlineStr">
@@ -70724,13 +70118,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5873" t="inlineStr"/>
-      <c r="D5873" t="inlineStr"/>
-      <c r="E5873" t="inlineStr"/>
-      <c r="F5873" t="inlineStr"/>
-      <c r="G5873" t="inlineStr"/>
-      <c r="H5873" t="inlineStr"/>
-      <c r="I5873" t="inlineStr"/>
     </row>
     <row r="5874">
       <c r="A5874" t="inlineStr">
@@ -70743,13 +70130,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5874" t="inlineStr"/>
-      <c r="D5874" t="inlineStr"/>
-      <c r="E5874" t="inlineStr"/>
-      <c r="F5874" t="inlineStr"/>
-      <c r="G5874" t="inlineStr"/>
-      <c r="H5874" t="inlineStr"/>
-      <c r="I5874" t="inlineStr"/>
     </row>
     <row r="5875">
       <c r="A5875" t="inlineStr">
@@ -70762,13 +70142,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5875" t="inlineStr"/>
-      <c r="D5875" t="inlineStr"/>
-      <c r="E5875" t="inlineStr"/>
-      <c r="F5875" t="inlineStr"/>
-      <c r="G5875" t="inlineStr"/>
-      <c r="H5875" t="inlineStr"/>
-      <c r="I5875" t="inlineStr"/>
     </row>
     <row r="5876">
       <c r="A5876" t="inlineStr">
@@ -70781,13 +70154,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5876" t="inlineStr"/>
-      <c r="D5876" t="inlineStr"/>
-      <c r="E5876" t="inlineStr"/>
-      <c r="F5876" t="inlineStr"/>
-      <c r="G5876" t="inlineStr"/>
-      <c r="H5876" t="inlineStr"/>
-      <c r="I5876" t="inlineStr"/>
     </row>
     <row r="5877">
       <c r="A5877" t="inlineStr">
@@ -70800,13 +70166,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5877" t="inlineStr"/>
-      <c r="D5877" t="inlineStr"/>
-      <c r="E5877" t="inlineStr"/>
-      <c r="F5877" t="inlineStr"/>
-      <c r="G5877" t="inlineStr"/>
-      <c r="H5877" t="inlineStr"/>
-      <c r="I5877" t="inlineStr"/>
     </row>
     <row r="5878"/>
     <row r="5879">
@@ -70820,13 +70179,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5879" t="inlineStr"/>
-      <c r="D5879" t="inlineStr"/>
-      <c r="E5879" t="inlineStr"/>
-      <c r="F5879" t="inlineStr"/>
-      <c r="G5879" t="inlineStr"/>
-      <c r="H5879" t="inlineStr"/>
-      <c r="I5879" t="inlineStr"/>
     </row>
     <row r="5880">
       <c r="A5880" t="inlineStr">
@@ -70839,13 +70191,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5880" t="inlineStr"/>
-      <c r="D5880" t="inlineStr"/>
-      <c r="E5880" t="inlineStr"/>
-      <c r="F5880" t="inlineStr"/>
-      <c r="G5880" t="inlineStr"/>
-      <c r="H5880" t="inlineStr"/>
-      <c r="I5880" t="inlineStr"/>
     </row>
     <row r="5881">
       <c r="A5881" t="inlineStr">
@@ -70858,13 +70203,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5881" t="inlineStr"/>
-      <c r="D5881" t="inlineStr"/>
-      <c r="E5881" t="inlineStr"/>
-      <c r="F5881" t="inlineStr"/>
-      <c r="G5881" t="inlineStr"/>
-      <c r="H5881" t="inlineStr"/>
-      <c r="I5881" t="inlineStr"/>
     </row>
     <row r="5882">
       <c r="A5882" t="inlineStr">
@@ -70877,13 +70215,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5882" t="inlineStr"/>
-      <c r="D5882" t="inlineStr"/>
-      <c r="E5882" t="inlineStr"/>
-      <c r="F5882" t="inlineStr"/>
-      <c r="G5882" t="inlineStr"/>
-      <c r="H5882" t="inlineStr"/>
-      <c r="I5882" t="inlineStr"/>
     </row>
     <row r="5883">
       <c r="A5883" t="inlineStr">
@@ -70896,13 +70227,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5883" t="inlineStr"/>
-      <c r="D5883" t="inlineStr"/>
-      <c r="E5883" t="inlineStr"/>
-      <c r="F5883" t="inlineStr"/>
-      <c r="G5883" t="inlineStr"/>
-      <c r="H5883" t="inlineStr"/>
-      <c r="I5883" t="inlineStr"/>
     </row>
     <row r="5884">
       <c r="A5884" t="inlineStr">
@@ -70915,13 +70239,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5884" t="inlineStr"/>
-      <c r="D5884" t="inlineStr"/>
-      <c r="E5884" t="inlineStr"/>
-      <c r="F5884" t="inlineStr"/>
-      <c r="G5884" t="inlineStr"/>
-      <c r="H5884" t="inlineStr"/>
-      <c r="I5884" t="inlineStr"/>
     </row>
     <row r="5885">
       <c r="A5885" t="inlineStr">
@@ -70934,13 +70251,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5885" t="inlineStr"/>
-      <c r="D5885" t="inlineStr"/>
-      <c r="E5885" t="inlineStr"/>
-      <c r="F5885" t="inlineStr"/>
-      <c r="G5885" t="inlineStr"/>
-      <c r="H5885" t="inlineStr"/>
-      <c r="I5885" t="inlineStr"/>
     </row>
     <row r="5886">
       <c r="A5886" t="inlineStr">
@@ -70953,13 +70263,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5886" t="inlineStr"/>
-      <c r="D5886" t="inlineStr"/>
-      <c r="E5886" t="inlineStr"/>
-      <c r="F5886" t="inlineStr"/>
-      <c r="G5886" t="inlineStr"/>
-      <c r="H5886" t="inlineStr"/>
-      <c r="I5886" t="inlineStr"/>
     </row>
     <row r="5887">
       <c r="A5887" t="inlineStr">
@@ -70972,13 +70275,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5887" t="inlineStr"/>
-      <c r="D5887" t="inlineStr"/>
-      <c r="E5887" t="inlineStr"/>
-      <c r="F5887" t="inlineStr"/>
-      <c r="G5887" t="inlineStr"/>
-      <c r="H5887" t="inlineStr"/>
-      <c r="I5887" t="inlineStr"/>
     </row>
     <row r="5888">
       <c r="A5888" t="inlineStr">
@@ -70991,13 +70287,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5888" t="inlineStr"/>
-      <c r="D5888" t="inlineStr"/>
-      <c r="E5888" t="inlineStr"/>
-      <c r="F5888" t="inlineStr"/>
-      <c r="G5888" t="inlineStr"/>
-      <c r="H5888" t="inlineStr"/>
-      <c r="I5888" t="inlineStr"/>
     </row>
     <row r="5889">
       <c r="A5889" t="inlineStr">
@@ -71010,13 +70299,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5889" t="inlineStr"/>
-      <c r="D5889" t="inlineStr"/>
-      <c r="E5889" t="inlineStr"/>
-      <c r="F5889" t="inlineStr"/>
-      <c r="G5889" t="inlineStr"/>
-      <c r="H5889" t="inlineStr"/>
-      <c r="I5889" t="inlineStr"/>
     </row>
     <row r="5890">
       <c r="A5890" t="inlineStr">
@@ -71029,13 +70311,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5890" t="inlineStr"/>
-      <c r="D5890" t="inlineStr"/>
-      <c r="E5890" t="inlineStr"/>
-      <c r="F5890" t="inlineStr"/>
-      <c r="G5890" t="inlineStr"/>
-      <c r="H5890" t="inlineStr"/>
-      <c r="I5890" t="inlineStr"/>
     </row>
     <row r="5891">
       <c r="A5891" t="inlineStr">
@@ -71048,13 +70323,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5891" t="inlineStr"/>
-      <c r="D5891" t="inlineStr"/>
-      <c r="E5891" t="inlineStr"/>
-      <c r="F5891" t="inlineStr"/>
-      <c r="G5891" t="inlineStr"/>
-      <c r="H5891" t="inlineStr"/>
-      <c r="I5891" t="inlineStr"/>
     </row>
     <row r="5892">
       <c r="A5892" t="inlineStr">
@@ -71067,13 +70335,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5892" t="inlineStr"/>
-      <c r="D5892" t="inlineStr"/>
-      <c r="E5892" t="inlineStr"/>
-      <c r="F5892" t="inlineStr"/>
-      <c r="G5892" t="inlineStr"/>
-      <c r="H5892" t="inlineStr"/>
-      <c r="I5892" t="inlineStr"/>
     </row>
     <row r="5893">
       <c r="A5893" t="inlineStr">
@@ -71086,13 +70347,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5893" t="inlineStr"/>
-      <c r="D5893" t="inlineStr"/>
-      <c r="E5893" t="inlineStr"/>
-      <c r="F5893" t="inlineStr"/>
-      <c r="G5893" t="inlineStr"/>
-      <c r="H5893" t="inlineStr"/>
-      <c r="I5893" t="inlineStr"/>
     </row>
     <row r="5894">
       <c r="A5894" t="inlineStr">
@@ -71105,13 +70359,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5894" t="inlineStr"/>
-      <c r="D5894" t="inlineStr"/>
-      <c r="E5894" t="inlineStr"/>
-      <c r="F5894" t="inlineStr"/>
-      <c r="G5894" t="inlineStr"/>
-      <c r="H5894" t="inlineStr"/>
-      <c r="I5894" t="inlineStr"/>
     </row>
     <row r="5895">
       <c r="A5895" t="inlineStr">
@@ -71124,13 +70371,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5895" t="inlineStr"/>
-      <c r="D5895" t="inlineStr"/>
-      <c r="E5895" t="inlineStr"/>
-      <c r="F5895" t="inlineStr"/>
-      <c r="G5895" t="inlineStr"/>
-      <c r="H5895" t="inlineStr"/>
-      <c r="I5895" t="inlineStr"/>
     </row>
     <row r="5896">
       <c r="A5896" t="inlineStr">
@@ -71143,13 +70383,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5896" t="inlineStr"/>
-      <c r="D5896" t="inlineStr"/>
-      <c r="E5896" t="inlineStr"/>
-      <c r="F5896" t="inlineStr"/>
-      <c r="G5896" t="inlineStr"/>
-      <c r="H5896" t="inlineStr"/>
-      <c r="I5896" t="inlineStr"/>
     </row>
     <row r="5897">
       <c r="A5897" t="inlineStr">
@@ -71162,13 +70395,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5897" t="inlineStr"/>
-      <c r="D5897" t="inlineStr"/>
-      <c r="E5897" t="inlineStr"/>
-      <c r="F5897" t="inlineStr"/>
-      <c r="G5897" t="inlineStr"/>
-      <c r="H5897" t="inlineStr"/>
-      <c r="I5897" t="inlineStr"/>
     </row>
     <row r="5898"/>
     <row r="5899">
@@ -71182,13 +70408,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C5899" t="inlineStr"/>
-      <c r="D5899" t="inlineStr"/>
-      <c r="E5899" t="inlineStr"/>
-      <c r="F5899" t="inlineStr"/>
-      <c r="G5899" t="inlineStr"/>
-      <c r="H5899" t="inlineStr"/>
-      <c r="I5899" t="inlineStr"/>
     </row>
     <row r="5900">
       <c r="A5900" t="inlineStr">
@@ -71201,13 +70420,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C5900" t="inlineStr"/>
-      <c r="D5900" t="inlineStr"/>
-      <c r="E5900" t="inlineStr"/>
-      <c r="F5900" t="inlineStr"/>
-      <c r="G5900" t="inlineStr"/>
-      <c r="H5900" t="inlineStr"/>
-      <c r="I5900" t="inlineStr"/>
     </row>
     <row r="5901">
       <c r="A5901" t="inlineStr">
@@ -71220,13 +70432,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C5901" t="inlineStr"/>
-      <c r="D5901" t="inlineStr"/>
-      <c r="E5901" t="inlineStr"/>
-      <c r="F5901" t="inlineStr"/>
-      <c r="G5901" t="inlineStr"/>
-      <c r="H5901" t="inlineStr"/>
-      <c r="I5901" t="inlineStr"/>
     </row>
     <row r="5902">
       <c r="A5902" t="inlineStr">
@@ -71239,13 +70444,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C5902" t="inlineStr"/>
-      <c r="D5902" t="inlineStr"/>
-      <c r="E5902" t="inlineStr"/>
-      <c r="F5902" t="inlineStr"/>
-      <c r="G5902" t="inlineStr"/>
-      <c r="H5902" t="inlineStr"/>
-      <c r="I5902" t="inlineStr"/>
     </row>
     <row r="5903">
       <c r="A5903" t="inlineStr">
@@ -71258,13 +70456,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C5903" t="inlineStr"/>
-      <c r="D5903" t="inlineStr"/>
-      <c r="E5903" t="inlineStr"/>
-      <c r="F5903" t="inlineStr"/>
-      <c r="G5903" t="inlineStr"/>
-      <c r="H5903" t="inlineStr"/>
-      <c r="I5903" t="inlineStr"/>
     </row>
     <row r="5904">
       <c r="A5904" t="inlineStr">
@@ -71277,13 +70468,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C5904" t="inlineStr"/>
-      <c r="D5904" t="inlineStr"/>
-      <c r="E5904" t="inlineStr"/>
-      <c r="F5904" t="inlineStr"/>
-      <c r="G5904" t="inlineStr"/>
-      <c r="H5904" t="inlineStr"/>
-      <c r="I5904" t="inlineStr"/>
     </row>
     <row r="5905">
       <c r="A5905" t="inlineStr">
@@ -71296,13 +70480,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C5905" t="inlineStr"/>
-      <c r="D5905" t="inlineStr"/>
-      <c r="E5905" t="inlineStr"/>
-      <c r="F5905" t="inlineStr"/>
-      <c r="G5905" t="inlineStr"/>
-      <c r="H5905" t="inlineStr"/>
-      <c r="I5905" t="inlineStr"/>
     </row>
     <row r="5906">
       <c r="A5906" t="inlineStr">
@@ -71315,13 +70492,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C5906" t="inlineStr"/>
-      <c r="D5906" t="inlineStr"/>
-      <c r="E5906" t="inlineStr"/>
-      <c r="F5906" t="inlineStr"/>
-      <c r="G5906" t="inlineStr"/>
-      <c r="H5906" t="inlineStr"/>
-      <c r="I5906" t="inlineStr"/>
     </row>
     <row r="5907">
       <c r="A5907" t="inlineStr">
@@ -71334,13 +70504,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C5907" t="inlineStr"/>
-      <c r="D5907" t="inlineStr"/>
-      <c r="E5907" t="inlineStr"/>
-      <c r="F5907" t="inlineStr"/>
-      <c r="G5907" t="inlineStr"/>
-      <c r="H5907" t="inlineStr"/>
-      <c r="I5907" t="inlineStr"/>
     </row>
     <row r="5908">
       <c r="A5908" t="inlineStr">
@@ -71353,13 +70516,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C5908" t="inlineStr"/>
-      <c r="D5908" t="inlineStr"/>
-      <c r="E5908" t="inlineStr"/>
-      <c r="F5908" t="inlineStr"/>
-      <c r="G5908" t="inlineStr"/>
-      <c r="H5908" t="inlineStr"/>
-      <c r="I5908" t="inlineStr"/>
     </row>
     <row r="5909">
       <c r="A5909" t="inlineStr">
@@ -71372,13 +70528,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C5909" t="inlineStr"/>
-      <c r="D5909" t="inlineStr"/>
-      <c r="E5909" t="inlineStr"/>
-      <c r="F5909" t="inlineStr"/>
-      <c r="G5909" t="inlineStr"/>
-      <c r="H5909" t="inlineStr"/>
-      <c r="I5909" t="inlineStr"/>
     </row>
     <row r="5910">
       <c r="A5910" t="inlineStr">
@@ -71391,13 +70540,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C5910" t="inlineStr"/>
-      <c r="D5910" t="inlineStr"/>
-      <c r="E5910" t="inlineStr"/>
-      <c r="F5910" t="inlineStr"/>
-      <c r="G5910" t="inlineStr"/>
-      <c r="H5910" t="inlineStr"/>
-      <c r="I5910" t="inlineStr"/>
     </row>
     <row r="5911">
       <c r="A5911" t="inlineStr">
@@ -71410,13 +70552,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C5911" t="inlineStr"/>
-      <c r="D5911" t="inlineStr"/>
-      <c r="E5911" t="inlineStr"/>
-      <c r="F5911" t="inlineStr"/>
-      <c r="G5911" t="inlineStr"/>
-      <c r="H5911" t="inlineStr"/>
-      <c r="I5911" t="inlineStr"/>
     </row>
     <row r="5912">
       <c r="A5912" t="inlineStr">
@@ -71429,13 +70564,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C5912" t="inlineStr"/>
-      <c r="D5912" t="inlineStr"/>
-      <c r="E5912" t="inlineStr"/>
-      <c r="F5912" t="inlineStr"/>
-      <c r="G5912" t="inlineStr"/>
-      <c r="H5912" t="inlineStr"/>
-      <c r="I5912" t="inlineStr"/>
     </row>
     <row r="5913">
       <c r="A5913" t="inlineStr">
@@ -71448,13 +70576,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C5913" t="inlineStr"/>
-      <c r="D5913" t="inlineStr"/>
-      <c r="E5913" t="inlineStr"/>
-      <c r="F5913" t="inlineStr"/>
-      <c r="G5913" t="inlineStr"/>
-      <c r="H5913" t="inlineStr"/>
-      <c r="I5913" t="inlineStr"/>
     </row>
     <row r="5914">
       <c r="A5914" t="inlineStr">
@@ -71467,13 +70588,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C5914" t="inlineStr"/>
-      <c r="D5914" t="inlineStr"/>
-      <c r="E5914" t="inlineStr"/>
-      <c r="F5914" t="inlineStr"/>
-      <c r="G5914" t="inlineStr"/>
-      <c r="H5914" t="inlineStr"/>
-      <c r="I5914" t="inlineStr"/>
     </row>
     <row r="5915">
       <c r="A5915" t="inlineStr">
@@ -71486,13 +70600,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C5915" t="inlineStr"/>
-      <c r="D5915" t="inlineStr"/>
-      <c r="E5915" t="inlineStr"/>
-      <c r="F5915" t="inlineStr"/>
-      <c r="G5915" t="inlineStr"/>
-      <c r="H5915" t="inlineStr"/>
-      <c r="I5915" t="inlineStr"/>
     </row>
     <row r="5916">
       <c r="A5916" t="inlineStr">
@@ -71505,13 +70612,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C5916" t="inlineStr"/>
-      <c r="D5916" t="inlineStr"/>
-      <c r="E5916" t="inlineStr"/>
-      <c r="F5916" t="inlineStr"/>
-      <c r="G5916" t="inlineStr"/>
-      <c r="H5916" t="inlineStr"/>
-      <c r="I5916" t="inlineStr"/>
     </row>
     <row r="5917">
       <c r="A5917" t="inlineStr">
@@ -71524,15 +70624,1456 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5917" t="inlineStr"/>
-      <c r="D5917" t="inlineStr"/>
-      <c r="E5917" t="inlineStr"/>
-      <c r="F5917" t="inlineStr"/>
-      <c r="G5917" t="inlineStr"/>
-      <c r="H5917" t="inlineStr"/>
-      <c r="I5917" t="inlineStr"/>
     </row>
     <row r="5918"/>
+    <row r="5919">
+      <c r="A5919" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5919" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5919" t="inlineStr"/>
+      <c r="D5919" t="inlineStr"/>
+      <c r="E5919" t="inlineStr"/>
+      <c r="F5919" t="inlineStr"/>
+      <c r="G5919" t="inlineStr"/>
+      <c r="H5919" t="inlineStr"/>
+      <c r="I5919" t="inlineStr"/>
+    </row>
+    <row r="5920">
+      <c r="A5920" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5920" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5920" t="inlineStr"/>
+      <c r="D5920" t="inlineStr"/>
+      <c r="E5920" t="inlineStr"/>
+      <c r="F5920" t="inlineStr"/>
+      <c r="G5920" t="inlineStr"/>
+      <c r="H5920" t="inlineStr"/>
+      <c r="I5920" t="inlineStr"/>
+    </row>
+    <row r="5921">
+      <c r="A5921" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5921" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5921" t="inlineStr"/>
+      <c r="D5921" t="inlineStr"/>
+      <c r="E5921" t="inlineStr"/>
+      <c r="F5921" t="inlineStr"/>
+      <c r="G5921" t="inlineStr"/>
+      <c r="H5921" t="inlineStr"/>
+      <c r="I5921" t="inlineStr"/>
+    </row>
+    <row r="5922">
+      <c r="A5922" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5922" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5922" t="inlineStr"/>
+      <c r="D5922" t="inlineStr"/>
+      <c r="E5922" t="inlineStr"/>
+      <c r="F5922" t="inlineStr"/>
+      <c r="G5922" t="inlineStr"/>
+      <c r="H5922" t="inlineStr"/>
+      <c r="I5922" t="inlineStr"/>
+    </row>
+    <row r="5923">
+      <c r="A5923" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5923" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5923" t="inlineStr"/>
+      <c r="D5923" t="inlineStr"/>
+      <c r="E5923" t="inlineStr"/>
+      <c r="F5923" t="inlineStr"/>
+      <c r="G5923" t="inlineStr"/>
+      <c r="H5923" t="inlineStr"/>
+      <c r="I5923" t="inlineStr"/>
+    </row>
+    <row r="5924">
+      <c r="A5924" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5924" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5924" t="inlineStr"/>
+      <c r="D5924" t="inlineStr"/>
+      <c r="E5924" t="inlineStr"/>
+      <c r="F5924" t="inlineStr"/>
+      <c r="G5924" t="inlineStr"/>
+      <c r="H5924" t="inlineStr"/>
+      <c r="I5924" t="inlineStr"/>
+    </row>
+    <row r="5925">
+      <c r="A5925" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5925" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5925" t="inlineStr"/>
+      <c r="D5925" t="inlineStr"/>
+      <c r="E5925" t="inlineStr"/>
+      <c r="F5925" t="inlineStr"/>
+      <c r="G5925" t="inlineStr"/>
+      <c r="H5925" t="inlineStr"/>
+      <c r="I5925" t="inlineStr"/>
+    </row>
+    <row r="5926">
+      <c r="A5926" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5926" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5926" t="inlineStr"/>
+      <c r="D5926" t="inlineStr"/>
+      <c r="E5926" t="inlineStr"/>
+      <c r="F5926" t="inlineStr"/>
+      <c r="G5926" t="inlineStr"/>
+      <c r="H5926" t="inlineStr"/>
+      <c r="I5926" t="inlineStr"/>
+    </row>
+    <row r="5927">
+      <c r="A5927" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5927" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5927" t="inlineStr"/>
+      <c r="D5927" t="inlineStr"/>
+      <c r="E5927" t="inlineStr"/>
+      <c r="F5927" t="inlineStr"/>
+      <c r="G5927" t="inlineStr"/>
+      <c r="H5927" t="inlineStr"/>
+      <c r="I5927" t="inlineStr"/>
+    </row>
+    <row r="5928">
+      <c r="A5928" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5928" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5928" t="inlineStr"/>
+      <c r="D5928" t="inlineStr"/>
+      <c r="E5928" t="inlineStr"/>
+      <c r="F5928" t="inlineStr"/>
+      <c r="G5928" t="inlineStr"/>
+      <c r="H5928" t="inlineStr"/>
+      <c r="I5928" t="inlineStr"/>
+    </row>
+    <row r="5929">
+      <c r="A5929" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5929" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5929" t="inlineStr"/>
+      <c r="D5929" t="inlineStr"/>
+      <c r="E5929" t="inlineStr"/>
+      <c r="F5929" t="inlineStr"/>
+      <c r="G5929" t="inlineStr"/>
+      <c r="H5929" t="inlineStr"/>
+      <c r="I5929" t="inlineStr"/>
+    </row>
+    <row r="5930">
+      <c r="A5930" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5930" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5930" t="inlineStr"/>
+      <c r="D5930" t="inlineStr"/>
+      <c r="E5930" t="inlineStr"/>
+      <c r="F5930" t="inlineStr"/>
+      <c r="G5930" t="inlineStr"/>
+      <c r="H5930" t="inlineStr"/>
+      <c r="I5930" t="inlineStr"/>
+    </row>
+    <row r="5931">
+      <c r="A5931" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5931" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5931" t="inlineStr"/>
+      <c r="D5931" t="inlineStr"/>
+      <c r="E5931" t="inlineStr"/>
+      <c r="F5931" t="inlineStr"/>
+      <c r="G5931" t="inlineStr"/>
+      <c r="H5931" t="inlineStr"/>
+      <c r="I5931" t="inlineStr"/>
+    </row>
+    <row r="5932">
+      <c r="A5932" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5932" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5932" t="inlineStr"/>
+      <c r="D5932" t="inlineStr"/>
+      <c r="E5932" t="inlineStr"/>
+      <c r="F5932" t="inlineStr"/>
+      <c r="G5932" t="inlineStr"/>
+      <c r="H5932" t="inlineStr"/>
+      <c r="I5932" t="inlineStr"/>
+    </row>
+    <row r="5933">
+      <c r="A5933" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5933" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5933" t="inlineStr"/>
+      <c r="D5933" t="inlineStr"/>
+      <c r="E5933" t="inlineStr"/>
+      <c r="F5933" t="inlineStr"/>
+      <c r="G5933" t="inlineStr"/>
+      <c r="H5933" t="inlineStr"/>
+      <c r="I5933" t="inlineStr"/>
+    </row>
+    <row r="5934">
+      <c r="A5934" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5934" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5934" t="inlineStr"/>
+      <c r="D5934" t="inlineStr"/>
+      <c r="E5934" t="inlineStr"/>
+      <c r="F5934" t="inlineStr"/>
+      <c r="G5934" t="inlineStr"/>
+      <c r="H5934" t="inlineStr"/>
+      <c r="I5934" t="inlineStr"/>
+    </row>
+    <row r="5935">
+      <c r="A5935" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5935" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5935" t="inlineStr"/>
+      <c r="D5935" t="inlineStr"/>
+      <c r="E5935" t="inlineStr"/>
+      <c r="F5935" t="inlineStr"/>
+      <c r="G5935" t="inlineStr"/>
+      <c r="H5935" t="inlineStr"/>
+      <c r="I5935" t="inlineStr"/>
+    </row>
+    <row r="5936">
+      <c r="A5936" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5936" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5936" t="inlineStr"/>
+      <c r="D5936" t="inlineStr"/>
+      <c r="E5936" t="inlineStr"/>
+      <c r="F5936" t="inlineStr"/>
+      <c r="G5936" t="inlineStr"/>
+      <c r="H5936" t="inlineStr"/>
+      <c r="I5936" t="inlineStr"/>
+    </row>
+    <row r="5937">
+      <c r="A5937" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5937" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5937" t="inlineStr"/>
+      <c r="D5937" t="inlineStr"/>
+      <c r="E5937" t="inlineStr"/>
+      <c r="F5937" t="inlineStr"/>
+      <c r="G5937" t="inlineStr"/>
+      <c r="H5937" t="inlineStr"/>
+      <c r="I5937" t="inlineStr"/>
+    </row>
+    <row r="5938"/>
+    <row r="5939">
+      <c r="A5939" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5939" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5939" t="inlineStr"/>
+      <c r="D5939" t="inlineStr"/>
+      <c r="E5939" t="inlineStr"/>
+      <c r="F5939" t="inlineStr"/>
+      <c r="G5939" t="inlineStr"/>
+      <c r="H5939" t="inlineStr"/>
+      <c r="I5939" t="inlineStr"/>
+    </row>
+    <row r="5940">
+      <c r="A5940" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5940" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5940" t="inlineStr"/>
+      <c r="D5940" t="inlineStr"/>
+      <c r="E5940" t="inlineStr"/>
+      <c r="F5940" t="inlineStr"/>
+      <c r="G5940" t="inlineStr"/>
+      <c r="H5940" t="inlineStr"/>
+      <c r="I5940" t="inlineStr"/>
+    </row>
+    <row r="5941">
+      <c r="A5941" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5941" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5941" t="inlineStr"/>
+      <c r="D5941" t="inlineStr"/>
+      <c r="E5941" t="inlineStr"/>
+      <c r="F5941" t="inlineStr"/>
+      <c r="G5941" t="inlineStr"/>
+      <c r="H5941" t="inlineStr"/>
+      <c r="I5941" t="inlineStr"/>
+    </row>
+    <row r="5942">
+      <c r="A5942" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5942" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5942" t="inlineStr"/>
+      <c r="D5942" t="inlineStr"/>
+      <c r="E5942" t="inlineStr"/>
+      <c r="F5942" t="inlineStr"/>
+      <c r="G5942" t="inlineStr"/>
+      <c r="H5942" t="inlineStr"/>
+      <c r="I5942" t="inlineStr"/>
+    </row>
+    <row r="5943">
+      <c r="A5943" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5943" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5943" t="inlineStr"/>
+      <c r="D5943" t="inlineStr"/>
+      <c r="E5943" t="inlineStr"/>
+      <c r="F5943" t="inlineStr"/>
+      <c r="G5943" t="inlineStr"/>
+      <c r="H5943" t="inlineStr"/>
+      <c r="I5943" t="inlineStr"/>
+    </row>
+    <row r="5944">
+      <c r="A5944" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5944" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5944" t="inlineStr"/>
+      <c r="D5944" t="inlineStr"/>
+      <c r="E5944" t="inlineStr"/>
+      <c r="F5944" t="inlineStr"/>
+      <c r="G5944" t="inlineStr"/>
+      <c r="H5944" t="inlineStr"/>
+      <c r="I5944" t="inlineStr"/>
+    </row>
+    <row r="5945">
+      <c r="A5945" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5945" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5945" t="inlineStr"/>
+      <c r="D5945" t="inlineStr"/>
+      <c r="E5945" t="inlineStr"/>
+      <c r="F5945" t="inlineStr"/>
+      <c r="G5945" t="inlineStr"/>
+      <c r="H5945" t="inlineStr"/>
+      <c r="I5945" t="inlineStr"/>
+    </row>
+    <row r="5946">
+      <c r="A5946" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5946" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5946" t="inlineStr"/>
+      <c r="D5946" t="inlineStr"/>
+      <c r="E5946" t="inlineStr"/>
+      <c r="F5946" t="inlineStr"/>
+      <c r="G5946" t="inlineStr"/>
+      <c r="H5946" t="inlineStr"/>
+      <c r="I5946" t="inlineStr"/>
+    </row>
+    <row r="5947">
+      <c r="A5947" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5947" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5947" t="inlineStr"/>
+      <c r="D5947" t="inlineStr"/>
+      <c r="E5947" t="inlineStr"/>
+      <c r="F5947" t="inlineStr"/>
+      <c r="G5947" t="inlineStr"/>
+      <c r="H5947" t="inlineStr"/>
+      <c r="I5947" t="inlineStr"/>
+    </row>
+    <row r="5948">
+      <c r="A5948" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5948" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5948" t="inlineStr"/>
+      <c r="D5948" t="inlineStr"/>
+      <c r="E5948" t="inlineStr"/>
+      <c r="F5948" t="inlineStr"/>
+      <c r="G5948" t="inlineStr"/>
+      <c r="H5948" t="inlineStr"/>
+      <c r="I5948" t="inlineStr"/>
+    </row>
+    <row r="5949">
+      <c r="A5949" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5949" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5949" t="inlineStr"/>
+      <c r="D5949" t="inlineStr"/>
+      <c r="E5949" t="inlineStr"/>
+      <c r="F5949" t="inlineStr"/>
+      <c r="G5949" t="inlineStr"/>
+      <c r="H5949" t="inlineStr"/>
+      <c r="I5949" t="inlineStr"/>
+    </row>
+    <row r="5950">
+      <c r="A5950" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5950" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5950" t="inlineStr"/>
+      <c r="D5950" t="inlineStr"/>
+      <c r="E5950" t="inlineStr"/>
+      <c r="F5950" t="inlineStr"/>
+      <c r="G5950" t="inlineStr"/>
+      <c r="H5950" t="inlineStr"/>
+      <c r="I5950" t="inlineStr"/>
+    </row>
+    <row r="5951">
+      <c r="A5951" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5951" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5951" t="inlineStr"/>
+      <c r="D5951" t="inlineStr"/>
+      <c r="E5951" t="inlineStr"/>
+      <c r="F5951" t="inlineStr"/>
+      <c r="G5951" t="inlineStr"/>
+      <c r="H5951" t="inlineStr"/>
+      <c r="I5951" t="inlineStr"/>
+    </row>
+    <row r="5952">
+      <c r="A5952" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5952" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5952" t="inlineStr"/>
+      <c r="D5952" t="inlineStr"/>
+      <c r="E5952" t="inlineStr"/>
+      <c r="F5952" t="inlineStr"/>
+      <c r="G5952" t="inlineStr"/>
+      <c r="H5952" t="inlineStr"/>
+      <c r="I5952" t="inlineStr"/>
+    </row>
+    <row r="5953">
+      <c r="A5953" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5953" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5953" t="inlineStr"/>
+      <c r="D5953" t="inlineStr"/>
+      <c r="E5953" t="inlineStr"/>
+      <c r="F5953" t="inlineStr"/>
+      <c r="G5953" t="inlineStr"/>
+      <c r="H5953" t="inlineStr"/>
+      <c r="I5953" t="inlineStr"/>
+    </row>
+    <row r="5954">
+      <c r="A5954" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5954" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5954" t="inlineStr"/>
+      <c r="D5954" t="inlineStr"/>
+      <c r="E5954" t="inlineStr"/>
+      <c r="F5954" t="inlineStr"/>
+      <c r="G5954" t="inlineStr"/>
+      <c r="H5954" t="inlineStr"/>
+      <c r="I5954" t="inlineStr"/>
+    </row>
+    <row r="5955">
+      <c r="A5955" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5955" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5955" t="inlineStr"/>
+      <c r="D5955" t="inlineStr"/>
+      <c r="E5955" t="inlineStr"/>
+      <c r="F5955" t="inlineStr"/>
+      <c r="G5955" t="inlineStr"/>
+      <c r="H5955" t="inlineStr"/>
+      <c r="I5955" t="inlineStr"/>
+    </row>
+    <row r="5956">
+      <c r="A5956" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5956" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5956" t="inlineStr"/>
+      <c r="D5956" t="inlineStr"/>
+      <c r="E5956" t="inlineStr"/>
+      <c r="F5956" t="inlineStr"/>
+      <c r="G5956" t="inlineStr"/>
+      <c r="H5956" t="inlineStr"/>
+      <c r="I5956" t="inlineStr"/>
+    </row>
+    <row r="5957">
+      <c r="A5957" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5957" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5957" t="inlineStr"/>
+      <c r="D5957" t="inlineStr"/>
+      <c r="E5957" t="inlineStr"/>
+      <c r="F5957" t="inlineStr"/>
+      <c r="G5957" t="inlineStr"/>
+      <c r="H5957" t="inlineStr"/>
+      <c r="I5957" t="inlineStr"/>
+    </row>
+    <row r="5958"/>
+    <row r="5959">
+      <c r="A5959" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5959" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5959" t="inlineStr"/>
+      <c r="D5959" t="inlineStr"/>
+      <c r="E5959" t="inlineStr"/>
+      <c r="F5959" t="inlineStr"/>
+      <c r="G5959" t="inlineStr"/>
+      <c r="H5959" t="inlineStr"/>
+      <c r="I5959" t="inlineStr"/>
+    </row>
+    <row r="5960">
+      <c r="A5960" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5960" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5960" t="inlineStr"/>
+      <c r="D5960" t="inlineStr"/>
+      <c r="E5960" t="inlineStr"/>
+      <c r="F5960" t="inlineStr"/>
+      <c r="G5960" t="inlineStr"/>
+      <c r="H5960" t="inlineStr"/>
+      <c r="I5960" t="inlineStr"/>
+    </row>
+    <row r="5961">
+      <c r="A5961" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5961" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5961" t="inlineStr"/>
+      <c r="D5961" t="inlineStr"/>
+      <c r="E5961" t="inlineStr"/>
+      <c r="F5961" t="inlineStr"/>
+      <c r="G5961" t="inlineStr"/>
+      <c r="H5961" t="inlineStr"/>
+      <c r="I5961" t="inlineStr"/>
+    </row>
+    <row r="5962">
+      <c r="A5962" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5962" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5962" t="inlineStr"/>
+      <c r="D5962" t="inlineStr"/>
+      <c r="E5962" t="inlineStr"/>
+      <c r="F5962" t="inlineStr"/>
+      <c r="G5962" t="inlineStr"/>
+      <c r="H5962" t="inlineStr"/>
+      <c r="I5962" t="inlineStr"/>
+    </row>
+    <row r="5963">
+      <c r="A5963" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5963" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5963" t="inlineStr"/>
+      <c r="D5963" t="inlineStr"/>
+      <c r="E5963" t="inlineStr"/>
+      <c r="F5963" t="inlineStr"/>
+      <c r="G5963" t="inlineStr"/>
+      <c r="H5963" t="inlineStr"/>
+      <c r="I5963" t="inlineStr"/>
+    </row>
+    <row r="5964">
+      <c r="A5964" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5964" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5964" t="inlineStr"/>
+      <c r="D5964" t="inlineStr"/>
+      <c r="E5964" t="inlineStr"/>
+      <c r="F5964" t="inlineStr"/>
+      <c r="G5964" t="inlineStr"/>
+      <c r="H5964" t="inlineStr"/>
+      <c r="I5964" t="inlineStr"/>
+    </row>
+    <row r="5965">
+      <c r="A5965" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5965" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5965" t="inlineStr"/>
+      <c r="D5965" t="inlineStr"/>
+      <c r="E5965" t="inlineStr"/>
+      <c r="F5965" t="inlineStr"/>
+      <c r="G5965" t="inlineStr"/>
+      <c r="H5965" t="inlineStr"/>
+      <c r="I5965" t="inlineStr"/>
+    </row>
+    <row r="5966">
+      <c r="A5966" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5966" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5966" t="inlineStr"/>
+      <c r="D5966" t="inlineStr"/>
+      <c r="E5966" t="inlineStr"/>
+      <c r="F5966" t="inlineStr"/>
+      <c r="G5966" t="inlineStr"/>
+      <c r="H5966" t="inlineStr"/>
+      <c r="I5966" t="inlineStr"/>
+    </row>
+    <row r="5967">
+      <c r="A5967" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5967" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5967" t="inlineStr"/>
+      <c r="D5967" t="inlineStr"/>
+      <c r="E5967" t="inlineStr"/>
+      <c r="F5967" t="inlineStr"/>
+      <c r="G5967" t="inlineStr"/>
+      <c r="H5967" t="inlineStr"/>
+      <c r="I5967" t="inlineStr"/>
+    </row>
+    <row r="5968">
+      <c r="A5968" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5968" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5968" t="inlineStr"/>
+      <c r="D5968" t="inlineStr"/>
+      <c r="E5968" t="inlineStr"/>
+      <c r="F5968" t="inlineStr"/>
+      <c r="G5968" t="inlineStr"/>
+      <c r="H5968" t="inlineStr"/>
+      <c r="I5968" t="inlineStr"/>
+    </row>
+    <row r="5969">
+      <c r="A5969" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5969" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5969" t="inlineStr"/>
+      <c r="D5969" t="inlineStr"/>
+      <c r="E5969" t="inlineStr"/>
+      <c r="F5969" t="inlineStr"/>
+      <c r="G5969" t="inlineStr"/>
+      <c r="H5969" t="inlineStr"/>
+      <c r="I5969" t="inlineStr"/>
+    </row>
+    <row r="5970">
+      <c r="A5970" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5970" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5970" t="inlineStr"/>
+      <c r="D5970" t="inlineStr"/>
+      <c r="E5970" t="inlineStr"/>
+      <c r="F5970" t="inlineStr"/>
+      <c r="G5970" t="inlineStr"/>
+      <c r="H5970" t="inlineStr"/>
+      <c r="I5970" t="inlineStr"/>
+    </row>
+    <row r="5971">
+      <c r="A5971" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5971" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5971" t="inlineStr"/>
+      <c r="D5971" t="inlineStr"/>
+      <c r="E5971" t="inlineStr"/>
+      <c r="F5971" t="inlineStr"/>
+      <c r="G5971" t="inlineStr"/>
+      <c r="H5971" t="inlineStr"/>
+      <c r="I5971" t="inlineStr"/>
+    </row>
+    <row r="5972">
+      <c r="A5972" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5972" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5972" t="inlineStr"/>
+      <c r="D5972" t="inlineStr"/>
+      <c r="E5972" t="inlineStr"/>
+      <c r="F5972" t="inlineStr"/>
+      <c r="G5972" t="inlineStr"/>
+      <c r="H5972" t="inlineStr"/>
+      <c r="I5972" t="inlineStr"/>
+    </row>
+    <row r="5973">
+      <c r="A5973" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5973" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5973" t="inlineStr"/>
+      <c r="D5973" t="inlineStr"/>
+      <c r="E5973" t="inlineStr"/>
+      <c r="F5973" t="inlineStr"/>
+      <c r="G5973" t="inlineStr"/>
+      <c r="H5973" t="inlineStr"/>
+      <c r="I5973" t="inlineStr"/>
+    </row>
+    <row r="5974">
+      <c r="A5974" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5974" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5974" t="inlineStr"/>
+      <c r="D5974" t="inlineStr"/>
+      <c r="E5974" t="inlineStr"/>
+      <c r="F5974" t="inlineStr"/>
+      <c r="G5974" t="inlineStr"/>
+      <c r="H5974" t="inlineStr"/>
+      <c r="I5974" t="inlineStr"/>
+    </row>
+    <row r="5975">
+      <c r="A5975" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5975" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5975" t="inlineStr"/>
+      <c r="D5975" t="inlineStr"/>
+      <c r="E5975" t="inlineStr"/>
+      <c r="F5975" t="inlineStr"/>
+      <c r="G5975" t="inlineStr"/>
+      <c r="H5975" t="inlineStr"/>
+      <c r="I5975" t="inlineStr"/>
+    </row>
+    <row r="5976">
+      <c r="A5976" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5976" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5976" t="inlineStr"/>
+      <c r="D5976" t="inlineStr"/>
+      <c r="E5976" t="inlineStr"/>
+      <c r="F5976" t="inlineStr"/>
+      <c r="G5976" t="inlineStr"/>
+      <c r="H5976" t="inlineStr"/>
+      <c r="I5976" t="inlineStr"/>
+    </row>
+    <row r="5977">
+      <c r="A5977" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5977" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5977" t="inlineStr"/>
+      <c r="D5977" t="inlineStr"/>
+      <c r="E5977" t="inlineStr"/>
+      <c r="F5977" t="inlineStr"/>
+      <c r="G5977" t="inlineStr"/>
+      <c r="H5977" t="inlineStr"/>
+      <c r="I5977" t="inlineStr"/>
+    </row>
+    <row r="5978"/>
+    <row r="5979">
+      <c r="A5979" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5979" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C5979" t="inlineStr"/>
+      <c r="D5979" t="inlineStr"/>
+      <c r="E5979" t="inlineStr"/>
+      <c r="F5979" t="inlineStr"/>
+      <c r="G5979" t="inlineStr"/>
+      <c r="H5979" t="inlineStr"/>
+      <c r="I5979" t="inlineStr"/>
+    </row>
+    <row r="5980">
+      <c r="A5980" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5980" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C5980" t="inlineStr"/>
+      <c r="D5980" t="inlineStr"/>
+      <c r="E5980" t="inlineStr"/>
+      <c r="F5980" t="inlineStr"/>
+      <c r="G5980" t="inlineStr"/>
+      <c r="H5980" t="inlineStr"/>
+      <c r="I5980" t="inlineStr"/>
+    </row>
+    <row r="5981">
+      <c r="A5981" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5981" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C5981" t="inlineStr"/>
+      <c r="D5981" t="inlineStr"/>
+      <c r="E5981" t="inlineStr"/>
+      <c r="F5981" t="inlineStr"/>
+      <c r="G5981" t="inlineStr"/>
+      <c r="H5981" t="inlineStr"/>
+      <c r="I5981" t="inlineStr"/>
+    </row>
+    <row r="5982">
+      <c r="A5982" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5982" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C5982" t="inlineStr"/>
+      <c r="D5982" t="inlineStr"/>
+      <c r="E5982" t="inlineStr"/>
+      <c r="F5982" t="inlineStr"/>
+      <c r="G5982" t="inlineStr"/>
+      <c r="H5982" t="inlineStr"/>
+      <c r="I5982" t="inlineStr"/>
+    </row>
+    <row r="5983">
+      <c r="A5983" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5983" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C5983" t="inlineStr"/>
+      <c r="D5983" t="inlineStr"/>
+      <c r="E5983" t="inlineStr"/>
+      <c r="F5983" t="inlineStr"/>
+      <c r="G5983" t="inlineStr"/>
+      <c r="H5983" t="inlineStr"/>
+      <c r="I5983" t="inlineStr"/>
+    </row>
+    <row r="5984">
+      <c r="A5984" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5984" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C5984" t="inlineStr"/>
+      <c r="D5984" t="inlineStr"/>
+      <c r="E5984" t="inlineStr"/>
+      <c r="F5984" t="inlineStr"/>
+      <c r="G5984" t="inlineStr"/>
+      <c r="H5984" t="inlineStr"/>
+      <c r="I5984" t="inlineStr"/>
+    </row>
+    <row r="5985">
+      <c r="A5985" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5985" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C5985" t="inlineStr"/>
+      <c r="D5985" t="inlineStr"/>
+      <c r="E5985" t="inlineStr"/>
+      <c r="F5985" t="inlineStr"/>
+      <c r="G5985" t="inlineStr"/>
+      <c r="H5985" t="inlineStr"/>
+      <c r="I5985" t="inlineStr"/>
+    </row>
+    <row r="5986">
+      <c r="A5986" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5986" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C5986" t="inlineStr"/>
+      <c r="D5986" t="inlineStr"/>
+      <c r="E5986" t="inlineStr"/>
+      <c r="F5986" t="inlineStr"/>
+      <c r="G5986" t="inlineStr"/>
+      <c r="H5986" t="inlineStr"/>
+      <c r="I5986" t="inlineStr"/>
+    </row>
+    <row r="5987">
+      <c r="A5987" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5987" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C5987" t="inlineStr"/>
+      <c r="D5987" t="inlineStr"/>
+      <c r="E5987" t="inlineStr"/>
+      <c r="F5987" t="inlineStr"/>
+      <c r="G5987" t="inlineStr"/>
+      <c r="H5987" t="inlineStr"/>
+      <c r="I5987" t="inlineStr"/>
+    </row>
+    <row r="5988">
+      <c r="A5988" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5988" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C5988" t="inlineStr"/>
+      <c r="D5988" t="inlineStr"/>
+      <c r="E5988" t="inlineStr"/>
+      <c r="F5988" t="inlineStr"/>
+      <c r="G5988" t="inlineStr"/>
+      <c r="H5988" t="inlineStr"/>
+      <c r="I5988" t="inlineStr"/>
+    </row>
+    <row r="5989">
+      <c r="A5989" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5989" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C5989" t="inlineStr"/>
+      <c r="D5989" t="inlineStr"/>
+      <c r="E5989" t="inlineStr"/>
+      <c r="F5989" t="inlineStr"/>
+      <c r="G5989" t="inlineStr"/>
+      <c r="H5989" t="inlineStr"/>
+      <c r="I5989" t="inlineStr"/>
+    </row>
+    <row r="5990">
+      <c r="A5990" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5990" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C5990" t="inlineStr"/>
+      <c r="D5990" t="inlineStr"/>
+      <c r="E5990" t="inlineStr"/>
+      <c r="F5990" t="inlineStr"/>
+      <c r="G5990" t="inlineStr"/>
+      <c r="H5990" t="inlineStr"/>
+      <c r="I5990" t="inlineStr"/>
+    </row>
+    <row r="5991">
+      <c r="A5991" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5991" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C5991" t="inlineStr"/>
+      <c r="D5991" t="inlineStr"/>
+      <c r="E5991" t="inlineStr"/>
+      <c r="F5991" t="inlineStr"/>
+      <c r="G5991" t="inlineStr"/>
+      <c r="H5991" t="inlineStr"/>
+      <c r="I5991" t="inlineStr"/>
+    </row>
+    <row r="5992">
+      <c r="A5992" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5992" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C5992" t="inlineStr"/>
+      <c r="D5992" t="inlineStr"/>
+      <c r="E5992" t="inlineStr"/>
+      <c r="F5992" t="inlineStr"/>
+      <c r="G5992" t="inlineStr"/>
+      <c r="H5992" t="inlineStr"/>
+      <c r="I5992" t="inlineStr"/>
+    </row>
+    <row r="5993">
+      <c r="A5993" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5993" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C5993" t="inlineStr"/>
+      <c r="D5993" t="inlineStr"/>
+      <c r="E5993" t="inlineStr"/>
+      <c r="F5993" t="inlineStr"/>
+      <c r="G5993" t="inlineStr"/>
+      <c r="H5993" t="inlineStr"/>
+      <c r="I5993" t="inlineStr"/>
+    </row>
+    <row r="5994">
+      <c r="A5994" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5994" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C5994" t="inlineStr"/>
+      <c r="D5994" t="inlineStr"/>
+      <c r="E5994" t="inlineStr"/>
+      <c r="F5994" t="inlineStr"/>
+      <c r="G5994" t="inlineStr"/>
+      <c r="H5994" t="inlineStr"/>
+      <c r="I5994" t="inlineStr"/>
+    </row>
+    <row r="5995">
+      <c r="A5995" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5995" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C5995" t="inlineStr"/>
+      <c r="D5995" t="inlineStr"/>
+      <c r="E5995" t="inlineStr"/>
+      <c r="F5995" t="inlineStr"/>
+      <c r="G5995" t="inlineStr"/>
+      <c r="H5995" t="inlineStr"/>
+      <c r="I5995" t="inlineStr"/>
+    </row>
+    <row r="5996">
+      <c r="A5996" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5996" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C5996" t="inlineStr"/>
+      <c r="D5996" t="inlineStr"/>
+      <c r="E5996" t="inlineStr"/>
+      <c r="F5996" t="inlineStr"/>
+      <c r="G5996" t="inlineStr"/>
+      <c r="H5996" t="inlineStr"/>
+      <c r="I5996" t="inlineStr"/>
+    </row>
+    <row r="5997">
+      <c r="A5997" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5997" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C5997" t="inlineStr"/>
+      <c r="D5997" t="inlineStr"/>
+      <c r="E5997" t="inlineStr"/>
+      <c r="F5997" t="inlineStr"/>
+      <c r="G5997" t="inlineStr"/>
+      <c r="H5997" t="inlineStr"/>
+      <c r="I5997" t="inlineStr"/>
+    </row>
+    <row r="5998"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/data/blumen_data.xlsx
+++ b/data/blumen_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="5475" windowWidth="16440" windowHeight="28320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
@@ -48,7 +48,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +121,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.3999755851924192"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -134,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +172,8 @@
     <xf numFmtId="14" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -509,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5998"/>
+  <dimension ref="A1:AC6062"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -519,40 +527,39 @@
     <col width="15.140625" customWidth="1" min="5" max="6"/>
     <col width="8.5703125" customWidth="1" min="7" max="7"/>
     <col width="11.5703125" customWidth="1" min="8" max="9"/>
-    <col width="11.42578125" customWidth="1" min="10" max="10"/>
-    <col width="74.28515625" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="13"/>
-    <col width="27" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
-    <col width="15.7109375" customWidth="1" min="16" max="16"/>
-    <col width="26.7109375" customWidth="1" min="17" max="17"/>
-    <col width="22.28515625" customWidth="1" min="18" max="18"/>
-    <col width="27.5703125" customWidth="1" min="19" max="19"/>
-    <col width="37.5703125" customWidth="1" min="20" max="21"/>
-    <col width="38.85546875" customWidth="1" min="22" max="22"/>
-    <col width="37" customWidth="1" min="23" max="23"/>
-    <col width="31.5703125" customWidth="1" min="24" max="24"/>
-    <col width="27.85546875" customWidth="1" min="25" max="25"/>
-    <col width="26.42578125" customWidth="1" min="26" max="26"/>
-    <col width="29" customWidth="1" min="27" max="27"/>
-    <col width="37.28515625" customWidth="1" min="28" max="30"/>
-    <col width="36.42578125" customWidth="1" min="31" max="31"/>
-    <col width="28.5703125" customWidth="1" min="32" max="32"/>
-    <col width="30.140625" customWidth="1" min="33" max="34"/>
-    <col width="30.28515625" customWidth="1" min="35" max="35"/>
-    <col width="31" customWidth="1" min="36" max="36"/>
-    <col width="39.140625" customWidth="1" min="37" max="37"/>
-    <col width="41.7109375" customWidth="1" min="38" max="38"/>
-    <col width="39.5703125" customWidth="1" min="39" max="39"/>
-    <col width="29.42578125" customWidth="1" min="40" max="40"/>
-    <col width="30.28515625" customWidth="1" min="41" max="41"/>
-    <col width="25.85546875" customWidth="1" min="42" max="42"/>
-    <col width="30" customWidth="1" min="43" max="43"/>
-    <col width="37.7109375" customWidth="1" min="44" max="44"/>
-    <col width="36" customWidth="1" min="45" max="45"/>
-    <col width="37.7109375" customWidth="1" min="46" max="46"/>
-    <col width="37.28515625" customWidth="1" min="47" max="47"/>
-    <col width="38.5703125" customWidth="1" min="48" max="48"/>
+    <col width="74.28515625" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="15.7109375" customWidth="1" min="15" max="15"/>
+    <col width="26.7109375" customWidth="1" min="16" max="16"/>
+    <col width="22.28515625" customWidth="1" min="17" max="17"/>
+    <col width="27.5703125" customWidth="1" min="18" max="18"/>
+    <col width="37.5703125" customWidth="1" min="19" max="20"/>
+    <col width="38.85546875" customWidth="1" min="21" max="21"/>
+    <col width="37" customWidth="1" min="22" max="22"/>
+    <col width="31.5703125" customWidth="1" min="23" max="23"/>
+    <col width="27.85546875" customWidth="1" min="24" max="24"/>
+    <col width="26.42578125" customWidth="1" min="25" max="25"/>
+    <col width="29" customWidth="1" min="26" max="26"/>
+    <col width="37.28515625" customWidth="1" min="27" max="29"/>
+    <col width="36.42578125" customWidth="1" min="30" max="30"/>
+    <col width="28.5703125" customWidth="1" min="31" max="31"/>
+    <col width="30.140625" customWidth="1" min="32" max="33"/>
+    <col width="30.28515625" customWidth="1" min="34" max="34"/>
+    <col width="31" customWidth="1" min="35" max="35"/>
+    <col width="39.140625" customWidth="1" min="36" max="36"/>
+    <col width="41.7109375" customWidth="1" min="37" max="37"/>
+    <col width="39.5703125" customWidth="1" min="38" max="38"/>
+    <col width="29.42578125" customWidth="1" min="39" max="39"/>
+    <col width="30.28515625" customWidth="1" min="40" max="40"/>
+    <col width="25.85546875" customWidth="1" min="41" max="41"/>
+    <col width="30" customWidth="1" min="42" max="42"/>
+    <col width="37.7109375" customWidth="1" min="43" max="43"/>
+    <col width="36" customWidth="1" min="44" max="44"/>
+    <col width="37.7109375" customWidth="1" min="45" max="45"/>
+    <col width="37.28515625" customWidth="1" min="46" max="46"/>
+    <col width="38.5703125" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customFormat="1" customHeight="1" s="6">
@@ -603,11 +610,6 @@
       </c>
       <c r="J1" s="6" t="inlineStr">
         <is>
-          <t>size</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
-        <is>
           <t>condition</t>
         </is>
       </c>
@@ -624,7 +626,7 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="AD2" s="3" t="n"/>
+      <c r="AC2" s="3" t="n"/>
     </row>
     <row r="3" customFormat="1" s="1">
       <c r="A3" s="5" t="n">
@@ -641,7 +643,7 @@
       <c r="D3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
     </row>
     <row r="4" customFormat="1" s="1">
       <c r="A4" s="5" t="n">
@@ -658,7 +660,7 @@
       <c r="D4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
     </row>
     <row r="5" customFormat="1" s="1">
       <c r="A5" s="5" t="n">
@@ -675,7 +677,7 @@
       <c r="D5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD5" s="3" t="n"/>
+      <c r="AC5" s="3" t="n"/>
     </row>
     <row r="6" customFormat="1" s="1">
       <c r="A6" s="5" t="n">
@@ -692,7 +694,7 @@
       <c r="D6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD6" s="3" t="n"/>
+      <c r="AC6" s="3" t="n"/>
     </row>
     <row r="7" customFormat="1" s="10">
       <c r="A7" s="8" t="n"/>
@@ -707,8 +709,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
-      <c r="O7" s="9" t="n"/>
-      <c r="AD7" s="11" t="n"/>
+      <c r="AC7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1157,7 +1158,7 @@
       <c r="F44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>hat angefangen blätter zu gelben und blätter haben angefangen sich zu krümmen</t>
         </is>
@@ -1244,7 +1245,7 @@
       <c r="F50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>hat angefangen blätter zu gelben und blätter haben angefangen sich zu krümmen</t>
         </is>
@@ -1327,7 +1328,7 @@
       <c r="F56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>hat angefangen blätter zu gelben und blätter haben angefangen sich zu krümmen</t>
         </is>
@@ -1369,7 +1370,7 @@
       <c r="C58" t="n">
         <v>2</v>
       </c>
-      <c r="K58" s="4" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>es hat sich links ein neuer ast angefangen zu bilden</t>
         </is>
@@ -12988,7 +12989,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="K1047" t="inlineStr">
+      <c r="J1047" t="inlineStr">
         <is>
           <t>etwas Spinnmilben</t>
         </is>
@@ -13016,7 +13017,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="K1048" s="7" t="inlineStr">
+      <c r="J1048" s="7" t="inlineStr">
         <is>
           <t>heftige Spinnmilben</t>
         </is>
@@ -17791,7 +17792,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="K1467" t="inlineStr">
+      <c r="J1467" t="inlineStr">
         <is>
           <t>Habe eine Überlebte larve gesehen daher noch mal Pestmix</t>
         </is>
@@ -20927,7 +20928,7 @@
       <c r="D1728" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="K1728" s="7" t="inlineStr">
+      <c r="J1728" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt größeres Gefäß</t>
         </is>
@@ -20956,7 +20957,7 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="K1730" s="7" t="inlineStr">
+      <c r="J1730" s="7" t="inlineStr">
         <is>
           <t>zweiten Zweig dazu gepflanzt</t>
         </is>
@@ -21024,7 +21025,7 @@
       <c r="D1735" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="K1735" s="7" t="inlineStr">
+      <c r="J1735" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt größeres Gefäß</t>
         </is>
@@ -21056,7 +21057,7 @@
       <c r="D1737" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="K1737" s="7" t="inlineStr">
+      <c r="J1737" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt größeres Gefäß</t>
         </is>
@@ -22079,7 +22080,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="K1823" s="7" t="inlineStr">
+      <c r="J1823" s="7" t="inlineStr">
         <is>
           <t>wieder ein wurm nach dem wässern entdeckt</t>
         </is>
@@ -33570,7 +33571,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2828" s="4" t="inlineStr">
+      <c r="J2828" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33593,7 +33594,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2829" s="4" t="inlineStr">
+      <c r="J2829" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33677,7 +33678,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2836" s="4" t="inlineStr">
+      <c r="J2836" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33720,7 +33721,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2839" s="4" t="inlineStr">
+      <c r="J2839" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33743,7 +33744,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2840" s="4" t="inlineStr">
+      <c r="J2840" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33776,7 +33777,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2842" s="4" t="inlineStr">
+      <c r="J2842" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33799,7 +33800,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2843" s="4" t="inlineStr">
+      <c r="J2843" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33822,7 +33823,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2844" s="4" t="inlineStr">
+      <c r="J2844" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -34246,7 +34247,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2887" s="4" t="inlineStr">
+      <c r="J2887" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -34271,7 +34272,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2888" s="4" t="inlineStr">
+      <c r="J2888" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -34329,7 +34330,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2891" s="4" t="inlineStr">
+      <c r="J2891" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -34426,7 +34427,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2898" s="4" t="inlineStr">
+      <c r="J2898" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35139,7 +35140,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2960" s="24" t="inlineStr">
+      <c r="J2960" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35164,7 +35165,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2961" s="24" t="inlineStr">
+      <c r="J2961" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35237,7 +35238,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2966" s="24" t="inlineStr">
+      <c r="J2966" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35390,7 +35391,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K2977" s="24" t="inlineStr">
+      <c r="J2977" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35898,7 +35899,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3021" s="24" t="inlineStr">
+      <c r="J3021" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35959,7 +35960,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3025" s="24" t="inlineStr">
+      <c r="J3025" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35996,7 +35997,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3027" s="24" t="inlineStr">
+      <c r="J3027" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -36021,7 +36022,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3028" s="24" t="inlineStr">
+      <c r="J3028" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -36046,7 +36047,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3029" s="24" t="inlineStr">
+      <c r="J3029" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37012,7 +37013,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3113" s="24" t="inlineStr">
+      <c r="J3113" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37037,7 +37038,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3114" s="24" t="inlineStr">
+      <c r="J3114" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37062,7 +37063,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3115" s="24" t="inlineStr">
+      <c r="J3115" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37179,7 +37180,7 @@
         <v>700</v>
       </c>
       <c r="E3124" s="24" t="n"/>
-      <c r="K3124" s="24" t="inlineStr">
+      <c r="J3124" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37204,7 +37205,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3125" s="24" t="inlineStr">
+      <c r="J3125" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37241,7 +37242,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3127" s="24" t="inlineStr">
+      <c r="J3127" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37266,7 +37267,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3128" s="24" t="inlineStr">
+      <c r="J3128" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37291,7 +37292,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3129" s="24" t="inlineStr">
+      <c r="J3129" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38667,7 +38668,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3249" s="24" t="inlineStr">
+      <c r="J3249" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38692,7 +38693,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3250" s="24" t="inlineStr">
+      <c r="J3250" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38753,7 +38754,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3254" s="24" t="inlineStr">
+      <c r="J3254" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38802,7 +38803,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3257" s="24" t="inlineStr">
+      <c r="J3257" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38839,7 +38840,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3259" s="24" t="inlineStr">
+      <c r="J3259" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38888,7 +38889,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3262" s="24" t="inlineStr">
+      <c r="J3262" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39646,7 +39647,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3341" s="24" t="inlineStr">
+      <c r="J3341" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39679,7 +39680,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3343" s="24" t="inlineStr">
+      <c r="J3343" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39722,7 +39723,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3346" s="24" t="inlineStr">
+      <c r="J3346" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39745,7 +39746,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3347" s="24" t="inlineStr">
+      <c r="J3347" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39768,7 +39769,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3348" s="24" t="inlineStr">
+      <c r="J3348" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39811,7 +39812,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3351" s="24" t="inlineStr">
+      <c r="J3351" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39864,7 +39865,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3355" s="24" t="inlineStr">
+      <c r="J3355" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40778,7 +40779,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3435" t="inlineStr">
+      <c r="J3435" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40815,7 +40816,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3437" t="inlineStr">
+      <c r="J3437" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40924,7 +40925,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3445" t="inlineStr">
+      <c r="J3445" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40961,7 +40962,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3447" t="inlineStr">
+      <c r="J3447" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40986,7 +40987,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3448" t="inlineStr">
+      <c r="J3448" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41035,7 +41036,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3451" t="inlineStr">
+      <c r="J3451" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41060,7 +41061,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3452" t="inlineStr">
+      <c r="J3452" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41749,7 +41750,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3512" t="inlineStr">
+      <c r="J3512" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41786,7 +41787,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3514" t="inlineStr">
+      <c r="J3514" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41811,7 +41812,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3515" t="inlineStr">
+      <c r="J3515" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41836,7 +41837,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3516" t="inlineStr">
+      <c r="J3516" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41861,7 +41862,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3517" t="inlineStr">
+      <c r="J3517" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41898,7 +41899,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3519" t="inlineStr">
+      <c r="J3519" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41923,7 +41924,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3520" t="inlineStr">
+      <c r="J3520" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41972,7 +41973,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3523" t="inlineStr">
+      <c r="J3523" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -42009,7 +42010,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3525" t="inlineStr">
+      <c r="J3525" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -42034,7 +42035,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3526" t="inlineStr">
+      <c r="J3526" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -42071,7 +42072,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3528" t="inlineStr">
+      <c r="J3528" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -43374,7 +43375,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="L3641" s="7" t="inlineStr">
+      <c r="K3641" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt</t>
         </is>
@@ -43399,7 +43400,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="L3642" s="7" t="inlineStr">
+      <c r="K3642" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt</t>
         </is>
@@ -46779,8 +46780,7 @@
       <c r="G3920" s="24" t="n"/>
       <c r="H3920" s="24" t="n"/>
       <c r="I3920" s="24" t="n"/>
-      <c r="J3920" s="24" t="n"/>
-      <c r="K3920" t="inlineStr">
+      <c r="J3920" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -46821,8 +46821,7 @@
       <c r="G3922" s="24" t="n"/>
       <c r="H3922" s="24" t="n"/>
       <c r="I3922" s="24" t="n"/>
-      <c r="J3922" s="24" t="n"/>
-      <c r="K3922" t="inlineStr">
+      <c r="J3922" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -46851,8 +46850,7 @@
       <c r="G3923" s="24" t="n"/>
       <c r="H3923" s="24" t="n"/>
       <c r="I3923" s="24" t="n"/>
-      <c r="J3923" s="24" t="n"/>
-      <c r="K3923" t="inlineStr">
+      <c r="J3923" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -46881,8 +46879,7 @@
       <c r="G3924" s="24" t="n"/>
       <c r="H3924" s="24" t="n"/>
       <c r="I3924" s="24" t="n"/>
-      <c r="J3924" s="24" t="n"/>
-      <c r="K3924" t="inlineStr">
+      <c r="J3924" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -46947,8 +46944,7 @@
       <c r="G3928" s="24" t="n"/>
       <c r="H3928" s="24" t="n"/>
       <c r="I3928" s="24" t="n"/>
-      <c r="J3928" s="24" t="n"/>
-      <c r="K3928" t="inlineStr">
+      <c r="J3928" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -47025,8 +47021,7 @@
       <c r="G3933" s="24" t="n"/>
       <c r="H3933" s="24" t="n"/>
       <c r="I3933" s="24" t="n"/>
-      <c r="J3933" s="24" t="n"/>
-      <c r="K3933" t="inlineStr">
+      <c r="J3933" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -47067,8 +47062,7 @@
       <c r="G3935" s="24" t="n"/>
       <c r="H3935" s="24" t="n"/>
       <c r="I3935" s="24" t="n"/>
-      <c r="J3935" s="24" t="n"/>
-      <c r="K3935" t="inlineStr">
+      <c r="J3935" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -47097,8 +47091,7 @@
       <c r="G3936" s="24" t="n"/>
       <c r="H3936" s="24" t="n"/>
       <c r="I3936" s="24" t="n"/>
-      <c r="J3936" s="24" t="n"/>
-      <c r="K3936" t="inlineStr">
+      <c r="J3936" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -64969,7 +64962,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="K5440" s="7" t="inlineStr">
+      <c r="J5440" s="7" t="inlineStr">
         <is>
           <t>bad, some pest bugs with black little shits</t>
         </is>
@@ -65196,7 +65189,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="K5456" s="7" t="inlineStr">
+      <c r="J5456" s="7" t="inlineStr">
         <is>
           <t>very bad, some pest bugs with black little shits</t>
         </is>
@@ -69504,6 +69497,8 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
+      <c r="D5820" s="24" t="n"/>
+      <c r="E5820" s="24" t="n"/>
     </row>
     <row r="5821">
       <c r="A5821" t="inlineStr">
@@ -69516,6 +69511,8 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
+      <c r="D5821" s="24" t="n"/>
+      <c r="E5821" s="24" t="n"/>
     </row>
     <row r="5822">
       <c r="A5822" t="inlineStr">
@@ -69552,6 +69549,8 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
+      <c r="D5824" s="24" t="n"/>
+      <c r="E5824" s="24" t="n"/>
     </row>
     <row r="5825">
       <c r="A5825" t="inlineStr">
@@ -69600,6 +69599,8 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
+      <c r="D5828" s="24" t="n"/>
+      <c r="E5828" s="24" t="n"/>
     </row>
     <row r="5829">
       <c r="A5829" t="inlineStr">
@@ -69648,6 +69649,8 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
+      <c r="D5832" s="24" t="n"/>
+      <c r="E5832" s="24" t="n"/>
     </row>
     <row r="5833">
       <c r="A5833" t="inlineStr">
@@ -69660,6 +69663,8 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
+      <c r="D5833" s="24" t="n"/>
+      <c r="E5833" s="24" t="n"/>
     </row>
     <row r="5834">
       <c r="A5834" t="inlineStr">
@@ -69672,6 +69677,8 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
+      <c r="D5834" s="24" t="n"/>
+      <c r="E5834" s="24" t="n"/>
     </row>
     <row r="5835">
       <c r="A5835" t="inlineStr">
@@ -69684,6 +69691,8 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
+      <c r="D5835" s="24" t="n"/>
+      <c r="E5835" s="24" t="n"/>
     </row>
     <row r="5836">
       <c r="A5836" t="inlineStr">
@@ -69696,6 +69705,8 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
+      <c r="D5836" s="24" t="n"/>
+      <c r="E5836" s="24" t="n"/>
     </row>
     <row r="5837">
       <c r="A5837" t="inlineStr">
@@ -69711,10 +69722,8 @@
     </row>
     <row r="5838"/>
     <row r="5839">
-      <c r="A5839" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5839" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5839" t="inlineStr">
         <is>
@@ -69723,10 +69732,8 @@
       </c>
     </row>
     <row r="5840">
-      <c r="A5840" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5840" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5840" t="inlineStr">
         <is>
@@ -69735,10 +69742,8 @@
       </c>
     </row>
     <row r="5841">
-      <c r="A5841" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5841" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5841" t="inlineStr">
         <is>
@@ -69747,10 +69752,8 @@
       </c>
     </row>
     <row r="5842">
-      <c r="A5842" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5842" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5842" t="inlineStr">
         <is>
@@ -69759,10 +69762,8 @@
       </c>
     </row>
     <row r="5843">
-      <c r="A5843" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5843" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5843" t="inlineStr">
         <is>
@@ -69771,10 +69772,8 @@
       </c>
     </row>
     <row r="5844">
-      <c r="A5844" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5844" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5844" t="inlineStr">
         <is>
@@ -69783,10 +69782,8 @@
       </c>
     </row>
     <row r="5845">
-      <c r="A5845" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5845" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5845" t="inlineStr">
         <is>
@@ -69795,10 +69792,8 @@
       </c>
     </row>
     <row r="5846">
-      <c r="A5846" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5846" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5846" t="inlineStr">
         <is>
@@ -69807,10 +69802,8 @@
       </c>
     </row>
     <row r="5847">
-      <c r="A5847" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5847" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5847" t="inlineStr">
         <is>
@@ -69819,10 +69812,8 @@
       </c>
     </row>
     <row r="5848">
-      <c r="A5848" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5848" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5848" t="inlineStr">
         <is>
@@ -69831,10 +69822,8 @@
       </c>
     </row>
     <row r="5849">
-      <c r="A5849" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5849" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5849" t="inlineStr">
         <is>
@@ -69843,10 +69832,8 @@
       </c>
     </row>
     <row r="5850">
-      <c r="A5850" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5850" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5850" t="inlineStr">
         <is>
@@ -69855,10 +69842,8 @@
       </c>
     </row>
     <row r="5851">
-      <c r="A5851" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5851" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5851" t="inlineStr">
         <is>
@@ -69867,10 +69852,8 @@
       </c>
     </row>
     <row r="5852">
-      <c r="A5852" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5852" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5852" t="inlineStr">
         <is>
@@ -69879,10 +69862,8 @@
       </c>
     </row>
     <row r="5853">
-      <c r="A5853" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5853" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5853" t="inlineStr">
         <is>
@@ -69891,10 +69872,8 @@
       </c>
     </row>
     <row r="5854">
-      <c r="A5854" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5854" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5854" t="inlineStr">
         <is>
@@ -69903,10 +69882,8 @@
       </c>
     </row>
     <row r="5855">
-      <c r="A5855" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5855" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5855" t="inlineStr">
         <is>
@@ -69915,10 +69892,8 @@
       </c>
     </row>
     <row r="5856">
-      <c r="A5856" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5856" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5856" t="inlineStr">
         <is>
@@ -69927,10 +69902,8 @@
       </c>
     </row>
     <row r="5857">
-      <c r="A5857" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
+      <c r="A5857" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B5857" t="inlineStr">
         <is>
@@ -69940,10 +69913,8 @@
     </row>
     <row r="5858"/>
     <row r="5859">
-      <c r="A5859" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5859" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5859" t="inlineStr">
         <is>
@@ -69952,10 +69923,8 @@
       </c>
     </row>
     <row r="5860">
-      <c r="A5860" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5860" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5860" t="inlineStr">
         <is>
@@ -69964,10 +69933,8 @@
       </c>
     </row>
     <row r="5861">
-      <c r="A5861" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5861" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5861" t="inlineStr">
         <is>
@@ -69976,10 +69943,8 @@
       </c>
     </row>
     <row r="5862">
-      <c r="A5862" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5862" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5862" t="inlineStr">
         <is>
@@ -69988,10 +69953,8 @@
       </c>
     </row>
     <row r="5863">
-      <c r="A5863" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5863" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5863" t="inlineStr">
         <is>
@@ -70000,10 +69963,8 @@
       </c>
     </row>
     <row r="5864">
-      <c r="A5864" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5864" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5864" t="inlineStr">
         <is>
@@ -70012,10 +69973,8 @@
       </c>
     </row>
     <row r="5865">
-      <c r="A5865" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5865" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5865" t="inlineStr">
         <is>
@@ -70024,10 +69983,8 @@
       </c>
     </row>
     <row r="5866">
-      <c r="A5866" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5866" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5866" t="inlineStr">
         <is>
@@ -70036,10 +69993,8 @@
       </c>
     </row>
     <row r="5867">
-      <c r="A5867" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5867" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5867" t="inlineStr">
         <is>
@@ -70048,10 +70003,8 @@
       </c>
     </row>
     <row r="5868">
-      <c r="A5868" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5868" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5868" t="inlineStr">
         <is>
@@ -70060,10 +70013,8 @@
       </c>
     </row>
     <row r="5869">
-      <c r="A5869" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5869" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5869" t="inlineStr">
         <is>
@@ -70072,10 +70023,8 @@
       </c>
     </row>
     <row r="5870">
-      <c r="A5870" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5870" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5870" t="inlineStr">
         <is>
@@ -70084,10 +70033,8 @@
       </c>
     </row>
     <row r="5871">
-      <c r="A5871" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5871" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5871" t="inlineStr">
         <is>
@@ -70096,10 +70043,8 @@
       </c>
     </row>
     <row r="5872">
-      <c r="A5872" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5872" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5872" t="inlineStr">
         <is>
@@ -70108,10 +70053,8 @@
       </c>
     </row>
     <row r="5873">
-      <c r="A5873" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5873" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5873" t="inlineStr">
         <is>
@@ -70120,10 +70063,8 @@
       </c>
     </row>
     <row r="5874">
-      <c r="A5874" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5874" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5874" t="inlineStr">
         <is>
@@ -70132,10 +70073,8 @@
       </c>
     </row>
     <row r="5875">
-      <c r="A5875" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5875" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5875" t="inlineStr">
         <is>
@@ -70144,10 +70083,8 @@
       </c>
     </row>
     <row r="5876">
-      <c r="A5876" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5876" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5876" t="inlineStr">
         <is>
@@ -70156,10 +70093,8 @@
       </c>
     </row>
     <row r="5877">
-      <c r="A5877" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
+      <c r="A5877" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B5877" t="inlineStr">
         <is>
@@ -70169,22 +70104,26 @@
     </row>
     <row r="5878"/>
     <row r="5879">
-      <c r="A5879" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5879" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5879" t="inlineStr">
         <is>
           <t>Epipremnum Aureum</t>
         </is>
       </c>
+      <c r="D5879" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5879" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5880">
-      <c r="A5880" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5880" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5880" t="inlineStr">
         <is>
@@ -70193,46 +70132,62 @@
       </c>
     </row>
     <row r="5881">
-      <c r="A5881" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5881" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5881" t="inlineStr">
         <is>
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
+      <c r="D5881" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5881" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5882">
-      <c r="A5882" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5882" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5882" t="inlineStr">
         <is>
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
+      <c r="D5882" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5882" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5883">
-      <c r="A5883" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5883" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5883" t="inlineStr">
         <is>
           <t>Monstera Adenossii</t>
         </is>
       </c>
+      <c r="D5883" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5883" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5884">
-      <c r="A5884" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5884" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5884" t="inlineStr">
         <is>
@@ -70241,10 +70196,8 @@
       </c>
     </row>
     <row r="5885">
-      <c r="A5885" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5885" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5885" t="inlineStr">
         <is>
@@ -70253,22 +70206,26 @@
       </c>
     </row>
     <row r="5886">
-      <c r="A5886" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5886" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5886" t="inlineStr">
         <is>
           <t>Hoya Mathilde</t>
         </is>
       </c>
+      <c r="D5886" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5886" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5887">
-      <c r="A5887" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5887" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5887" t="inlineStr">
         <is>
@@ -70277,10 +70234,8 @@
       </c>
     </row>
     <row r="5888">
-      <c r="A5888" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5888" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5888" t="inlineStr">
         <is>
@@ -70289,10 +70244,8 @@
       </c>
     </row>
     <row r="5889">
-      <c r="A5889" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5889" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5889" t="inlineStr">
         <is>
@@ -70301,22 +70254,26 @@
       </c>
     </row>
     <row r="5890">
-      <c r="A5890" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5890" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5890" t="inlineStr">
         <is>
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
+      <c r="D5890" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5890" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5891">
-      <c r="A5891" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5891" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5891" t="inlineStr">
         <is>
@@ -70325,22 +70282,26 @@
       </c>
     </row>
     <row r="5892">
-      <c r="A5892" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5892" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5892" t="inlineStr">
         <is>
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
+      <c r="D5892" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5892" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5893">
-      <c r="A5893" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5893" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5893" t="inlineStr">
         <is>
@@ -70348,91 +70309,132 @@
         </is>
       </c>
     </row>
-    <row r="5894">
-      <c r="A5894" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
-      </c>
-      <c r="B5894" t="inlineStr">
+    <row r="5894" customFormat="1" s="26">
+      <c r="A5894" s="25" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B5894" s="26" t="inlineStr">
         <is>
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
+      <c r="D5894" s="26" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5894" s="26" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="I5894" s="26" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="5895">
-      <c r="A5895" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
+      <c r="A5895" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5895" t="inlineStr">
         <is>
           <t>Philodendron Birkin</t>
         </is>
       </c>
-    </row>
-    <row r="5896">
-      <c r="A5896" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
-      </c>
-      <c r="B5896" t="inlineStr">
+      <c r="D5895" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5895" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5896" customFormat="1" s="26">
+      <c r="A5896" s="25" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B5896" s="26" t="inlineStr">
         <is>
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-    </row>
-    <row r="5897">
-      <c r="A5897" t="inlineStr">
-        <is>
-          <t>19.04.2026</t>
-        </is>
-      </c>
-      <c r="B5897" t="inlineStr">
+      <c r="D5896" s="26" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5896" s="26" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="I5896" s="26" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5897" customFormat="1" s="26">
+      <c r="A5897" s="25" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B5897" s="26" t="inlineStr">
         <is>
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-    </row>
-    <row r="5898"/>
-    <row r="5899">
-      <c r="A5899" t="inlineStr">
-        <is>
-          <t>20.04.2026</t>
-        </is>
+      <c r="D5897" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5897" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="I5897" s="26" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5898" customFormat="1" s="26">
+      <c r="A5898" s="25" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B5898" s="26" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+      <c r="D5898" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5898" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+    </row>
+    <row r="5899" customFormat="1" s="26">
+      <c r="A5899" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5899" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum</t>
+          <t>Senecio rowleyanus</t>
         </is>
       </c>
     </row>
     <row r="5900">
-      <c r="A5900" t="inlineStr">
-        <is>
-          <t>20.04.2026</t>
-        </is>
+      <c r="A5900" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B5900" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philodendron Scandens Micans </t>
-        </is>
-      </c>
-    </row>
-    <row r="5901">
-      <c r="A5901" t="inlineStr">
-        <is>
-          <t>20.04.2026</t>
-        </is>
-      </c>
-      <c r="B5901" t="inlineStr">
-        <is>
-          <t>Scindapsus Treubii Moonlight</t>
-        </is>
-      </c>
-    </row>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5901"/>
     <row r="5902">
       <c r="A5902" t="inlineStr">
         <is>
@@ -70441,7 +70443,7 @@
       </c>
       <c r="B5902" t="inlineStr">
         <is>
-          <t>Philodendron Hedaracium Brasil</t>
+          <t>Epipremnum Aureum</t>
         </is>
       </c>
     </row>
@@ -70453,7 +70455,7 @@
       </c>
       <c r="B5903" t="inlineStr">
         <is>
-          <t>Monstera Adenossii</t>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
     </row>
@@ -70465,7 +70467,7 @@
       </c>
       <c r="B5904" t="inlineStr">
         <is>
-          <t>Ficus Elastica Abidjan</t>
+          <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
     </row>
@@ -70477,7 +70479,7 @@
       </c>
       <c r="B5905" t="inlineStr">
         <is>
-          <t>Peperomia Hope</t>
+          <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
     </row>
@@ -70489,7 +70491,7 @@
       </c>
       <c r="B5906" t="inlineStr">
         <is>
-          <t>Hoya Mathilde</t>
+          <t>Monstera Adenossii</t>
         </is>
       </c>
     </row>
@@ -70501,7 +70503,7 @@
       </c>
       <c r="B5907" t="inlineStr">
         <is>
-          <t>Epipremnum Pinnatum Blue</t>
+          <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
     </row>
@@ -70513,7 +70515,7 @@
       </c>
       <c r="B5908" t="inlineStr">
         <is>
-          <t>Sansevieria Laurentii</t>
+          <t>Peperomia Hope</t>
         </is>
       </c>
     </row>
@@ -70525,7 +70527,7 @@
       </c>
       <c r="B5909" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum Saal</t>
+          <t>Hoya Mathilde</t>
         </is>
       </c>
     </row>
@@ -70537,7 +70539,7 @@
       </c>
       <c r="B5910" t="inlineStr">
         <is>
-          <t>Monstera Deliciosa Variegata</t>
+          <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
     </row>
@@ -70549,7 +70551,7 @@
       </c>
       <c r="B5911" t="inlineStr">
         <is>
-          <t>Pachira Aquatica</t>
+          <t>Sansevieria Laurentii</t>
         </is>
       </c>
     </row>
@@ -70561,7 +70563,7 @@
       </c>
       <c r="B5912" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monstera Deliciosa </t>
+          <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
     </row>
@@ -70573,7 +70575,7 @@
       </c>
       <c r="B5913" t="inlineStr">
         <is>
-          <t>Philodendron Imperial Red</t>
+          <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
     </row>
@@ -70585,7 +70587,7 @@
       </c>
       <c r="B5914" t="inlineStr">
         <is>
-          <t>Philodendron McColleys Finale</t>
+          <t>Pachira Aquatica</t>
         </is>
       </c>
     </row>
@@ -70597,7 +70599,7 @@
       </c>
       <c r="B5915" t="inlineStr">
         <is>
-          <t>Philodendron Birkin</t>
+          <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
     </row>
@@ -70609,7 +70611,7 @@
       </c>
       <c r="B5916" t="inlineStr">
         <is>
-          <t>Rhaphidophora Tetrasperma</t>
+          <t>Philodendron Imperial Red</t>
         </is>
       </c>
     </row>
@@ -70621,125 +70623,83 @@
       </c>
       <c r="B5917" t="inlineStr">
         <is>
-          <t>Philodendron Scandens Micans little</t>
-        </is>
-      </c>
-    </row>
-    <row r="5918"/>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5918">
+      <c r="A5918" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="B5918" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
     <row r="5919">
       <c r="A5919" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="B5919" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum</t>
-        </is>
-      </c>
-      <c r="C5919" t="inlineStr"/>
-      <c r="D5919" t="inlineStr"/>
-      <c r="E5919" t="inlineStr"/>
-      <c r="F5919" t="inlineStr"/>
-      <c r="G5919" t="inlineStr"/>
-      <c r="H5919" t="inlineStr"/>
-      <c r="I5919" t="inlineStr"/>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
     </row>
     <row r="5920">
       <c r="A5920" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="B5920" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philodendron Scandens Micans </t>
-        </is>
-      </c>
-      <c r="C5920" t="inlineStr"/>
-      <c r="D5920" t="inlineStr"/>
-      <c r="E5920" t="inlineStr"/>
-      <c r="F5920" t="inlineStr"/>
-      <c r="G5920" t="inlineStr"/>
-      <c r="H5920" t="inlineStr"/>
-      <c r="I5920" t="inlineStr"/>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
     </row>
     <row r="5921">
       <c r="A5921" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="B5921" t="inlineStr">
         <is>
-          <t>Scindapsus Treubii Moonlight</t>
-        </is>
-      </c>
-      <c r="C5921" t="inlineStr"/>
-      <c r="D5921" t="inlineStr"/>
-      <c r="E5921" t="inlineStr"/>
-      <c r="F5921" t="inlineStr"/>
-      <c r="G5921" t="inlineStr"/>
-      <c r="H5921" t="inlineStr"/>
-      <c r="I5921" t="inlineStr"/>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
     </row>
     <row r="5922">
       <c r="A5922" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="B5922" t="inlineStr">
         <is>
-          <t>Philodendron Hedaracium Brasil</t>
-        </is>
-      </c>
-      <c r="C5922" t="inlineStr"/>
-      <c r="D5922" t="inlineStr"/>
-      <c r="E5922" t="inlineStr"/>
-      <c r="F5922" t="inlineStr"/>
-      <c r="G5922" t="inlineStr"/>
-      <c r="H5922" t="inlineStr"/>
-      <c r="I5922" t="inlineStr"/>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
     </row>
     <row r="5923">
       <c r="A5923" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="B5923" t="inlineStr">
         <is>
-          <t>Monstera Adenossii</t>
-        </is>
-      </c>
-      <c r="C5923" t="inlineStr"/>
-      <c r="D5923" t="inlineStr"/>
-      <c r="E5923" t="inlineStr"/>
-      <c r="F5923" t="inlineStr"/>
-      <c r="G5923" t="inlineStr"/>
-      <c r="H5923" t="inlineStr"/>
-      <c r="I5923" t="inlineStr"/>
-    </row>
-    <row r="5924">
-      <c r="A5924" t="inlineStr">
-        <is>
-          <t>21.04.2026</t>
-        </is>
-      </c>
-      <c r="B5924" t="inlineStr">
-        <is>
-          <t>Ficus Elastica Abidjan</t>
-        </is>
-      </c>
-      <c r="C5924" t="inlineStr"/>
-      <c r="D5924" t="inlineStr"/>
-      <c r="E5924" t="inlineStr"/>
-      <c r="F5924" t="inlineStr"/>
-      <c r="G5924" t="inlineStr"/>
-      <c r="H5924" t="inlineStr"/>
-      <c r="I5924" t="inlineStr"/>
-    </row>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5924"/>
     <row r="5925">
       <c r="A5925" t="inlineStr">
         <is>
@@ -70748,16 +70708,9 @@
       </c>
       <c r="B5925" t="inlineStr">
         <is>
-          <t>Peperomia Hope</t>
-        </is>
-      </c>
-      <c r="C5925" t="inlineStr"/>
-      <c r="D5925" t="inlineStr"/>
-      <c r="E5925" t="inlineStr"/>
-      <c r="F5925" t="inlineStr"/>
-      <c r="G5925" t="inlineStr"/>
-      <c r="H5925" t="inlineStr"/>
-      <c r="I5925" t="inlineStr"/>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
     </row>
     <row r="5926">
       <c r="A5926" t="inlineStr">
@@ -70767,16 +70720,9 @@
       </c>
       <c r="B5926" t="inlineStr">
         <is>
-          <t>Hoya Mathilde</t>
-        </is>
-      </c>
-      <c r="C5926" t="inlineStr"/>
-      <c r="D5926" t="inlineStr"/>
-      <c r="E5926" t="inlineStr"/>
-      <c r="F5926" t="inlineStr"/>
-      <c r="G5926" t="inlineStr"/>
-      <c r="H5926" t="inlineStr"/>
-      <c r="I5926" t="inlineStr"/>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
     </row>
     <row r="5927">
       <c r="A5927" t="inlineStr">
@@ -70786,16 +70732,9 @@
       </c>
       <c r="B5927" t="inlineStr">
         <is>
-          <t>Epipremnum Pinnatum Blue</t>
-        </is>
-      </c>
-      <c r="C5927" t="inlineStr"/>
-      <c r="D5927" t="inlineStr"/>
-      <c r="E5927" t="inlineStr"/>
-      <c r="F5927" t="inlineStr"/>
-      <c r="G5927" t="inlineStr"/>
-      <c r="H5927" t="inlineStr"/>
-      <c r="I5927" t="inlineStr"/>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
     </row>
     <row r="5928">
       <c r="A5928" t="inlineStr">
@@ -70805,16 +70744,9 @@
       </c>
       <c r="B5928" t="inlineStr">
         <is>
-          <t>Sansevieria Laurentii</t>
-        </is>
-      </c>
-      <c r="C5928" t="inlineStr"/>
-      <c r="D5928" t="inlineStr"/>
-      <c r="E5928" t="inlineStr"/>
-      <c r="F5928" t="inlineStr"/>
-      <c r="G5928" t="inlineStr"/>
-      <c r="H5928" t="inlineStr"/>
-      <c r="I5928" t="inlineStr"/>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="5929">
       <c r="A5929" t="inlineStr">
@@ -70824,16 +70756,9 @@
       </c>
       <c r="B5929" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum Saal</t>
-        </is>
-      </c>
-      <c r="C5929" t="inlineStr"/>
-      <c r="D5929" t="inlineStr"/>
-      <c r="E5929" t="inlineStr"/>
-      <c r="F5929" t="inlineStr"/>
-      <c r="G5929" t="inlineStr"/>
-      <c r="H5929" t="inlineStr"/>
-      <c r="I5929" t="inlineStr"/>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
     </row>
     <row r="5930">
       <c r="A5930" t="inlineStr">
@@ -70843,16 +70768,9 @@
       </c>
       <c r="B5930" t="inlineStr">
         <is>
-          <t>Monstera Deliciosa Variegata</t>
-        </is>
-      </c>
-      <c r="C5930" t="inlineStr"/>
-      <c r="D5930" t="inlineStr"/>
-      <c r="E5930" t="inlineStr"/>
-      <c r="F5930" t="inlineStr"/>
-      <c r="G5930" t="inlineStr"/>
-      <c r="H5930" t="inlineStr"/>
-      <c r="I5930" t="inlineStr"/>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
     </row>
     <row r="5931">
       <c r="A5931" t="inlineStr">
@@ -70862,16 +70780,9 @@
       </c>
       <c r="B5931" t="inlineStr">
         <is>
-          <t>Pachira Aquatica</t>
-        </is>
-      </c>
-      <c r="C5931" t="inlineStr"/>
-      <c r="D5931" t="inlineStr"/>
-      <c r="E5931" t="inlineStr"/>
-      <c r="F5931" t="inlineStr"/>
-      <c r="G5931" t="inlineStr"/>
-      <c r="H5931" t="inlineStr"/>
-      <c r="I5931" t="inlineStr"/>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
     </row>
     <row r="5932">
       <c r="A5932" t="inlineStr">
@@ -70881,16 +70792,9 @@
       </c>
       <c r="B5932" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monstera Deliciosa </t>
-        </is>
-      </c>
-      <c r="C5932" t="inlineStr"/>
-      <c r="D5932" t="inlineStr"/>
-      <c r="E5932" t="inlineStr"/>
-      <c r="F5932" t="inlineStr"/>
-      <c r="G5932" t="inlineStr"/>
-      <c r="H5932" t="inlineStr"/>
-      <c r="I5932" t="inlineStr"/>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
     </row>
     <row r="5933">
       <c r="A5933" t="inlineStr">
@@ -70900,16 +70804,9 @@
       </c>
       <c r="B5933" t="inlineStr">
         <is>
-          <t>Philodendron Imperial Red</t>
-        </is>
-      </c>
-      <c r="C5933" t="inlineStr"/>
-      <c r="D5933" t="inlineStr"/>
-      <c r="E5933" t="inlineStr"/>
-      <c r="F5933" t="inlineStr"/>
-      <c r="G5933" t="inlineStr"/>
-      <c r="H5933" t="inlineStr"/>
-      <c r="I5933" t="inlineStr"/>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
     </row>
     <row r="5934">
       <c r="A5934" t="inlineStr">
@@ -70919,16 +70816,9 @@
       </c>
       <c r="B5934" t="inlineStr">
         <is>
-          <t>Philodendron McColleys Finale</t>
-        </is>
-      </c>
-      <c r="C5934" t="inlineStr"/>
-      <c r="D5934" t="inlineStr"/>
-      <c r="E5934" t="inlineStr"/>
-      <c r="F5934" t="inlineStr"/>
-      <c r="G5934" t="inlineStr"/>
-      <c r="H5934" t="inlineStr"/>
-      <c r="I5934" t="inlineStr"/>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
     </row>
     <row r="5935">
       <c r="A5935" t="inlineStr">
@@ -70938,16 +70828,9 @@
       </c>
       <c r="B5935" t="inlineStr">
         <is>
-          <t>Philodendron Birkin</t>
-        </is>
-      </c>
-      <c r="C5935" t="inlineStr"/>
-      <c r="D5935" t="inlineStr"/>
-      <c r="E5935" t="inlineStr"/>
-      <c r="F5935" t="inlineStr"/>
-      <c r="G5935" t="inlineStr"/>
-      <c r="H5935" t="inlineStr"/>
-      <c r="I5935" t="inlineStr"/>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
     </row>
     <row r="5936">
       <c r="A5936" t="inlineStr">
@@ -70957,16 +70840,9 @@
       </c>
       <c r="B5936" t="inlineStr">
         <is>
-          <t>Rhaphidophora Tetrasperma</t>
-        </is>
-      </c>
-      <c r="C5936" t="inlineStr"/>
-      <c r="D5936" t="inlineStr"/>
-      <c r="E5936" t="inlineStr"/>
-      <c r="F5936" t="inlineStr"/>
-      <c r="G5936" t="inlineStr"/>
-      <c r="H5936" t="inlineStr"/>
-      <c r="I5936" t="inlineStr"/>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
     </row>
     <row r="5937">
       <c r="A5937" t="inlineStr">
@@ -70976,189 +70852,119 @@
       </c>
       <c r="B5937" t="inlineStr">
         <is>
-          <t>Philodendron Scandens Micans little</t>
-        </is>
-      </c>
-      <c r="C5937" t="inlineStr"/>
-      <c r="D5937" t="inlineStr"/>
-      <c r="E5937" t="inlineStr"/>
-      <c r="F5937" t="inlineStr"/>
-      <c r="G5937" t="inlineStr"/>
-      <c r="H5937" t="inlineStr"/>
-      <c r="I5937" t="inlineStr"/>
-    </row>
-    <row r="5938"/>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5938">
+      <c r="A5938" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B5938" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
     <row r="5939">
       <c r="A5939" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="B5939" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum</t>
-        </is>
-      </c>
-      <c r="C5939" t="inlineStr"/>
-      <c r="D5939" t="inlineStr"/>
-      <c r="E5939" t="inlineStr"/>
-      <c r="F5939" t="inlineStr"/>
-      <c r="G5939" t="inlineStr"/>
-      <c r="H5939" t="inlineStr"/>
-      <c r="I5939" t="inlineStr"/>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
     </row>
     <row r="5940">
       <c r="A5940" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="B5940" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philodendron Scandens Micans </t>
-        </is>
-      </c>
-      <c r="C5940" t="inlineStr"/>
-      <c r="D5940" t="inlineStr"/>
-      <c r="E5940" t="inlineStr"/>
-      <c r="F5940" t="inlineStr"/>
-      <c r="G5940" t="inlineStr"/>
-      <c r="H5940" t="inlineStr"/>
-      <c r="I5940" t="inlineStr"/>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
     </row>
     <row r="5941">
       <c r="A5941" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="B5941" t="inlineStr">
         <is>
-          <t>Scindapsus Treubii Moonlight</t>
-        </is>
-      </c>
-      <c r="C5941" t="inlineStr"/>
-      <c r="D5941" t="inlineStr"/>
-      <c r="E5941" t="inlineStr"/>
-      <c r="F5941" t="inlineStr"/>
-      <c r="G5941" t="inlineStr"/>
-      <c r="H5941" t="inlineStr"/>
-      <c r="I5941" t="inlineStr"/>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
     </row>
     <row r="5942">
       <c r="A5942" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="B5942" t="inlineStr">
         <is>
-          <t>Philodendron Hedaracium Brasil</t>
-        </is>
-      </c>
-      <c r="C5942" t="inlineStr"/>
-      <c r="D5942" t="inlineStr"/>
-      <c r="E5942" t="inlineStr"/>
-      <c r="F5942" t="inlineStr"/>
-      <c r="G5942" t="inlineStr"/>
-      <c r="H5942" t="inlineStr"/>
-      <c r="I5942" t="inlineStr"/>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
     </row>
     <row r="5943">
       <c r="A5943" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="B5943" t="inlineStr">
         <is>
-          <t>Monstera Adenossii</t>
-        </is>
-      </c>
-      <c r="C5943" t="inlineStr"/>
-      <c r="D5943" t="inlineStr"/>
-      <c r="E5943" t="inlineStr"/>
-      <c r="F5943" t="inlineStr"/>
-      <c r="G5943" t="inlineStr"/>
-      <c r="H5943" t="inlineStr"/>
-      <c r="I5943" t="inlineStr"/>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
     </row>
     <row r="5944">
       <c r="A5944" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="B5944" t="inlineStr">
         <is>
-          <t>Ficus Elastica Abidjan</t>
-        </is>
-      </c>
-      <c r="C5944" t="inlineStr"/>
-      <c r="D5944" t="inlineStr"/>
-      <c r="E5944" t="inlineStr"/>
-      <c r="F5944" t="inlineStr"/>
-      <c r="G5944" t="inlineStr"/>
-      <c r="H5944" t="inlineStr"/>
-      <c r="I5944" t="inlineStr"/>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
     </row>
     <row r="5945">
       <c r="A5945" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="B5945" t="inlineStr">
         <is>
-          <t>Peperomia Hope</t>
-        </is>
-      </c>
-      <c r="C5945" t="inlineStr"/>
-      <c r="D5945" t="inlineStr"/>
-      <c r="E5945" t="inlineStr"/>
-      <c r="F5945" t="inlineStr"/>
-      <c r="G5945" t="inlineStr"/>
-      <c r="H5945" t="inlineStr"/>
-      <c r="I5945" t="inlineStr"/>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
     </row>
     <row r="5946">
       <c r="A5946" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="B5946" t="inlineStr">
         <is>
-          <t>Hoya Mathilde</t>
-        </is>
-      </c>
-      <c r="C5946" t="inlineStr"/>
-      <c r="D5946" t="inlineStr"/>
-      <c r="E5946" t="inlineStr"/>
-      <c r="F5946" t="inlineStr"/>
-      <c r="G5946" t="inlineStr"/>
-      <c r="H5946" t="inlineStr"/>
-      <c r="I5946" t="inlineStr"/>
-    </row>
-    <row r="5947">
-      <c r="A5947" t="inlineStr">
-        <is>
-          <t>22.04.2026</t>
-        </is>
-      </c>
-      <c r="B5947" t="inlineStr">
-        <is>
-          <t>Epipremnum Pinnatum Blue</t>
-        </is>
-      </c>
-      <c r="C5947" t="inlineStr"/>
-      <c r="D5947" t="inlineStr"/>
-      <c r="E5947" t="inlineStr"/>
-      <c r="F5947" t="inlineStr"/>
-      <c r="G5947" t="inlineStr"/>
-      <c r="H5947" t="inlineStr"/>
-      <c r="I5947" t="inlineStr"/>
-    </row>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5947"/>
     <row r="5948">
       <c r="A5948" t="inlineStr">
         <is>
@@ -71167,16 +70973,9 @@
       </c>
       <c r="B5948" t="inlineStr">
         <is>
-          <t>Sansevieria Laurentii</t>
-        </is>
-      </c>
-      <c r="C5948" t="inlineStr"/>
-      <c r="D5948" t="inlineStr"/>
-      <c r="E5948" t="inlineStr"/>
-      <c r="F5948" t="inlineStr"/>
-      <c r="G5948" t="inlineStr"/>
-      <c r="H5948" t="inlineStr"/>
-      <c r="I5948" t="inlineStr"/>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
     </row>
     <row r="5949">
       <c r="A5949" t="inlineStr">
@@ -71186,16 +70985,9 @@
       </c>
       <c r="B5949" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum Saal</t>
-        </is>
-      </c>
-      <c r="C5949" t="inlineStr"/>
-      <c r="D5949" t="inlineStr"/>
-      <c r="E5949" t="inlineStr"/>
-      <c r="F5949" t="inlineStr"/>
-      <c r="G5949" t="inlineStr"/>
-      <c r="H5949" t="inlineStr"/>
-      <c r="I5949" t="inlineStr"/>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
     </row>
     <row r="5950">
       <c r="A5950" t="inlineStr">
@@ -71205,16 +70997,9 @@
       </c>
       <c r="B5950" t="inlineStr">
         <is>
-          <t>Monstera Deliciosa Variegata</t>
-        </is>
-      </c>
-      <c r="C5950" t="inlineStr"/>
-      <c r="D5950" t="inlineStr"/>
-      <c r="E5950" t="inlineStr"/>
-      <c r="F5950" t="inlineStr"/>
-      <c r="G5950" t="inlineStr"/>
-      <c r="H5950" t="inlineStr"/>
-      <c r="I5950" t="inlineStr"/>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
     </row>
     <row r="5951">
       <c r="A5951" t="inlineStr">
@@ -71224,16 +71009,9 @@
       </c>
       <c r="B5951" t="inlineStr">
         <is>
-          <t>Pachira Aquatica</t>
-        </is>
-      </c>
-      <c r="C5951" t="inlineStr"/>
-      <c r="D5951" t="inlineStr"/>
-      <c r="E5951" t="inlineStr"/>
-      <c r="F5951" t="inlineStr"/>
-      <c r="G5951" t="inlineStr"/>
-      <c r="H5951" t="inlineStr"/>
-      <c r="I5951" t="inlineStr"/>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="5952">
       <c r="A5952" t="inlineStr">
@@ -71243,16 +71021,9 @@
       </c>
       <c r="B5952" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monstera Deliciosa </t>
-        </is>
-      </c>
-      <c r="C5952" t="inlineStr"/>
-      <c r="D5952" t="inlineStr"/>
-      <c r="E5952" t="inlineStr"/>
-      <c r="F5952" t="inlineStr"/>
-      <c r="G5952" t="inlineStr"/>
-      <c r="H5952" t="inlineStr"/>
-      <c r="I5952" t="inlineStr"/>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
     </row>
     <row r="5953">
       <c r="A5953" t="inlineStr">
@@ -71262,16 +71033,9 @@
       </c>
       <c r="B5953" t="inlineStr">
         <is>
-          <t>Philodendron Imperial Red</t>
-        </is>
-      </c>
-      <c r="C5953" t="inlineStr"/>
-      <c r="D5953" t="inlineStr"/>
-      <c r="E5953" t="inlineStr"/>
-      <c r="F5953" t="inlineStr"/>
-      <c r="G5953" t="inlineStr"/>
-      <c r="H5953" t="inlineStr"/>
-      <c r="I5953" t="inlineStr"/>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
     </row>
     <row r="5954">
       <c r="A5954" t="inlineStr">
@@ -71281,16 +71045,9 @@
       </c>
       <c r="B5954" t="inlineStr">
         <is>
-          <t>Philodendron McColleys Finale</t>
-        </is>
-      </c>
-      <c r="C5954" t="inlineStr"/>
-      <c r="D5954" t="inlineStr"/>
-      <c r="E5954" t="inlineStr"/>
-      <c r="F5954" t="inlineStr"/>
-      <c r="G5954" t="inlineStr"/>
-      <c r="H5954" t="inlineStr"/>
-      <c r="I5954" t="inlineStr"/>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
     </row>
     <row r="5955">
       <c r="A5955" t="inlineStr">
@@ -71300,16 +71057,9 @@
       </c>
       <c r="B5955" t="inlineStr">
         <is>
-          <t>Philodendron Birkin</t>
-        </is>
-      </c>
-      <c r="C5955" t="inlineStr"/>
-      <c r="D5955" t="inlineStr"/>
-      <c r="E5955" t="inlineStr"/>
-      <c r="F5955" t="inlineStr"/>
-      <c r="G5955" t="inlineStr"/>
-      <c r="H5955" t="inlineStr"/>
-      <c r="I5955" t="inlineStr"/>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
     </row>
     <row r="5956">
       <c r="A5956" t="inlineStr">
@@ -71319,16 +71069,9 @@
       </c>
       <c r="B5956" t="inlineStr">
         <is>
-          <t>Rhaphidophora Tetrasperma</t>
-        </is>
-      </c>
-      <c r="C5956" t="inlineStr"/>
-      <c r="D5956" t="inlineStr"/>
-      <c r="E5956" t="inlineStr"/>
-      <c r="F5956" t="inlineStr"/>
-      <c r="G5956" t="inlineStr"/>
-      <c r="H5956" t="inlineStr"/>
-      <c r="I5956" t="inlineStr"/>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
     </row>
     <row r="5957">
       <c r="A5957" t="inlineStr">
@@ -71338,246 +71081,155 @@
       </c>
       <c r="B5957" t="inlineStr">
         <is>
-          <t>Philodendron Scandens Micans little</t>
-        </is>
-      </c>
-      <c r="C5957" t="inlineStr"/>
-      <c r="D5957" t="inlineStr"/>
-      <c r="E5957" t="inlineStr"/>
-      <c r="F5957" t="inlineStr"/>
-      <c r="G5957" t="inlineStr"/>
-      <c r="H5957" t="inlineStr"/>
-      <c r="I5957" t="inlineStr"/>
-    </row>
-    <row r="5958"/>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5958">
+      <c r="A5958" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B5958" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
     <row r="5959">
       <c r="A5959" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5959" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum</t>
-        </is>
-      </c>
-      <c r="C5959" t="inlineStr"/>
-      <c r="D5959" t="inlineStr"/>
-      <c r="E5959" t="inlineStr"/>
-      <c r="F5959" t="inlineStr"/>
-      <c r="G5959" t="inlineStr"/>
-      <c r="H5959" t="inlineStr"/>
-      <c r="I5959" t="inlineStr"/>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
     </row>
     <row r="5960">
       <c r="A5960" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5960" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philodendron Scandens Micans </t>
-        </is>
-      </c>
-      <c r="C5960" t="inlineStr"/>
-      <c r="D5960" t="inlineStr"/>
-      <c r="E5960" t="inlineStr"/>
-      <c r="F5960" t="inlineStr"/>
-      <c r="G5960" t="inlineStr"/>
-      <c r="H5960" t="inlineStr"/>
-      <c r="I5960" t="inlineStr"/>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
     </row>
     <row r="5961">
       <c r="A5961" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5961" t="inlineStr">
         <is>
-          <t>Scindapsus Treubii Moonlight</t>
-        </is>
-      </c>
-      <c r="C5961" t="inlineStr"/>
-      <c r="D5961" t="inlineStr"/>
-      <c r="E5961" t="inlineStr"/>
-      <c r="F5961" t="inlineStr"/>
-      <c r="G5961" t="inlineStr"/>
-      <c r="H5961" t="inlineStr"/>
-      <c r="I5961" t="inlineStr"/>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
     </row>
     <row r="5962">
       <c r="A5962" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5962" t="inlineStr">
         <is>
-          <t>Philodendron Hedaracium Brasil</t>
-        </is>
-      </c>
-      <c r="C5962" t="inlineStr"/>
-      <c r="D5962" t="inlineStr"/>
-      <c r="E5962" t="inlineStr"/>
-      <c r="F5962" t="inlineStr"/>
-      <c r="G5962" t="inlineStr"/>
-      <c r="H5962" t="inlineStr"/>
-      <c r="I5962" t="inlineStr"/>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
     </row>
     <row r="5963">
       <c r="A5963" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5963" t="inlineStr">
         <is>
-          <t>Monstera Adenossii</t>
-        </is>
-      </c>
-      <c r="C5963" t="inlineStr"/>
-      <c r="D5963" t="inlineStr"/>
-      <c r="E5963" t="inlineStr"/>
-      <c r="F5963" t="inlineStr"/>
-      <c r="G5963" t="inlineStr"/>
-      <c r="H5963" t="inlineStr"/>
-      <c r="I5963" t="inlineStr"/>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
     </row>
     <row r="5964">
       <c r="A5964" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5964" t="inlineStr">
         <is>
-          <t>Ficus Elastica Abidjan</t>
-        </is>
-      </c>
-      <c r="C5964" t="inlineStr"/>
-      <c r="D5964" t="inlineStr"/>
-      <c r="E5964" t="inlineStr"/>
-      <c r="F5964" t="inlineStr"/>
-      <c r="G5964" t="inlineStr"/>
-      <c r="H5964" t="inlineStr"/>
-      <c r="I5964" t="inlineStr"/>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
     </row>
     <row r="5965">
       <c r="A5965" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5965" t="inlineStr">
         <is>
-          <t>Peperomia Hope</t>
-        </is>
-      </c>
-      <c r="C5965" t="inlineStr"/>
-      <c r="D5965" t="inlineStr"/>
-      <c r="E5965" t="inlineStr"/>
-      <c r="F5965" t="inlineStr"/>
-      <c r="G5965" t="inlineStr"/>
-      <c r="H5965" t="inlineStr"/>
-      <c r="I5965" t="inlineStr"/>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
     </row>
     <row r="5966">
       <c r="A5966" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5966" t="inlineStr">
         <is>
-          <t>Hoya Mathilde</t>
-        </is>
-      </c>
-      <c r="C5966" t="inlineStr"/>
-      <c r="D5966" t="inlineStr"/>
-      <c r="E5966" t="inlineStr"/>
-      <c r="F5966" t="inlineStr"/>
-      <c r="G5966" t="inlineStr"/>
-      <c r="H5966" t="inlineStr"/>
-      <c r="I5966" t="inlineStr"/>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
     </row>
     <row r="5967">
       <c r="A5967" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5967" t="inlineStr">
         <is>
-          <t>Epipremnum Pinnatum Blue</t>
-        </is>
-      </c>
-      <c r="C5967" t="inlineStr"/>
-      <c r="D5967" t="inlineStr"/>
-      <c r="E5967" t="inlineStr"/>
-      <c r="F5967" t="inlineStr"/>
-      <c r="G5967" t="inlineStr"/>
-      <c r="H5967" t="inlineStr"/>
-      <c r="I5967" t="inlineStr"/>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
     </row>
     <row r="5968">
       <c r="A5968" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5968" t="inlineStr">
         <is>
-          <t>Sansevieria Laurentii</t>
-        </is>
-      </c>
-      <c r="C5968" t="inlineStr"/>
-      <c r="D5968" t="inlineStr"/>
-      <c r="E5968" t="inlineStr"/>
-      <c r="F5968" t="inlineStr"/>
-      <c r="G5968" t="inlineStr"/>
-      <c r="H5968" t="inlineStr"/>
-      <c r="I5968" t="inlineStr"/>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
     </row>
     <row r="5969">
       <c r="A5969" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="B5969" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum Saal</t>
-        </is>
-      </c>
-      <c r="C5969" t="inlineStr"/>
-      <c r="D5969" t="inlineStr"/>
-      <c r="E5969" t="inlineStr"/>
-      <c r="F5969" t="inlineStr"/>
-      <c r="G5969" t="inlineStr"/>
-      <c r="H5969" t="inlineStr"/>
-      <c r="I5969" t="inlineStr"/>
-    </row>
-    <row r="5970">
-      <c r="A5970" t="inlineStr">
-        <is>
-          <t>23.04.2026</t>
-        </is>
-      </c>
-      <c r="B5970" t="inlineStr">
-        <is>
-          <t>Monstera Deliciosa Variegata</t>
-        </is>
-      </c>
-      <c r="C5970" t="inlineStr"/>
-      <c r="D5970" t="inlineStr"/>
-      <c r="E5970" t="inlineStr"/>
-      <c r="F5970" t="inlineStr"/>
-      <c r="G5970" t="inlineStr"/>
-      <c r="H5970" t="inlineStr"/>
-      <c r="I5970" t="inlineStr"/>
-    </row>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5970"/>
     <row r="5971">
       <c r="A5971" t="inlineStr">
         <is>
@@ -71586,16 +71238,9 @@
       </c>
       <c r="B5971" t="inlineStr">
         <is>
-          <t>Pachira Aquatica</t>
-        </is>
-      </c>
-      <c r="C5971" t="inlineStr"/>
-      <c r="D5971" t="inlineStr"/>
-      <c r="E5971" t="inlineStr"/>
-      <c r="F5971" t="inlineStr"/>
-      <c r="G5971" t="inlineStr"/>
-      <c r="H5971" t="inlineStr"/>
-      <c r="I5971" t="inlineStr"/>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
     </row>
     <row r="5972">
       <c r="A5972" t="inlineStr">
@@ -71605,16 +71250,9 @@
       </c>
       <c r="B5972" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monstera Deliciosa </t>
-        </is>
-      </c>
-      <c r="C5972" t="inlineStr"/>
-      <c r="D5972" t="inlineStr"/>
-      <c r="E5972" t="inlineStr"/>
-      <c r="F5972" t="inlineStr"/>
-      <c r="G5972" t="inlineStr"/>
-      <c r="H5972" t="inlineStr"/>
-      <c r="I5972" t="inlineStr"/>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
     </row>
     <row r="5973">
       <c r="A5973" t="inlineStr">
@@ -71624,16 +71262,9 @@
       </c>
       <c r="B5973" t="inlineStr">
         <is>
-          <t>Philodendron Imperial Red</t>
-        </is>
-      </c>
-      <c r="C5973" t="inlineStr"/>
-      <c r="D5973" t="inlineStr"/>
-      <c r="E5973" t="inlineStr"/>
-      <c r="F5973" t="inlineStr"/>
-      <c r="G5973" t="inlineStr"/>
-      <c r="H5973" t="inlineStr"/>
-      <c r="I5973" t="inlineStr"/>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
     </row>
     <row r="5974">
       <c r="A5974" t="inlineStr">
@@ -71643,16 +71274,9 @@
       </c>
       <c r="B5974" t="inlineStr">
         <is>
-          <t>Philodendron McColleys Finale</t>
-        </is>
-      </c>
-      <c r="C5974" t="inlineStr"/>
-      <c r="D5974" t="inlineStr"/>
-      <c r="E5974" t="inlineStr"/>
-      <c r="F5974" t="inlineStr"/>
-      <c r="G5974" t="inlineStr"/>
-      <c r="H5974" t="inlineStr"/>
-      <c r="I5974" t="inlineStr"/>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="5975">
       <c r="A5975" t="inlineStr">
@@ -71662,16 +71286,9 @@
       </c>
       <c r="B5975" t="inlineStr">
         <is>
-          <t>Philodendron Birkin</t>
-        </is>
-      </c>
-      <c r="C5975" t="inlineStr"/>
-      <c r="D5975" t="inlineStr"/>
-      <c r="E5975" t="inlineStr"/>
-      <c r="F5975" t="inlineStr"/>
-      <c r="G5975" t="inlineStr"/>
-      <c r="H5975" t="inlineStr"/>
-      <c r="I5975" t="inlineStr"/>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
     </row>
     <row r="5976">
       <c r="A5976" t="inlineStr">
@@ -71681,16 +71298,9 @@
       </c>
       <c r="B5976" t="inlineStr">
         <is>
-          <t>Rhaphidophora Tetrasperma</t>
-        </is>
-      </c>
-      <c r="C5976" t="inlineStr"/>
-      <c r="D5976" t="inlineStr"/>
-      <c r="E5976" t="inlineStr"/>
-      <c r="F5976" t="inlineStr"/>
-      <c r="G5976" t="inlineStr"/>
-      <c r="H5976" t="inlineStr"/>
-      <c r="I5976" t="inlineStr"/>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
     </row>
     <row r="5977">
       <c r="A5977" t="inlineStr">
@@ -71700,303 +71310,191 @@
       </c>
       <c r="B5977" t="inlineStr">
         <is>
-          <t>Philodendron Scandens Micans little</t>
-        </is>
-      </c>
-      <c r="C5977" t="inlineStr"/>
-      <c r="D5977" t="inlineStr"/>
-      <c r="E5977" t="inlineStr"/>
-      <c r="F5977" t="inlineStr"/>
-      <c r="G5977" t="inlineStr"/>
-      <c r="H5977" t="inlineStr"/>
-      <c r="I5977" t="inlineStr"/>
-    </row>
-    <row r="5978"/>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5978">
+      <c r="A5978" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B5978" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
     <row r="5979">
       <c r="A5979" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5979" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum</t>
-        </is>
-      </c>
-      <c r="C5979" t="inlineStr"/>
-      <c r="D5979" t="inlineStr"/>
-      <c r="E5979" t="inlineStr"/>
-      <c r="F5979" t="inlineStr"/>
-      <c r="G5979" t="inlineStr"/>
-      <c r="H5979" t="inlineStr"/>
-      <c r="I5979" t="inlineStr"/>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
     </row>
     <row r="5980">
       <c r="A5980" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5980" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philodendron Scandens Micans </t>
-        </is>
-      </c>
-      <c r="C5980" t="inlineStr"/>
-      <c r="D5980" t="inlineStr"/>
-      <c r="E5980" t="inlineStr"/>
-      <c r="F5980" t="inlineStr"/>
-      <c r="G5980" t="inlineStr"/>
-      <c r="H5980" t="inlineStr"/>
-      <c r="I5980" t="inlineStr"/>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
     </row>
     <row r="5981">
       <c r="A5981" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5981" t="inlineStr">
         <is>
-          <t>Scindapsus Treubii Moonlight</t>
-        </is>
-      </c>
-      <c r="C5981" t="inlineStr"/>
-      <c r="D5981" t="inlineStr"/>
-      <c r="E5981" t="inlineStr"/>
-      <c r="F5981" t="inlineStr"/>
-      <c r="G5981" t="inlineStr"/>
-      <c r="H5981" t="inlineStr"/>
-      <c r="I5981" t="inlineStr"/>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
     </row>
     <row r="5982">
       <c r="A5982" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5982" t="inlineStr">
         <is>
-          <t>Philodendron Hedaracium Brasil</t>
-        </is>
-      </c>
-      <c r="C5982" t="inlineStr"/>
-      <c r="D5982" t="inlineStr"/>
-      <c r="E5982" t="inlineStr"/>
-      <c r="F5982" t="inlineStr"/>
-      <c r="G5982" t="inlineStr"/>
-      <c r="H5982" t="inlineStr"/>
-      <c r="I5982" t="inlineStr"/>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
     </row>
     <row r="5983">
       <c r="A5983" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5983" t="inlineStr">
         <is>
-          <t>Monstera Adenossii</t>
-        </is>
-      </c>
-      <c r="C5983" t="inlineStr"/>
-      <c r="D5983" t="inlineStr"/>
-      <c r="E5983" t="inlineStr"/>
-      <c r="F5983" t="inlineStr"/>
-      <c r="G5983" t="inlineStr"/>
-      <c r="H5983" t="inlineStr"/>
-      <c r="I5983" t="inlineStr"/>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
     </row>
     <row r="5984">
       <c r="A5984" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5984" t="inlineStr">
         <is>
-          <t>Ficus Elastica Abidjan</t>
-        </is>
-      </c>
-      <c r="C5984" t="inlineStr"/>
-      <c r="D5984" t="inlineStr"/>
-      <c r="E5984" t="inlineStr"/>
-      <c r="F5984" t="inlineStr"/>
-      <c r="G5984" t="inlineStr"/>
-      <c r="H5984" t="inlineStr"/>
-      <c r="I5984" t="inlineStr"/>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
     </row>
     <row r="5985">
       <c r="A5985" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5985" t="inlineStr">
         <is>
-          <t>Peperomia Hope</t>
-        </is>
-      </c>
-      <c r="C5985" t="inlineStr"/>
-      <c r="D5985" t="inlineStr"/>
-      <c r="E5985" t="inlineStr"/>
-      <c r="F5985" t="inlineStr"/>
-      <c r="G5985" t="inlineStr"/>
-      <c r="H5985" t="inlineStr"/>
-      <c r="I5985" t="inlineStr"/>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
     </row>
     <row r="5986">
       <c r="A5986" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5986" t="inlineStr">
         <is>
-          <t>Hoya Mathilde</t>
-        </is>
-      </c>
-      <c r="C5986" t="inlineStr"/>
-      <c r="D5986" t="inlineStr"/>
-      <c r="E5986" t="inlineStr"/>
-      <c r="F5986" t="inlineStr"/>
-      <c r="G5986" t="inlineStr"/>
-      <c r="H5986" t="inlineStr"/>
-      <c r="I5986" t="inlineStr"/>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
     </row>
     <row r="5987">
       <c r="A5987" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5987" t="inlineStr">
         <is>
-          <t>Epipremnum Pinnatum Blue</t>
-        </is>
-      </c>
-      <c r="C5987" t="inlineStr"/>
-      <c r="D5987" t="inlineStr"/>
-      <c r="E5987" t="inlineStr"/>
-      <c r="F5987" t="inlineStr"/>
-      <c r="G5987" t="inlineStr"/>
-      <c r="H5987" t="inlineStr"/>
-      <c r="I5987" t="inlineStr"/>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
     </row>
     <row r="5988">
       <c r="A5988" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5988" t="inlineStr">
         <is>
-          <t>Sansevieria Laurentii</t>
-        </is>
-      </c>
-      <c r="C5988" t="inlineStr"/>
-      <c r="D5988" t="inlineStr"/>
-      <c r="E5988" t="inlineStr"/>
-      <c r="F5988" t="inlineStr"/>
-      <c r="G5988" t="inlineStr"/>
-      <c r="H5988" t="inlineStr"/>
-      <c r="I5988" t="inlineStr"/>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
     </row>
     <row r="5989">
       <c r="A5989" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5989" t="inlineStr">
         <is>
-          <t>Epipremnum Aureum Saal</t>
-        </is>
-      </c>
-      <c r="C5989" t="inlineStr"/>
-      <c r="D5989" t="inlineStr"/>
-      <c r="E5989" t="inlineStr"/>
-      <c r="F5989" t="inlineStr"/>
-      <c r="G5989" t="inlineStr"/>
-      <c r="H5989" t="inlineStr"/>
-      <c r="I5989" t="inlineStr"/>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
     </row>
     <row r="5990">
       <c r="A5990" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5990" t="inlineStr">
         <is>
-          <t>Monstera Deliciosa Variegata</t>
-        </is>
-      </c>
-      <c r="C5990" t="inlineStr"/>
-      <c r="D5990" t="inlineStr"/>
-      <c r="E5990" t="inlineStr"/>
-      <c r="F5990" t="inlineStr"/>
-      <c r="G5990" t="inlineStr"/>
-      <c r="H5990" t="inlineStr"/>
-      <c r="I5990" t="inlineStr"/>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
     </row>
     <row r="5991">
       <c r="A5991" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5991" t="inlineStr">
         <is>
-          <t>Pachira Aquatica</t>
-        </is>
-      </c>
-      <c r="C5991" t="inlineStr"/>
-      <c r="D5991" t="inlineStr"/>
-      <c r="E5991" t="inlineStr"/>
-      <c r="F5991" t="inlineStr"/>
-      <c r="G5991" t="inlineStr"/>
-      <c r="H5991" t="inlineStr"/>
-      <c r="I5991" t="inlineStr"/>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
     </row>
     <row r="5992">
       <c r="A5992" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="B5992" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monstera Deliciosa </t>
-        </is>
-      </c>
-      <c r="C5992" t="inlineStr"/>
-      <c r="D5992" t="inlineStr"/>
-      <c r="E5992" t="inlineStr"/>
-      <c r="F5992" t="inlineStr"/>
-      <c r="G5992" t="inlineStr"/>
-      <c r="H5992" t="inlineStr"/>
-      <c r="I5992" t="inlineStr"/>
-    </row>
-    <row r="5993">
-      <c r="A5993" t="inlineStr">
-        <is>
-          <t>24.04.2026</t>
-        </is>
-      </c>
-      <c r="B5993" t="inlineStr">
-        <is>
-          <t>Philodendron Imperial Red</t>
-        </is>
-      </c>
-      <c r="C5993" t="inlineStr"/>
-      <c r="D5993" t="inlineStr"/>
-      <c r="E5993" t="inlineStr"/>
-      <c r="F5993" t="inlineStr"/>
-      <c r="G5993" t="inlineStr"/>
-      <c r="H5993" t="inlineStr"/>
-      <c r="I5993" t="inlineStr"/>
-    </row>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5993"/>
     <row r="5994">
       <c r="A5994" t="inlineStr">
         <is>
@@ -72005,16 +71503,9 @@
       </c>
       <c r="B5994" t="inlineStr">
         <is>
-          <t>Philodendron McColleys Finale</t>
-        </is>
-      </c>
-      <c r="C5994" t="inlineStr"/>
-      <c r="D5994" t="inlineStr"/>
-      <c r="E5994" t="inlineStr"/>
-      <c r="F5994" t="inlineStr"/>
-      <c r="G5994" t="inlineStr"/>
-      <c r="H5994" t="inlineStr"/>
-      <c r="I5994" t="inlineStr"/>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
     </row>
     <row r="5995">
       <c r="A5995" t="inlineStr">
@@ -72024,16 +71515,9 @@
       </c>
       <c r="B5995" t="inlineStr">
         <is>
-          <t>Philodendron Birkin</t>
-        </is>
-      </c>
-      <c r="C5995" t="inlineStr"/>
-      <c r="D5995" t="inlineStr"/>
-      <c r="E5995" t="inlineStr"/>
-      <c r="F5995" t="inlineStr"/>
-      <c r="G5995" t="inlineStr"/>
-      <c r="H5995" t="inlineStr"/>
-      <c r="I5995" t="inlineStr"/>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
     </row>
     <row r="5996">
       <c r="A5996" t="inlineStr">
@@ -72043,16 +71527,9 @@
       </c>
       <c r="B5996" t="inlineStr">
         <is>
-          <t>Rhaphidophora Tetrasperma</t>
-        </is>
-      </c>
-      <c r="C5996" t="inlineStr"/>
-      <c r="D5996" t="inlineStr"/>
-      <c r="E5996" t="inlineStr"/>
-      <c r="F5996" t="inlineStr"/>
-      <c r="G5996" t="inlineStr"/>
-      <c r="H5996" t="inlineStr"/>
-      <c r="I5996" t="inlineStr"/>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
     </row>
     <row r="5997">
       <c r="A5997" t="inlineStr">
@@ -72062,18 +71539,757 @@
       </c>
       <c r="B5997" t="inlineStr">
         <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5998">
+      <c r="A5998" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5998" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5999">
+      <c r="A5999" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B5999" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6000">
+      <c r="A6000" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6000" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="6001">
+      <c r="A6001" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6001" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="6002">
+      <c r="A6002" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6002" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6003">
+      <c r="A6003" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6003" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6004">
+      <c r="A6004" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6004" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6005">
+      <c r="A6005" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6005" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="6006">
+      <c r="A6006" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6006" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="6007">
+      <c r="A6007" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6007" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="6008">
+      <c r="A6008" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6008" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="6009">
+      <c r="A6009" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6009" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="6010">
+      <c r="A6010" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6010" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6011">
+      <c r="A6011" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6011" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="6012">
+      <c r="A6012" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6012" t="inlineStr">
+        <is>
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C5997" t="inlineStr"/>
-      <c r="D5997" t="inlineStr"/>
-      <c r="E5997" t="inlineStr"/>
-      <c r="F5997" t="inlineStr"/>
-      <c r="G5997" t="inlineStr"/>
-      <c r="H5997" t="inlineStr"/>
-      <c r="I5997" t="inlineStr"/>
-    </row>
-    <row r="5998"/>
+    </row>
+    <row r="6013">
+      <c r="A6013" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6013" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6014">
+      <c r="A6014" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6014" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6015">
+      <c r="A6015" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B6015" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6016"/>
+    <row r="6017">
+      <c r="A6017" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6017" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="6018">
+      <c r="A6018" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6018" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="6019">
+      <c r="A6019" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6019" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6020">
+      <c r="A6020" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6020" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6021">
+      <c r="A6021" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6021" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6022">
+      <c r="A6022" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6022" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6023">
+      <c r="A6023" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6023" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="6024">
+      <c r="A6024" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6024" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="6025">
+      <c r="A6025" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6025" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6026">
+      <c r="A6026" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6026" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6027">
+      <c r="A6027" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6027" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6028">
+      <c r="A6028" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6028" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="6029">
+      <c r="A6029" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6029" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="6030">
+      <c r="A6030" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6030" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="6031">
+      <c r="A6031" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6031" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="6032">
+      <c r="A6032" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6032" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="6033">
+      <c r="A6033" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6033" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6034">
+      <c r="A6034" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6034" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="6035">
+      <c r="A6035" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6035" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="6036">
+      <c r="A6036" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6036" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6037">
+      <c r="A6037" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6037" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6038">
+      <c r="A6038" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="B6038" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6039"/>
+    <row r="6040">
+      <c r="A6040" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6040" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="6041">
+      <c r="A6041" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6041" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="6042">
+      <c r="A6042" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6042" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6043">
+      <c r="A6043" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6043" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6044">
+      <c r="A6044" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6044" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6045">
+      <c r="A6045" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6045" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6046">
+      <c r="A6046" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6046" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="6047">
+      <c r="A6047" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6047" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="6048">
+      <c r="A6048" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6048" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6049">
+      <c r="A6049" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6049" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6050">
+      <c r="A6050" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6050" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6051">
+      <c r="A6051" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6051" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="6052">
+      <c r="A6052" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6052" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="6053">
+      <c r="A6053" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6053" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="6054">
+      <c r="A6054" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6054" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="6055">
+      <c r="A6055" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6055" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="6056">
+      <c r="A6056" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6056" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6057">
+      <c r="A6057" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6057" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="6058">
+      <c r="A6058" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6058" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="6059">
+      <c r="A6059" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6059" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6060">
+      <c r="A6060" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6060" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6061">
+      <c r="A6061" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="B6061" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6062"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/data/blumen_data.xlsx
+++ b/data/blumen_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="5475" windowWidth="16440" windowHeight="28320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6062"/>
+  <dimension ref="A1:AC6154"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -70458,6 +70458,14 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
+      <c r="D5903" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5903" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5904">
       <c r="A5904" t="inlineStr">
@@ -70542,6 +70550,14 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
+      <c r="D5910" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5910" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5911">
       <c r="A5911" t="inlineStr">
@@ -70590,6 +70606,14 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
+      <c r="D5914" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5914" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5915">
       <c r="A5915" t="inlineStr">
@@ -70696,6 +70720,14 @@
       <c r="B5923" t="inlineStr">
         <is>
           <t>Ledebouria socialis</t>
+        </is>
+      </c>
+      <c r="D5923" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5923" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -71807,6 +71839,14 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
+      <c r="D6020" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6020" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6021">
       <c r="A6021" t="inlineStr">
@@ -71819,6 +71859,14 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
+      <c r="D6021" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6021" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6022">
       <c r="A6022" t="inlineStr">
@@ -71843,6 +71891,14 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
+      <c r="D6023" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6023" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6024">
       <c r="A6024" t="inlineStr">
@@ -71855,6 +71911,14 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
+      <c r="D6024" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6024" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6025">
       <c r="A6025" t="inlineStr">
@@ -71879,6 +71943,14 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
+      <c r="D6026" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6026" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6027">
       <c r="A6027" t="inlineStr">
@@ -71891,6 +71963,14 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
+      <c r="D6027" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6027" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6028">
       <c r="A6028" t="inlineStr">
@@ -71927,6 +72007,14 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
+      <c r="D6030" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6030" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6031">
       <c r="A6031" t="inlineStr">
@@ -71975,6 +72063,14 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
+      <c r="D6034" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6034" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6035">
       <c r="A6035" t="inlineStr">
@@ -72009,6 +72105,14 @@
       <c r="B6037" t="inlineStr">
         <is>
           <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+      <c r="D6037" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6037" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -72290,6 +72394,1374 @@
       </c>
     </row>
     <row r="6062"/>
+    <row r="6063">
+      <c r="A6063" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6063" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="6064">
+      <c r="A6064" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6064" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="6065">
+      <c r="A6065" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6065" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6066">
+      <c r="A6066" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6066" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6067">
+      <c r="A6067" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6067" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6068">
+      <c r="A6068" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6068" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6069">
+      <c r="A6069" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6069" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="6070">
+      <c r="A6070" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6070" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="6071">
+      <c r="A6071" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6071" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6072">
+      <c r="A6072" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6072" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6073">
+      <c r="A6073" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6073" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6074">
+      <c r="A6074" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6074" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="6075">
+      <c r="A6075" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6075" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="6076">
+      <c r="A6076" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6076" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="6077">
+      <c r="A6077" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6077" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="6078">
+      <c r="A6078" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6078" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="6079">
+      <c r="A6079" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6079" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6080">
+      <c r="A6080" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6080" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="6081">
+      <c r="A6081" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6081" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="6082">
+      <c r="A6082" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6082" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6083">
+      <c r="A6083" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6083" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6084">
+      <c r="A6084" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="B6084" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6085"/>
+    <row r="6086">
+      <c r="A6086" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6086" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="6087">
+      <c r="A6087" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6087" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="6088">
+      <c r="A6088" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6088" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6089">
+      <c r="A6089" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6089" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6090">
+      <c r="A6090" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6090" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6091">
+      <c r="A6091" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6091" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6092">
+      <c r="A6092" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6092" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="6093">
+      <c r="A6093" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6093" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="6094">
+      <c r="A6094" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6094" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6095">
+      <c r="A6095" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6095" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6096">
+      <c r="A6096" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6096" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6097">
+      <c r="A6097" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6097" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="6098">
+      <c r="A6098" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6098" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="6099">
+      <c r="A6099" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6099" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="6100">
+      <c r="A6100" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6100" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="6101">
+      <c r="A6101" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6101" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="6102">
+      <c r="A6102" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6102" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6103">
+      <c r="A6103" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6103" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="6104">
+      <c r="A6104" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6104" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="6105">
+      <c r="A6105" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6105" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6106">
+      <c r="A6106" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6106" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6107">
+      <c r="A6107" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B6107" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6108"/>
+    <row r="6109">
+      <c r="A6109" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6109" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C6109" t="inlineStr"/>
+      <c r="D6109" t="inlineStr"/>
+      <c r="E6109" t="inlineStr"/>
+      <c r="F6109" t="inlineStr"/>
+      <c r="G6109" t="inlineStr"/>
+      <c r="H6109" t="inlineStr"/>
+      <c r="I6109" t="inlineStr"/>
+    </row>
+    <row r="6110">
+      <c r="A6110" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C6110" t="inlineStr"/>
+      <c r="D6110" t="inlineStr"/>
+      <c r="E6110" t="inlineStr"/>
+      <c r="F6110" t="inlineStr"/>
+      <c r="G6110" t="inlineStr"/>
+      <c r="H6110" t="inlineStr"/>
+      <c r="I6110" t="inlineStr"/>
+    </row>
+    <row r="6111">
+      <c r="A6111" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6111" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C6111" t="inlineStr"/>
+      <c r="D6111" t="inlineStr"/>
+      <c r="E6111" t="inlineStr"/>
+      <c r="F6111" t="inlineStr"/>
+      <c r="G6111" t="inlineStr"/>
+      <c r="H6111" t="inlineStr"/>
+      <c r="I6111" t="inlineStr"/>
+    </row>
+    <row r="6112">
+      <c r="A6112" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6112" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C6112" t="inlineStr"/>
+      <c r="D6112" t="inlineStr"/>
+      <c r="E6112" t="inlineStr"/>
+      <c r="F6112" t="inlineStr"/>
+      <c r="G6112" t="inlineStr"/>
+      <c r="H6112" t="inlineStr"/>
+      <c r="I6112" t="inlineStr"/>
+    </row>
+    <row r="6113">
+      <c r="A6113" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6113" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C6113" t="inlineStr"/>
+      <c r="D6113" t="inlineStr"/>
+      <c r="E6113" t="inlineStr"/>
+      <c r="F6113" t="inlineStr"/>
+      <c r="G6113" t="inlineStr"/>
+      <c r="H6113" t="inlineStr"/>
+      <c r="I6113" t="inlineStr"/>
+    </row>
+    <row r="6114">
+      <c r="A6114" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6114" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C6114" t="inlineStr"/>
+      <c r="D6114" t="inlineStr"/>
+      <c r="E6114" t="inlineStr"/>
+      <c r="F6114" t="inlineStr"/>
+      <c r="G6114" t="inlineStr"/>
+      <c r="H6114" t="inlineStr"/>
+      <c r="I6114" t="inlineStr"/>
+    </row>
+    <row r="6115">
+      <c r="A6115" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6115" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C6115" t="inlineStr"/>
+      <c r="D6115" t="inlineStr"/>
+      <c r="E6115" t="inlineStr"/>
+      <c r="F6115" t="inlineStr"/>
+      <c r="G6115" t="inlineStr"/>
+      <c r="H6115" t="inlineStr"/>
+      <c r="I6115" t="inlineStr"/>
+    </row>
+    <row r="6116">
+      <c r="A6116" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6116" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C6116" t="inlineStr"/>
+      <c r="D6116" t="inlineStr"/>
+      <c r="E6116" t="inlineStr"/>
+      <c r="F6116" t="inlineStr"/>
+      <c r="G6116" t="inlineStr"/>
+      <c r="H6116" t="inlineStr"/>
+      <c r="I6116" t="inlineStr"/>
+    </row>
+    <row r="6117">
+      <c r="A6117" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6117" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C6117" t="inlineStr"/>
+      <c r="D6117" t="inlineStr"/>
+      <c r="E6117" t="inlineStr"/>
+      <c r="F6117" t="inlineStr"/>
+      <c r="G6117" t="inlineStr"/>
+      <c r="H6117" t="inlineStr"/>
+      <c r="I6117" t="inlineStr"/>
+    </row>
+    <row r="6118">
+      <c r="A6118" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6118" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C6118" t="inlineStr"/>
+      <c r="D6118" t="inlineStr"/>
+      <c r="E6118" t="inlineStr"/>
+      <c r="F6118" t="inlineStr"/>
+      <c r="G6118" t="inlineStr"/>
+      <c r="H6118" t="inlineStr"/>
+      <c r="I6118" t="inlineStr"/>
+    </row>
+    <row r="6119">
+      <c r="A6119" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6119" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C6119" t="inlineStr"/>
+      <c r="D6119" t="inlineStr"/>
+      <c r="E6119" t="inlineStr"/>
+      <c r="F6119" t="inlineStr"/>
+      <c r="G6119" t="inlineStr"/>
+      <c r="H6119" t="inlineStr"/>
+      <c r="I6119" t="inlineStr"/>
+    </row>
+    <row r="6120">
+      <c r="A6120" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6120" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C6120" t="inlineStr"/>
+      <c r="D6120" t="inlineStr"/>
+      <c r="E6120" t="inlineStr"/>
+      <c r="F6120" t="inlineStr"/>
+      <c r="G6120" t="inlineStr"/>
+      <c r="H6120" t="inlineStr"/>
+      <c r="I6120" t="inlineStr"/>
+    </row>
+    <row r="6121">
+      <c r="A6121" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6121" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C6121" t="inlineStr"/>
+      <c r="D6121" t="inlineStr"/>
+      <c r="E6121" t="inlineStr"/>
+      <c r="F6121" t="inlineStr"/>
+      <c r="G6121" t="inlineStr"/>
+      <c r="H6121" t="inlineStr"/>
+      <c r="I6121" t="inlineStr"/>
+    </row>
+    <row r="6122">
+      <c r="A6122" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C6122" t="inlineStr"/>
+      <c r="D6122" t="inlineStr"/>
+      <c r="E6122" t="inlineStr"/>
+      <c r="F6122" t="inlineStr"/>
+      <c r="G6122" t="inlineStr"/>
+      <c r="H6122" t="inlineStr"/>
+      <c r="I6122" t="inlineStr"/>
+    </row>
+    <row r="6123">
+      <c r="A6123" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6123" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C6123" t="inlineStr"/>
+      <c r="D6123" t="inlineStr"/>
+      <c r="E6123" t="inlineStr"/>
+      <c r="F6123" t="inlineStr"/>
+      <c r="G6123" t="inlineStr"/>
+      <c r="H6123" t="inlineStr"/>
+      <c r="I6123" t="inlineStr"/>
+    </row>
+    <row r="6124">
+      <c r="A6124" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6124" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C6124" t="inlineStr"/>
+      <c r="D6124" t="inlineStr"/>
+      <c r="E6124" t="inlineStr"/>
+      <c r="F6124" t="inlineStr"/>
+      <c r="G6124" t="inlineStr"/>
+      <c r="H6124" t="inlineStr"/>
+      <c r="I6124" t="inlineStr"/>
+    </row>
+    <row r="6125">
+      <c r="A6125" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6125" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C6125" t="inlineStr"/>
+      <c r="D6125" t="inlineStr"/>
+      <c r="E6125" t="inlineStr"/>
+      <c r="F6125" t="inlineStr"/>
+      <c r="G6125" t="inlineStr"/>
+      <c r="H6125" t="inlineStr"/>
+      <c r="I6125" t="inlineStr"/>
+    </row>
+    <row r="6126">
+      <c r="A6126" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6126" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C6126" t="inlineStr"/>
+      <c r="D6126" t="inlineStr"/>
+      <c r="E6126" t="inlineStr"/>
+      <c r="F6126" t="inlineStr"/>
+      <c r="G6126" t="inlineStr"/>
+      <c r="H6126" t="inlineStr"/>
+      <c r="I6126" t="inlineStr"/>
+    </row>
+    <row r="6127">
+      <c r="A6127" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6127" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C6127" t="inlineStr"/>
+      <c r="D6127" t="inlineStr"/>
+      <c r="E6127" t="inlineStr"/>
+      <c r="F6127" t="inlineStr"/>
+      <c r="G6127" t="inlineStr"/>
+      <c r="H6127" t="inlineStr"/>
+      <c r="I6127" t="inlineStr"/>
+    </row>
+    <row r="6128">
+      <c r="A6128" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6128" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+      <c r="C6128" t="inlineStr"/>
+      <c r="D6128" t="inlineStr"/>
+      <c r="E6128" t="inlineStr"/>
+      <c r="F6128" t="inlineStr"/>
+      <c r="G6128" t="inlineStr"/>
+      <c r="H6128" t="inlineStr"/>
+      <c r="I6128" t="inlineStr"/>
+    </row>
+    <row r="6129">
+      <c r="A6129" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6129" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+      <c r="C6129" t="inlineStr"/>
+      <c r="D6129" t="inlineStr"/>
+      <c r="E6129" t="inlineStr"/>
+      <c r="F6129" t="inlineStr"/>
+      <c r="G6129" t="inlineStr"/>
+      <c r="H6129" t="inlineStr"/>
+      <c r="I6129" t="inlineStr"/>
+    </row>
+    <row r="6130">
+      <c r="A6130" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="B6130" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+      <c r="C6130" t="inlineStr"/>
+      <c r="D6130" t="inlineStr"/>
+      <c r="E6130" t="inlineStr"/>
+      <c r="F6130" t="inlineStr"/>
+      <c r="G6130" t="inlineStr"/>
+      <c r="H6130" t="inlineStr"/>
+      <c r="I6130" t="inlineStr"/>
+    </row>
+    <row r="6131"/>
+    <row r="6132">
+      <c r="A6132" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6132" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C6132" t="inlineStr"/>
+      <c r="D6132" t="inlineStr"/>
+      <c r="E6132" t="inlineStr"/>
+      <c r="F6132" t="inlineStr"/>
+      <c r="G6132" t="inlineStr"/>
+      <c r="H6132" t="inlineStr"/>
+      <c r="I6132" t="inlineStr"/>
+    </row>
+    <row r="6133">
+      <c r="A6133" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C6133" t="inlineStr"/>
+      <c r="D6133" t="inlineStr"/>
+      <c r="E6133" t="inlineStr"/>
+      <c r="F6133" t="inlineStr"/>
+      <c r="G6133" t="inlineStr"/>
+      <c r="H6133" t="inlineStr"/>
+      <c r="I6133" t="inlineStr"/>
+    </row>
+    <row r="6134">
+      <c r="A6134" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6134" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C6134" t="inlineStr"/>
+      <c r="D6134" t="inlineStr"/>
+      <c r="E6134" t="inlineStr"/>
+      <c r="F6134" t="inlineStr"/>
+      <c r="G6134" t="inlineStr"/>
+      <c r="H6134" t="inlineStr"/>
+      <c r="I6134" t="inlineStr"/>
+    </row>
+    <row r="6135">
+      <c r="A6135" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6135" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C6135" t="inlineStr"/>
+      <c r="D6135" t="inlineStr"/>
+      <c r="E6135" t="inlineStr"/>
+      <c r="F6135" t="inlineStr"/>
+      <c r="G6135" t="inlineStr"/>
+      <c r="H6135" t="inlineStr"/>
+      <c r="I6135" t="inlineStr"/>
+    </row>
+    <row r="6136">
+      <c r="A6136" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6136" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C6136" t="inlineStr"/>
+      <c r="D6136" t="inlineStr"/>
+      <c r="E6136" t="inlineStr"/>
+      <c r="F6136" t="inlineStr"/>
+      <c r="G6136" t="inlineStr"/>
+      <c r="H6136" t="inlineStr"/>
+      <c r="I6136" t="inlineStr"/>
+    </row>
+    <row r="6137">
+      <c r="A6137" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6137" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C6137" t="inlineStr"/>
+      <c r="D6137" t="inlineStr"/>
+      <c r="E6137" t="inlineStr"/>
+      <c r="F6137" t="inlineStr"/>
+      <c r="G6137" t="inlineStr"/>
+      <c r="H6137" t="inlineStr"/>
+      <c r="I6137" t="inlineStr"/>
+    </row>
+    <row r="6138">
+      <c r="A6138" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6138" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C6138" t="inlineStr"/>
+      <c r="D6138" t="inlineStr"/>
+      <c r="E6138" t="inlineStr"/>
+      <c r="F6138" t="inlineStr"/>
+      <c r="G6138" t="inlineStr"/>
+      <c r="H6138" t="inlineStr"/>
+      <c r="I6138" t="inlineStr"/>
+    </row>
+    <row r="6139">
+      <c r="A6139" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6139" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C6139" t="inlineStr"/>
+      <c r="D6139" t="inlineStr"/>
+      <c r="E6139" t="inlineStr"/>
+      <c r="F6139" t="inlineStr"/>
+      <c r="G6139" t="inlineStr"/>
+      <c r="H6139" t="inlineStr"/>
+      <c r="I6139" t="inlineStr"/>
+    </row>
+    <row r="6140">
+      <c r="A6140" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6140" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C6140" t="inlineStr"/>
+      <c r="D6140" t="inlineStr"/>
+      <c r="E6140" t="inlineStr"/>
+      <c r="F6140" t="inlineStr"/>
+      <c r="G6140" t="inlineStr"/>
+      <c r="H6140" t="inlineStr"/>
+      <c r="I6140" t="inlineStr"/>
+    </row>
+    <row r="6141">
+      <c r="A6141" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6141" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C6141" t="inlineStr"/>
+      <c r="D6141" t="inlineStr"/>
+      <c r="E6141" t="inlineStr"/>
+      <c r="F6141" t="inlineStr"/>
+      <c r="G6141" t="inlineStr"/>
+      <c r="H6141" t="inlineStr"/>
+      <c r="I6141" t="inlineStr"/>
+    </row>
+    <row r="6142">
+      <c r="A6142" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6142" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C6142" t="inlineStr"/>
+      <c r="D6142" t="inlineStr"/>
+      <c r="E6142" t="inlineStr"/>
+      <c r="F6142" t="inlineStr"/>
+      <c r="G6142" t="inlineStr"/>
+      <c r="H6142" t="inlineStr"/>
+      <c r="I6142" t="inlineStr"/>
+    </row>
+    <row r="6143">
+      <c r="A6143" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6143" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C6143" t="inlineStr"/>
+      <c r="D6143" t="inlineStr"/>
+      <c r="E6143" t="inlineStr"/>
+      <c r="F6143" t="inlineStr"/>
+      <c r="G6143" t="inlineStr"/>
+      <c r="H6143" t="inlineStr"/>
+      <c r="I6143" t="inlineStr"/>
+    </row>
+    <row r="6144">
+      <c r="A6144" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6144" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C6144" t="inlineStr"/>
+      <c r="D6144" t="inlineStr"/>
+      <c r="E6144" t="inlineStr"/>
+      <c r="F6144" t="inlineStr"/>
+      <c r="G6144" t="inlineStr"/>
+      <c r="H6144" t="inlineStr"/>
+      <c r="I6144" t="inlineStr"/>
+    </row>
+    <row r="6145">
+      <c r="A6145" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C6145" t="inlineStr"/>
+      <c r="D6145" t="inlineStr"/>
+      <c r="E6145" t="inlineStr"/>
+      <c r="F6145" t="inlineStr"/>
+      <c r="G6145" t="inlineStr"/>
+      <c r="H6145" t="inlineStr"/>
+      <c r="I6145" t="inlineStr"/>
+    </row>
+    <row r="6146">
+      <c r="A6146" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6146" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C6146" t="inlineStr"/>
+      <c r="D6146" t="inlineStr"/>
+      <c r="E6146" t="inlineStr"/>
+      <c r="F6146" t="inlineStr"/>
+      <c r="G6146" t="inlineStr"/>
+      <c r="H6146" t="inlineStr"/>
+      <c r="I6146" t="inlineStr"/>
+    </row>
+    <row r="6147">
+      <c r="A6147" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6147" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C6147" t="inlineStr"/>
+      <c r="D6147" t="inlineStr"/>
+      <c r="E6147" t="inlineStr"/>
+      <c r="F6147" t="inlineStr"/>
+      <c r="G6147" t="inlineStr"/>
+      <c r="H6147" t="inlineStr"/>
+      <c r="I6147" t="inlineStr"/>
+    </row>
+    <row r="6148">
+      <c r="A6148" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6148" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C6148" t="inlineStr"/>
+      <c r="D6148" t="inlineStr"/>
+      <c r="E6148" t="inlineStr"/>
+      <c r="F6148" t="inlineStr"/>
+      <c r="G6148" t="inlineStr"/>
+      <c r="H6148" t="inlineStr"/>
+      <c r="I6148" t="inlineStr"/>
+    </row>
+    <row r="6149">
+      <c r="A6149" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6149" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C6149" t="inlineStr"/>
+      <c r="D6149" t="inlineStr"/>
+      <c r="E6149" t="inlineStr"/>
+      <c r="F6149" t="inlineStr"/>
+      <c r="G6149" t="inlineStr"/>
+      <c r="H6149" t="inlineStr"/>
+      <c r="I6149" t="inlineStr"/>
+    </row>
+    <row r="6150">
+      <c r="A6150" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6150" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C6150" t="inlineStr"/>
+      <c r="D6150" t="inlineStr"/>
+      <c r="E6150" t="inlineStr"/>
+      <c r="F6150" t="inlineStr"/>
+      <c r="G6150" t="inlineStr"/>
+      <c r="H6150" t="inlineStr"/>
+      <c r="I6150" t="inlineStr"/>
+    </row>
+    <row r="6151">
+      <c r="A6151" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6151" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+      <c r="C6151" t="inlineStr"/>
+      <c r="D6151" t="inlineStr"/>
+      <c r="E6151" t="inlineStr"/>
+      <c r="F6151" t="inlineStr"/>
+      <c r="G6151" t="inlineStr"/>
+      <c r="H6151" t="inlineStr"/>
+      <c r="I6151" t="inlineStr"/>
+    </row>
+    <row r="6152">
+      <c r="A6152" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6152" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+      <c r="C6152" t="inlineStr"/>
+      <c r="D6152" t="inlineStr"/>
+      <c r="E6152" t="inlineStr"/>
+      <c r="F6152" t="inlineStr"/>
+      <c r="G6152" t="inlineStr"/>
+      <c r="H6152" t="inlineStr"/>
+      <c r="I6152" t="inlineStr"/>
+    </row>
+    <row r="6153">
+      <c r="A6153" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="B6153" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+      <c r="C6153" t="inlineStr"/>
+      <c r="D6153" t="inlineStr"/>
+      <c r="E6153" t="inlineStr"/>
+      <c r="F6153" t="inlineStr"/>
+      <c r="G6153" t="inlineStr"/>
+      <c r="H6153" t="inlineStr"/>
+      <c r="I6153" t="inlineStr"/>
+    </row>
+    <row r="6154"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/data/blumen_data.xlsx
+++ b/data/blumen_data.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6154"/>
+  <dimension ref="A1:AC6177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -71574,6 +71574,14 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
+      <c r="D5997" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5997" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5998">
       <c r="A5998" t="inlineStr">
@@ -71586,6 +71594,14 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
+      <c r="D5998" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5998" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="5999">
       <c r="A5999" t="inlineStr">
@@ -71610,6 +71626,14 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
+      <c r="D6000" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6000" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6001">
       <c r="A6001" t="inlineStr">
@@ -71622,6 +71646,14 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
+      <c r="D6001" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6001" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6002">
       <c r="A6002" t="inlineStr">
@@ -71646,6 +71678,14 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
+      <c r="D6003" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6003" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6004">
       <c r="A6004" t="inlineStr">
@@ -71658,6 +71698,14 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
+      <c r="D6004" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6004" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6005">
       <c r="A6005" t="inlineStr">
@@ -71694,6 +71742,14 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
+      <c r="D6007" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6007" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6008">
       <c r="A6008" t="inlineStr">
@@ -71742,6 +71798,14 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
+      <c r="D6011" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6011" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6012">
       <c r="A6012" t="inlineStr">
@@ -71776,6 +71840,14 @@
       <c r="B6014" t="inlineStr">
         <is>
           <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+      <c r="D6014" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6014" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -71839,14 +71911,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="D6020" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6020" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
-        </is>
-      </c>
     </row>
     <row r="6021">
       <c r="A6021" t="inlineStr">
@@ -71859,14 +71923,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="D6021" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6021" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
-        </is>
-      </c>
     </row>
     <row r="6022">
       <c r="A6022" t="inlineStr">
@@ -71891,14 +71947,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="D6023" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6023" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
-        </is>
-      </c>
     </row>
     <row r="6024">
       <c r="A6024" t="inlineStr">
@@ -71911,14 +71959,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="D6024" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6024" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
-        </is>
-      </c>
     </row>
     <row r="6025">
       <c r="A6025" t="inlineStr">
@@ -71943,14 +71983,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="D6026" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6026" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
-        </is>
-      </c>
     </row>
     <row r="6027">
       <c r="A6027" t="inlineStr">
@@ -71963,14 +71995,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="D6027" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6027" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
-        </is>
-      </c>
     </row>
     <row r="6028">
       <c r="A6028" t="inlineStr">
@@ -72007,14 +72031,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="D6030" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6030" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
-        </is>
-      </c>
     </row>
     <row r="6031">
       <c r="A6031" t="inlineStr">
@@ -72063,14 +72079,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="D6034" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6034" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
-        </is>
-      </c>
     </row>
     <row r="6035">
       <c r="A6035" t="inlineStr">
@@ -72105,14 +72113,6 @@
       <c r="B6037" t="inlineStr">
         <is>
           <t>Senecio rowleyanus</t>
-        </is>
-      </c>
-      <c r="D6037" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6037" s="24" t="inlineStr">
-        <is>
-          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -72152,6 +72152,14 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
+      <c r="D6041" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6041" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6042">
       <c r="A6042" t="inlineStr">
@@ -72200,6 +72208,14 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
+      <c r="D6045" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6045" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6046">
       <c r="A6046" t="inlineStr">
@@ -72284,6 +72300,14 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
+      <c r="D6052" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6052" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6053">
       <c r="A6053" t="inlineStr">
@@ -72308,6 +72332,14 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
+      <c r="D6054" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6054" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6055">
       <c r="A6055" t="inlineStr">
@@ -72332,6 +72364,14 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
+      <c r="D6056" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6056" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="6057">
       <c r="A6057" t="inlineStr">
@@ -72354,6 +72394,14 @@
       <c r="B6058" t="inlineStr">
         <is>
           <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="D6058" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6058" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -72695,15 +72743,23 @@
         </is>
       </c>
     </row>
-    <row r="6089">
-      <c r="A6089" t="inlineStr">
+    <row r="6089" customFormat="1" s="7">
+      <c r="A6089" s="7" t="inlineStr">
         <is>
           <t>28.04.2026</t>
         </is>
       </c>
-      <c r="B6089" t="inlineStr">
+      <c r="B6089" s="7" t="inlineStr">
         <is>
           <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="D6089" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6089" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -72755,15 +72811,23 @@
         </is>
       </c>
     </row>
-    <row r="6094">
-      <c r="A6094" t="inlineStr">
+    <row r="6094" customFormat="1" s="7">
+      <c r="A6094" s="7" t="inlineStr">
         <is>
           <t>28.04.2026</t>
         </is>
       </c>
-      <c r="B6094" t="inlineStr">
+      <c r="B6094" s="7" t="inlineStr">
         <is>
           <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="D6094" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6094" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -72863,15 +72927,23 @@
         </is>
       </c>
     </row>
-    <row r="6103">
-      <c r="A6103" t="inlineStr">
+    <row r="6103" customFormat="1" s="7">
+      <c r="A6103" s="7" t="inlineStr">
         <is>
           <t>28.04.2026</t>
         </is>
       </c>
-      <c r="B6103" t="inlineStr">
+      <c r="B6103" s="7" t="inlineStr">
         <is>
           <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="D6103" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6103" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -72911,15 +72983,23 @@
         </is>
       </c>
     </row>
-    <row r="6107">
-      <c r="A6107" t="inlineStr">
+    <row r="6107" customFormat="1" s="7">
+      <c r="A6107" s="7" t="inlineStr">
         <is>
           <t>28.04.2026</t>
         </is>
       </c>
-      <c r="B6107" t="inlineStr">
+      <c r="B6107" s="7" t="inlineStr">
         <is>
           <t>Ledebouria socialis</t>
+        </is>
+      </c>
+      <c r="D6107" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6107" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
         </is>
       </c>
     </row>
@@ -72935,13 +73015,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C6109" t="inlineStr"/>
-      <c r="D6109" t="inlineStr"/>
-      <c r="E6109" t="inlineStr"/>
-      <c r="F6109" t="inlineStr"/>
-      <c r="G6109" t="inlineStr"/>
-      <c r="H6109" t="inlineStr"/>
-      <c r="I6109" t="inlineStr"/>
     </row>
     <row r="6110">
       <c r="A6110" t="inlineStr">
@@ -72954,13 +73027,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C6110" t="inlineStr"/>
-      <c r="D6110" t="inlineStr"/>
-      <c r="E6110" t="inlineStr"/>
-      <c r="F6110" t="inlineStr"/>
-      <c r="G6110" t="inlineStr"/>
-      <c r="H6110" t="inlineStr"/>
-      <c r="I6110" t="inlineStr"/>
     </row>
     <row r="6111">
       <c r="A6111" t="inlineStr">
@@ -72973,13 +73039,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C6111" t="inlineStr"/>
-      <c r="D6111" t="inlineStr"/>
-      <c r="E6111" t="inlineStr"/>
-      <c r="F6111" t="inlineStr"/>
-      <c r="G6111" t="inlineStr"/>
-      <c r="H6111" t="inlineStr"/>
-      <c r="I6111" t="inlineStr"/>
     </row>
     <row r="6112">
       <c r="A6112" t="inlineStr">
@@ -72992,13 +73051,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C6112" t="inlineStr"/>
-      <c r="D6112" t="inlineStr"/>
-      <c r="E6112" t="inlineStr"/>
-      <c r="F6112" t="inlineStr"/>
-      <c r="G6112" t="inlineStr"/>
-      <c r="H6112" t="inlineStr"/>
-      <c r="I6112" t="inlineStr"/>
     </row>
     <row r="6113">
       <c r="A6113" t="inlineStr">
@@ -73011,13 +73063,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C6113" t="inlineStr"/>
-      <c r="D6113" t="inlineStr"/>
-      <c r="E6113" t="inlineStr"/>
-      <c r="F6113" t="inlineStr"/>
-      <c r="G6113" t="inlineStr"/>
-      <c r="H6113" t="inlineStr"/>
-      <c r="I6113" t="inlineStr"/>
     </row>
     <row r="6114">
       <c r="A6114" t="inlineStr">
@@ -73030,13 +73075,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C6114" t="inlineStr"/>
-      <c r="D6114" t="inlineStr"/>
-      <c r="E6114" t="inlineStr"/>
-      <c r="F6114" t="inlineStr"/>
-      <c r="G6114" t="inlineStr"/>
-      <c r="H6114" t="inlineStr"/>
-      <c r="I6114" t="inlineStr"/>
     </row>
     <row r="6115">
       <c r="A6115" t="inlineStr">
@@ -73049,13 +73087,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C6115" t="inlineStr"/>
-      <c r="D6115" t="inlineStr"/>
-      <c r="E6115" t="inlineStr"/>
-      <c r="F6115" t="inlineStr"/>
-      <c r="G6115" t="inlineStr"/>
-      <c r="H6115" t="inlineStr"/>
-      <c r="I6115" t="inlineStr"/>
     </row>
     <row r="6116">
       <c r="A6116" t="inlineStr">
@@ -73068,13 +73099,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C6116" t="inlineStr"/>
-      <c r="D6116" t="inlineStr"/>
-      <c r="E6116" t="inlineStr"/>
-      <c r="F6116" t="inlineStr"/>
-      <c r="G6116" t="inlineStr"/>
-      <c r="H6116" t="inlineStr"/>
-      <c r="I6116" t="inlineStr"/>
     </row>
     <row r="6117">
       <c r="A6117" t="inlineStr">
@@ -73087,13 +73111,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C6117" t="inlineStr"/>
-      <c r="D6117" t="inlineStr"/>
-      <c r="E6117" t="inlineStr"/>
-      <c r="F6117" t="inlineStr"/>
-      <c r="G6117" t="inlineStr"/>
-      <c r="H6117" t="inlineStr"/>
-      <c r="I6117" t="inlineStr"/>
     </row>
     <row r="6118">
       <c r="A6118" t="inlineStr">
@@ -73106,13 +73123,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C6118" t="inlineStr"/>
-      <c r="D6118" t="inlineStr"/>
-      <c r="E6118" t="inlineStr"/>
-      <c r="F6118" t="inlineStr"/>
-      <c r="G6118" t="inlineStr"/>
-      <c r="H6118" t="inlineStr"/>
-      <c r="I6118" t="inlineStr"/>
     </row>
     <row r="6119">
       <c r="A6119" t="inlineStr">
@@ -73125,13 +73135,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C6119" t="inlineStr"/>
-      <c r="D6119" t="inlineStr"/>
-      <c r="E6119" t="inlineStr"/>
-      <c r="F6119" t="inlineStr"/>
-      <c r="G6119" t="inlineStr"/>
-      <c r="H6119" t="inlineStr"/>
-      <c r="I6119" t="inlineStr"/>
     </row>
     <row r="6120">
       <c r="A6120" t="inlineStr">
@@ -73144,13 +73147,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C6120" t="inlineStr"/>
-      <c r="D6120" t="inlineStr"/>
-      <c r="E6120" t="inlineStr"/>
-      <c r="F6120" t="inlineStr"/>
-      <c r="G6120" t="inlineStr"/>
-      <c r="H6120" t="inlineStr"/>
-      <c r="I6120" t="inlineStr"/>
     </row>
     <row r="6121">
       <c r="A6121" t="inlineStr">
@@ -73163,13 +73159,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C6121" t="inlineStr"/>
-      <c r="D6121" t="inlineStr"/>
-      <c r="E6121" t="inlineStr"/>
-      <c r="F6121" t="inlineStr"/>
-      <c r="G6121" t="inlineStr"/>
-      <c r="H6121" t="inlineStr"/>
-      <c r="I6121" t="inlineStr"/>
     </row>
     <row r="6122">
       <c r="A6122" t="inlineStr">
@@ -73182,13 +73171,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C6122" t="inlineStr"/>
-      <c r="D6122" t="inlineStr"/>
-      <c r="E6122" t="inlineStr"/>
-      <c r="F6122" t="inlineStr"/>
-      <c r="G6122" t="inlineStr"/>
-      <c r="H6122" t="inlineStr"/>
-      <c r="I6122" t="inlineStr"/>
     </row>
     <row r="6123">
       <c r="A6123" t="inlineStr">
@@ -73201,13 +73183,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C6123" t="inlineStr"/>
-      <c r="D6123" t="inlineStr"/>
-      <c r="E6123" t="inlineStr"/>
-      <c r="F6123" t="inlineStr"/>
-      <c r="G6123" t="inlineStr"/>
-      <c r="H6123" t="inlineStr"/>
-      <c r="I6123" t="inlineStr"/>
     </row>
     <row r="6124">
       <c r="A6124" t="inlineStr">
@@ -73220,13 +73195,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C6124" t="inlineStr"/>
-      <c r="D6124" t="inlineStr"/>
-      <c r="E6124" t="inlineStr"/>
-      <c r="F6124" t="inlineStr"/>
-      <c r="G6124" t="inlineStr"/>
-      <c r="H6124" t="inlineStr"/>
-      <c r="I6124" t="inlineStr"/>
     </row>
     <row r="6125">
       <c r="A6125" t="inlineStr">
@@ -73239,13 +73207,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C6125" t="inlineStr"/>
-      <c r="D6125" t="inlineStr"/>
-      <c r="E6125" t="inlineStr"/>
-      <c r="F6125" t="inlineStr"/>
-      <c r="G6125" t="inlineStr"/>
-      <c r="H6125" t="inlineStr"/>
-      <c r="I6125" t="inlineStr"/>
     </row>
     <row r="6126">
       <c r="A6126" t="inlineStr">
@@ -73258,13 +73219,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C6126" t="inlineStr"/>
-      <c r="D6126" t="inlineStr"/>
-      <c r="E6126" t="inlineStr"/>
-      <c r="F6126" t="inlineStr"/>
-      <c r="G6126" t="inlineStr"/>
-      <c r="H6126" t="inlineStr"/>
-      <c r="I6126" t="inlineStr"/>
     </row>
     <row r="6127">
       <c r="A6127" t="inlineStr">
@@ -73277,13 +73231,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C6127" t="inlineStr"/>
-      <c r="D6127" t="inlineStr"/>
-      <c r="E6127" t="inlineStr"/>
-      <c r="F6127" t="inlineStr"/>
-      <c r="G6127" t="inlineStr"/>
-      <c r="H6127" t="inlineStr"/>
-      <c r="I6127" t="inlineStr"/>
     </row>
     <row r="6128">
       <c r="A6128" t="inlineStr">
@@ -73296,13 +73243,6 @@
           <t>Tradescantia zebrina</t>
         </is>
       </c>
-      <c r="C6128" t="inlineStr"/>
-      <c r="D6128" t="inlineStr"/>
-      <c r="E6128" t="inlineStr"/>
-      <c r="F6128" t="inlineStr"/>
-      <c r="G6128" t="inlineStr"/>
-      <c r="H6128" t="inlineStr"/>
-      <c r="I6128" t="inlineStr"/>
     </row>
     <row r="6129">
       <c r="A6129" t="inlineStr">
@@ -73315,13 +73255,6 @@
           <t>Senecio rowleyanus</t>
         </is>
       </c>
-      <c r="C6129" t="inlineStr"/>
-      <c r="D6129" t="inlineStr"/>
-      <c r="E6129" t="inlineStr"/>
-      <c r="F6129" t="inlineStr"/>
-      <c r="G6129" t="inlineStr"/>
-      <c r="H6129" t="inlineStr"/>
-      <c r="I6129" t="inlineStr"/>
     </row>
     <row r="6130">
       <c r="A6130" t="inlineStr">
@@ -73334,13 +73267,6 @@
           <t>Ledebouria socialis</t>
         </is>
       </c>
-      <c r="C6130" t="inlineStr"/>
-      <c r="D6130" t="inlineStr"/>
-      <c r="E6130" t="inlineStr"/>
-      <c r="F6130" t="inlineStr"/>
-      <c r="G6130" t="inlineStr"/>
-      <c r="H6130" t="inlineStr"/>
-      <c r="I6130" t="inlineStr"/>
     </row>
     <row r="6131"/>
     <row r="6132">
@@ -73354,13 +73280,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C6132" t="inlineStr"/>
-      <c r="D6132" t="inlineStr"/>
-      <c r="E6132" t="inlineStr"/>
-      <c r="F6132" t="inlineStr"/>
-      <c r="G6132" t="inlineStr"/>
-      <c r="H6132" t="inlineStr"/>
-      <c r="I6132" t="inlineStr"/>
     </row>
     <row r="6133">
       <c r="A6133" t="inlineStr">
@@ -73373,13 +73292,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C6133" t="inlineStr"/>
-      <c r="D6133" t="inlineStr"/>
-      <c r="E6133" t="inlineStr"/>
-      <c r="F6133" t="inlineStr"/>
-      <c r="G6133" t="inlineStr"/>
-      <c r="H6133" t="inlineStr"/>
-      <c r="I6133" t="inlineStr"/>
     </row>
     <row r="6134">
       <c r="A6134" t="inlineStr">
@@ -73392,13 +73304,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C6134" t="inlineStr"/>
-      <c r="D6134" t="inlineStr"/>
-      <c r="E6134" t="inlineStr"/>
-      <c r="F6134" t="inlineStr"/>
-      <c r="G6134" t="inlineStr"/>
-      <c r="H6134" t="inlineStr"/>
-      <c r="I6134" t="inlineStr"/>
     </row>
     <row r="6135">
       <c r="A6135" t="inlineStr">
@@ -73411,13 +73316,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C6135" t="inlineStr"/>
-      <c r="D6135" t="inlineStr"/>
-      <c r="E6135" t="inlineStr"/>
-      <c r="F6135" t="inlineStr"/>
-      <c r="G6135" t="inlineStr"/>
-      <c r="H6135" t="inlineStr"/>
-      <c r="I6135" t="inlineStr"/>
     </row>
     <row r="6136">
       <c r="A6136" t="inlineStr">
@@ -73430,13 +73328,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C6136" t="inlineStr"/>
-      <c r="D6136" t="inlineStr"/>
-      <c r="E6136" t="inlineStr"/>
-      <c r="F6136" t="inlineStr"/>
-      <c r="G6136" t="inlineStr"/>
-      <c r="H6136" t="inlineStr"/>
-      <c r="I6136" t="inlineStr"/>
     </row>
     <row r="6137">
       <c r="A6137" t="inlineStr">
@@ -73449,13 +73340,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C6137" t="inlineStr"/>
-      <c r="D6137" t="inlineStr"/>
-      <c r="E6137" t="inlineStr"/>
-      <c r="F6137" t="inlineStr"/>
-      <c r="G6137" t="inlineStr"/>
-      <c r="H6137" t="inlineStr"/>
-      <c r="I6137" t="inlineStr"/>
     </row>
     <row r="6138">
       <c r="A6138" t="inlineStr">
@@ -73468,13 +73352,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C6138" t="inlineStr"/>
-      <c r="D6138" t="inlineStr"/>
-      <c r="E6138" t="inlineStr"/>
-      <c r="F6138" t="inlineStr"/>
-      <c r="G6138" t="inlineStr"/>
-      <c r="H6138" t="inlineStr"/>
-      <c r="I6138" t="inlineStr"/>
     </row>
     <row r="6139">
       <c r="A6139" t="inlineStr">
@@ -73487,13 +73364,6 @@
           <t>Hoya Mathilde</t>
         </is>
       </c>
-      <c r="C6139" t="inlineStr"/>
-      <c r="D6139" t="inlineStr"/>
-      <c r="E6139" t="inlineStr"/>
-      <c r="F6139" t="inlineStr"/>
-      <c r="G6139" t="inlineStr"/>
-      <c r="H6139" t="inlineStr"/>
-      <c r="I6139" t="inlineStr"/>
     </row>
     <row r="6140">
       <c r="A6140" t="inlineStr">
@@ -73506,13 +73376,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C6140" t="inlineStr"/>
-      <c r="D6140" t="inlineStr"/>
-      <c r="E6140" t="inlineStr"/>
-      <c r="F6140" t="inlineStr"/>
-      <c r="G6140" t="inlineStr"/>
-      <c r="H6140" t="inlineStr"/>
-      <c r="I6140" t="inlineStr"/>
     </row>
     <row r="6141">
       <c r="A6141" t="inlineStr">
@@ -73525,13 +73388,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C6141" t="inlineStr"/>
-      <c r="D6141" t="inlineStr"/>
-      <c r="E6141" t="inlineStr"/>
-      <c r="F6141" t="inlineStr"/>
-      <c r="G6141" t="inlineStr"/>
-      <c r="H6141" t="inlineStr"/>
-      <c r="I6141" t="inlineStr"/>
     </row>
     <row r="6142">
       <c r="A6142" t="inlineStr">
@@ -73544,13 +73400,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C6142" t="inlineStr"/>
-      <c r="D6142" t="inlineStr"/>
-      <c r="E6142" t="inlineStr"/>
-      <c r="F6142" t="inlineStr"/>
-      <c r="G6142" t="inlineStr"/>
-      <c r="H6142" t="inlineStr"/>
-      <c r="I6142" t="inlineStr"/>
     </row>
     <row r="6143">
       <c r="A6143" t="inlineStr">
@@ -73563,13 +73412,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C6143" t="inlineStr"/>
-      <c r="D6143" t="inlineStr"/>
-      <c r="E6143" t="inlineStr"/>
-      <c r="F6143" t="inlineStr"/>
-      <c r="G6143" t="inlineStr"/>
-      <c r="H6143" t="inlineStr"/>
-      <c r="I6143" t="inlineStr"/>
     </row>
     <row r="6144">
       <c r="A6144" t="inlineStr">
@@ -73582,13 +73424,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C6144" t="inlineStr"/>
-      <c r="D6144" t="inlineStr"/>
-      <c r="E6144" t="inlineStr"/>
-      <c r="F6144" t="inlineStr"/>
-      <c r="G6144" t="inlineStr"/>
-      <c r="H6144" t="inlineStr"/>
-      <c r="I6144" t="inlineStr"/>
     </row>
     <row r="6145">
       <c r="A6145" t="inlineStr">
@@ -73601,13 +73436,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C6145" t="inlineStr"/>
-      <c r="D6145" t="inlineStr"/>
-      <c r="E6145" t="inlineStr"/>
-      <c r="F6145" t="inlineStr"/>
-      <c r="G6145" t="inlineStr"/>
-      <c r="H6145" t="inlineStr"/>
-      <c r="I6145" t="inlineStr"/>
     </row>
     <row r="6146">
       <c r="A6146" t="inlineStr">
@@ -73620,13 +73448,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C6146" t="inlineStr"/>
-      <c r="D6146" t="inlineStr"/>
-      <c r="E6146" t="inlineStr"/>
-      <c r="F6146" t="inlineStr"/>
-      <c r="G6146" t="inlineStr"/>
-      <c r="H6146" t="inlineStr"/>
-      <c r="I6146" t="inlineStr"/>
     </row>
     <row r="6147">
       <c r="A6147" t="inlineStr">
@@ -73639,13 +73460,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C6147" t="inlineStr"/>
-      <c r="D6147" t="inlineStr"/>
-      <c r="E6147" t="inlineStr"/>
-      <c r="F6147" t="inlineStr"/>
-      <c r="G6147" t="inlineStr"/>
-      <c r="H6147" t="inlineStr"/>
-      <c r="I6147" t="inlineStr"/>
     </row>
     <row r="6148">
       <c r="A6148" t="inlineStr">
@@ -73658,13 +73472,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C6148" t="inlineStr"/>
-      <c r="D6148" t="inlineStr"/>
-      <c r="E6148" t="inlineStr"/>
-      <c r="F6148" t="inlineStr"/>
-      <c r="G6148" t="inlineStr"/>
-      <c r="H6148" t="inlineStr"/>
-      <c r="I6148" t="inlineStr"/>
     </row>
     <row r="6149">
       <c r="A6149" t="inlineStr">
@@ -73677,13 +73484,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C6149" t="inlineStr"/>
-      <c r="D6149" t="inlineStr"/>
-      <c r="E6149" t="inlineStr"/>
-      <c r="F6149" t="inlineStr"/>
-      <c r="G6149" t="inlineStr"/>
-      <c r="H6149" t="inlineStr"/>
-      <c r="I6149" t="inlineStr"/>
     </row>
     <row r="6150">
       <c r="A6150" t="inlineStr">
@@ -73696,13 +73496,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C6150" t="inlineStr"/>
-      <c r="D6150" t="inlineStr"/>
-      <c r="E6150" t="inlineStr"/>
-      <c r="F6150" t="inlineStr"/>
-      <c r="G6150" t="inlineStr"/>
-      <c r="H6150" t="inlineStr"/>
-      <c r="I6150" t="inlineStr"/>
     </row>
     <row r="6151">
       <c r="A6151" t="inlineStr">
@@ -73715,13 +73508,6 @@
           <t>Tradescantia zebrina</t>
         </is>
       </c>
-      <c r="C6151" t="inlineStr"/>
-      <c r="D6151" t="inlineStr"/>
-      <c r="E6151" t="inlineStr"/>
-      <c r="F6151" t="inlineStr"/>
-      <c r="G6151" t="inlineStr"/>
-      <c r="H6151" t="inlineStr"/>
-      <c r="I6151" t="inlineStr"/>
     </row>
     <row r="6152">
       <c r="A6152" t="inlineStr">
@@ -73734,13 +73520,6 @@
           <t>Senecio rowleyanus</t>
         </is>
       </c>
-      <c r="C6152" t="inlineStr"/>
-      <c r="D6152" t="inlineStr"/>
-      <c r="E6152" t="inlineStr"/>
-      <c r="F6152" t="inlineStr"/>
-      <c r="G6152" t="inlineStr"/>
-      <c r="H6152" t="inlineStr"/>
-      <c r="I6152" t="inlineStr"/>
     </row>
     <row r="6153">
       <c r="A6153" t="inlineStr">
@@ -73753,15 +73532,427 @@
           <t>Ledebouria socialis</t>
         </is>
       </c>
-      <c r="C6153" t="inlineStr"/>
-      <c r="D6153" t="inlineStr"/>
-      <c r="E6153" t="inlineStr"/>
-      <c r="F6153" t="inlineStr"/>
-      <c r="G6153" t="inlineStr"/>
-      <c r="H6153" t="inlineStr"/>
-      <c r="I6153" t="inlineStr"/>
     </row>
     <row r="6154"/>
+    <row r="6155">
+      <c r="A6155" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6155" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C6155" t="inlineStr"/>
+      <c r="D6155" t="inlineStr"/>
+      <c r="E6155" t="inlineStr"/>
+      <c r="F6155" t="inlineStr"/>
+      <c r="G6155" t="inlineStr"/>
+      <c r="H6155" t="inlineStr"/>
+      <c r="I6155" t="inlineStr"/>
+    </row>
+    <row r="6156">
+      <c r="A6156" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C6156" t="inlineStr"/>
+      <c r="D6156" t="inlineStr"/>
+      <c r="E6156" t="inlineStr"/>
+      <c r="F6156" t="inlineStr"/>
+      <c r="G6156" t="inlineStr"/>
+      <c r="H6156" t="inlineStr"/>
+      <c r="I6156" t="inlineStr"/>
+    </row>
+    <row r="6157">
+      <c r="A6157" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6157" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C6157" t="inlineStr"/>
+      <c r="D6157" t="inlineStr"/>
+      <c r="E6157" t="inlineStr"/>
+      <c r="F6157" t="inlineStr"/>
+      <c r="G6157" t="inlineStr"/>
+      <c r="H6157" t="inlineStr"/>
+      <c r="I6157" t="inlineStr"/>
+    </row>
+    <row r="6158">
+      <c r="A6158" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6158" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C6158" t="inlineStr"/>
+      <c r="D6158" t="inlineStr"/>
+      <c r="E6158" t="inlineStr"/>
+      <c r="F6158" t="inlineStr"/>
+      <c r="G6158" t="inlineStr"/>
+      <c r="H6158" t="inlineStr"/>
+      <c r="I6158" t="inlineStr"/>
+    </row>
+    <row r="6159">
+      <c r="A6159" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6159" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C6159" t="inlineStr"/>
+      <c r="D6159" t="inlineStr"/>
+      <c r="E6159" t="inlineStr"/>
+      <c r="F6159" t="inlineStr"/>
+      <c r="G6159" t="inlineStr"/>
+      <c r="H6159" t="inlineStr"/>
+      <c r="I6159" t="inlineStr"/>
+    </row>
+    <row r="6160">
+      <c r="A6160" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6160" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C6160" t="inlineStr"/>
+      <c r="D6160" t="inlineStr"/>
+      <c r="E6160" t="inlineStr"/>
+      <c r="F6160" t="inlineStr"/>
+      <c r="G6160" t="inlineStr"/>
+      <c r="H6160" t="inlineStr"/>
+      <c r="I6160" t="inlineStr"/>
+    </row>
+    <row r="6161">
+      <c r="A6161" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6161" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C6161" t="inlineStr"/>
+      <c r="D6161" t="inlineStr"/>
+      <c r="E6161" t="inlineStr"/>
+      <c r="F6161" t="inlineStr"/>
+      <c r="G6161" t="inlineStr"/>
+      <c r="H6161" t="inlineStr"/>
+      <c r="I6161" t="inlineStr"/>
+    </row>
+    <row r="6162">
+      <c r="A6162" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6162" t="inlineStr">
+        <is>
+          <t>Hoya Mathilde</t>
+        </is>
+      </c>
+      <c r="C6162" t="inlineStr"/>
+      <c r="D6162" t="inlineStr"/>
+      <c r="E6162" t="inlineStr"/>
+      <c r="F6162" t="inlineStr"/>
+      <c r="G6162" t="inlineStr"/>
+      <c r="H6162" t="inlineStr"/>
+      <c r="I6162" t="inlineStr"/>
+    </row>
+    <row r="6163">
+      <c r="A6163" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6163" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C6163" t="inlineStr"/>
+      <c r="D6163" t="inlineStr"/>
+      <c r="E6163" t="inlineStr"/>
+      <c r="F6163" t="inlineStr"/>
+      <c r="G6163" t="inlineStr"/>
+      <c r="H6163" t="inlineStr"/>
+      <c r="I6163" t="inlineStr"/>
+    </row>
+    <row r="6164">
+      <c r="A6164" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6164" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C6164" t="inlineStr"/>
+      <c r="D6164" t="inlineStr"/>
+      <c r="E6164" t="inlineStr"/>
+      <c r="F6164" t="inlineStr"/>
+      <c r="G6164" t="inlineStr"/>
+      <c r="H6164" t="inlineStr"/>
+      <c r="I6164" t="inlineStr"/>
+    </row>
+    <row r="6165">
+      <c r="A6165" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6165" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C6165" t="inlineStr"/>
+      <c r="D6165" t="inlineStr"/>
+      <c r="E6165" t="inlineStr"/>
+      <c r="F6165" t="inlineStr"/>
+      <c r="G6165" t="inlineStr"/>
+      <c r="H6165" t="inlineStr"/>
+      <c r="I6165" t="inlineStr"/>
+    </row>
+    <row r="6166">
+      <c r="A6166" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6166" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C6166" t="inlineStr"/>
+      <c r="D6166" t="inlineStr"/>
+      <c r="E6166" t="inlineStr"/>
+      <c r="F6166" t="inlineStr"/>
+      <c r="G6166" t="inlineStr"/>
+      <c r="H6166" t="inlineStr"/>
+      <c r="I6166" t="inlineStr"/>
+    </row>
+    <row r="6167">
+      <c r="A6167" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6167" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C6167" t="inlineStr"/>
+      <c r="D6167" t="inlineStr"/>
+      <c r="E6167" t="inlineStr"/>
+      <c r="F6167" t="inlineStr"/>
+      <c r="G6167" t="inlineStr"/>
+      <c r="H6167" t="inlineStr"/>
+      <c r="I6167" t="inlineStr"/>
+    </row>
+    <row r="6168">
+      <c r="A6168" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C6168" t="inlineStr"/>
+      <c r="D6168" t="inlineStr"/>
+      <c r="E6168" t="inlineStr"/>
+      <c r="F6168" t="inlineStr"/>
+      <c r="G6168" t="inlineStr"/>
+      <c r="H6168" t="inlineStr"/>
+      <c r="I6168" t="inlineStr"/>
+    </row>
+    <row r="6169">
+      <c r="A6169" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6169" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C6169" t="inlineStr"/>
+      <c r="D6169" t="inlineStr"/>
+      <c r="E6169" t="inlineStr"/>
+      <c r="F6169" t="inlineStr"/>
+      <c r="G6169" t="inlineStr"/>
+      <c r="H6169" t="inlineStr"/>
+      <c r="I6169" t="inlineStr"/>
+    </row>
+    <row r="6170">
+      <c r="A6170" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6170" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C6170" t="inlineStr"/>
+      <c r="D6170" t="inlineStr"/>
+      <c r="E6170" t="inlineStr"/>
+      <c r="F6170" t="inlineStr"/>
+      <c r="G6170" t="inlineStr"/>
+      <c r="H6170" t="inlineStr"/>
+      <c r="I6170" t="inlineStr"/>
+    </row>
+    <row r="6171">
+      <c r="A6171" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6171" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C6171" t="inlineStr"/>
+      <c r="D6171" t="inlineStr"/>
+      <c r="E6171" t="inlineStr"/>
+      <c r="F6171" t="inlineStr"/>
+      <c r="G6171" t="inlineStr"/>
+      <c r="H6171" t="inlineStr"/>
+      <c r="I6171" t="inlineStr"/>
+    </row>
+    <row r="6172">
+      <c r="A6172" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6172" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C6172" t="inlineStr"/>
+      <c r="D6172" t="inlineStr"/>
+      <c r="E6172" t="inlineStr"/>
+      <c r="F6172" t="inlineStr"/>
+      <c r="G6172" t="inlineStr"/>
+      <c r="H6172" t="inlineStr"/>
+      <c r="I6172" t="inlineStr"/>
+    </row>
+    <row r="6173">
+      <c r="A6173" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6173" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C6173" t="inlineStr"/>
+      <c r="D6173" t="inlineStr"/>
+      <c r="E6173" t="inlineStr"/>
+      <c r="F6173" t="inlineStr"/>
+      <c r="G6173" t="inlineStr"/>
+      <c r="H6173" t="inlineStr"/>
+      <c r="I6173" t="inlineStr"/>
+    </row>
+    <row r="6174">
+      <c r="A6174" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6174" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+      <c r="C6174" t="inlineStr"/>
+      <c r="D6174" t="inlineStr"/>
+      <c r="E6174" t="inlineStr"/>
+      <c r="F6174" t="inlineStr"/>
+      <c r="G6174" t="inlineStr"/>
+      <c r="H6174" t="inlineStr"/>
+      <c r="I6174" t="inlineStr"/>
+    </row>
+    <row r="6175">
+      <c r="A6175" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6175" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+      <c r="C6175" t="inlineStr"/>
+      <c r="D6175" t="inlineStr"/>
+      <c r="E6175" t="inlineStr"/>
+      <c r="F6175" t="inlineStr"/>
+      <c r="G6175" t="inlineStr"/>
+      <c r="H6175" t="inlineStr"/>
+      <c r="I6175" t="inlineStr"/>
+    </row>
+    <row r="6176">
+      <c r="A6176" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B6176" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+      <c r="C6176" t="inlineStr"/>
+      <c r="D6176" t="inlineStr"/>
+      <c r="E6176" t="inlineStr"/>
+      <c r="F6176" t="inlineStr"/>
+      <c r="G6176" t="inlineStr"/>
+      <c r="H6176" t="inlineStr"/>
+      <c r="I6176" t="inlineStr"/>
+    </row>
+    <row r="6177"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/data/blumen_data.xlsx
+++ b/data/blumen_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
@@ -517,49 +517,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7174"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AD7414"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="14.44140625" customWidth="1" min="1" max="1"/>
-    <col width="40.109375" customWidth="1" min="2" max="2"/>
-    <col width="16.33203125" customWidth="1" min="3" max="3"/>
-    <col width="7.88671875" customWidth="1" min="4" max="4"/>
-    <col width="15.109375" customWidth="1" min="5" max="6"/>
-    <col width="8.5546875" customWidth="1" min="7" max="7"/>
-    <col width="11.5546875" customWidth="1" min="8" max="9"/>
-    <col width="74.33203125" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="15.6640625" customWidth="1" min="15" max="15"/>
-    <col width="26.6640625" customWidth="1" min="16" max="16"/>
-    <col width="22.33203125" customWidth="1" min="17" max="17"/>
-    <col width="27.5546875" customWidth="1" min="18" max="18"/>
-    <col width="37.5546875" customWidth="1" min="19" max="20"/>
-    <col width="38.88671875" customWidth="1" min="21" max="21"/>
-    <col width="37" customWidth="1" min="22" max="22"/>
-    <col width="31.5546875" customWidth="1" min="23" max="23"/>
-    <col width="27.88671875" customWidth="1" min="24" max="24"/>
-    <col width="26.44140625" customWidth="1" min="25" max="25"/>
-    <col width="29" customWidth="1" min="26" max="26"/>
-    <col width="37.33203125" customWidth="1" min="27" max="29"/>
-    <col width="36.44140625" customWidth="1" min="30" max="30"/>
-    <col width="28.5546875" customWidth="1" min="31" max="31"/>
-    <col width="30.109375" customWidth="1" min="32" max="33"/>
-    <col width="30.33203125" customWidth="1" min="34" max="34"/>
-    <col width="31" customWidth="1" min="35" max="35"/>
-    <col width="39.109375" customWidth="1" min="36" max="36"/>
-    <col width="41.6640625" customWidth="1" min="37" max="37"/>
-    <col width="39.5546875" customWidth="1" min="38" max="38"/>
-    <col width="29.44140625" customWidth="1" min="39" max="39"/>
-    <col width="30.33203125" customWidth="1" min="40" max="40"/>
-    <col width="25.88671875" customWidth="1" min="41" max="41"/>
-    <col width="30" customWidth="1" min="42" max="42"/>
-    <col width="37.6640625" customWidth="1" min="43" max="43"/>
-    <col width="36" customWidth="1" min="44" max="44"/>
-    <col width="37.6640625" customWidth="1" min="45" max="45"/>
-    <col width="37.33203125" customWidth="1" min="46" max="46"/>
-    <col width="38.5546875" customWidth="1" min="47" max="47"/>
+    <col width="14.42578125" customWidth="1" min="1" max="1"/>
+    <col width="40.140625" customWidth="1" min="2" max="2"/>
+    <col width="16.28515625" customWidth="1" min="3" max="3"/>
+    <col width="7.85546875" customWidth="1" min="4" max="4"/>
+    <col width="15.140625" customWidth="1" min="5" max="6"/>
+    <col width="8.5703125" customWidth="1" min="7" max="7"/>
+    <col width="11.5703125" customWidth="1" min="8" max="9"/>
+    <col width="18.7109375" customWidth="1" min="10" max="10"/>
+    <col width="74.28515625" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="13"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="15.7109375" customWidth="1" min="16" max="16"/>
+    <col width="26.7109375" customWidth="1" min="17" max="17"/>
+    <col width="22.28515625" customWidth="1" min="18" max="18"/>
+    <col width="27.5703125" customWidth="1" min="19" max="19"/>
+    <col width="37.5703125" customWidth="1" min="20" max="21"/>
+    <col width="38.85546875" customWidth="1" min="22" max="22"/>
+    <col width="37" customWidth="1" min="23" max="23"/>
+    <col width="31.5703125" customWidth="1" min="24" max="24"/>
+    <col width="27.85546875" customWidth="1" min="25" max="25"/>
+    <col width="26.42578125" customWidth="1" min="26" max="26"/>
+    <col width="29" customWidth="1" min="27" max="27"/>
+    <col width="37.28515625" customWidth="1" min="28" max="30"/>
+    <col width="36.42578125" customWidth="1" min="31" max="31"/>
+    <col width="28.5703125" customWidth="1" min="32" max="32"/>
+    <col width="30.140625" customWidth="1" min="33" max="34"/>
+    <col width="30.28515625" customWidth="1" min="35" max="35"/>
+    <col width="31" customWidth="1" min="36" max="36"/>
+    <col width="39.140625" customWidth="1" min="37" max="37"/>
+    <col width="41.7109375" customWidth="1" min="38" max="38"/>
+    <col width="39.5703125" customWidth="1" min="39" max="39"/>
+    <col width="29.42578125" customWidth="1" min="40" max="40"/>
+    <col width="30.28515625" customWidth="1" min="41" max="41"/>
+    <col width="25.85546875" customWidth="1" min="42" max="42"/>
+    <col width="30" customWidth="1" min="43" max="43"/>
+    <col width="37.7109375" customWidth="1" min="44" max="44"/>
+    <col width="36" customWidth="1" min="45" max="45"/>
+    <col width="37.7109375" customWidth="1" min="46" max="46"/>
+    <col width="37.28515625" customWidth="1" min="47" max="47"/>
+    <col width="38.5703125" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customFormat="1" customHeight="1" s="6">
@@ -610,6 +611,11 @@
       </c>
       <c r="J1" s="6" t="inlineStr">
         <is>
+          <t>nematoden</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
           <t>condition</t>
         </is>
       </c>
@@ -626,7 +632,7 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" s="3" t="n"/>
+      <c r="AD2" s="3" t="n"/>
     </row>
     <row r="3" customFormat="1" s="1">
       <c r="A3" s="5" t="n">
@@ -643,7 +649,7 @@
       <c r="D3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
     </row>
     <row r="4" customFormat="1" s="1">
       <c r="A4" s="5" t="n">
@@ -660,7 +666,7 @@
       <c r="D4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
     </row>
     <row r="5" customFormat="1" s="1">
       <c r="A5" s="5" t="n">
@@ -677,7 +683,7 @@
       <c r="D5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
     </row>
     <row r="6" customFormat="1" s="1">
       <c r="A6" s="5" t="n">
@@ -694,7 +700,7 @@
       <c r="D6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
     </row>
     <row r="7" customFormat="1" s="10">
       <c r="A7" s="8" t="n"/>
@@ -704,12 +710,12 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
-      <c r="AC7" s="11" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="AD7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1158,7 +1164,7 @@
       <c r="F44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>hat angefangen blätter zu gelben und blätter haben angefangen sich zu krümmen</t>
         </is>
@@ -1245,7 +1251,7 @@
       <c r="F50" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>hat angefangen blätter zu gelben und blätter haben angefangen sich zu krümmen</t>
         </is>
@@ -1328,7 +1334,7 @@
       <c r="F56" t="n">
         <v>2</v>
       </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>hat angefangen blätter zu gelben und blätter haben angefangen sich zu krümmen</t>
         </is>
@@ -1370,7 +1376,7 @@
       <c r="C58" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr">
         <is>
           <t>es hat sich links ein neuer ast angefangen zu bilden</t>
         </is>
@@ -5785,6 +5791,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J413" s="7" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="18" t="n">
@@ -5800,6 +5807,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J414" s="7" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="18" t="n">
@@ -8429,6 +8437,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J643" s="7" t="n"/>
     </row>
     <row r="644" customFormat="1" s="19">
       <c r="A644" s="19" t="inlineStr">
@@ -8454,6 +8463,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J644" s="7" t="n"/>
     </row>
     <row r="645" customFormat="1" s="7">
       <c r="A645" s="7" t="inlineStr">
@@ -8491,6 +8501,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J646" s="7" t="n"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -8508,6 +8519,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J647" s="7" t="n"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -8525,6 +8537,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J648" s="7" t="n"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -8542,6 +8555,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J649" s="7" t="n"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -8559,6 +8573,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J650" s="7" t="n"/>
     </row>
     <row r="651"/>
     <row r="652">
@@ -12405,6 +12420,7 @@
       <c r="G997" s="13" t="n"/>
       <c r="H997" s="13" t="n"/>
       <c r="I997" s="13" t="n"/>
+      <c r="J997" s="13" t="n"/>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
@@ -12486,6 +12502,7 @@
       <c r="G1002" s="13" t="n"/>
       <c r="H1002" s="13" t="n"/>
       <c r="I1002" s="13" t="n"/>
+      <c r="J1002" s="13" t="n"/>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
@@ -12989,7 +13006,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J1047" t="inlineStr">
+      <c r="K1047" t="inlineStr">
         <is>
           <t>etwas Spinnmilben</t>
         </is>
@@ -13017,7 +13034,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J1048" s="7" t="inlineStr">
+      <c r="K1048" s="7" t="inlineStr">
         <is>
           <t>heftige Spinnmilben</t>
         </is>
@@ -17792,7 +17809,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J1467" t="inlineStr">
+      <c r="K1467" t="inlineStr">
         <is>
           <t>Habe eine Überlebte larve gesehen daher noch mal Pestmix</t>
         </is>
@@ -18809,6 +18826,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1547" s="7" t="n"/>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
@@ -18832,6 +18850,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1548" s="7" t="n"/>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
@@ -18855,6 +18874,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1549" s="7" t="n"/>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
@@ -18878,6 +18898,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1550" s="7" t="n"/>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
@@ -18901,6 +18922,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1551" s="7" t="n"/>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
@@ -18924,6 +18946,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1552" s="7" t="n"/>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
@@ -18947,6 +18970,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1553" s="7" t="n"/>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
@@ -18970,6 +18994,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1554" s="7" t="n"/>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
@@ -18993,6 +19018,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1555" s="7" t="n"/>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
@@ -19016,6 +19042,7 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1556" s="7" t="n"/>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
@@ -20928,7 +20955,7 @@
       <c r="D1728" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="J1728" s="7" t="inlineStr">
+      <c r="K1728" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt größeres Gefäß</t>
         </is>
@@ -20957,7 +20984,7 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="J1730" s="7" t="inlineStr">
+      <c r="K1730" s="7" t="inlineStr">
         <is>
           <t>zweiten Zweig dazu gepflanzt</t>
         </is>
@@ -21025,7 +21052,7 @@
       <c r="D1735" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="J1735" s="7" t="inlineStr">
+      <c r="K1735" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt größeres Gefäß</t>
         </is>
@@ -21057,7 +21084,7 @@
       <c r="D1737" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="J1737" s="7" t="inlineStr">
+      <c r="K1737" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt größeres Gefäß</t>
         </is>
@@ -22080,7 +22107,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J1823" s="7" t="inlineStr">
+      <c r="K1823" s="7" t="inlineStr">
         <is>
           <t>wieder ein wurm nach dem wässern entdeckt</t>
         </is>
@@ -33571,7 +33598,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2828" s="4" t="inlineStr">
+      <c r="K2828" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33594,7 +33621,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2829" s="4" t="inlineStr">
+      <c r="K2829" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33678,7 +33705,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2836" s="4" t="inlineStr">
+      <c r="K2836" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33721,7 +33748,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2839" s="4" t="inlineStr">
+      <c r="K2839" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33744,7 +33771,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2840" s="4" t="inlineStr">
+      <c r="K2840" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33777,7 +33804,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2842" s="4" t="inlineStr">
+      <c r="K2842" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33800,7 +33827,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2843" s="4" t="inlineStr">
+      <c r="K2843" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -33823,7 +33850,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2844" s="4" t="inlineStr">
+      <c r="K2844" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -34247,7 +34274,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2887" s="4" t="inlineStr">
+      <c r="K2887" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -34272,7 +34299,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2888" s="4" t="inlineStr">
+      <c r="K2888" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -34330,7 +34357,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2891" s="4" t="inlineStr">
+      <c r="K2891" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -34427,7 +34454,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2898" s="4" t="inlineStr">
+      <c r="K2898" s="4" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35140,7 +35167,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2960" s="24" t="inlineStr">
+      <c r="K2960" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35165,7 +35192,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2961" s="24" t="inlineStr">
+      <c r="K2961" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35238,7 +35265,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2966" s="24" t="inlineStr">
+      <c r="K2966" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35391,7 +35418,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J2977" s="24" t="inlineStr">
+      <c r="K2977" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35899,7 +35926,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3021" s="24" t="inlineStr">
+      <c r="K3021" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35960,7 +35987,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3025" s="24" t="inlineStr">
+      <c r="K3025" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -35997,7 +36024,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3027" s="24" t="inlineStr">
+      <c r="K3027" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -36022,7 +36049,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3028" s="24" t="inlineStr">
+      <c r="K3028" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -36047,7 +36074,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3029" s="24" t="inlineStr">
+      <c r="K3029" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37013,7 +37040,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3113" s="24" t="inlineStr">
+      <c r="K3113" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37038,7 +37065,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3114" s="24" t="inlineStr">
+      <c r="K3114" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37063,7 +37090,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3115" s="24" t="inlineStr">
+      <c r="K3115" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37180,7 +37207,7 @@
         <v>700</v>
       </c>
       <c r="E3124" s="24" t="n"/>
-      <c r="J3124" s="24" t="inlineStr">
+      <c r="K3124" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37205,7 +37232,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3125" s="24" t="inlineStr">
+      <c r="K3125" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37242,7 +37269,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3127" s="24" t="inlineStr">
+      <c r="K3127" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37267,7 +37294,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3128" s="24" t="inlineStr">
+      <c r="K3128" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -37292,7 +37319,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3129" s="24" t="inlineStr">
+      <c r="K3129" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38668,7 +38695,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3249" s="24" t="inlineStr">
+      <c r="K3249" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38693,7 +38720,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3250" s="24" t="inlineStr">
+      <c r="K3250" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38754,7 +38781,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3254" s="24" t="inlineStr">
+      <c r="K3254" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38803,7 +38830,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3257" s="24" t="inlineStr">
+      <c r="K3257" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38840,7 +38867,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3259" s="24" t="inlineStr">
+      <c r="K3259" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -38889,7 +38916,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3262" s="24" t="inlineStr">
+      <c r="K3262" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39647,7 +39674,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3341" s="24" t="inlineStr">
+      <c r="K3341" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39680,7 +39707,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3343" s="24" t="inlineStr">
+      <c r="K3343" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39723,7 +39750,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3346" s="24" t="inlineStr">
+      <c r="K3346" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39746,7 +39773,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3347" s="24" t="inlineStr">
+      <c r="K3347" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39769,7 +39796,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3348" s="24" t="inlineStr">
+      <c r="K3348" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39812,7 +39839,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3351" s="24" t="inlineStr">
+      <c r="K3351" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -39865,7 +39892,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3355" s="24" t="inlineStr">
+      <c r="K3355" s="24" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40779,7 +40806,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3435" t="inlineStr">
+      <c r="K3435" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40816,7 +40843,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3437" t="inlineStr">
+      <c r="K3437" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40925,7 +40952,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3445" t="inlineStr">
+      <c r="K3445" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40962,7 +40989,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3447" t="inlineStr">
+      <c r="K3447" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -40987,7 +41014,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3448" t="inlineStr">
+      <c r="K3448" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41036,7 +41063,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3451" t="inlineStr">
+      <c r="K3451" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41061,7 +41088,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3452" t="inlineStr">
+      <c r="K3452" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41750,7 +41777,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3512" t="inlineStr">
+      <c r="K3512" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41787,7 +41814,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3514" t="inlineStr">
+      <c r="K3514" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41812,7 +41839,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3515" t="inlineStr">
+      <c r="K3515" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41837,7 +41864,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3516" t="inlineStr">
+      <c r="K3516" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41862,7 +41889,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3517" t="inlineStr">
+      <c r="K3517" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41899,7 +41926,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3519" t="inlineStr">
+      <c r="K3519" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41924,7 +41951,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3520" t="inlineStr">
+      <c r="K3520" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -41973,7 +42000,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3523" t="inlineStr">
+      <c r="K3523" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -42010,7 +42037,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3525" t="inlineStr">
+      <c r="K3525" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -42035,7 +42062,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3526" t="inlineStr">
+      <c r="K3526" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -42072,7 +42099,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="J3528" t="inlineStr">
+      <c r="K3528" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -43375,7 +43402,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3641" s="7" t="inlineStr">
+      <c r="L3641" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt</t>
         </is>
@@ -43400,7 +43427,7 @@
           <t>SYBA org</t>
         </is>
       </c>
-      <c r="K3642" s="7" t="inlineStr">
+      <c r="L3642" s="7" t="inlineStr">
         <is>
           <t>umgepflanzt</t>
         </is>
@@ -46780,7 +46807,8 @@
       <c r="G3920" s="24" t="n"/>
       <c r="H3920" s="24" t="n"/>
       <c r="I3920" s="24" t="n"/>
-      <c r="J3920" t="inlineStr">
+      <c r="J3920" s="24" t="n"/>
+      <c r="K3920" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -46821,7 +46849,8 @@
       <c r="G3922" s="24" t="n"/>
       <c r="H3922" s="24" t="n"/>
       <c r="I3922" s="24" t="n"/>
-      <c r="J3922" t="inlineStr">
+      <c r="J3922" s="24" t="n"/>
+      <c r="K3922" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -46850,7 +46879,8 @@
       <c r="G3923" s="24" t="n"/>
       <c r="H3923" s="24" t="n"/>
       <c r="I3923" s="24" t="n"/>
-      <c r="J3923" t="inlineStr">
+      <c r="J3923" s="24" t="n"/>
+      <c r="K3923" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -46879,7 +46909,8 @@
       <c r="G3924" s="24" t="n"/>
       <c r="H3924" s="24" t="n"/>
       <c r="I3924" s="24" t="n"/>
-      <c r="J3924" t="inlineStr">
+      <c r="J3924" s="24" t="n"/>
+      <c r="K3924" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -46944,7 +46975,8 @@
       <c r="G3928" s="24" t="n"/>
       <c r="H3928" s="24" t="n"/>
       <c r="I3928" s="24" t="n"/>
-      <c r="J3928" t="inlineStr">
+      <c r="J3928" s="24" t="n"/>
+      <c r="K3928" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -47021,7 +47053,8 @@
       <c r="G3933" s="24" t="n"/>
       <c r="H3933" s="24" t="n"/>
       <c r="I3933" s="24" t="n"/>
-      <c r="J3933" t="inlineStr">
+      <c r="J3933" s="24" t="n"/>
+      <c r="K3933" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -47062,7 +47095,8 @@
       <c r="G3935" s="24" t="n"/>
       <c r="H3935" s="24" t="n"/>
       <c r="I3935" s="24" t="n"/>
-      <c r="J3935" t="inlineStr">
+      <c r="J3935" s="24" t="n"/>
+      <c r="K3935" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -47091,7 +47125,8 @@
       <c r="G3936" s="24" t="n"/>
       <c r="H3936" s="24" t="n"/>
       <c r="I3936" s="24" t="n"/>
-      <c r="J3936" t="inlineStr">
+      <c r="J3936" s="24" t="n"/>
+      <c r="K3936" t="inlineStr">
         <is>
           <t>nematoden</t>
         </is>
@@ -64962,7 +64997,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J5440" s="7" t="inlineStr">
+      <c r="K5440" s="7" t="inlineStr">
         <is>
           <t>bad, some pest bugs with black little shits</t>
         </is>
@@ -65189,7 +65224,7 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J5456" s="7" t="inlineStr">
+      <c r="K5456" s="7" t="inlineStr">
         <is>
           <t>very bad, some pest bugs with black little shits</t>
         </is>
@@ -83777,13 +83812,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C7031" t="inlineStr"/>
-      <c r="D7031" t="inlineStr"/>
-      <c r="E7031" t="inlineStr"/>
-      <c r="F7031" t="inlineStr"/>
-      <c r="G7031" t="inlineStr"/>
-      <c r="H7031" t="inlineStr"/>
-      <c r="I7031" t="inlineStr"/>
     </row>
     <row r="7032">
       <c r="A7032" t="inlineStr">
@@ -83796,13 +83824,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C7032" t="inlineStr"/>
-      <c r="D7032" t="inlineStr"/>
-      <c r="E7032" t="inlineStr"/>
-      <c r="F7032" t="inlineStr"/>
-      <c r="G7032" t="inlineStr"/>
-      <c r="H7032" t="inlineStr"/>
-      <c r="I7032" t="inlineStr"/>
     </row>
     <row r="7033">
       <c r="A7033" t="inlineStr">
@@ -83815,13 +83836,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C7033" t="inlineStr"/>
-      <c r="D7033" t="inlineStr"/>
-      <c r="E7033" t="inlineStr"/>
-      <c r="F7033" t="inlineStr"/>
-      <c r="G7033" t="inlineStr"/>
-      <c r="H7033" t="inlineStr"/>
-      <c r="I7033" t="inlineStr"/>
     </row>
     <row r="7034">
       <c r="A7034" t="inlineStr">
@@ -83834,13 +83848,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C7034" t="inlineStr"/>
-      <c r="D7034" t="inlineStr"/>
-      <c r="E7034" t="inlineStr"/>
-      <c r="F7034" t="inlineStr"/>
-      <c r="G7034" t="inlineStr"/>
-      <c r="H7034" t="inlineStr"/>
-      <c r="I7034" t="inlineStr"/>
     </row>
     <row r="7035">
       <c r="A7035" t="inlineStr">
@@ -83853,13 +83860,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C7035" t="inlineStr"/>
-      <c r="D7035" t="inlineStr"/>
-      <c r="E7035" t="inlineStr"/>
-      <c r="F7035" t="inlineStr"/>
-      <c r="G7035" t="inlineStr"/>
-      <c r="H7035" t="inlineStr"/>
-      <c r="I7035" t="inlineStr"/>
     </row>
     <row r="7036">
       <c r="A7036" t="inlineStr">
@@ -83872,13 +83872,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C7036" t="inlineStr"/>
-      <c r="D7036" t="inlineStr"/>
-      <c r="E7036" t="inlineStr"/>
-      <c r="F7036" t="inlineStr"/>
-      <c r="G7036" t="inlineStr"/>
-      <c r="H7036" t="inlineStr"/>
-      <c r="I7036" t="inlineStr"/>
     </row>
     <row r="7037">
       <c r="A7037" t="inlineStr">
@@ -83891,13 +83884,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C7037" t="inlineStr"/>
-      <c r="D7037" t="inlineStr"/>
-      <c r="E7037" t="inlineStr"/>
-      <c r="F7037" t="inlineStr"/>
-      <c r="G7037" t="inlineStr"/>
-      <c r="H7037" t="inlineStr"/>
-      <c r="I7037" t="inlineStr"/>
     </row>
     <row r="7038">
       <c r="A7038" t="inlineStr">
@@ -83910,13 +83896,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C7038" t="inlineStr"/>
-      <c r="D7038" t="inlineStr"/>
-      <c r="E7038" t="inlineStr"/>
-      <c r="F7038" t="inlineStr"/>
-      <c r="G7038" t="inlineStr"/>
-      <c r="H7038" t="inlineStr"/>
-      <c r="I7038" t="inlineStr"/>
     </row>
     <row r="7039">
       <c r="A7039" t="inlineStr">
@@ -83929,13 +83908,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C7039" t="inlineStr"/>
-      <c r="D7039" t="inlineStr"/>
-      <c r="E7039" t="inlineStr"/>
-      <c r="F7039" t="inlineStr"/>
-      <c r="G7039" t="inlineStr"/>
-      <c r="H7039" t="inlineStr"/>
-      <c r="I7039" t="inlineStr"/>
     </row>
     <row r="7040">
       <c r="A7040" t="inlineStr">
@@ -83948,13 +83920,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C7040" t="inlineStr"/>
-      <c r="D7040" t="inlineStr"/>
-      <c r="E7040" t="inlineStr"/>
-      <c r="F7040" t="inlineStr"/>
-      <c r="G7040" t="inlineStr"/>
-      <c r="H7040" t="inlineStr"/>
-      <c r="I7040" t="inlineStr"/>
     </row>
     <row r="7041">
       <c r="A7041" t="inlineStr">
@@ -83967,13 +83932,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C7041" t="inlineStr"/>
-      <c r="D7041" t="inlineStr"/>
-      <c r="E7041" t="inlineStr"/>
-      <c r="F7041" t="inlineStr"/>
-      <c r="G7041" t="inlineStr"/>
-      <c r="H7041" t="inlineStr"/>
-      <c r="I7041" t="inlineStr"/>
     </row>
     <row r="7042">
       <c r="A7042" t="inlineStr">
@@ -83986,13 +83944,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C7042" t="inlineStr"/>
-      <c r="D7042" t="inlineStr"/>
-      <c r="E7042" t="inlineStr"/>
-      <c r="F7042" t="inlineStr"/>
-      <c r="G7042" t="inlineStr"/>
-      <c r="H7042" t="inlineStr"/>
-      <c r="I7042" t="inlineStr"/>
     </row>
     <row r="7043">
       <c r="A7043" t="inlineStr">
@@ -84005,13 +83956,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C7043" t="inlineStr"/>
-      <c r="D7043" t="inlineStr"/>
-      <c r="E7043" t="inlineStr"/>
-      <c r="F7043" t="inlineStr"/>
-      <c r="G7043" t="inlineStr"/>
-      <c r="H7043" t="inlineStr"/>
-      <c r="I7043" t="inlineStr"/>
     </row>
     <row r="7044">
       <c r="A7044" t="inlineStr">
@@ -84024,13 +83968,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C7044" t="inlineStr"/>
-      <c r="D7044" t="inlineStr"/>
-      <c r="E7044" t="inlineStr"/>
-      <c r="F7044" t="inlineStr"/>
-      <c r="G7044" t="inlineStr"/>
-      <c r="H7044" t="inlineStr"/>
-      <c r="I7044" t="inlineStr"/>
     </row>
     <row r="7045">
       <c r="A7045" t="inlineStr">
@@ -84043,13 +83980,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C7045" t="inlineStr"/>
-      <c r="D7045" t="inlineStr"/>
-      <c r="E7045" t="inlineStr"/>
-      <c r="F7045" t="inlineStr"/>
-      <c r="G7045" t="inlineStr"/>
-      <c r="H7045" t="inlineStr"/>
-      <c r="I7045" t="inlineStr"/>
     </row>
     <row r="7046">
       <c r="A7046" t="inlineStr">
@@ -84062,13 +83992,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C7046" t="inlineStr"/>
-      <c r="D7046" t="inlineStr"/>
-      <c r="E7046" t="inlineStr"/>
-      <c r="F7046" t="inlineStr"/>
-      <c r="G7046" t="inlineStr"/>
-      <c r="H7046" t="inlineStr"/>
-      <c r="I7046" t="inlineStr"/>
     </row>
     <row r="7047">
       <c r="A7047" t="inlineStr">
@@ -84081,13 +84004,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C7047" t="inlineStr"/>
-      <c r="D7047" t="inlineStr"/>
-      <c r="E7047" t="inlineStr"/>
-      <c r="F7047" t="inlineStr"/>
-      <c r="G7047" t="inlineStr"/>
-      <c r="H7047" t="inlineStr"/>
-      <c r="I7047" t="inlineStr"/>
     </row>
     <row r="7048">
       <c r="A7048" t="inlineStr">
@@ -84100,13 +84016,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C7048" t="inlineStr"/>
-      <c r="D7048" t="inlineStr"/>
-      <c r="E7048" t="inlineStr"/>
-      <c r="F7048" t="inlineStr"/>
-      <c r="G7048" t="inlineStr"/>
-      <c r="H7048" t="inlineStr"/>
-      <c r="I7048" t="inlineStr"/>
     </row>
     <row r="7049">
       <c r="A7049" t="inlineStr">
@@ -84119,13 +84028,6 @@
           <t>Tradescantia zebrina</t>
         </is>
       </c>
-      <c r="C7049" t="inlineStr"/>
-      <c r="D7049" t="inlineStr"/>
-      <c r="E7049" t="inlineStr"/>
-      <c r="F7049" t="inlineStr"/>
-      <c r="G7049" t="inlineStr"/>
-      <c r="H7049" t="inlineStr"/>
-      <c r="I7049" t="inlineStr"/>
     </row>
     <row r="7050">
       <c r="A7050" t="inlineStr">
@@ -84138,13 +84040,6 @@
           <t>Senecio rowleyanus</t>
         </is>
       </c>
-      <c r="C7050" t="inlineStr"/>
-      <c r="D7050" t="inlineStr"/>
-      <c r="E7050" t="inlineStr"/>
-      <c r="F7050" t="inlineStr"/>
-      <c r="G7050" t="inlineStr"/>
-      <c r="H7050" t="inlineStr"/>
-      <c r="I7050" t="inlineStr"/>
     </row>
     <row r="7051">
       <c r="A7051" t="inlineStr">
@@ -84157,13 +84052,6 @@
           <t>Ledebouria socialis</t>
         </is>
       </c>
-      <c r="C7051" t="inlineStr"/>
-      <c r="D7051" t="inlineStr"/>
-      <c r="E7051" t="inlineStr"/>
-      <c r="F7051" t="inlineStr"/>
-      <c r="G7051" t="inlineStr"/>
-      <c r="H7051" t="inlineStr"/>
-      <c r="I7051" t="inlineStr"/>
     </row>
     <row r="7052">
       <c r="A7052" t="inlineStr">
@@ -84176,13 +84064,6 @@
           <t>Peperomia Axillaris</t>
         </is>
       </c>
-      <c r="C7052" t="inlineStr"/>
-      <c r="D7052" t="inlineStr"/>
-      <c r="E7052" t="inlineStr"/>
-      <c r="F7052" t="inlineStr"/>
-      <c r="G7052" t="inlineStr"/>
-      <c r="H7052" t="inlineStr"/>
-      <c r="I7052" t="inlineStr"/>
     </row>
     <row r="7053">
       <c r="A7053" t="inlineStr">
@@ -84195,13 +84076,6 @@
           <t>Hoya Sabah</t>
         </is>
       </c>
-      <c r="C7053" t="inlineStr"/>
-      <c r="D7053" t="inlineStr"/>
-      <c r="E7053" t="inlineStr"/>
-      <c r="F7053" t="inlineStr"/>
-      <c r="G7053" t="inlineStr"/>
-      <c r="H7053" t="inlineStr"/>
-      <c r="I7053" t="inlineStr"/>
     </row>
     <row r="7054"/>
     <row r="7055">
@@ -84215,13 +84089,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C7055" t="inlineStr"/>
-      <c r="D7055" t="inlineStr"/>
-      <c r="E7055" t="inlineStr"/>
-      <c r="F7055" t="inlineStr"/>
-      <c r="G7055" t="inlineStr"/>
-      <c r="H7055" t="inlineStr"/>
-      <c r="I7055" t="inlineStr"/>
     </row>
     <row r="7056">
       <c r="A7056" t="inlineStr">
@@ -84234,13 +84101,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C7056" t="inlineStr"/>
-      <c r="D7056" t="inlineStr"/>
-      <c r="E7056" t="inlineStr"/>
-      <c r="F7056" t="inlineStr"/>
-      <c r="G7056" t="inlineStr"/>
-      <c r="H7056" t="inlineStr"/>
-      <c r="I7056" t="inlineStr"/>
     </row>
     <row r="7057">
       <c r="A7057" t="inlineStr">
@@ -84253,13 +84113,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C7057" t="inlineStr"/>
-      <c r="D7057" t="inlineStr"/>
-      <c r="E7057" t="inlineStr"/>
-      <c r="F7057" t="inlineStr"/>
-      <c r="G7057" t="inlineStr"/>
-      <c r="H7057" t="inlineStr"/>
-      <c r="I7057" t="inlineStr"/>
     </row>
     <row r="7058">
       <c r="A7058" t="inlineStr">
@@ -84272,13 +84125,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C7058" t="inlineStr"/>
-      <c r="D7058" t="inlineStr"/>
-      <c r="E7058" t="inlineStr"/>
-      <c r="F7058" t="inlineStr"/>
-      <c r="G7058" t="inlineStr"/>
-      <c r="H7058" t="inlineStr"/>
-      <c r="I7058" t="inlineStr"/>
     </row>
     <row r="7059">
       <c r="A7059" t="inlineStr">
@@ -84291,13 +84137,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C7059" t="inlineStr"/>
-      <c r="D7059" t="inlineStr"/>
-      <c r="E7059" t="inlineStr"/>
-      <c r="F7059" t="inlineStr"/>
-      <c r="G7059" t="inlineStr"/>
-      <c r="H7059" t="inlineStr"/>
-      <c r="I7059" t="inlineStr"/>
     </row>
     <row r="7060">
       <c r="A7060" t="inlineStr">
@@ -84310,13 +84149,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C7060" t="inlineStr"/>
-      <c r="D7060" t="inlineStr"/>
-      <c r="E7060" t="inlineStr"/>
-      <c r="F7060" t="inlineStr"/>
-      <c r="G7060" t="inlineStr"/>
-      <c r="H7060" t="inlineStr"/>
-      <c r="I7060" t="inlineStr"/>
     </row>
     <row r="7061">
       <c r="A7061" t="inlineStr">
@@ -84329,13 +84161,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C7061" t="inlineStr"/>
-      <c r="D7061" t="inlineStr"/>
-      <c r="E7061" t="inlineStr"/>
-      <c r="F7061" t="inlineStr"/>
-      <c r="G7061" t="inlineStr"/>
-      <c r="H7061" t="inlineStr"/>
-      <c r="I7061" t="inlineStr"/>
     </row>
     <row r="7062">
       <c r="A7062" t="inlineStr">
@@ -84348,13 +84173,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C7062" t="inlineStr"/>
-      <c r="D7062" t="inlineStr"/>
-      <c r="E7062" t="inlineStr"/>
-      <c r="F7062" t="inlineStr"/>
-      <c r="G7062" t="inlineStr"/>
-      <c r="H7062" t="inlineStr"/>
-      <c r="I7062" t="inlineStr"/>
     </row>
     <row r="7063">
       <c r="A7063" t="inlineStr">
@@ -84367,13 +84185,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C7063" t="inlineStr"/>
-      <c r="D7063" t="inlineStr"/>
-      <c r="E7063" t="inlineStr"/>
-      <c r="F7063" t="inlineStr"/>
-      <c r="G7063" t="inlineStr"/>
-      <c r="H7063" t="inlineStr"/>
-      <c r="I7063" t="inlineStr"/>
     </row>
     <row r="7064">
       <c r="A7064" t="inlineStr">
@@ -84386,13 +84197,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C7064" t="inlineStr"/>
-      <c r="D7064" t="inlineStr"/>
-      <c r="E7064" t="inlineStr"/>
-      <c r="F7064" t="inlineStr"/>
-      <c r="G7064" t="inlineStr"/>
-      <c r="H7064" t="inlineStr"/>
-      <c r="I7064" t="inlineStr"/>
     </row>
     <row r="7065">
       <c r="A7065" t="inlineStr">
@@ -84405,13 +84209,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C7065" t="inlineStr"/>
-      <c r="D7065" t="inlineStr"/>
-      <c r="E7065" t="inlineStr"/>
-      <c r="F7065" t="inlineStr"/>
-      <c r="G7065" t="inlineStr"/>
-      <c r="H7065" t="inlineStr"/>
-      <c r="I7065" t="inlineStr"/>
     </row>
     <row r="7066">
       <c r="A7066" t="inlineStr">
@@ -84424,13 +84221,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C7066" t="inlineStr"/>
-      <c r="D7066" t="inlineStr"/>
-      <c r="E7066" t="inlineStr"/>
-      <c r="F7066" t="inlineStr"/>
-      <c r="G7066" t="inlineStr"/>
-      <c r="H7066" t="inlineStr"/>
-      <c r="I7066" t="inlineStr"/>
     </row>
     <row r="7067">
       <c r="A7067" t="inlineStr">
@@ -84443,13 +84233,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C7067" t="inlineStr"/>
-      <c r="D7067" t="inlineStr"/>
-      <c r="E7067" t="inlineStr"/>
-      <c r="F7067" t="inlineStr"/>
-      <c r="G7067" t="inlineStr"/>
-      <c r="H7067" t="inlineStr"/>
-      <c r="I7067" t="inlineStr"/>
     </row>
     <row r="7068">
       <c r="A7068" t="inlineStr">
@@ -84462,13 +84245,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C7068" t="inlineStr"/>
-      <c r="D7068" t="inlineStr"/>
-      <c r="E7068" t="inlineStr"/>
-      <c r="F7068" t="inlineStr"/>
-      <c r="G7068" t="inlineStr"/>
-      <c r="H7068" t="inlineStr"/>
-      <c r="I7068" t="inlineStr"/>
     </row>
     <row r="7069">
       <c r="A7069" t="inlineStr">
@@ -84481,13 +84257,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C7069" t="inlineStr"/>
-      <c r="D7069" t="inlineStr"/>
-      <c r="E7069" t="inlineStr"/>
-      <c r="F7069" t="inlineStr"/>
-      <c r="G7069" t="inlineStr"/>
-      <c r="H7069" t="inlineStr"/>
-      <c r="I7069" t="inlineStr"/>
     </row>
     <row r="7070">
       <c r="A7070" t="inlineStr">
@@ -84500,13 +84269,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C7070" t="inlineStr"/>
-      <c r="D7070" t="inlineStr"/>
-      <c r="E7070" t="inlineStr"/>
-      <c r="F7070" t="inlineStr"/>
-      <c r="G7070" t="inlineStr"/>
-      <c r="H7070" t="inlineStr"/>
-      <c r="I7070" t="inlineStr"/>
     </row>
     <row r="7071">
       <c r="A7071" t="inlineStr">
@@ -84519,13 +84281,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C7071" t="inlineStr"/>
-      <c r="D7071" t="inlineStr"/>
-      <c r="E7071" t="inlineStr"/>
-      <c r="F7071" t="inlineStr"/>
-      <c r="G7071" t="inlineStr"/>
-      <c r="H7071" t="inlineStr"/>
-      <c r="I7071" t="inlineStr"/>
     </row>
     <row r="7072">
       <c r="A7072" t="inlineStr">
@@ -84538,13 +84293,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C7072" t="inlineStr"/>
-      <c r="D7072" t="inlineStr"/>
-      <c r="E7072" t="inlineStr"/>
-      <c r="F7072" t="inlineStr"/>
-      <c r="G7072" t="inlineStr"/>
-      <c r="H7072" t="inlineStr"/>
-      <c r="I7072" t="inlineStr"/>
     </row>
     <row r="7073">
       <c r="A7073" t="inlineStr">
@@ -84557,13 +84305,6 @@
           <t>Tradescantia zebrina</t>
         </is>
       </c>
-      <c r="C7073" t="inlineStr"/>
-      <c r="D7073" t="inlineStr"/>
-      <c r="E7073" t="inlineStr"/>
-      <c r="F7073" t="inlineStr"/>
-      <c r="G7073" t="inlineStr"/>
-      <c r="H7073" t="inlineStr"/>
-      <c r="I7073" t="inlineStr"/>
     </row>
     <row r="7074">
       <c r="A7074" t="inlineStr">
@@ -84576,13 +84317,6 @@
           <t>Senecio rowleyanus</t>
         </is>
       </c>
-      <c r="C7074" t="inlineStr"/>
-      <c r="D7074" t="inlineStr"/>
-      <c r="E7074" t="inlineStr"/>
-      <c r="F7074" t="inlineStr"/>
-      <c r="G7074" t="inlineStr"/>
-      <c r="H7074" t="inlineStr"/>
-      <c r="I7074" t="inlineStr"/>
     </row>
     <row r="7075">
       <c r="A7075" t="inlineStr">
@@ -84595,13 +84329,6 @@
           <t>Ledebouria socialis</t>
         </is>
       </c>
-      <c r="C7075" t="inlineStr"/>
-      <c r="D7075" t="inlineStr"/>
-      <c r="E7075" t="inlineStr"/>
-      <c r="F7075" t="inlineStr"/>
-      <c r="G7075" t="inlineStr"/>
-      <c r="H7075" t="inlineStr"/>
-      <c r="I7075" t="inlineStr"/>
     </row>
     <row r="7076">
       <c r="A7076" t="inlineStr">
@@ -84614,13 +84341,6 @@
           <t>Peperomia Axillaris</t>
         </is>
       </c>
-      <c r="C7076" t="inlineStr"/>
-      <c r="D7076" t="inlineStr"/>
-      <c r="E7076" t="inlineStr"/>
-      <c r="F7076" t="inlineStr"/>
-      <c r="G7076" t="inlineStr"/>
-      <c r="H7076" t="inlineStr"/>
-      <c r="I7076" t="inlineStr"/>
     </row>
     <row r="7077">
       <c r="A7077" t="inlineStr">
@@ -84633,13 +84353,6 @@
           <t>Hoya Sabah</t>
         </is>
       </c>
-      <c r="C7077" t="inlineStr"/>
-      <c r="D7077" t="inlineStr"/>
-      <c r="E7077" t="inlineStr"/>
-      <c r="F7077" t="inlineStr"/>
-      <c r="G7077" t="inlineStr"/>
-      <c r="H7077" t="inlineStr"/>
-      <c r="I7077" t="inlineStr"/>
     </row>
     <row r="7078"/>
     <row r="7079">
@@ -84653,13 +84366,8 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C7079" t="inlineStr"/>
-      <c r="D7079" t="inlineStr"/>
-      <c r="E7079" t="inlineStr"/>
-      <c r="F7079" t="inlineStr"/>
-      <c r="G7079" t="inlineStr"/>
-      <c r="H7079" t="inlineStr"/>
-      <c r="I7079" t="inlineStr"/>
+      <c r="D7079" s="24" t="n"/>
+      <c r="E7079" s="24" t="n"/>
     </row>
     <row r="7080">
       <c r="A7080" t="inlineStr">
@@ -84672,13 +84380,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C7080" t="inlineStr"/>
-      <c r="D7080" t="inlineStr"/>
-      <c r="E7080" t="inlineStr"/>
-      <c r="F7080" t="inlineStr"/>
-      <c r="G7080" t="inlineStr"/>
-      <c r="H7080" t="inlineStr"/>
-      <c r="I7080" t="inlineStr"/>
     </row>
     <row r="7081">
       <c r="A7081" t="inlineStr">
@@ -84691,13 +84392,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C7081" t="inlineStr"/>
-      <c r="D7081" t="inlineStr"/>
-      <c r="E7081" t="inlineStr"/>
-      <c r="F7081" t="inlineStr"/>
-      <c r="G7081" t="inlineStr"/>
-      <c r="H7081" t="inlineStr"/>
-      <c r="I7081" t="inlineStr"/>
     </row>
     <row r="7082">
       <c r="A7082" t="inlineStr">
@@ -84710,13 +84404,14 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C7082" t="inlineStr"/>
-      <c r="D7082" t="inlineStr"/>
-      <c r="E7082" t="inlineStr"/>
-      <c r="F7082" t="inlineStr"/>
-      <c r="G7082" t="inlineStr"/>
-      <c r="H7082" t="inlineStr"/>
-      <c r="I7082" t="inlineStr"/>
+      <c r="D7082" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7082" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7083">
       <c r="A7083" t="inlineStr">
@@ -84729,13 +84424,14 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C7083" t="inlineStr"/>
-      <c r="D7083" t="inlineStr"/>
-      <c r="E7083" t="inlineStr"/>
-      <c r="F7083" t="inlineStr"/>
-      <c r="G7083" t="inlineStr"/>
-      <c r="H7083" t="inlineStr"/>
-      <c r="I7083" t="inlineStr"/>
+      <c r="D7083" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7083" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7084">
       <c r="A7084" t="inlineStr">
@@ -84748,13 +84444,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C7084" t="inlineStr"/>
-      <c r="D7084" t="inlineStr"/>
-      <c r="E7084" t="inlineStr"/>
-      <c r="F7084" t="inlineStr"/>
-      <c r="G7084" t="inlineStr"/>
-      <c r="H7084" t="inlineStr"/>
-      <c r="I7084" t="inlineStr"/>
     </row>
     <row r="7085">
       <c r="A7085" t="inlineStr">
@@ -84767,13 +84456,14 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C7085" t="inlineStr"/>
-      <c r="D7085" t="inlineStr"/>
-      <c r="E7085" t="inlineStr"/>
-      <c r="F7085" t="inlineStr"/>
-      <c r="G7085" t="inlineStr"/>
-      <c r="H7085" t="inlineStr"/>
-      <c r="I7085" t="inlineStr"/>
+      <c r="D7085" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7085" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7086">
       <c r="A7086" t="inlineStr">
@@ -84786,13 +84476,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C7086" t="inlineStr"/>
-      <c r="D7086" t="inlineStr"/>
-      <c r="E7086" t="inlineStr"/>
-      <c r="F7086" t="inlineStr"/>
-      <c r="G7086" t="inlineStr"/>
-      <c r="H7086" t="inlineStr"/>
-      <c r="I7086" t="inlineStr"/>
     </row>
     <row r="7087">
       <c r="A7087" t="inlineStr">
@@ -84805,13 +84488,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C7087" t="inlineStr"/>
-      <c r="D7087" t="inlineStr"/>
-      <c r="E7087" t="inlineStr"/>
-      <c r="F7087" t="inlineStr"/>
-      <c r="G7087" t="inlineStr"/>
-      <c r="H7087" t="inlineStr"/>
-      <c r="I7087" t="inlineStr"/>
     </row>
     <row r="7088">
       <c r="A7088" t="inlineStr">
@@ -84824,13 +84500,14 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C7088" t="inlineStr"/>
-      <c r="D7088" t="inlineStr"/>
-      <c r="E7088" t="inlineStr"/>
-      <c r="F7088" t="inlineStr"/>
-      <c r="G7088" t="inlineStr"/>
-      <c r="H7088" t="inlineStr"/>
-      <c r="I7088" t="inlineStr"/>
+      <c r="D7088" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7088" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7089">
       <c r="A7089" t="inlineStr">
@@ -84843,13 +84520,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C7089" t="inlineStr"/>
-      <c r="D7089" t="inlineStr"/>
-      <c r="E7089" t="inlineStr"/>
-      <c r="F7089" t="inlineStr"/>
-      <c r="G7089" t="inlineStr"/>
-      <c r="H7089" t="inlineStr"/>
-      <c r="I7089" t="inlineStr"/>
     </row>
     <row r="7090">
       <c r="A7090" t="inlineStr">
@@ -84862,13 +84532,14 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C7090" t="inlineStr"/>
-      <c r="D7090" t="inlineStr"/>
-      <c r="E7090" t="inlineStr"/>
-      <c r="F7090" t="inlineStr"/>
-      <c r="G7090" t="inlineStr"/>
-      <c r="H7090" t="inlineStr"/>
-      <c r="I7090" t="inlineStr"/>
+      <c r="D7090" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7090" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7091">
       <c r="A7091" t="inlineStr">
@@ -84881,13 +84552,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C7091" t="inlineStr"/>
-      <c r="D7091" t="inlineStr"/>
-      <c r="E7091" t="inlineStr"/>
-      <c r="F7091" t="inlineStr"/>
-      <c r="G7091" t="inlineStr"/>
-      <c r="H7091" t="inlineStr"/>
-      <c r="I7091" t="inlineStr"/>
     </row>
     <row r="7092">
       <c r="A7092" t="inlineStr">
@@ -84900,13 +84564,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C7092" t="inlineStr"/>
-      <c r="D7092" t="inlineStr"/>
-      <c r="E7092" t="inlineStr"/>
-      <c r="F7092" t="inlineStr"/>
-      <c r="G7092" t="inlineStr"/>
-      <c r="H7092" t="inlineStr"/>
-      <c r="I7092" t="inlineStr"/>
     </row>
     <row r="7093">
       <c r="A7093" t="inlineStr">
@@ -84919,13 +84576,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C7093" t="inlineStr"/>
-      <c r="D7093" t="inlineStr"/>
-      <c r="E7093" t="inlineStr"/>
-      <c r="F7093" t="inlineStr"/>
-      <c r="G7093" t="inlineStr"/>
-      <c r="H7093" t="inlineStr"/>
-      <c r="I7093" t="inlineStr"/>
     </row>
     <row r="7094">
       <c r="A7094" t="inlineStr">
@@ -84938,13 +84588,14 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C7094" t="inlineStr"/>
-      <c r="D7094" t="inlineStr"/>
-      <c r="E7094" t="inlineStr"/>
-      <c r="F7094" t="inlineStr"/>
-      <c r="G7094" t="inlineStr"/>
-      <c r="H7094" t="inlineStr"/>
-      <c r="I7094" t="inlineStr"/>
+      <c r="D7094" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7094" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7095">
       <c r="A7095" t="inlineStr">
@@ -84957,13 +84608,14 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C7095" t="inlineStr"/>
-      <c r="D7095" t="inlineStr"/>
-      <c r="E7095" t="inlineStr"/>
-      <c r="F7095" t="inlineStr"/>
-      <c r="G7095" t="inlineStr"/>
-      <c r="H7095" t="inlineStr"/>
-      <c r="I7095" t="inlineStr"/>
+      <c r="D7095" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7095" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7096">
       <c r="A7096" t="inlineStr">
@@ -84976,13 +84628,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C7096" t="inlineStr"/>
-      <c r="D7096" t="inlineStr"/>
-      <c r="E7096" t="inlineStr"/>
-      <c r="F7096" t="inlineStr"/>
-      <c r="G7096" t="inlineStr"/>
-      <c r="H7096" t="inlineStr"/>
-      <c r="I7096" t="inlineStr"/>
     </row>
     <row r="7097">
       <c r="A7097" t="inlineStr">
@@ -84995,13 +84640,14 @@
           <t>Tradescantia zebrina</t>
         </is>
       </c>
-      <c r="C7097" t="inlineStr"/>
-      <c r="D7097" t="inlineStr"/>
-      <c r="E7097" t="inlineStr"/>
-      <c r="F7097" t="inlineStr"/>
-      <c r="G7097" t="inlineStr"/>
-      <c r="H7097" t="inlineStr"/>
-      <c r="I7097" t="inlineStr"/>
+      <c r="D7097" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7097" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7098">
       <c r="A7098" t="inlineStr">
@@ -85014,13 +84660,6 @@
           <t>Senecio rowleyanus</t>
         </is>
       </c>
-      <c r="C7098" t="inlineStr"/>
-      <c r="D7098" t="inlineStr"/>
-      <c r="E7098" t="inlineStr"/>
-      <c r="F7098" t="inlineStr"/>
-      <c r="G7098" t="inlineStr"/>
-      <c r="H7098" t="inlineStr"/>
-      <c r="I7098" t="inlineStr"/>
     </row>
     <row r="7099">
       <c r="A7099" t="inlineStr">
@@ -85033,13 +84672,6 @@
           <t>Ledebouria socialis</t>
         </is>
       </c>
-      <c r="C7099" t="inlineStr"/>
-      <c r="D7099" t="inlineStr"/>
-      <c r="E7099" t="inlineStr"/>
-      <c r="F7099" t="inlineStr"/>
-      <c r="G7099" t="inlineStr"/>
-      <c r="H7099" t="inlineStr"/>
-      <c r="I7099" t="inlineStr"/>
     </row>
     <row r="7100">
       <c r="A7100" t="inlineStr">
@@ -85052,13 +84684,14 @@
           <t>Peperomia Axillaris</t>
         </is>
       </c>
-      <c r="C7100" t="inlineStr"/>
-      <c r="D7100" t="inlineStr"/>
-      <c r="E7100" t="inlineStr"/>
-      <c r="F7100" t="inlineStr"/>
-      <c r="G7100" t="inlineStr"/>
-      <c r="H7100" t="inlineStr"/>
-      <c r="I7100" t="inlineStr"/>
+      <c r="D7100" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7100" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
     </row>
     <row r="7101">
       <c r="A7101" t="inlineStr">
@@ -85071,13 +84704,6 @@
           <t>Hoya Sabah</t>
         </is>
       </c>
-      <c r="C7101" t="inlineStr"/>
-      <c r="D7101" t="inlineStr"/>
-      <c r="E7101" t="inlineStr"/>
-      <c r="F7101" t="inlineStr"/>
-      <c r="G7101" t="inlineStr"/>
-      <c r="H7101" t="inlineStr"/>
-      <c r="I7101" t="inlineStr"/>
     </row>
     <row r="7102"/>
     <row r="7103">
@@ -85091,13 +84717,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C7103" t="inlineStr"/>
-      <c r="D7103" t="inlineStr"/>
-      <c r="E7103" t="inlineStr"/>
-      <c r="F7103" t="inlineStr"/>
-      <c r="G7103" t="inlineStr"/>
-      <c r="H7103" t="inlineStr"/>
-      <c r="I7103" t="inlineStr"/>
     </row>
     <row r="7104">
       <c r="A7104" t="inlineStr">
@@ -85110,13 +84729,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C7104" t="inlineStr"/>
-      <c r="D7104" t="inlineStr"/>
-      <c r="E7104" t="inlineStr"/>
-      <c r="F7104" t="inlineStr"/>
-      <c r="G7104" t="inlineStr"/>
-      <c r="H7104" t="inlineStr"/>
-      <c r="I7104" t="inlineStr"/>
     </row>
     <row r="7105">
       <c r="A7105" t="inlineStr">
@@ -85129,13 +84741,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C7105" t="inlineStr"/>
-      <c r="D7105" t="inlineStr"/>
-      <c r="E7105" t="inlineStr"/>
-      <c r="F7105" t="inlineStr"/>
-      <c r="G7105" t="inlineStr"/>
-      <c r="H7105" t="inlineStr"/>
-      <c r="I7105" t="inlineStr"/>
     </row>
     <row r="7106">
       <c r="A7106" t="inlineStr">
@@ -85148,13 +84753,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C7106" t="inlineStr"/>
-      <c r="D7106" t="inlineStr"/>
-      <c r="E7106" t="inlineStr"/>
-      <c r="F7106" t="inlineStr"/>
-      <c r="G7106" t="inlineStr"/>
-      <c r="H7106" t="inlineStr"/>
-      <c r="I7106" t="inlineStr"/>
     </row>
     <row r="7107">
       <c r="A7107" t="inlineStr">
@@ -85167,13 +84765,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C7107" t="inlineStr"/>
-      <c r="D7107" t="inlineStr"/>
-      <c r="E7107" t="inlineStr"/>
-      <c r="F7107" t="inlineStr"/>
-      <c r="G7107" t="inlineStr"/>
-      <c r="H7107" t="inlineStr"/>
-      <c r="I7107" t="inlineStr"/>
     </row>
     <row r="7108">
       <c r="A7108" t="inlineStr">
@@ -85186,13 +84777,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C7108" t="inlineStr"/>
-      <c r="D7108" t="inlineStr"/>
-      <c r="E7108" t="inlineStr"/>
-      <c r="F7108" t="inlineStr"/>
-      <c r="G7108" t="inlineStr"/>
-      <c r="H7108" t="inlineStr"/>
-      <c r="I7108" t="inlineStr"/>
     </row>
     <row r="7109">
       <c r="A7109" t="inlineStr">
@@ -85205,13 +84789,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C7109" t="inlineStr"/>
-      <c r="D7109" t="inlineStr"/>
-      <c r="E7109" t="inlineStr"/>
-      <c r="F7109" t="inlineStr"/>
-      <c r="G7109" t="inlineStr"/>
-      <c r="H7109" t="inlineStr"/>
-      <c r="I7109" t="inlineStr"/>
     </row>
     <row r="7110">
       <c r="A7110" t="inlineStr">
@@ -85224,13 +84801,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C7110" t="inlineStr"/>
-      <c r="D7110" t="inlineStr"/>
-      <c r="E7110" t="inlineStr"/>
-      <c r="F7110" t="inlineStr"/>
-      <c r="G7110" t="inlineStr"/>
-      <c r="H7110" t="inlineStr"/>
-      <c r="I7110" t="inlineStr"/>
     </row>
     <row r="7111">
       <c r="A7111" t="inlineStr">
@@ -85243,13 +84813,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C7111" t="inlineStr"/>
-      <c r="D7111" t="inlineStr"/>
-      <c r="E7111" t="inlineStr"/>
-      <c r="F7111" t="inlineStr"/>
-      <c r="G7111" t="inlineStr"/>
-      <c r="H7111" t="inlineStr"/>
-      <c r="I7111" t="inlineStr"/>
     </row>
     <row r="7112">
       <c r="A7112" t="inlineStr">
@@ -85262,13 +84825,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C7112" t="inlineStr"/>
-      <c r="D7112" t="inlineStr"/>
-      <c r="E7112" t="inlineStr"/>
-      <c r="F7112" t="inlineStr"/>
-      <c r="G7112" t="inlineStr"/>
-      <c r="H7112" t="inlineStr"/>
-      <c r="I7112" t="inlineStr"/>
     </row>
     <row r="7113">
       <c r="A7113" t="inlineStr">
@@ -85281,13 +84837,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C7113" t="inlineStr"/>
-      <c r="D7113" t="inlineStr"/>
-      <c r="E7113" t="inlineStr"/>
-      <c r="F7113" t="inlineStr"/>
-      <c r="G7113" t="inlineStr"/>
-      <c r="H7113" t="inlineStr"/>
-      <c r="I7113" t="inlineStr"/>
     </row>
     <row r="7114">
       <c r="A7114" t="inlineStr">
@@ -85300,13 +84849,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C7114" t="inlineStr"/>
-      <c r="D7114" t="inlineStr"/>
-      <c r="E7114" t="inlineStr"/>
-      <c r="F7114" t="inlineStr"/>
-      <c r="G7114" t="inlineStr"/>
-      <c r="H7114" t="inlineStr"/>
-      <c r="I7114" t="inlineStr"/>
     </row>
     <row r="7115">
       <c r="A7115" t="inlineStr">
@@ -85319,13 +84861,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C7115" t="inlineStr"/>
-      <c r="D7115" t="inlineStr"/>
-      <c r="E7115" t="inlineStr"/>
-      <c r="F7115" t="inlineStr"/>
-      <c r="G7115" t="inlineStr"/>
-      <c r="H7115" t="inlineStr"/>
-      <c r="I7115" t="inlineStr"/>
     </row>
     <row r="7116">
       <c r="A7116" t="inlineStr">
@@ -85338,13 +84873,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C7116" t="inlineStr"/>
-      <c r="D7116" t="inlineStr"/>
-      <c r="E7116" t="inlineStr"/>
-      <c r="F7116" t="inlineStr"/>
-      <c r="G7116" t="inlineStr"/>
-      <c r="H7116" t="inlineStr"/>
-      <c r="I7116" t="inlineStr"/>
     </row>
     <row r="7117">
       <c r="A7117" t="inlineStr">
@@ -85357,13 +84885,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C7117" t="inlineStr"/>
-      <c r="D7117" t="inlineStr"/>
-      <c r="E7117" t="inlineStr"/>
-      <c r="F7117" t="inlineStr"/>
-      <c r="G7117" t="inlineStr"/>
-      <c r="H7117" t="inlineStr"/>
-      <c r="I7117" t="inlineStr"/>
     </row>
     <row r="7118">
       <c r="A7118" t="inlineStr">
@@ -85376,13 +84897,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C7118" t="inlineStr"/>
-      <c r="D7118" t="inlineStr"/>
-      <c r="E7118" t="inlineStr"/>
-      <c r="F7118" t="inlineStr"/>
-      <c r="G7118" t="inlineStr"/>
-      <c r="H7118" t="inlineStr"/>
-      <c r="I7118" t="inlineStr"/>
     </row>
     <row r="7119">
       <c r="A7119" t="inlineStr">
@@ -85395,13 +84909,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C7119" t="inlineStr"/>
-      <c r="D7119" t="inlineStr"/>
-      <c r="E7119" t="inlineStr"/>
-      <c r="F7119" t="inlineStr"/>
-      <c r="G7119" t="inlineStr"/>
-      <c r="H7119" t="inlineStr"/>
-      <c r="I7119" t="inlineStr"/>
     </row>
     <row r="7120">
       <c r="A7120" t="inlineStr">
@@ -85414,13 +84921,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C7120" t="inlineStr"/>
-      <c r="D7120" t="inlineStr"/>
-      <c r="E7120" t="inlineStr"/>
-      <c r="F7120" t="inlineStr"/>
-      <c r="G7120" t="inlineStr"/>
-      <c r="H7120" t="inlineStr"/>
-      <c r="I7120" t="inlineStr"/>
     </row>
     <row r="7121">
       <c r="A7121" t="inlineStr">
@@ -85433,13 +84933,6 @@
           <t>Tradescantia zebrina</t>
         </is>
       </c>
-      <c r="C7121" t="inlineStr"/>
-      <c r="D7121" t="inlineStr"/>
-      <c r="E7121" t="inlineStr"/>
-      <c r="F7121" t="inlineStr"/>
-      <c r="G7121" t="inlineStr"/>
-      <c r="H7121" t="inlineStr"/>
-      <c r="I7121" t="inlineStr"/>
     </row>
     <row r="7122">
       <c r="A7122" t="inlineStr">
@@ -85452,13 +84945,6 @@
           <t>Senecio rowleyanus</t>
         </is>
       </c>
-      <c r="C7122" t="inlineStr"/>
-      <c r="D7122" t="inlineStr"/>
-      <c r="E7122" t="inlineStr"/>
-      <c r="F7122" t="inlineStr"/>
-      <c r="G7122" t="inlineStr"/>
-      <c r="H7122" t="inlineStr"/>
-      <c r="I7122" t="inlineStr"/>
     </row>
     <row r="7123">
       <c r="A7123" t="inlineStr">
@@ -85471,13 +84957,6 @@
           <t>Ledebouria socialis</t>
         </is>
       </c>
-      <c r="C7123" t="inlineStr"/>
-      <c r="D7123" t="inlineStr"/>
-      <c r="E7123" t="inlineStr"/>
-      <c r="F7123" t="inlineStr"/>
-      <c r="G7123" t="inlineStr"/>
-      <c r="H7123" t="inlineStr"/>
-      <c r="I7123" t="inlineStr"/>
     </row>
     <row r="7124">
       <c r="A7124" t="inlineStr">
@@ -85490,13 +84969,6 @@
           <t>Peperomia Axillaris</t>
         </is>
       </c>
-      <c r="C7124" t="inlineStr"/>
-      <c r="D7124" t="inlineStr"/>
-      <c r="E7124" t="inlineStr"/>
-      <c r="F7124" t="inlineStr"/>
-      <c r="G7124" t="inlineStr"/>
-      <c r="H7124" t="inlineStr"/>
-      <c r="I7124" t="inlineStr"/>
     </row>
     <row r="7125">
       <c r="A7125" t="inlineStr">
@@ -85509,13 +84981,6 @@
           <t>Hoya Sabah</t>
         </is>
       </c>
-      <c r="C7125" t="inlineStr"/>
-      <c r="D7125" t="inlineStr"/>
-      <c r="E7125" t="inlineStr"/>
-      <c r="F7125" t="inlineStr"/>
-      <c r="G7125" t="inlineStr"/>
-      <c r="H7125" t="inlineStr"/>
-      <c r="I7125" t="inlineStr"/>
     </row>
     <row r="7126"/>
     <row r="7127">
@@ -85529,13 +84994,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C7127" t="inlineStr"/>
-      <c r="D7127" t="inlineStr"/>
-      <c r="E7127" t="inlineStr"/>
-      <c r="F7127" t="inlineStr"/>
-      <c r="G7127" t="inlineStr"/>
-      <c r="H7127" t="inlineStr"/>
-      <c r="I7127" t="inlineStr"/>
     </row>
     <row r="7128">
       <c r="A7128" t="inlineStr">
@@ -85548,13 +85006,6 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C7128" t="inlineStr"/>
-      <c r="D7128" t="inlineStr"/>
-      <c r="E7128" t="inlineStr"/>
-      <c r="F7128" t="inlineStr"/>
-      <c r="G7128" t="inlineStr"/>
-      <c r="H7128" t="inlineStr"/>
-      <c r="I7128" t="inlineStr"/>
     </row>
     <row r="7129">
       <c r="A7129" t="inlineStr">
@@ -85567,13 +85018,6 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C7129" t="inlineStr"/>
-      <c r="D7129" t="inlineStr"/>
-      <c r="E7129" t="inlineStr"/>
-      <c r="F7129" t="inlineStr"/>
-      <c r="G7129" t="inlineStr"/>
-      <c r="H7129" t="inlineStr"/>
-      <c r="I7129" t="inlineStr"/>
     </row>
     <row r="7130">
       <c r="A7130" t="inlineStr">
@@ -85586,13 +85030,6 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C7130" t="inlineStr"/>
-      <c r="D7130" t="inlineStr"/>
-      <c r="E7130" t="inlineStr"/>
-      <c r="F7130" t="inlineStr"/>
-      <c r="G7130" t="inlineStr"/>
-      <c r="H7130" t="inlineStr"/>
-      <c r="I7130" t="inlineStr"/>
     </row>
     <row r="7131">
       <c r="A7131" t="inlineStr">
@@ -85605,13 +85042,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C7131" t="inlineStr"/>
-      <c r="D7131" t="inlineStr"/>
-      <c r="E7131" t="inlineStr"/>
-      <c r="F7131" t="inlineStr"/>
-      <c r="G7131" t="inlineStr"/>
-      <c r="H7131" t="inlineStr"/>
-      <c r="I7131" t="inlineStr"/>
     </row>
     <row r="7132">
       <c r="A7132" t="inlineStr">
@@ -85624,13 +85054,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C7132" t="inlineStr"/>
-      <c r="D7132" t="inlineStr"/>
-      <c r="E7132" t="inlineStr"/>
-      <c r="F7132" t="inlineStr"/>
-      <c r="G7132" t="inlineStr"/>
-      <c r="H7132" t="inlineStr"/>
-      <c r="I7132" t="inlineStr"/>
     </row>
     <row r="7133">
       <c r="A7133" t="inlineStr">
@@ -85643,13 +85066,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C7133" t="inlineStr"/>
-      <c r="D7133" t="inlineStr"/>
-      <c r="E7133" t="inlineStr"/>
-      <c r="F7133" t="inlineStr"/>
-      <c r="G7133" t="inlineStr"/>
-      <c r="H7133" t="inlineStr"/>
-      <c r="I7133" t="inlineStr"/>
     </row>
     <row r="7134">
       <c r="A7134" t="inlineStr">
@@ -85662,13 +85078,6 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C7134" t="inlineStr"/>
-      <c r="D7134" t="inlineStr"/>
-      <c r="E7134" t="inlineStr"/>
-      <c r="F7134" t="inlineStr"/>
-      <c r="G7134" t="inlineStr"/>
-      <c r="H7134" t="inlineStr"/>
-      <c r="I7134" t="inlineStr"/>
     </row>
     <row r="7135">
       <c r="A7135" t="inlineStr">
@@ -85681,13 +85090,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C7135" t="inlineStr"/>
-      <c r="D7135" t="inlineStr"/>
-      <c r="E7135" t="inlineStr"/>
-      <c r="F7135" t="inlineStr"/>
-      <c r="G7135" t="inlineStr"/>
-      <c r="H7135" t="inlineStr"/>
-      <c r="I7135" t="inlineStr"/>
     </row>
     <row r="7136">
       <c r="A7136" t="inlineStr">
@@ -85700,13 +85102,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C7136" t="inlineStr"/>
-      <c r="D7136" t="inlineStr"/>
-      <c r="E7136" t="inlineStr"/>
-      <c r="F7136" t="inlineStr"/>
-      <c r="G7136" t="inlineStr"/>
-      <c r="H7136" t="inlineStr"/>
-      <c r="I7136" t="inlineStr"/>
     </row>
     <row r="7137">
       <c r="A7137" t="inlineStr">
@@ -85719,13 +85114,6 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C7137" t="inlineStr"/>
-      <c r="D7137" t="inlineStr"/>
-      <c r="E7137" t="inlineStr"/>
-      <c r="F7137" t="inlineStr"/>
-      <c r="G7137" t="inlineStr"/>
-      <c r="H7137" t="inlineStr"/>
-      <c r="I7137" t="inlineStr"/>
     </row>
     <row r="7138">
       <c r="A7138" t="inlineStr">
@@ -85738,13 +85126,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C7138" t="inlineStr"/>
-      <c r="D7138" t="inlineStr"/>
-      <c r="E7138" t="inlineStr"/>
-      <c r="F7138" t="inlineStr"/>
-      <c r="G7138" t="inlineStr"/>
-      <c r="H7138" t="inlineStr"/>
-      <c r="I7138" t="inlineStr"/>
     </row>
     <row r="7139">
       <c r="A7139" t="inlineStr">
@@ -85757,13 +85138,6 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C7139" t="inlineStr"/>
-      <c r="D7139" t="inlineStr"/>
-      <c r="E7139" t="inlineStr"/>
-      <c r="F7139" t="inlineStr"/>
-      <c r="G7139" t="inlineStr"/>
-      <c r="H7139" t="inlineStr"/>
-      <c r="I7139" t="inlineStr"/>
     </row>
     <row r="7140">
       <c r="A7140" t="inlineStr">
@@ -85776,13 +85150,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C7140" t="inlineStr"/>
-      <c r="D7140" t="inlineStr"/>
-      <c r="E7140" t="inlineStr"/>
-      <c r="F7140" t="inlineStr"/>
-      <c r="G7140" t="inlineStr"/>
-      <c r="H7140" t="inlineStr"/>
-      <c r="I7140" t="inlineStr"/>
     </row>
     <row r="7141">
       <c r="A7141" t="inlineStr">
@@ -85795,13 +85162,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C7141" t="inlineStr"/>
-      <c r="D7141" t="inlineStr"/>
-      <c r="E7141" t="inlineStr"/>
-      <c r="F7141" t="inlineStr"/>
-      <c r="G7141" t="inlineStr"/>
-      <c r="H7141" t="inlineStr"/>
-      <c r="I7141" t="inlineStr"/>
     </row>
     <row r="7142">
       <c r="A7142" t="inlineStr">
@@ -85814,13 +85174,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C7142" t="inlineStr"/>
-      <c r="D7142" t="inlineStr"/>
-      <c r="E7142" t="inlineStr"/>
-      <c r="F7142" t="inlineStr"/>
-      <c r="G7142" t="inlineStr"/>
-      <c r="H7142" t="inlineStr"/>
-      <c r="I7142" t="inlineStr"/>
     </row>
     <row r="7143">
       <c r="A7143" t="inlineStr">
@@ -85833,13 +85186,6 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C7143" t="inlineStr"/>
-      <c r="D7143" t="inlineStr"/>
-      <c r="E7143" t="inlineStr"/>
-      <c r="F7143" t="inlineStr"/>
-      <c r="G7143" t="inlineStr"/>
-      <c r="H7143" t="inlineStr"/>
-      <c r="I7143" t="inlineStr"/>
     </row>
     <row r="7144">
       <c r="A7144" t="inlineStr">
@@ -85852,13 +85198,6 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C7144" t="inlineStr"/>
-      <c r="D7144" t="inlineStr"/>
-      <c r="E7144" t="inlineStr"/>
-      <c r="F7144" t="inlineStr"/>
-      <c r="G7144" t="inlineStr"/>
-      <c r="H7144" t="inlineStr"/>
-      <c r="I7144" t="inlineStr"/>
     </row>
     <row r="7145">
       <c r="A7145" t="inlineStr">
@@ -85871,13 +85210,6 @@
           <t>Tradescantia zebrina</t>
         </is>
       </c>
-      <c r="C7145" t="inlineStr"/>
-      <c r="D7145" t="inlineStr"/>
-      <c r="E7145" t="inlineStr"/>
-      <c r="F7145" t="inlineStr"/>
-      <c r="G7145" t="inlineStr"/>
-      <c r="H7145" t="inlineStr"/>
-      <c r="I7145" t="inlineStr"/>
     </row>
     <row r="7146">
       <c r="A7146" t="inlineStr">
@@ -85890,13 +85222,6 @@
           <t>Senecio rowleyanus</t>
         </is>
       </c>
-      <c r="C7146" t="inlineStr"/>
-      <c r="D7146" t="inlineStr"/>
-      <c r="E7146" t="inlineStr"/>
-      <c r="F7146" t="inlineStr"/>
-      <c r="G7146" t="inlineStr"/>
-      <c r="H7146" t="inlineStr"/>
-      <c r="I7146" t="inlineStr"/>
     </row>
     <row r="7147">
       <c r="A7147" t="inlineStr">
@@ -85909,13 +85234,6 @@
           <t>Ledebouria socialis</t>
         </is>
       </c>
-      <c r="C7147" t="inlineStr"/>
-      <c r="D7147" t="inlineStr"/>
-      <c r="E7147" t="inlineStr"/>
-      <c r="F7147" t="inlineStr"/>
-      <c r="G7147" t="inlineStr"/>
-      <c r="H7147" t="inlineStr"/>
-      <c r="I7147" t="inlineStr"/>
     </row>
     <row r="7148">
       <c r="A7148" t="inlineStr">
@@ -85928,13 +85246,6 @@
           <t>Peperomia Axillaris</t>
         </is>
       </c>
-      <c r="C7148" t="inlineStr"/>
-      <c r="D7148" t="inlineStr"/>
-      <c r="E7148" t="inlineStr"/>
-      <c r="F7148" t="inlineStr"/>
-      <c r="G7148" t="inlineStr"/>
-      <c r="H7148" t="inlineStr"/>
-      <c r="I7148" t="inlineStr"/>
     </row>
     <row r="7149">
       <c r="A7149" t="inlineStr">
@@ -85947,13 +85258,6 @@
           <t>Hoya Sabah</t>
         </is>
       </c>
-      <c r="C7149" t="inlineStr"/>
-      <c r="D7149" t="inlineStr"/>
-      <c r="E7149" t="inlineStr"/>
-      <c r="F7149" t="inlineStr"/>
-      <c r="G7149" t="inlineStr"/>
-      <c r="H7149" t="inlineStr"/>
-      <c r="I7149" t="inlineStr"/>
     </row>
     <row r="7150"/>
     <row r="7151">
@@ -85967,13 +85271,6 @@
           <t>Epipremnum Aureum</t>
         </is>
       </c>
-      <c r="C7151" t="inlineStr"/>
-      <c r="D7151" t="inlineStr"/>
-      <c r="E7151" t="inlineStr"/>
-      <c r="F7151" t="inlineStr"/>
-      <c r="G7151" t="inlineStr"/>
-      <c r="H7151" t="inlineStr"/>
-      <c r="I7151" t="inlineStr"/>
     </row>
     <row r="7152">
       <c r="A7152" t="inlineStr">
@@ -85986,13 +85283,19 @@
           <t xml:space="preserve">Philodendron Scandens Micans </t>
         </is>
       </c>
-      <c r="C7152" t="inlineStr"/>
-      <c r="D7152" t="inlineStr"/>
-      <c r="E7152" t="inlineStr"/>
-      <c r="F7152" t="inlineStr"/>
-      <c r="G7152" t="inlineStr"/>
-      <c r="H7152" t="inlineStr"/>
-      <c r="I7152" t="inlineStr"/>
+      <c r="D7152" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7152" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7152" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="7153">
       <c r="A7153" t="inlineStr">
@@ -86005,13 +85308,19 @@
           <t>Scindapsus Treubii Moonlight</t>
         </is>
       </c>
-      <c r="C7153" t="inlineStr"/>
-      <c r="D7153" t="inlineStr"/>
-      <c r="E7153" t="inlineStr"/>
-      <c r="F7153" t="inlineStr"/>
-      <c r="G7153" t="inlineStr"/>
-      <c r="H7153" t="inlineStr"/>
-      <c r="I7153" t="inlineStr"/>
+      <c r="D7153" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7153" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7153" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="7154">
       <c r="A7154" t="inlineStr">
@@ -86024,13 +85333,19 @@
           <t>Philodendron Hedaracium Brasil</t>
         </is>
       </c>
-      <c r="C7154" t="inlineStr"/>
-      <c r="D7154" t="inlineStr"/>
-      <c r="E7154" t="inlineStr"/>
-      <c r="F7154" t="inlineStr"/>
-      <c r="G7154" t="inlineStr"/>
-      <c r="H7154" t="inlineStr"/>
-      <c r="I7154" t="inlineStr"/>
+      <c r="D7154" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7154" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7154" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="7155">
       <c r="A7155" t="inlineStr">
@@ -86043,13 +85358,6 @@
           <t>Monstera Adenossii</t>
         </is>
       </c>
-      <c r="C7155" t="inlineStr"/>
-      <c r="D7155" t="inlineStr"/>
-      <c r="E7155" t="inlineStr"/>
-      <c r="F7155" t="inlineStr"/>
-      <c r="G7155" t="inlineStr"/>
-      <c r="H7155" t="inlineStr"/>
-      <c r="I7155" t="inlineStr"/>
     </row>
     <row r="7156">
       <c r="A7156" t="inlineStr">
@@ -86062,13 +85370,6 @@
           <t>Ficus Elastica Abidjan</t>
         </is>
       </c>
-      <c r="C7156" t="inlineStr"/>
-      <c r="D7156" t="inlineStr"/>
-      <c r="E7156" t="inlineStr"/>
-      <c r="F7156" t="inlineStr"/>
-      <c r="G7156" t="inlineStr"/>
-      <c r="H7156" t="inlineStr"/>
-      <c r="I7156" t="inlineStr"/>
     </row>
     <row r="7157">
       <c r="A7157" t="inlineStr">
@@ -86081,13 +85382,6 @@
           <t>Peperomia Hope</t>
         </is>
       </c>
-      <c r="C7157" t="inlineStr"/>
-      <c r="D7157" t="inlineStr"/>
-      <c r="E7157" t="inlineStr"/>
-      <c r="F7157" t="inlineStr"/>
-      <c r="G7157" t="inlineStr"/>
-      <c r="H7157" t="inlineStr"/>
-      <c r="I7157" t="inlineStr"/>
     </row>
     <row r="7158">
       <c r="A7158" t="inlineStr">
@@ -86100,13 +85394,19 @@
           <t>Epipremnum Pinnatum Blue</t>
         </is>
       </c>
-      <c r="C7158" t="inlineStr"/>
-      <c r="D7158" t="inlineStr"/>
-      <c r="E7158" t="inlineStr"/>
-      <c r="F7158" t="inlineStr"/>
-      <c r="G7158" t="inlineStr"/>
-      <c r="H7158" t="inlineStr"/>
-      <c r="I7158" t="inlineStr"/>
+      <c r="D7158" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7158" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7158" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="7159">
       <c r="A7159" t="inlineStr">
@@ -86119,13 +85419,6 @@
           <t>Sansevieria Laurentii</t>
         </is>
       </c>
-      <c r="C7159" t="inlineStr"/>
-      <c r="D7159" t="inlineStr"/>
-      <c r="E7159" t="inlineStr"/>
-      <c r="F7159" t="inlineStr"/>
-      <c r="G7159" t="inlineStr"/>
-      <c r="H7159" t="inlineStr"/>
-      <c r="I7159" t="inlineStr"/>
     </row>
     <row r="7160">
       <c r="A7160" t="inlineStr">
@@ -86138,13 +85431,6 @@
           <t>Epipremnum Aureum Saal</t>
         </is>
       </c>
-      <c r="C7160" t="inlineStr"/>
-      <c r="D7160" t="inlineStr"/>
-      <c r="E7160" t="inlineStr"/>
-      <c r="F7160" t="inlineStr"/>
-      <c r="G7160" t="inlineStr"/>
-      <c r="H7160" t="inlineStr"/>
-      <c r="I7160" t="inlineStr"/>
     </row>
     <row r="7161">
       <c r="A7161" t="inlineStr">
@@ -86157,13 +85443,19 @@
           <t>Monstera Deliciosa Variegata</t>
         </is>
       </c>
-      <c r="C7161" t="inlineStr"/>
-      <c r="D7161" t="inlineStr"/>
-      <c r="E7161" t="inlineStr"/>
-      <c r="F7161" t="inlineStr"/>
-      <c r="G7161" t="inlineStr"/>
-      <c r="H7161" t="inlineStr"/>
-      <c r="I7161" t="inlineStr"/>
+      <c r="D7161" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7161" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7161" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="7162">
       <c r="A7162" t="inlineStr">
@@ -86176,13 +85468,6 @@
           <t>Pachira Aquatica</t>
         </is>
       </c>
-      <c r="C7162" t="inlineStr"/>
-      <c r="D7162" t="inlineStr"/>
-      <c r="E7162" t="inlineStr"/>
-      <c r="F7162" t="inlineStr"/>
-      <c r="G7162" t="inlineStr"/>
-      <c r="H7162" t="inlineStr"/>
-      <c r="I7162" t="inlineStr"/>
     </row>
     <row r="7163">
       <c r="A7163" t="inlineStr">
@@ -86195,13 +85480,19 @@
           <t xml:space="preserve">Monstera Deliciosa </t>
         </is>
       </c>
-      <c r="C7163" t="inlineStr"/>
-      <c r="D7163" t="inlineStr"/>
-      <c r="E7163" t="inlineStr"/>
-      <c r="F7163" t="inlineStr"/>
-      <c r="G7163" t="inlineStr"/>
-      <c r="H7163" t="inlineStr"/>
-      <c r="I7163" t="inlineStr"/>
+      <c r="D7163" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7163" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7163" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="7164">
       <c r="A7164" t="inlineStr">
@@ -86214,13 +85505,6 @@
           <t>Philodendron Imperial Red</t>
         </is>
       </c>
-      <c r="C7164" t="inlineStr"/>
-      <c r="D7164" t="inlineStr"/>
-      <c r="E7164" t="inlineStr"/>
-      <c r="F7164" t="inlineStr"/>
-      <c r="G7164" t="inlineStr"/>
-      <c r="H7164" t="inlineStr"/>
-      <c r="I7164" t="inlineStr"/>
     </row>
     <row r="7165">
       <c r="A7165" t="inlineStr">
@@ -86233,13 +85517,6 @@
           <t>Philodendron McColleys Finale</t>
         </is>
       </c>
-      <c r="C7165" t="inlineStr"/>
-      <c r="D7165" t="inlineStr"/>
-      <c r="E7165" t="inlineStr"/>
-      <c r="F7165" t="inlineStr"/>
-      <c r="G7165" t="inlineStr"/>
-      <c r="H7165" t="inlineStr"/>
-      <c r="I7165" t="inlineStr"/>
     </row>
     <row r="7166">
       <c r="A7166" t="inlineStr">
@@ -86252,13 +85529,6 @@
           <t>Philodendron Birkin</t>
         </is>
       </c>
-      <c r="C7166" t="inlineStr"/>
-      <c r="D7166" t="inlineStr"/>
-      <c r="E7166" t="inlineStr"/>
-      <c r="F7166" t="inlineStr"/>
-      <c r="G7166" t="inlineStr"/>
-      <c r="H7166" t="inlineStr"/>
-      <c r="I7166" t="inlineStr"/>
     </row>
     <row r="7167">
       <c r="A7167" t="inlineStr">
@@ -86271,13 +85541,19 @@
           <t>Rhaphidophora Tetrasperma</t>
         </is>
       </c>
-      <c r="C7167" t="inlineStr"/>
-      <c r="D7167" t="inlineStr"/>
-      <c r="E7167" t="inlineStr"/>
-      <c r="F7167" t="inlineStr"/>
-      <c r="G7167" t="inlineStr"/>
-      <c r="H7167" t="inlineStr"/>
-      <c r="I7167" t="inlineStr"/>
+      <c r="D7167" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7167" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7167" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="7168">
       <c r="A7168" t="inlineStr">
@@ -86290,13 +85566,19 @@
           <t>Philodendron Scandens Micans little</t>
         </is>
       </c>
-      <c r="C7168" t="inlineStr"/>
-      <c r="D7168" t="inlineStr"/>
-      <c r="E7168" t="inlineStr"/>
-      <c r="F7168" t="inlineStr"/>
-      <c r="G7168" t="inlineStr"/>
-      <c r="H7168" t="inlineStr"/>
-      <c r="I7168" t="inlineStr"/>
+      <c r="D7168" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7168" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7168" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="7169">
       <c r="A7169" t="inlineStr">
@@ -86309,13 +85591,6 @@
           <t>Tradescantia zebrina</t>
         </is>
       </c>
-      <c r="C7169" t="inlineStr"/>
-      <c r="D7169" t="inlineStr"/>
-      <c r="E7169" t="inlineStr"/>
-      <c r="F7169" t="inlineStr"/>
-      <c r="G7169" t="inlineStr"/>
-      <c r="H7169" t="inlineStr"/>
-      <c r="I7169" t="inlineStr"/>
     </row>
     <row r="7170">
       <c r="A7170" t="inlineStr">
@@ -86328,13 +85603,6 @@
           <t>Senecio rowleyanus</t>
         </is>
       </c>
-      <c r="C7170" t="inlineStr"/>
-      <c r="D7170" t="inlineStr"/>
-      <c r="E7170" t="inlineStr"/>
-      <c r="F7170" t="inlineStr"/>
-      <c r="G7170" t="inlineStr"/>
-      <c r="H7170" t="inlineStr"/>
-      <c r="I7170" t="inlineStr"/>
     </row>
     <row r="7171">
       <c r="A7171" t="inlineStr">
@@ -86347,13 +85615,6 @@
           <t>Ledebouria socialis</t>
         </is>
       </c>
-      <c r="C7171" t="inlineStr"/>
-      <c r="D7171" t="inlineStr"/>
-      <c r="E7171" t="inlineStr"/>
-      <c r="F7171" t="inlineStr"/>
-      <c r="G7171" t="inlineStr"/>
-      <c r="H7171" t="inlineStr"/>
-      <c r="I7171" t="inlineStr"/>
     </row>
     <row r="7172">
       <c r="A7172" t="inlineStr">
@@ -86366,13 +85627,6 @@
           <t>Peperomia Axillaris</t>
         </is>
       </c>
-      <c r="C7172" t="inlineStr"/>
-      <c r="D7172" t="inlineStr"/>
-      <c r="E7172" t="inlineStr"/>
-      <c r="F7172" t="inlineStr"/>
-      <c r="G7172" t="inlineStr"/>
-      <c r="H7172" t="inlineStr"/>
-      <c r="I7172" t="inlineStr"/>
     </row>
     <row r="7173">
       <c r="A7173" t="inlineStr">
@@ -86385,15 +85639,3165 @@
           <t>Hoya Sabah</t>
         </is>
       </c>
-      <c r="C7173" t="inlineStr"/>
-      <c r="D7173" t="inlineStr"/>
-      <c r="E7173" t="inlineStr"/>
-      <c r="F7173" t="inlineStr"/>
-      <c r="G7173" t="inlineStr"/>
-      <c r="H7173" t="inlineStr"/>
-      <c r="I7173" t="inlineStr"/>
     </row>
     <row r="7174"/>
+    <row r="7175">
+      <c r="A7175" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7175" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7176">
+      <c r="A7176" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="7177">
+      <c r="A7177" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7177" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7178">
+      <c r="A7178" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7178" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7179">
+      <c r="A7179" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7179" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7180">
+      <c r="A7180" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7180" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7181">
+      <c r="A7181" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7181" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7182">
+      <c r="A7182" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7182" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7183">
+      <c r="A7183" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7183" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7184">
+      <c r="A7184" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7184" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7185">
+      <c r="A7185" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7185" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7186">
+      <c r="A7186" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7186" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7187">
+      <c r="A7187" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="7188">
+      <c r="A7188" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7188" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="7189">
+      <c r="A7189" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7189" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7190">
+      <c r="A7190" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7190" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7191">
+      <c r="A7191" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7191" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7192">
+      <c r="A7192" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7192" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="7193">
+      <c r="A7193" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7193" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7194">
+      <c r="A7194" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7194" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7195">
+      <c r="A7195" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7195" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7196">
+      <c r="A7196" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7196" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7197">
+      <c r="A7197" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="B7197" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7198"/>
+    <row r="7199">
+      <c r="A7199" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7199" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7200">
+      <c r="A7200" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="7201">
+      <c r="A7201" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7201" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7202">
+      <c r="A7202" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7202" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7203">
+      <c r="A7203" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7203" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="D7203" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7203" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7203" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="7204">
+      <c r="A7204" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7204" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7205">
+      <c r="A7205" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7205" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="D7205" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7205" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7205" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="7206">
+      <c r="A7206" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7206" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7207">
+      <c r="A7207" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7207" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="D7207" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7207" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7207" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="7208">
+      <c r="A7208" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7208" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7209">
+      <c r="A7209" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7209" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7210">
+      <c r="A7210" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7210" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7211">
+      <c r="A7211" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="7212">
+      <c r="A7212" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7212" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="7213">
+      <c r="A7213" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7213" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7214">
+      <c r="A7214" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7214" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7215">
+      <c r="A7215" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7215" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7216">
+      <c r="A7216" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7216" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="7217">
+      <c r="A7217" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7217" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7218">
+      <c r="A7218" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7218" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7219">
+      <c r="A7219" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7219" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+      <c r="D7219" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7219" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7219" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="7220">
+      <c r="A7220" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7220" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7221">
+      <c r="A7221" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="B7221" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+      <c r="D7221" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7221" s="24" t="inlineStr">
+        <is>
+          <t>SYBA org</t>
+        </is>
+      </c>
+      <c r="J7221" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="7222"/>
+    <row r="7223">
+      <c r="A7223" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7223" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7224">
+      <c r="A7224" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="7225">
+      <c r="A7225" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7225" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7226">
+      <c r="A7226" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7226" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7227">
+      <c r="A7227" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7227" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7228">
+      <c r="A7228" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7228" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7229">
+      <c r="A7229" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7229" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7230">
+      <c r="A7230" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7230" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7231">
+      <c r="A7231" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7231" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7232">
+      <c r="A7232" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7232" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7233">
+      <c r="A7233" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7233" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7234">
+      <c r="A7234" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7234" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7235">
+      <c r="A7235" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="7236">
+      <c r="A7236" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7236" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="7237">
+      <c r="A7237" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7237" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7238">
+      <c r="A7238" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7238" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7239">
+      <c r="A7239" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7239" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7240">
+      <c r="A7240" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7240" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="7241">
+      <c r="A7241" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7241" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7242">
+      <c r="A7242" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7242" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7243">
+      <c r="A7243" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7243" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7244">
+      <c r="A7244" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7244" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7245">
+      <c r="A7245" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="B7245" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7246"/>
+    <row r="7247">
+      <c r="A7247" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7247" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7248">
+      <c r="A7248" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="7249">
+      <c r="A7249" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7249" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7250">
+      <c r="A7250" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7250" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7251">
+      <c r="A7251" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7251" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7252">
+      <c r="A7252" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7252" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7253">
+      <c r="A7253" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7253" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7254">
+      <c r="A7254" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7254" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7255">
+      <c r="A7255" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7255" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7256">
+      <c r="A7256" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7256" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7257">
+      <c r="A7257" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7257" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7258">
+      <c r="A7258" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7258" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7259">
+      <c r="A7259" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="7260">
+      <c r="A7260" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7260" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="7261">
+      <c r="A7261" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7261" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7262">
+      <c r="A7262" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7262" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7263">
+      <c r="A7263" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7263" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7264">
+      <c r="A7264" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7264" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="7265">
+      <c r="A7265" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7265" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7266">
+      <c r="A7266" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7266" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7267">
+      <c r="A7267" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7267" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7268">
+      <c r="A7268" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7268" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7269">
+      <c r="A7269" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="B7269" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7270"/>
+    <row r="7271">
+      <c r="A7271" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7271" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7272">
+      <c r="A7272" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="7273">
+      <c r="A7273" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7273" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7274">
+      <c r="A7274" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7274" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7275">
+      <c r="A7275" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7275" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7276">
+      <c r="A7276" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7276" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7277">
+      <c r="A7277" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7277" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7278">
+      <c r="A7278" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7278" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7279">
+      <c r="A7279" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7279" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7280">
+      <c r="A7280" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7280" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7281">
+      <c r="A7281" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7281" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7282">
+      <c r="A7282" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7282" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7283">
+      <c r="A7283" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="7284">
+      <c r="A7284" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7284" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="7285">
+      <c r="A7285" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7285" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7286">
+      <c r="A7286" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7286" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7287">
+      <c r="A7287" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7287" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7288">
+      <c r="A7288" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7288" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="7289">
+      <c r="A7289" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7289" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7290">
+      <c r="A7290" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7290" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7291">
+      <c r="A7291" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7291" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7292">
+      <c r="A7292" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7292" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7293">
+      <c r="A7293" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="B7293" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7294"/>
+    <row r="7295">
+      <c r="A7295" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7295" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7296">
+      <c r="A7296" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="7297">
+      <c r="A7297" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7297" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7298">
+      <c r="A7298" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7298" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7299">
+      <c r="A7299" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7299" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7300">
+      <c r="A7300" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7300" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7301">
+      <c r="A7301" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7301" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7302">
+      <c r="A7302" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7302" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7303">
+      <c r="A7303" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7303" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7304">
+      <c r="A7304" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7304" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7305">
+      <c r="A7305" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7305" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7306">
+      <c r="A7306" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7306" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7307">
+      <c r="A7307" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="7308">
+      <c r="A7308" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7308" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="7309">
+      <c r="A7309" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7309" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7310">
+      <c r="A7310" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7310" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7311">
+      <c r="A7311" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7311" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7312">
+      <c r="A7312" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7312" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="7313">
+      <c r="A7313" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7313" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7314">
+      <c r="A7314" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7314" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7315">
+      <c r="A7315" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7315" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7316">
+      <c r="A7316" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7316" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7317">
+      <c r="A7317" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="B7317" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7318"/>
+    <row r="7319">
+      <c r="A7319" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7319" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7320">
+      <c r="A7320" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="7321">
+      <c r="A7321" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7321" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7322">
+      <c r="A7322" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7322" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7323">
+      <c r="A7323" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7323" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7324">
+      <c r="A7324" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7324" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7325">
+      <c r="A7325" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7325" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7326">
+      <c r="A7326" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7326" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7327">
+      <c r="A7327" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7327" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7328">
+      <c r="A7328" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7328" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7329">
+      <c r="A7329" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7329" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7330">
+      <c r="A7330" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7330" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7331">
+      <c r="A7331" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="7332">
+      <c r="A7332" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7332" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="7333">
+      <c r="A7333" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7333" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7334">
+      <c r="A7334" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7334" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7335">
+      <c r="A7335" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7335" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7336">
+      <c r="A7336" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7336" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="7337">
+      <c r="A7337" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7337" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7338">
+      <c r="A7338" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7338" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7339">
+      <c r="A7339" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7339" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7340">
+      <c r="A7340" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7340" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7341">
+      <c r="A7341" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="B7341" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7342"/>
+    <row r="7343">
+      <c r="A7343" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7343" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7344">
+      <c r="A7344" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+    </row>
+    <row r="7345">
+      <c r="A7345" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7345" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7346">
+      <c r="A7346" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7346" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7347">
+      <c r="A7347" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7347" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7348">
+      <c r="A7348" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7348" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7349">
+      <c r="A7349" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7349" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7350">
+      <c r="A7350" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7350" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7351">
+      <c r="A7351" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7351" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7352">
+      <c r="A7352" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7352" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7353">
+      <c r="A7353" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7353" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7354">
+      <c r="A7354" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7354" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7355">
+      <c r="A7355" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+    </row>
+    <row r="7356">
+      <c r="A7356" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7356" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="7357">
+      <c r="A7357" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7357" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7358">
+      <c r="A7358" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7358" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7359">
+      <c r="A7359" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7359" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7360">
+      <c r="A7360" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7360" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+    </row>
+    <row r="7361">
+      <c r="A7361" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7361" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7362">
+      <c r="A7362" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7362" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7363">
+      <c r="A7363" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7363" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7364">
+      <c r="A7364" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7364" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7365">
+      <c r="A7365" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="B7365" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7366"/>
+    <row r="7367">
+      <c r="A7367" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7367" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C7367" t="inlineStr"/>
+      <c r="D7367" t="inlineStr"/>
+      <c r="E7367" t="inlineStr"/>
+      <c r="F7367" t="inlineStr"/>
+      <c r="G7367" t="inlineStr"/>
+      <c r="H7367" t="inlineStr"/>
+      <c r="I7367" t="inlineStr"/>
+    </row>
+    <row r="7368">
+      <c r="A7368" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C7368" t="inlineStr"/>
+      <c r="D7368" t="inlineStr"/>
+      <c r="E7368" t="inlineStr"/>
+      <c r="F7368" t="inlineStr"/>
+      <c r="G7368" t="inlineStr"/>
+      <c r="H7368" t="inlineStr"/>
+      <c r="I7368" t="inlineStr"/>
+    </row>
+    <row r="7369">
+      <c r="A7369" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7369" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C7369" t="inlineStr"/>
+      <c r="D7369" t="inlineStr"/>
+      <c r="E7369" t="inlineStr"/>
+      <c r="F7369" t="inlineStr"/>
+      <c r="G7369" t="inlineStr"/>
+      <c r="H7369" t="inlineStr"/>
+      <c r="I7369" t="inlineStr"/>
+    </row>
+    <row r="7370">
+      <c r="A7370" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7370" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C7370" t="inlineStr"/>
+      <c r="D7370" t="inlineStr"/>
+      <c r="E7370" t="inlineStr"/>
+      <c r="F7370" t="inlineStr"/>
+      <c r="G7370" t="inlineStr"/>
+      <c r="H7370" t="inlineStr"/>
+      <c r="I7370" t="inlineStr"/>
+    </row>
+    <row r="7371">
+      <c r="A7371" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7371" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C7371" t="inlineStr"/>
+      <c r="D7371" t="inlineStr"/>
+      <c r="E7371" t="inlineStr"/>
+      <c r="F7371" t="inlineStr"/>
+      <c r="G7371" t="inlineStr"/>
+      <c r="H7371" t="inlineStr"/>
+      <c r="I7371" t="inlineStr"/>
+    </row>
+    <row r="7372">
+      <c r="A7372" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7372" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C7372" t="inlineStr"/>
+      <c r="D7372" t="inlineStr"/>
+      <c r="E7372" t="inlineStr"/>
+      <c r="F7372" t="inlineStr"/>
+      <c r="G7372" t="inlineStr"/>
+      <c r="H7372" t="inlineStr"/>
+      <c r="I7372" t="inlineStr"/>
+    </row>
+    <row r="7373">
+      <c r="A7373" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7373" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C7373" t="inlineStr"/>
+      <c r="D7373" t="inlineStr"/>
+      <c r="E7373" t="inlineStr"/>
+      <c r="F7373" t="inlineStr"/>
+      <c r="G7373" t="inlineStr"/>
+      <c r="H7373" t="inlineStr"/>
+      <c r="I7373" t="inlineStr"/>
+    </row>
+    <row r="7374">
+      <c r="A7374" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7374" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C7374" t="inlineStr"/>
+      <c r="D7374" t="inlineStr"/>
+      <c r="E7374" t="inlineStr"/>
+      <c r="F7374" t="inlineStr"/>
+      <c r="G7374" t="inlineStr"/>
+      <c r="H7374" t="inlineStr"/>
+      <c r="I7374" t="inlineStr"/>
+    </row>
+    <row r="7375">
+      <c r="A7375" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7375" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C7375" t="inlineStr"/>
+      <c r="D7375" t="inlineStr"/>
+      <c r="E7375" t="inlineStr"/>
+      <c r="F7375" t="inlineStr"/>
+      <c r="G7375" t="inlineStr"/>
+      <c r="H7375" t="inlineStr"/>
+      <c r="I7375" t="inlineStr"/>
+    </row>
+    <row r="7376">
+      <c r="A7376" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7376" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C7376" t="inlineStr"/>
+      <c r="D7376" t="inlineStr"/>
+      <c r="E7376" t="inlineStr"/>
+      <c r="F7376" t="inlineStr"/>
+      <c r="G7376" t="inlineStr"/>
+      <c r="H7376" t="inlineStr"/>
+      <c r="I7376" t="inlineStr"/>
+    </row>
+    <row r="7377">
+      <c r="A7377" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7377" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C7377" t="inlineStr"/>
+      <c r="D7377" t="inlineStr"/>
+      <c r="E7377" t="inlineStr"/>
+      <c r="F7377" t="inlineStr"/>
+      <c r="G7377" t="inlineStr"/>
+      <c r="H7377" t="inlineStr"/>
+      <c r="I7377" t="inlineStr"/>
+    </row>
+    <row r="7378">
+      <c r="A7378" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7378" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C7378" t="inlineStr"/>
+      <c r="D7378" t="inlineStr"/>
+      <c r="E7378" t="inlineStr"/>
+      <c r="F7378" t="inlineStr"/>
+      <c r="G7378" t="inlineStr"/>
+      <c r="H7378" t="inlineStr"/>
+      <c r="I7378" t="inlineStr"/>
+    </row>
+    <row r="7379">
+      <c r="A7379" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C7379" t="inlineStr"/>
+      <c r="D7379" t="inlineStr"/>
+      <c r="E7379" t="inlineStr"/>
+      <c r="F7379" t="inlineStr"/>
+      <c r="G7379" t="inlineStr"/>
+      <c r="H7379" t="inlineStr"/>
+      <c r="I7379" t="inlineStr"/>
+    </row>
+    <row r="7380">
+      <c r="A7380" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7380" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C7380" t="inlineStr"/>
+      <c r="D7380" t="inlineStr"/>
+      <c r="E7380" t="inlineStr"/>
+      <c r="F7380" t="inlineStr"/>
+      <c r="G7380" t="inlineStr"/>
+      <c r="H7380" t="inlineStr"/>
+      <c r="I7380" t="inlineStr"/>
+    </row>
+    <row r="7381">
+      <c r="A7381" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7381" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C7381" t="inlineStr"/>
+      <c r="D7381" t="inlineStr"/>
+      <c r="E7381" t="inlineStr"/>
+      <c r="F7381" t="inlineStr"/>
+      <c r="G7381" t="inlineStr"/>
+      <c r="H7381" t="inlineStr"/>
+      <c r="I7381" t="inlineStr"/>
+    </row>
+    <row r="7382">
+      <c r="A7382" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7382" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C7382" t="inlineStr"/>
+      <c r="D7382" t="inlineStr"/>
+      <c r="E7382" t="inlineStr"/>
+      <c r="F7382" t="inlineStr"/>
+      <c r="G7382" t="inlineStr"/>
+      <c r="H7382" t="inlineStr"/>
+      <c r="I7382" t="inlineStr"/>
+    </row>
+    <row r="7383">
+      <c r="A7383" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7383" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C7383" t="inlineStr"/>
+      <c r="D7383" t="inlineStr"/>
+      <c r="E7383" t="inlineStr"/>
+      <c r="F7383" t="inlineStr"/>
+      <c r="G7383" t="inlineStr"/>
+      <c r="H7383" t="inlineStr"/>
+      <c r="I7383" t="inlineStr"/>
+    </row>
+    <row r="7384">
+      <c r="A7384" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7384" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C7384" t="inlineStr"/>
+      <c r="D7384" t="inlineStr"/>
+      <c r="E7384" t="inlineStr"/>
+      <c r="F7384" t="inlineStr"/>
+      <c r="G7384" t="inlineStr"/>
+      <c r="H7384" t="inlineStr"/>
+      <c r="I7384" t="inlineStr"/>
+    </row>
+    <row r="7385">
+      <c r="A7385" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7385" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+      <c r="C7385" t="inlineStr"/>
+      <c r="D7385" t="inlineStr"/>
+      <c r="E7385" t="inlineStr"/>
+      <c r="F7385" t="inlineStr"/>
+      <c r="G7385" t="inlineStr"/>
+      <c r="H7385" t="inlineStr"/>
+      <c r="I7385" t="inlineStr"/>
+    </row>
+    <row r="7386">
+      <c r="A7386" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7386" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+      <c r="C7386" t="inlineStr"/>
+      <c r="D7386" t="inlineStr"/>
+      <c r="E7386" t="inlineStr"/>
+      <c r="F7386" t="inlineStr"/>
+      <c r="G7386" t="inlineStr"/>
+      <c r="H7386" t="inlineStr"/>
+      <c r="I7386" t="inlineStr"/>
+    </row>
+    <row r="7387">
+      <c r="A7387" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7387" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+      <c r="C7387" t="inlineStr"/>
+      <c r="D7387" t="inlineStr"/>
+      <c r="E7387" t="inlineStr"/>
+      <c r="F7387" t="inlineStr"/>
+      <c r="G7387" t="inlineStr"/>
+      <c r="H7387" t="inlineStr"/>
+      <c r="I7387" t="inlineStr"/>
+    </row>
+    <row r="7388">
+      <c r="A7388" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7388" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+      <c r="C7388" t="inlineStr"/>
+      <c r="D7388" t="inlineStr"/>
+      <c r="E7388" t="inlineStr"/>
+      <c r="F7388" t="inlineStr"/>
+      <c r="G7388" t="inlineStr"/>
+      <c r="H7388" t="inlineStr"/>
+      <c r="I7388" t="inlineStr"/>
+    </row>
+    <row r="7389">
+      <c r="A7389" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="B7389" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+      <c r="C7389" t="inlineStr"/>
+      <c r="D7389" t="inlineStr"/>
+      <c r="E7389" t="inlineStr"/>
+      <c r="F7389" t="inlineStr"/>
+      <c r="G7389" t="inlineStr"/>
+      <c r="H7389" t="inlineStr"/>
+      <c r="I7389" t="inlineStr"/>
+    </row>
+    <row r="7390"/>
+    <row r="7391">
+      <c r="A7391" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7391" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum</t>
+        </is>
+      </c>
+      <c r="C7391" t="inlineStr"/>
+      <c r="D7391" t="inlineStr"/>
+      <c r="E7391" t="inlineStr"/>
+      <c r="F7391" t="inlineStr"/>
+      <c r="G7391" t="inlineStr"/>
+      <c r="H7391" t="inlineStr"/>
+      <c r="I7391" t="inlineStr"/>
+    </row>
+    <row r="7392">
+      <c r="A7392" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philodendron Scandens Micans </t>
+        </is>
+      </c>
+      <c r="C7392" t="inlineStr"/>
+      <c r="D7392" t="inlineStr"/>
+      <c r="E7392" t="inlineStr"/>
+      <c r="F7392" t="inlineStr"/>
+      <c r="G7392" t="inlineStr"/>
+      <c r="H7392" t="inlineStr"/>
+      <c r="I7392" t="inlineStr"/>
+    </row>
+    <row r="7393">
+      <c r="A7393" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7393" t="inlineStr">
+        <is>
+          <t>Scindapsus Treubii Moonlight</t>
+        </is>
+      </c>
+      <c r="C7393" t="inlineStr"/>
+      <c r="D7393" t="inlineStr"/>
+      <c r="E7393" t="inlineStr"/>
+      <c r="F7393" t="inlineStr"/>
+      <c r="G7393" t="inlineStr"/>
+      <c r="H7393" t="inlineStr"/>
+      <c r="I7393" t="inlineStr"/>
+    </row>
+    <row r="7394">
+      <c r="A7394" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7394" t="inlineStr">
+        <is>
+          <t>Philodendron Hedaracium Brasil</t>
+        </is>
+      </c>
+      <c r="C7394" t="inlineStr"/>
+      <c r="D7394" t="inlineStr"/>
+      <c r="E7394" t="inlineStr"/>
+      <c r="F7394" t="inlineStr"/>
+      <c r="G7394" t="inlineStr"/>
+      <c r="H7394" t="inlineStr"/>
+      <c r="I7394" t="inlineStr"/>
+    </row>
+    <row r="7395">
+      <c r="A7395" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7395" t="inlineStr">
+        <is>
+          <t>Monstera Adenossii</t>
+        </is>
+      </c>
+      <c r="C7395" t="inlineStr"/>
+      <c r="D7395" t="inlineStr"/>
+      <c r="E7395" t="inlineStr"/>
+      <c r="F7395" t="inlineStr"/>
+      <c r="G7395" t="inlineStr"/>
+      <c r="H7395" t="inlineStr"/>
+      <c r="I7395" t="inlineStr"/>
+    </row>
+    <row r="7396">
+      <c r="A7396" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7396" t="inlineStr">
+        <is>
+          <t>Ficus Elastica Abidjan</t>
+        </is>
+      </c>
+      <c r="C7396" t="inlineStr"/>
+      <c r="D7396" t="inlineStr"/>
+      <c r="E7396" t="inlineStr"/>
+      <c r="F7396" t="inlineStr"/>
+      <c r="G7396" t="inlineStr"/>
+      <c r="H7396" t="inlineStr"/>
+      <c r="I7396" t="inlineStr"/>
+    </row>
+    <row r="7397">
+      <c r="A7397" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7397" t="inlineStr">
+        <is>
+          <t>Peperomia Hope</t>
+        </is>
+      </c>
+      <c r="C7397" t="inlineStr"/>
+      <c r="D7397" t="inlineStr"/>
+      <c r="E7397" t="inlineStr"/>
+      <c r="F7397" t="inlineStr"/>
+      <c r="G7397" t="inlineStr"/>
+      <c r="H7397" t="inlineStr"/>
+      <c r="I7397" t="inlineStr"/>
+    </row>
+    <row r="7398">
+      <c r="A7398" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7398" t="inlineStr">
+        <is>
+          <t>Epipremnum Pinnatum Blue</t>
+        </is>
+      </c>
+      <c r="C7398" t="inlineStr"/>
+      <c r="D7398" t="inlineStr"/>
+      <c r="E7398" t="inlineStr"/>
+      <c r="F7398" t="inlineStr"/>
+      <c r="G7398" t="inlineStr"/>
+      <c r="H7398" t="inlineStr"/>
+      <c r="I7398" t="inlineStr"/>
+    </row>
+    <row r="7399">
+      <c r="A7399" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7399" t="inlineStr">
+        <is>
+          <t>Sansevieria Laurentii</t>
+        </is>
+      </c>
+      <c r="C7399" t="inlineStr"/>
+      <c r="D7399" t="inlineStr"/>
+      <c r="E7399" t="inlineStr"/>
+      <c r="F7399" t="inlineStr"/>
+      <c r="G7399" t="inlineStr"/>
+      <c r="H7399" t="inlineStr"/>
+      <c r="I7399" t="inlineStr"/>
+    </row>
+    <row r="7400">
+      <c r="A7400" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7400" t="inlineStr">
+        <is>
+          <t>Epipremnum Aureum Saal</t>
+        </is>
+      </c>
+      <c r="C7400" t="inlineStr"/>
+      <c r="D7400" t="inlineStr"/>
+      <c r="E7400" t="inlineStr"/>
+      <c r="F7400" t="inlineStr"/>
+      <c r="G7400" t="inlineStr"/>
+      <c r="H7400" t="inlineStr"/>
+      <c r="I7400" t="inlineStr"/>
+    </row>
+    <row r="7401">
+      <c r="A7401" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7401" t="inlineStr">
+        <is>
+          <t>Monstera Deliciosa Variegata</t>
+        </is>
+      </c>
+      <c r="C7401" t="inlineStr"/>
+      <c r="D7401" t="inlineStr"/>
+      <c r="E7401" t="inlineStr"/>
+      <c r="F7401" t="inlineStr"/>
+      <c r="G7401" t="inlineStr"/>
+      <c r="H7401" t="inlineStr"/>
+      <c r="I7401" t="inlineStr"/>
+    </row>
+    <row r="7402">
+      <c r="A7402" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7402" t="inlineStr">
+        <is>
+          <t>Pachira Aquatica</t>
+        </is>
+      </c>
+      <c r="C7402" t="inlineStr"/>
+      <c r="D7402" t="inlineStr"/>
+      <c r="E7402" t="inlineStr"/>
+      <c r="F7402" t="inlineStr"/>
+      <c r="G7402" t="inlineStr"/>
+      <c r="H7402" t="inlineStr"/>
+      <c r="I7402" t="inlineStr"/>
+    </row>
+    <row r="7403">
+      <c r="A7403" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monstera Deliciosa </t>
+        </is>
+      </c>
+      <c r="C7403" t="inlineStr"/>
+      <c r="D7403" t="inlineStr"/>
+      <c r="E7403" t="inlineStr"/>
+      <c r="F7403" t="inlineStr"/>
+      <c r="G7403" t="inlineStr"/>
+      <c r="H7403" t="inlineStr"/>
+      <c r="I7403" t="inlineStr"/>
+    </row>
+    <row r="7404">
+      <c r="A7404" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7404" t="inlineStr">
+        <is>
+          <t>Philodendron Imperial Red</t>
+        </is>
+      </c>
+      <c r="C7404" t="inlineStr"/>
+      <c r="D7404" t="inlineStr"/>
+      <c r="E7404" t="inlineStr"/>
+      <c r="F7404" t="inlineStr"/>
+      <c r="G7404" t="inlineStr"/>
+      <c r="H7404" t="inlineStr"/>
+      <c r="I7404" t="inlineStr"/>
+    </row>
+    <row r="7405">
+      <c r="A7405" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7405" t="inlineStr">
+        <is>
+          <t>Philodendron McColleys Finale</t>
+        </is>
+      </c>
+      <c r="C7405" t="inlineStr"/>
+      <c r="D7405" t="inlineStr"/>
+      <c r="E7405" t="inlineStr"/>
+      <c r="F7405" t="inlineStr"/>
+      <c r="G7405" t="inlineStr"/>
+      <c r="H7405" t="inlineStr"/>
+      <c r="I7405" t="inlineStr"/>
+    </row>
+    <row r="7406">
+      <c r="A7406" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7406" t="inlineStr">
+        <is>
+          <t>Philodendron Birkin</t>
+        </is>
+      </c>
+      <c r="C7406" t="inlineStr"/>
+      <c r="D7406" t="inlineStr"/>
+      <c r="E7406" t="inlineStr"/>
+      <c r="F7406" t="inlineStr"/>
+      <c r="G7406" t="inlineStr"/>
+      <c r="H7406" t="inlineStr"/>
+      <c r="I7406" t="inlineStr"/>
+    </row>
+    <row r="7407">
+      <c r="A7407" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7407" t="inlineStr">
+        <is>
+          <t>Rhaphidophora Tetrasperma</t>
+        </is>
+      </c>
+      <c r="C7407" t="inlineStr"/>
+      <c r="D7407" t="inlineStr"/>
+      <c r="E7407" t="inlineStr"/>
+      <c r="F7407" t="inlineStr"/>
+      <c r="G7407" t="inlineStr"/>
+      <c r="H7407" t="inlineStr"/>
+      <c r="I7407" t="inlineStr"/>
+    </row>
+    <row r="7408">
+      <c r="A7408" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7408" t="inlineStr">
+        <is>
+          <t>Philodendron Scandens Micans little</t>
+        </is>
+      </c>
+      <c r="C7408" t="inlineStr"/>
+      <c r="D7408" t="inlineStr"/>
+      <c r="E7408" t="inlineStr"/>
+      <c r="F7408" t="inlineStr"/>
+      <c r="G7408" t="inlineStr"/>
+      <c r="H7408" t="inlineStr"/>
+      <c r="I7408" t="inlineStr"/>
+    </row>
+    <row r="7409">
+      <c r="A7409" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7409" t="inlineStr">
+        <is>
+          <t>Tradescantia zebrina</t>
+        </is>
+      </c>
+      <c r="C7409" t="inlineStr"/>
+      <c r="D7409" t="inlineStr"/>
+      <c r="E7409" t="inlineStr"/>
+      <c r="F7409" t="inlineStr"/>
+      <c r="G7409" t="inlineStr"/>
+      <c r="H7409" t="inlineStr"/>
+      <c r="I7409" t="inlineStr"/>
+    </row>
+    <row r="7410">
+      <c r="A7410" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7410" t="inlineStr">
+        <is>
+          <t>Senecio rowleyanus</t>
+        </is>
+      </c>
+      <c r="C7410" t="inlineStr"/>
+      <c r="D7410" t="inlineStr"/>
+      <c r="E7410" t="inlineStr"/>
+      <c r="F7410" t="inlineStr"/>
+      <c r="G7410" t="inlineStr"/>
+      <c r="H7410" t="inlineStr"/>
+      <c r="I7410" t="inlineStr"/>
+    </row>
+    <row r="7411">
+      <c r="A7411" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7411" t="inlineStr">
+        <is>
+          <t>Ledebouria socialis</t>
+        </is>
+      </c>
+      <c r="C7411" t="inlineStr"/>
+      <c r="D7411" t="inlineStr"/>
+      <c r="E7411" t="inlineStr"/>
+      <c r="F7411" t="inlineStr"/>
+      <c r="G7411" t="inlineStr"/>
+      <c r="H7411" t="inlineStr"/>
+      <c r="I7411" t="inlineStr"/>
+    </row>
+    <row r="7412">
+      <c r="A7412" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7412" t="inlineStr">
+        <is>
+          <t>Peperomia Axillaris</t>
+        </is>
+      </c>
+      <c r="C7412" t="inlineStr"/>
+      <c r="D7412" t="inlineStr"/>
+      <c r="E7412" t="inlineStr"/>
+      <c r="F7412" t="inlineStr"/>
+      <c r="G7412" t="inlineStr"/>
+      <c r="H7412" t="inlineStr"/>
+      <c r="I7412" t="inlineStr"/>
+    </row>
+    <row r="7413">
+      <c r="A7413" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="B7413" t="inlineStr">
+        <is>
+          <t>Hoya Sabah</t>
+        </is>
+      </c>
+      <c r="C7413" t="inlineStr"/>
+      <c r="D7413" t="inlineStr"/>
+      <c r="E7413" t="inlineStr"/>
+      <c r="F7413" t="inlineStr"/>
+      <c r="G7413" t="inlineStr"/>
+      <c r="H7413" t="inlineStr"/>
+      <c r="I7413" t="inlineStr"/>
+    </row>
+    <row r="7414"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
